--- a/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ53"/>
+  <dimension ref="A1:AQ52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0493</v>
+        <v>0.04805</v>
       </c>
       <c r="E2">
-        <v>0.1865</v>
+        <v>0.06795</v>
       </c>
       <c r="F2">
-        <v>0.07849999999999999</v>
+        <v>0.1136</v>
       </c>
       <c r="G2">
-        <v>0.1301459716010389</v>
+        <v>0.1687657367886011</v>
       </c>
       <c r="H2">
-        <v>0.1301459716010389</v>
+        <v>0.1687657367886011</v>
       </c>
       <c r="I2">
-        <v>0.1576092149966226</v>
+        <v>0.06492359510899157</v>
       </c>
       <c r="J2">
-        <v>0.1361157283220371</v>
+        <v>0.05768945288318047</v>
       </c>
       <c r="K2">
-        <v>26964.75</v>
+        <v>10805.474</v>
       </c>
       <c r="L2">
-        <v>0.1029505484587169</v>
+        <v>0.0405396257176756</v>
       </c>
       <c r="M2">
-        <v>13980.252</v>
+        <v>16682.03</v>
       </c>
       <c r="N2">
-        <v>0.04715762536694498</v>
+        <v>0.05180692892298094</v>
       </c>
       <c r="O2">
-        <v>0.5184639946596946</v>
+        <v>1.54384990422447</v>
       </c>
       <c r="P2">
-        <v>7305.661</v>
+        <v>7922.51</v>
       </c>
       <c r="Q2">
-        <v>0.02464316269090862</v>
+        <v>0.02460377498791249</v>
       </c>
       <c r="R2">
-        <v>0.2709337561075107</v>
+        <v>0.7331941199432807</v>
       </c>
       <c r="S2">
-        <v>6674.591</v>
+        <v>8759.52</v>
       </c>
       <c r="T2">
-        <v>0.4774299490452676</v>
+        <v>0.5250871746424147</v>
       </c>
       <c r="U2">
-        <v>23043.347</v>
+        <v>20176.55</v>
       </c>
       <c r="V2">
-        <v>0.07772889394458095</v>
+        <v>0.06265934612040448</v>
       </c>
       <c r="W2">
-        <v>0.1072030328559393</v>
+        <v>0.03948776138206447</v>
       </c>
       <c r="X2">
-        <v>0.05258895420233552</v>
+        <v>0.08732957371332983</v>
       </c>
       <c r="Y2">
-        <v>0.05461407865360382</v>
+        <v>-0.04784181233126536</v>
       </c>
       <c r="Z2">
-        <v>1.272970847754644</v>
+        <v>1.223591749574505</v>
       </c>
       <c r="AA2">
-        <v>0.09659269504118963</v>
+        <v>0.03351946924776143</v>
       </c>
       <c r="AB2">
-        <v>0.04707551283788499</v>
+        <v>0.07759320227278585</v>
       </c>
       <c r="AC2">
-        <v>0.05016483297876419</v>
+        <v>-0.04061941502377084</v>
       </c>
       <c r="AD2">
-        <v>65169.35</v>
+        <v>65237.41</v>
       </c>
       <c r="AE2">
-        <v>4447.603346224955</v>
+        <v>3889.822195552394</v>
       </c>
       <c r="AF2">
-        <v>69616.95334622495</v>
+        <v>69127.23219555239</v>
       </c>
       <c r="AG2">
-        <v>46573.60634622495</v>
+        <v>48950.68219555239</v>
       </c>
       <c r="AH2">
-        <v>0.1901713461187745</v>
+        <v>0.1767367444991122</v>
       </c>
       <c r="AI2">
-        <v>0.2679186212543927</v>
+        <v>0.3206831148242104</v>
       </c>
       <c r="AJ2">
-        <v>0.1357706257631595</v>
+        <v>0.1319587156878122</v>
       </c>
       <c r="AK2">
-        <v>0.1966788264121999</v>
+        <v>0.2505333632373704</v>
       </c>
       <c r="AL2">
-        <v>2717.253</v>
+        <v>2699.037</v>
       </c>
       <c r="AM2">
-        <v>2658.253</v>
+        <v>2661.837</v>
       </c>
       <c r="AN2">
-        <v>1.376986137961822</v>
+        <v>2.838654382631688</v>
       </c>
       <c r="AO2">
-        <v>15.13412626649046</v>
+        <v>6.329683142543062</v>
       </c>
       <c r="AP2">
-        <v>0.9840701239715066</v>
+        <v>2.129975248055</v>
       </c>
       <c r="AQ2">
-        <v>15.4700286240625</v>
+        <v>6.418142433214354</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fidelity National Financial, Inc. (NYSE:FNF)</t>
+          <t>Stewart Information Services Corporation (NYSE:STC)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="E3">
-        <v>0.366</v>
+        <v>0.361</v>
       </c>
       <c r="G3">
-        <v>0.1485182396824311</v>
+        <v>0.1405884962294839</v>
       </c>
       <c r="H3">
-        <v>0.1485182396824311</v>
+        <v>0.1405884962294839</v>
       </c>
       <c r="I3">
-        <v>0.2395294592036044</v>
+        <v>0.1094071368956501</v>
       </c>
       <c r="J3">
-        <v>0.1912132688208336</v>
+        <v>0.08531071840145475</v>
       </c>
       <c r="K3">
-        <v>2690</v>
+        <v>234.5</v>
       </c>
       <c r="L3">
-        <v>0.1841078639381288</v>
+        <v>0.0693479225195919</v>
       </c>
       <c r="M3">
-        <v>928</v>
+        <v>45.78</v>
       </c>
       <c r="N3">
-        <v>0.0625046305962861</v>
+        <v>0.03949616081442499</v>
       </c>
       <c r="O3">
-        <v>0.3449814126394052</v>
+        <v>0.1952238805970149</v>
       </c>
       <c r="P3">
-        <v>427</v>
+        <v>42.5</v>
       </c>
       <c r="Q3">
-        <v>0.02876021256962733</v>
+        <v>0.03666637908722285</v>
       </c>
       <c r="R3">
-        <v>0.1587360594795539</v>
+        <v>0.1812366737739872</v>
       </c>
       <c r="S3">
-        <v>501</v>
+        <v>3.280000000000001</v>
       </c>
       <c r="T3">
-        <v>0.5398706896551724</v>
+        <v>0.07164700742682396</v>
       </c>
       <c r="U3">
-        <v>4454</v>
+        <v>310.4</v>
       </c>
       <c r="V3">
-        <v>0.2999952852110542</v>
+        <v>0.2677939780864464</v>
       </c>
       <c r="W3">
-        <v>0.3766979414647809</v>
+        <v>0.1941385876314264</v>
       </c>
       <c r="X3">
-        <v>0.05350307882049594</v>
+        <v>0.09556069537062159</v>
       </c>
       <c r="Y3">
-        <v>0.3231948626442849</v>
+        <v>0.09857789226080485</v>
       </c>
       <c r="Z3">
-        <v>4.446202167806081</v>
+        <v>6.596776626717255</v>
       </c>
       <c r="AA3">
-        <v>0.8501728503444774</v>
+        <v>0.5627757531591744</v>
       </c>
       <c r="AB3">
-        <v>0.04651840075338356</v>
+        <v>0.07516575957469225</v>
       </c>
       <c r="AC3">
-        <v>0.8036544495910939</v>
+        <v>0.4876099935844821</v>
       </c>
       <c r="AD3">
-        <v>3097</v>
+        <v>446.4</v>
       </c>
       <c r="AE3">
-        <v>421.1753578806798</v>
+        <v>149.1988329367962</v>
       </c>
       <c r="AF3">
-        <v>3518.17535788068</v>
+        <v>595.5988329367962</v>
       </c>
       <c r="AG3">
-        <v>-935.8246421193203</v>
+        <v>285.1988329367962</v>
       </c>
       <c r="AH3">
-        <v>0.1915687950809844</v>
+        <v>0.3394308024585377</v>
       </c>
       <c r="AI3">
-        <v>0.2728922978642315</v>
+        <v>0.3049506880515709</v>
       </c>
       <c r="AJ3">
-        <v>-0.06727191234638606</v>
+        <v>0.1974652519498898</v>
       </c>
       <c r="AK3">
-        <v>-0.1109036731792169</v>
+        <v>0.1736160196978538</v>
       </c>
       <c r="AL3">
-        <v>111</v>
+        <v>16.5</v>
       </c>
       <c r="AM3">
-        <v>111</v>
+        <v>16.5</v>
       </c>
       <c r="AN3">
-        <v>0.7319782557315055</v>
+        <v>0.9791620969510858</v>
       </c>
       <c r="AO3">
-        <v>30.96396396396396</v>
+        <v>21.14545454545454</v>
       </c>
       <c r="AP3">
-        <v>-0.2211828508908817</v>
+        <v>0.6255732242526787</v>
       </c>
       <c r="AQ3">
-        <v>30.96396396396396</v>
+        <v>21.14545454545454</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stewart Information Services Corporation (NYSE:STC)</t>
+          <t>Fidelity National Financial, Inc. (NYSE:FNF)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,121 +859,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0926</v>
+        <v>0.158</v>
       </c>
       <c r="E4">
-        <v>0.484</v>
+        <v>0.162</v>
       </c>
       <c r="G4">
-        <v>0.0789379726703236</v>
+        <v>0.2783848324770244</v>
       </c>
       <c r="H4">
-        <v>0.0789379726703236</v>
+        <v>0.2783848324770244</v>
       </c>
       <c r="I4">
-        <v>0.1371199374661491</v>
+        <v>0.1720419029121613</v>
       </c>
       <c r="J4">
-        <v>0.1065243298244947</v>
+        <v>0.1259981386608053</v>
       </c>
       <c r="K4">
-        <v>297.4</v>
+        <v>1601</v>
       </c>
       <c r="L4">
-        <v>0.09653023467168684</v>
+        <v>0.1158549822707866</v>
       </c>
       <c r="M4">
-        <v>36.97</v>
+        <v>1114</v>
       </c>
       <c r="N4">
-        <v>0.01724347014925373</v>
+        <v>0.1088145659138861</v>
       </c>
       <c r="O4">
-        <v>0.124310692669805</v>
+        <v>0.6958151155527795</v>
       </c>
       <c r="P4">
-        <v>34.6</v>
+        <v>491</v>
       </c>
       <c r="Q4">
-        <v>0.01613805970149254</v>
+        <v>0.04796045948269125</v>
       </c>
       <c r="R4">
-        <v>0.1163416274377942</v>
+        <v>0.306683322923173</v>
       </c>
       <c r="S4">
-        <v>2.369999999999997</v>
+        <v>623</v>
       </c>
       <c r="T4">
-        <v>0.0641060319177711</v>
+        <v>0.559245960502693</v>
       </c>
       <c r="U4">
-        <v>583.6</v>
+        <v>2051</v>
       </c>
       <c r="V4">
-        <v>0.2722014925373135</v>
+        <v>0.2003399234195515</v>
       </c>
       <c r="W4">
-        <v>0.3150757495497404</v>
+        <v>0.1715602228889841</v>
       </c>
       <c r="X4">
-        <v>0.05225441665937493</v>
+        <v>0.08903304726830386</v>
       </c>
       <c r="Y4">
-        <v>0.2628213328903655</v>
+        <v>0.08252717562068029</v>
       </c>
       <c r="Z4">
-        <v>7.279391541148733</v>
+        <v>3.586774955246717</v>
       </c>
       <c r="AA4">
-        <v>0.7754323054509644</v>
+        <v>0.4519269681562796</v>
       </c>
       <c r="AB4">
-        <v>0.04676428971527882</v>
+        <v>0.07662870826421379</v>
       </c>
       <c r="AC4">
-        <v>0.7286680157356856</v>
+        <v>0.3752982598920658</v>
       </c>
       <c r="AD4">
-        <v>275.3</v>
+        <v>2693</v>
       </c>
       <c r="AE4">
-        <v>120.735923302707</v>
+        <v>392.7647182842155</v>
       </c>
       <c r="AF4">
-        <v>396.035923302707</v>
+        <v>3085.764718284216</v>
       </c>
       <c r="AG4">
-        <v>-187.564076697293</v>
+        <v>1034.764718284216</v>
       </c>
       <c r="AH4">
-        <v>0.1559174496980174</v>
+        <v>0.2316055128363701</v>
       </c>
       <c r="AI4">
-        <v>0.2455677445887537</v>
+        <v>0.3473096717951271</v>
       </c>
       <c r="AJ4">
-        <v>-0.09587028865257263</v>
+        <v>0.09179659673411621</v>
       </c>
       <c r="AK4">
-        <v>-0.1822539398832388</v>
+        <v>0.1514194241302499</v>
       </c>
       <c r="AL4">
-        <v>2.51</v>
+        <v>120</v>
       </c>
       <c r="AM4">
-        <v>2.51</v>
+        <v>120</v>
       </c>
       <c r="AN4">
-        <v>0.5798230834035384</v>
+        <v>0.8873146622734761</v>
       </c>
       <c r="AO4">
-        <v>162.988047808765</v>
+        <v>19.25833333333333</v>
       </c>
       <c r="AP4">
-        <v>-0.3950380722352422</v>
+        <v>0.3409438939980941</v>
       </c>
       <c r="AQ4">
-        <v>162.988047808765</v>
+        <v>19.25833333333333</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Universal Insurance Holdings, Inc. (NYSE:UVE)</t>
+          <t>RLI Corp. (NYSE:RLI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,121 +993,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.105</v>
+        <v>0.157</v>
       </c>
       <c r="E5">
-        <v>-0.15</v>
+        <v>0.487</v>
       </c>
       <c r="G5">
-        <v>0.02667150503492697</v>
+        <v>0.1940631021194605</v>
       </c>
       <c r="H5">
-        <v>0.02667150503492697</v>
+        <v>0.1940631021194605</v>
       </c>
       <c r="I5">
-        <v>0.05987480722126463</v>
+        <v>0.4354795017166902</v>
       </c>
       <c r="J5">
-        <v>0.0462462471557264</v>
+        <v>0.3495509776802893</v>
       </c>
       <c r="K5">
-        <v>50.9</v>
+        <v>580.9</v>
       </c>
       <c r="L5">
-        <v>0.04617617708427833</v>
+        <v>0.3497711946050096</v>
       </c>
       <c r="M5">
-        <v>24.88</v>
+        <v>91.5</v>
       </c>
       <c r="N5">
-        <v>0.04696111740279351</v>
+        <v>0.01536059629331184</v>
       </c>
       <c r="O5">
-        <v>0.4888015717092338</v>
+        <v>0.1575142021001894</v>
       </c>
       <c r="P5">
-        <v>20</v>
+        <v>91.5</v>
       </c>
       <c r="Q5">
-        <v>0.03775009437523594</v>
+        <v>0.01536059629331184</v>
       </c>
       <c r="R5">
-        <v>0.3929273084479372</v>
+        <v>0.1575142021001894</v>
       </c>
       <c r="S5">
-        <v>4.879999999999999</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.1961414790996784</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>224.8</v>
+        <v>723.5</v>
       </c>
       <c r="V5">
-        <v>0.424311060777652</v>
+        <v>0.1214578297072254</v>
       </c>
       <c r="W5">
-        <v>0.1072030328559393</v>
+        <v>0.4646084939614493</v>
       </c>
       <c r="X5">
-        <v>0.04817122734941754</v>
+        <v>0.08088185475990441</v>
       </c>
       <c r="Y5">
-        <v>0.0590318055065218</v>
+        <v>0.3837266392015449</v>
       </c>
       <c r="Z5">
-        <v>14.03846153846154</v>
+        <v>1.297775556537307</v>
       </c>
       <c r="AA5">
-        <v>0.6492261619938515</v>
+        <v>0.4536387145971971</v>
       </c>
       <c r="AB5">
-        <v>0.04774528496209851</v>
+        <v>0.07929773713241754</v>
       </c>
       <c r="AC5">
-        <v>0.601480877031753</v>
+        <v>0.3743409774647796</v>
       </c>
       <c r="AD5">
-        <v>7.35</v>
+        <v>199.8</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>15.52821774460456</v>
       </c>
       <c r="AF5">
-        <v>7.35</v>
+        <v>215.3282177446046</v>
       </c>
       <c r="AG5">
-        <v>-217.45</v>
+        <v>-508.1717822553954</v>
       </c>
       <c r="AH5">
-        <v>0.01368332867913991</v>
+        <v>0.03488719128120915</v>
       </c>
       <c r="AI5">
-        <v>0.01465164955646367</v>
+        <v>0.1338000635112063</v>
       </c>
       <c r="AJ5">
-        <v>-0.6961741635985276</v>
+        <v>-0.0932660042027509</v>
       </c>
       <c r="AK5">
-        <v>-0.7854433808921799</v>
+        <v>-0.5736685421347774</v>
       </c>
       <c r="AL5">
-        <v>0.114</v>
+        <v>8</v>
       </c>
       <c r="AM5">
-        <v>0.114</v>
+        <v>8</v>
       </c>
       <c r="AN5">
-        <v>0.1036671368124118</v>
+        <v>0.2703470671808403</v>
       </c>
       <c r="AO5">
-        <v>578.9473684210526</v>
+        <v>90.125</v>
       </c>
       <c r="AP5">
-        <v>-3.066995768688293</v>
+        <v>-0.6876013561401737</v>
       </c>
       <c r="AQ5">
-        <v>578.9473684210526</v>
+        <v>90.125</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Investors Title Company (NasdaqGS:ITIC)</t>
+          <t>Erie Indemnity Company (NasdaqGS:ERIE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1127,115 +1127,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.194</v>
+        <v>0.107</v>
       </c>
       <c r="E6">
-        <v>0.312</v>
+        <v>0.0646</v>
       </c>
       <c r="G6">
-        <v>0.1665596919127086</v>
+        <v>0.1265403185126468</v>
       </c>
       <c r="H6">
-        <v>0.1665596919127086</v>
+        <v>0.1265403185126468</v>
       </c>
       <c r="I6">
-        <v>0.2534093364743203</v>
+        <v>0.1297470634863443</v>
       </c>
       <c r="J6">
-        <v>0.1990415151943752</v>
+        <v>0.1026080949503591</v>
       </c>
       <c r="K6">
-        <v>64.7</v>
+        <v>288.1</v>
       </c>
       <c r="L6">
-        <v>0.2076379974326059</v>
+        <v>0.1038048569575557</v>
       </c>
       <c r="M6">
-        <v>3.416</v>
+        <v>203.3</v>
       </c>
       <c r="N6">
-        <v>0.009148366363149437</v>
+        <v>0.0156318480642805</v>
       </c>
       <c r="O6">
-        <v>0.05279752704791344</v>
+        <v>0.7056577577230129</v>
       </c>
       <c r="P6">
-        <v>3.41</v>
+        <v>203.3</v>
       </c>
       <c r="Q6">
-        <v>0.009132297803963579</v>
+        <v>0.0156318480642805</v>
       </c>
       <c r="R6">
-        <v>0.0527047913446677</v>
+        <v>0.7056577577230129</v>
       </c>
       <c r="S6">
-        <v>0.005999999999999783</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.001756440281030382</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>48.5</v>
+        <v>97.7</v>
       </c>
       <c r="V6">
-        <v>0.129887520085699</v>
+        <v>0.007512206374226289</v>
       </c>
       <c r="W6">
-        <v>0.3038985439173321</v>
+        <v>0.2238713186727795</v>
       </c>
       <c r="X6">
-        <v>0.04807893128933753</v>
+        <v>0.07977107850664222</v>
       </c>
       <c r="Y6">
-        <v>0.2558196126279945</v>
+        <v>0.1441002401661373</v>
       </c>
       <c r="Z6">
-        <v>1.824481444807915</v>
+        <v>2.423506811037373</v>
       </c>
       <c r="AA6">
-        <v>0.3631475512185904</v>
+        <v>0.2486714169797647</v>
       </c>
       <c r="AB6">
-        <v>0.04780470889309277</v>
+        <v>0.07977107850664222</v>
       </c>
       <c r="AC6">
-        <v>0.3153428423254976</v>
+        <v>0.1689003384731224</v>
       </c>
       <c r="AD6">
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>3.738253773008806</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>3.738253773008806</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-44.76174622699119</v>
+        <v>-97.7</v>
       </c>
       <c r="AH6">
-        <v>0.009912157506193415</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.01501076126407518</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.1362037003090585</v>
+        <v>-0.007569066765831513</v>
       </c>
       <c r="AK6">
-        <v>-0.2232080183447565</v>
+        <v>-0.07760743506235604</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>-34.14</v>
       </c>
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>117.6797385620915</v>
+      </c>
       <c r="AP6">
-        <v>-0.546474743340144</v>
+        <v>-0.238700219887613</v>
+      </c>
+      <c r="AQ6">
+        <v>-10.5477445811365</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1252,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First American Financial Corporation (NYSE:FAF)</t>
+          <t>American Financial Group, Inc. (NYSE:AFG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,121 +1261,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.106</v>
+        <v>0.00199</v>
       </c>
       <c r="E7">
-        <v>0.297</v>
+        <v>0.0708</v>
       </c>
       <c r="G7">
-        <v>0.1316435722778438</v>
+        <v>0.2429277054333184</v>
       </c>
       <c r="H7">
-        <v>0.1316435722778438</v>
+        <v>0.2429277054333184</v>
       </c>
       <c r="I7">
-        <v>0.1964146189187679</v>
+        <v>0.1995252945301436</v>
       </c>
       <c r="J7">
-        <v>0.1474881078958895</v>
+        <v>0.1595222690310559</v>
       </c>
       <c r="K7">
-        <v>1261.5</v>
+        <v>977</v>
       </c>
       <c r="L7">
-        <v>0.1401775693665063</v>
+        <v>0.1462355934740308</v>
       </c>
       <c r="M7">
-        <v>356.6</v>
+        <v>2282</v>
       </c>
       <c r="N7">
-        <v>0.041527407390155</v>
+        <v>0.1952346323309236</v>
       </c>
       <c r="O7">
-        <v>0.2826793499801823</v>
+        <v>2.335721596724667</v>
       </c>
       <c r="P7">
-        <v>208</v>
+        <v>2271</v>
       </c>
       <c r="Q7">
-        <v>0.02422238008175053</v>
+        <v>0.1942935363819139</v>
       </c>
       <c r="R7">
-        <v>0.1648830757035276</v>
+        <v>2.32446264073695</v>
       </c>
       <c r="S7">
-        <v>148.6</v>
+        <v>11</v>
       </c>
       <c r="T7">
-        <v>0.4167134043746495</v>
+        <v>0.004820333041191937</v>
       </c>
       <c r="U7">
-        <v>1954</v>
+        <v>794</v>
       </c>
       <c r="V7">
-        <v>0.2275506282679834</v>
+        <v>0.06793001668306455</v>
       </c>
       <c r="W7">
-        <v>0.2670519497015115</v>
+        <v>0.1864503816793893</v>
       </c>
       <c r="X7">
-        <v>0.05491056051718318</v>
+        <v>0.08423989378875284</v>
       </c>
       <c r="Y7">
-        <v>0.2121413891843283</v>
+        <v>0.1022104878906365</v>
       </c>
       <c r="Z7">
-        <v>2.437229947575613</v>
+        <v>1.544790769186458</v>
       </c>
       <c r="AA7">
-        <v>0.3594624334751252</v>
+        <v>0.246428528678854</v>
       </c>
       <c r="AB7">
-        <v>0.04703463665557929</v>
+        <v>0.0780484418510862</v>
       </c>
       <c r="AC7">
-        <v>0.3124277968195459</v>
+        <v>0.1683800868277678</v>
       </c>
       <c r="AD7">
-        <v>2242.5</v>
+        <v>1570</v>
       </c>
       <c r="AE7">
-        <v>298.0295998216641</v>
+        <v>129.8575362205534</v>
       </c>
       <c r="AF7">
-        <v>2540.529599821664</v>
+        <v>1699.857536220553</v>
       </c>
       <c r="AG7">
-        <v>586.5295998216643</v>
+        <v>905.8575362205534</v>
       </c>
       <c r="AH7">
-        <v>0.228308246336882</v>
+        <v>0.126965352667181</v>
       </c>
       <c r="AI7">
-        <v>0.3115864815008743</v>
+        <v>0.3018289303818753</v>
       </c>
       <c r="AJ7">
-        <v>0.0639364815681098</v>
+        <v>0.07192566461729913</v>
       </c>
       <c r="AK7">
-        <v>0.09460872641668433</v>
+        <v>0.1872435327908044</v>
       </c>
       <c r="AL7">
-        <v>67.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="AM7">
-        <v>67.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="AN7">
-        <v>1.130292338709677</v>
+        <v>1.072404371584699</v>
       </c>
       <c r="AO7">
-        <v>25.63328424153166</v>
+        <v>15.01136363636364</v>
       </c>
       <c r="AP7">
-        <v>0.2956298386197905</v>
+        <v>0.6187551476916348</v>
       </c>
       <c r="AQ7">
-        <v>25.63328424153166</v>
+        <v>15.01136363636364</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Heritage Insurance Holdings, Inc. (NYSE:HRTG)</t>
+          <t>Kinsale Capital Group, Inc. (NYSE:KNSL)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,121 +1395,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0737</v>
-      </c>
-      <c r="F8">
-        <v>0.07000000000000001</v>
+        <v>0.339</v>
+      </c>
+      <c r="E8">
+        <v>0.402</v>
       </c>
       <c r="G8">
-        <v>0.02930813581037797</v>
+        <v>0.2515135561989997</v>
       </c>
       <c r="H8">
-        <v>0.02930813581037797</v>
+        <v>0.2515135561989997</v>
       </c>
       <c r="I8">
-        <v>-0.0487594293907846</v>
+        <v>0.2276914977625691</v>
       </c>
       <c r="J8">
-        <v>-0.0487594293907846</v>
+        <v>0.1861361398618787</v>
       </c>
       <c r="K8">
-        <v>-22.7</v>
+        <v>140.2</v>
       </c>
       <c r="L8">
-        <v>-0.03635490070467649</v>
+        <v>0.1845222426954462</v>
       </c>
       <c r="M8">
-        <v>9.969999999999999</v>
+        <v>13.28</v>
       </c>
       <c r="N8">
-        <v>0.06135384615384615</v>
+        <v>0.002200168988883182</v>
       </c>
       <c r="O8">
-        <v>-0.4392070484581497</v>
+        <v>0.09472182596291014</v>
       </c>
       <c r="P8">
-        <v>6.71</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>0.04129230769230769</v>
+        <v>0.001656753756689143</v>
       </c>
       <c r="R8">
-        <v>-0.2955947136563877</v>
+        <v>0.07132667617689016</v>
       </c>
       <c r="S8">
-        <v>3.259999999999999</v>
+        <v>3.279999999999999</v>
       </c>
       <c r="T8">
-        <v>0.3269809428284854</v>
+        <v>0.2469879518072289</v>
       </c>
       <c r="U8">
-        <v>393.4</v>
+        <v>126.2</v>
       </c>
       <c r="V8">
-        <v>2.420923076923077</v>
+        <v>0.02090823240941699</v>
       </c>
       <c r="W8">
-        <v>-0.05122997066125028</v>
+        <v>0.2126820388349514</v>
       </c>
       <c r="X8">
-        <v>0.07071403660901331</v>
+        <v>0.08039828035790116</v>
       </c>
       <c r="Y8">
-        <v>-0.1219440072702636</v>
+        <v>0.1322837584770503</v>
       </c>
       <c r="Z8">
-        <v>-7.162763239830134</v>
+        <v>1.24170616113744</v>
       </c>
       <c r="AA8">
-        <v>0.349252248435405</v>
+        <v>0.231126391676835</v>
       </c>
       <c r="AB8">
-        <v>0.04446674895059179</v>
+        <v>0.07949968346223565</v>
       </c>
       <c r="AC8">
-        <v>0.3047854994848132</v>
+        <v>0.1516267082145994</v>
       </c>
       <c r="AD8">
-        <v>146.6</v>
+        <v>123.2</v>
       </c>
       <c r="AE8">
-        <v>8.926938558029518</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>155.5269385580295</v>
+        <v>123.2</v>
       </c>
       <c r="AG8">
-        <v>-237.8730614419705</v>
+        <v>-3</v>
       </c>
       <c r="AH8">
-        <v>0.4890369956180644</v>
+        <v>0.02000292250491143</v>
       </c>
       <c r="AI8">
-        <v>0.2774655914988255</v>
+        <v>0.1658812441093308</v>
       </c>
       <c r="AJ8">
-        <v>3.15594267887219</v>
+        <v>-0.0004972732848215619</v>
       </c>
       <c r="AK8">
-        <v>-1.423307717441235</v>
+        <v>-0.004866180048661801</v>
       </c>
       <c r="AL8">
-        <v>7.99</v>
+        <v>1.55</v>
       </c>
       <c r="AM8">
-        <v>7.99</v>
+        <v>1.55</v>
       </c>
       <c r="AN8">
-        <v>-7.235932872655479</v>
+        <v>0.7003979533826038</v>
       </c>
       <c r="AO8">
-        <v>-3.792240300375469</v>
+        <v>111.6129032258064</v>
       </c>
       <c r="AP8">
-        <v>11.7410198145099</v>
+        <v>-0.01705514496873223</v>
       </c>
       <c r="AQ8">
-        <v>-3.792240300375469</v>
+        <v>111.6129032258064</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Markel Corporation (NYSE:MKL)</t>
+          <t>Investors Title Company (NasdaqGS:ITIC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1523,121 +1529,115 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.173</v>
+        <v>0.141</v>
       </c>
       <c r="E9">
-        <v>0.358</v>
+        <v>0.108</v>
       </c>
       <c r="G9">
-        <v>0.1270491803278689</v>
+        <v>0.2699902881191324</v>
       </c>
       <c r="H9">
-        <v>0.1270491803278689</v>
+        <v>0.2699902881191324</v>
       </c>
       <c r="I9">
-        <v>0.2561910257178762</v>
+        <v>0.1469887548193473</v>
       </c>
       <c r="J9">
-        <v>0.2062842365384057</v>
+        <v>0.1159468343384829</v>
       </c>
       <c r="K9">
-        <v>2401.2</v>
+        <v>35.3</v>
       </c>
       <c r="L9">
-        <v>0.192960462873674</v>
+        <v>0.1142764648753642</v>
       </c>
       <c r="M9">
-        <v>125.3</v>
+        <v>3.576</v>
       </c>
       <c r="N9">
-        <v>0.007428883118115092</v>
+        <v>0.01277599142550911</v>
       </c>
       <c r="O9">
-        <v>0.05218224221222723</v>
+        <v>0.1013031161473088</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>3.49</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.01246873883529832</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.09886685552407934</v>
       </c>
       <c r="S9">
-        <v>125.3</v>
+        <v>0.08599999999999985</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0.02404921700223709</v>
       </c>
       <c r="U9">
-        <v>3938.6</v>
+        <v>41.4</v>
       </c>
       <c r="V9">
-        <v>0.233514756975324</v>
+        <v>0.1479099678456592</v>
       </c>
       <c r="W9">
-        <v>0.2124560922306474</v>
+        <v>0.1439054219323277</v>
       </c>
       <c r="X9">
-        <v>0.05468956529289521</v>
+        <v>0.08033381255723088</v>
       </c>
       <c r="Y9">
-        <v>0.1577665269377522</v>
+        <v>0.06357160937509687</v>
       </c>
       <c r="Z9">
-        <v>1.420467779609051</v>
+        <v>1.563450045003499</v>
       </c>
       <c r="AA9">
-        <v>0.2930201114440574</v>
+        <v>0.1812770833645143</v>
       </c>
       <c r="AB9">
-        <v>0.04630325842430435</v>
+        <v>0.07952707750046276</v>
       </c>
       <c r="AC9">
-        <v>0.246716853019753</v>
+        <v>0.1017500058640515</v>
       </c>
       <c r="AD9">
-        <v>4268.3</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>565.7943798337412</v>
+        <v>5.125868181518174</v>
       </c>
       <c r="AF9">
-        <v>4834.094379833741</v>
+        <v>5.125868181518174</v>
       </c>
       <c r="AG9">
-        <v>895.4943798337413</v>
+        <v>-36.27413181848183</v>
       </c>
       <c r="AH9">
-        <v>0.2227621980762985</v>
+        <v>0.01798387007544794</v>
       </c>
       <c r="AI9">
-        <v>0.2530118915222617</v>
+        <v>0.02099682520209972</v>
       </c>
       <c r="AJ9">
-        <v>0.05041603544514684</v>
+        <v>-0.1488927759980524</v>
       </c>
       <c r="AK9">
-        <v>0.05903997413224319</v>
+        <v>-0.1789319347543868</v>
       </c>
       <c r="AL9">
-        <v>179.8</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>179.8</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>1.182125349655192</v>
-      </c>
-      <c r="AO9">
-        <v>17.85817575083426</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>0.248011294162833</v>
-      </c>
-      <c r="AQ9">
-        <v>17.85817575083426</v>
+        <v>-0.7279576925242189</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kinsale Capital Group, Inc. (NasdaqGS:KNSL)</t>
+          <t>W. R. Berkley Corporation (NYSE:WRB)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1657,115 +1657,124 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.365</v>
+        <v>0.068</v>
       </c>
       <c r="E10">
-        <v>0.429</v>
+        <v>0.188</v>
+      </c>
+      <c r="F10">
+        <v>0.21</v>
       </c>
       <c r="G10">
-        <v>0.1712846347607053</v>
+        <v>0.1440326533655145</v>
       </c>
       <c r="H10">
-        <v>0.1712846347607053</v>
+        <v>0.1440326533655145</v>
       </c>
       <c r="I10">
-        <v>0.2879932829554996</v>
+        <v>0.1532279447045706</v>
       </c>
       <c r="J10">
-        <v>0.2392947103274559</v>
+        <v>0.1245583135943602</v>
       </c>
       <c r="K10">
-        <v>142.5</v>
+        <v>1293.3</v>
       </c>
       <c r="L10">
-        <v>0.2392947103274559</v>
+        <v>0.1205211119291019</v>
       </c>
       <c r="M10">
-        <v>11.64</v>
+        <v>122.87</v>
       </c>
       <c r="N10">
-        <v>0.002144278240365486</v>
+        <v>0.006377688730171914</v>
       </c>
       <c r="O10">
-        <v>0.08168421052631579</v>
+        <v>0.09500502590272945</v>
       </c>
       <c r="P10">
-        <v>9.56</v>
+        <v>116.3</v>
       </c>
       <c r="Q10">
-        <v>0.001761108245523543</v>
+        <v>0.006036666389834732</v>
       </c>
       <c r="R10">
-        <v>0.06708771929824561</v>
+        <v>0.08992499806696048</v>
       </c>
       <c r="S10">
-        <v>2.08</v>
+        <v>6.570000000000007</v>
       </c>
       <c r="T10">
-        <v>0.1786941580756014</v>
+        <v>0.05347114836819408</v>
       </c>
       <c r="U10">
-        <v>90</v>
+        <v>1130.8</v>
       </c>
       <c r="V10">
-        <v>0.01657947093066097</v>
+        <v>0.05869529108878</v>
       </c>
       <c r="W10">
-        <v>0.2668039692941397</v>
+        <v>0.1945280067384634</v>
       </c>
       <c r="X10">
-        <v>0.04802765742991248</v>
+        <v>0.08463040423811169</v>
       </c>
       <c r="Y10">
-        <v>0.2187763118642272</v>
+        <v>0.1098976025003517</v>
       </c>
       <c r="Z10">
-        <v>1.201816347124117</v>
+        <v>1.361801222880259</v>
       </c>
       <c r="AA10">
-        <v>0.2875882946518667</v>
+        <v>0.1696236637727025</v>
       </c>
       <c r="AB10">
-        <v>0.04778583050417293</v>
+        <v>0.07791846276566047</v>
       </c>
       <c r="AC10">
-        <v>0.2398024641476938</v>
+        <v>0.09170520100704205</v>
       </c>
       <c r="AD10">
-        <v>42.7</v>
+        <v>2842.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>204.1312408486151</v>
       </c>
       <c r="AF10">
-        <v>42.7</v>
+        <v>3046.631240848615</v>
       </c>
       <c r="AG10">
-        <v>-47.3</v>
+        <v>1915.831240848615</v>
       </c>
       <c r="AH10">
-        <v>0.007804646232019157</v>
+        <v>0.1365453417886297</v>
       </c>
       <c r="AI10">
-        <v>0.06083487676307166</v>
+        <v>0.3235372781332421</v>
       </c>
       <c r="AJ10">
-        <v>-0.008790024344464886</v>
+        <v>0.0904486207312523</v>
       </c>
       <c r="AK10">
-        <v>-0.07730021245301519</v>
+        <v>0.231217748124496</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>135.8</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>135.8</v>
       </c>
       <c r="AN10">
-        <v>0.2456846950517837</v>
+        <v>1.615515771526002</v>
+      </c>
+      <c r="AO10">
+        <v>12.07731958762886</v>
       </c>
       <c r="AP10">
-        <v>-0.2721518987341772</v>
+        <v>1.088849810087306</v>
+      </c>
+      <c r="AQ10">
+        <v>12.07731958762886</v>
       </c>
     </row>
     <row r="11">
@@ -1776,7 +1785,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation (NasdaqGS:CINF)</t>
+          <t>Palomar Holdings, Inc. (NasdaqGS:PLMR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1784,122 +1793,119 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.108</v>
-      </c>
-      <c r="E11">
-        <v>0.313</v>
+      <c r="F11">
+        <v>1.192</v>
       </c>
       <c r="G11">
-        <v>0.181535384957227</v>
+        <v>0.1880616174582798</v>
       </c>
       <c r="H11">
-        <v>0.181535384957227</v>
+        <v>0.1880616174582798</v>
       </c>
       <c r="I11">
-        <v>0.354735536591212</v>
+        <v>0.208588954202991</v>
       </c>
       <c r="J11">
-        <v>0.2852570795836976</v>
+        <v>0.1632860407120289</v>
       </c>
       <c r="K11">
-        <v>2525</v>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>0.2805243861793134</v>
+        <v>0.1604621309370988</v>
       </c>
       <c r="M11">
-        <v>435</v>
+        <v>23.3</v>
       </c>
       <c r="N11">
-        <v>0.02369435910843846</v>
+        <v>0.02044756472136902</v>
       </c>
       <c r="O11">
-        <v>0.1722772277227723</v>
+        <v>0.466</v>
       </c>
       <c r="P11">
-        <v>390</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02124321851101379</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.1544554455445545</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>45</v>
+        <v>23.3</v>
       </c>
       <c r="T11">
-        <v>0.103448275862069</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>1085</v>
+        <v>29.5</v>
       </c>
       <c r="V11">
-        <v>0.05909972329346145</v>
+        <v>0.02588854760860026</v>
       </c>
       <c r="W11">
-        <v>0.2591072344792201</v>
+        <v>0.1323451561672843</v>
       </c>
       <c r="X11">
-        <v>0.04895679122709423</v>
+        <v>0.08053796242644531</v>
       </c>
       <c r="Y11">
-        <v>0.2101504432521259</v>
+        <v>0.05180719374083895</v>
       </c>
       <c r="Z11">
-        <v>0.9229781193191192</v>
+        <v>0.9206992805481284</v>
       </c>
       <c r="AA11">
-        <v>0.2632860428366255</v>
+        <v>0.1503373402071174</v>
       </c>
       <c r="AB11">
-        <v>0.04753167361601204</v>
+        <v>0.07958133051064149</v>
       </c>
       <c r="AC11">
-        <v>0.2157543692206135</v>
+        <v>0.07075600969647593</v>
       </c>
       <c r="AD11">
-        <v>848</v>
+        <v>26.4</v>
       </c>
       <c r="AE11">
-        <v>10.1271757125035</v>
+        <v>2.038409351739969</v>
       </c>
       <c r="AF11">
-        <v>858.1271757125035</v>
+        <v>28.43840935173997</v>
       </c>
       <c r="AG11">
-        <v>-226.8728242874965</v>
+        <v>-1.061590648260033</v>
       </c>
       <c r="AH11">
-        <v>0.04465475504309845</v>
+        <v>0.02434923718924922</v>
       </c>
       <c r="AI11">
-        <v>0.06757371304649187</v>
+        <v>0.07177095576944752</v>
       </c>
       <c r="AJ11">
-        <v>-0.01251233926150939</v>
+        <v>-0.0009324972168362922</v>
       </c>
       <c r="AK11">
-        <v>-0.01953421215861435</v>
+        <v>-0.002894680843865083</v>
       </c>
       <c r="AL11">
-        <v>53</v>
+        <v>0.515</v>
       </c>
       <c r="AM11">
-        <v>53</v>
+        <v>0.515</v>
       </c>
       <c r="AN11">
-        <v>0.2583003350593969</v>
+        <v>0.3934191702432046</v>
       </c>
       <c r="AO11">
-        <v>60.24528301886792</v>
+        <v>125.2427184466019</v>
       </c>
       <c r="AP11">
-        <v>-0.06910533788836325</v>
+        <v>-0.01582007999910636</v>
       </c>
       <c r="AQ11">
-        <v>60.24528301886792</v>
+        <v>125.2427184466019</v>
       </c>
     </row>
     <row r="12">
@@ -1910,7 +1916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMERISAFE, Inc. (NasdaqGS:AMSF)</t>
+          <t>First American Financial Corporation (NYSE:FAF)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1919,118 +1925,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0404</v>
+        <v>0.0741</v>
       </c>
       <c r="E12">
-        <v>0.0208</v>
-      </c>
-      <c r="F12">
-        <v>0.075</v>
+        <v>0.106</v>
       </c>
       <c r="G12">
-        <v>0.3311847759361571</v>
+        <v>0.2250784455708424</v>
       </c>
       <c r="H12">
-        <v>0.3311847759361571</v>
+        <v>0.2250784455708424</v>
       </c>
       <c r="I12">
-        <v>0.3473646785275291</v>
+        <v>0.08605628708355248</v>
       </c>
       <c r="J12">
-        <v>0.2785674300835268</v>
+        <v>0.06758497088758197</v>
       </c>
       <c r="K12">
-        <v>90.7</v>
+        <v>469</v>
       </c>
       <c r="L12">
-        <v>0.2783916513198281</v>
+        <v>0.05660149650012068</v>
       </c>
       <c r="M12">
-        <v>22</v>
+        <v>647</v>
       </c>
       <c r="N12">
-        <v>0.0211112177334229</v>
+        <v>0.1193859098793224</v>
       </c>
       <c r="O12">
-        <v>0.2425578831312017</v>
+        <v>1.37953091684435</v>
       </c>
       <c r="P12">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="Q12">
-        <v>0.0211112177334229</v>
+        <v>0.04059489980440639</v>
       </c>
       <c r="R12">
-        <v>0.2425578831312017</v>
+        <v>0.4690831556503198</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>427</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.6599690880989181</v>
       </c>
       <c r="U12">
-        <v>123.1</v>
+        <v>2361</v>
       </c>
       <c r="V12">
-        <v>0.1181268592265618</v>
+        <v>0.4356570838100159</v>
       </c>
       <c r="W12">
-        <v>0.1882133222660303</v>
+        <v>0.08379339300709296</v>
       </c>
       <c r="X12">
-        <v>0.04784706591560089</v>
+        <v>0.09251559855179675</v>
       </c>
       <c r="Y12">
-        <v>0.1403662563504294</v>
+        <v>-0.008722205544703793</v>
       </c>
       <c r="Z12">
-        <v>0.8268554137801246</v>
+        <v>1.752171913783354</v>
       </c>
       <c r="AA12">
-        <v>0.2303349876673805</v>
+        <v>0.1184204877830868</v>
       </c>
       <c r="AB12">
-        <v>0.04783752282800986</v>
+        <v>0.07579354319894951</v>
       </c>
       <c r="AC12">
-        <v>0.1824974648393707</v>
+        <v>0.04262694458413725</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1988</v>
       </c>
       <c r="AE12">
-        <v>0.3229386786550678</v>
+        <v>259.6880261284208</v>
       </c>
       <c r="AF12">
-        <v>0.3229386786550678</v>
+        <v>2247.688026128421</v>
       </c>
       <c r="AG12">
-        <v>-122.7770613213449</v>
+        <v>-113.3119738715791</v>
       </c>
       <c r="AH12">
-        <v>0.0003097962129118298</v>
+        <v>0.2931605869749503</v>
       </c>
       <c r="AI12">
-        <v>0.0006720567379011845</v>
+        <v>0.3315815711631392</v>
       </c>
       <c r="AJ12">
-        <v>-0.1335516129922883</v>
+        <v>-0.02135508746059326</v>
       </c>
       <c r="AK12">
-        <v>-0.3435063842719087</v>
+        <v>-0.02564960975093653</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>2.139935414424112</v>
+      </c>
+      <c r="AO12">
+        <v>8.156626506024097</v>
       </c>
       <c r="AP12">
-        <v>-1.074766810124172</v>
+        <v>-0.1219719847917966</v>
+      </c>
+      <c r="AQ12">
+        <v>8.156626506024097</v>
       </c>
     </row>
     <row r="13">
@@ -2041,7 +2050,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trean Insurance Group, Inc. (NasdaqGS:TIG)</t>
+          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2049,116 +2058,125 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.0492</v>
+      </c>
+      <c r="E13">
+        <v>0.06509999999999999</v>
+      </c>
+      <c r="F13">
+        <v>0.06269999999999999</v>
+      </c>
       <c r="G13">
-        <v>0.5732780942516831</v>
+        <v>0.1563198102540059</v>
       </c>
       <c r="H13">
-        <v>0.5732780942516831</v>
+        <v>0.1563198102540059</v>
       </c>
       <c r="I13">
-        <v>0.2171587743229555</v>
+        <v>0.1213471476844822</v>
       </c>
       <c r="J13">
-        <v>0.1702167817364317</v>
+        <v>0.1013793944807374</v>
       </c>
       <c r="K13">
-        <v>28.6</v>
+        <v>3356</v>
       </c>
       <c r="L13">
-        <v>0.1481097876747799</v>
+        <v>0.09255633084199785</v>
       </c>
       <c r="M13">
-        <v>0.417</v>
+        <v>3231</v>
       </c>
       <c r="N13">
-        <v>0.0009144736842105264</v>
+        <v>0.07353577102176258</v>
       </c>
       <c r="O13">
-        <v>0.01458041958041958</v>
+        <v>0.9627532777115614</v>
       </c>
       <c r="P13">
-        <v>0.323</v>
+        <v>870</v>
       </c>
       <c r="Q13">
-        <v>0.0007083333333333334</v>
+        <v>0.01980071828812548</v>
       </c>
       <c r="R13">
-        <v>0.01129370629370629</v>
+        <v>0.2592371871275328</v>
       </c>
       <c r="S13">
-        <v>0.09400000000000003</v>
+        <v>2361</v>
       </c>
       <c r="T13">
-        <v>0.2254196642685852</v>
+        <v>0.7307335190343547</v>
       </c>
       <c r="U13">
-        <v>134.8</v>
+        <v>773</v>
       </c>
       <c r="V13">
-        <v>0.2956140350877193</v>
+        <v>0.01759305199623103</v>
       </c>
       <c r="W13">
-        <v>0.07117969138875062</v>
+        <v>0.1178619091100653</v>
       </c>
       <c r="X13">
-        <v>0.04983306238859147</v>
+        <v>0.08508366968583198</v>
       </c>
       <c r="Y13">
-        <v>0.02134662900015915</v>
+        <v>0.03277823942423334</v>
       </c>
       <c r="Z13">
-        <v>1.34159454142896</v>
+        <v>1.160422837028855</v>
       </c>
       <c r="AA13">
-        <v>0.2283619052372013</v>
+        <v>0.1176429645596048</v>
       </c>
       <c r="AB13">
-        <v>0.04773943045223088</v>
+        <v>0.07840128236204577</v>
       </c>
       <c r="AC13">
-        <v>0.1806224747849705</v>
+        <v>0.03924168219755905</v>
       </c>
       <c r="AD13">
-        <v>30.9</v>
+        <v>7291</v>
       </c>
       <c r="AE13">
-        <v>7.1332033911865</v>
+        <v>305.3688605417994</v>
       </c>
       <c r="AF13">
-        <v>38.0332033911865</v>
+        <v>7596.368860541799</v>
       </c>
       <c r="AG13">
-        <v>-96.76679660881351</v>
+        <v>6823.368860541799</v>
       </c>
       <c r="AH13">
-        <v>0.07698511583860278</v>
+        <v>0.1474045090568661</v>
       </c>
       <c r="AI13">
-        <v>0.08262102996482369</v>
+        <v>0.276207802282823</v>
       </c>
       <c r="AJ13">
-        <v>-0.2693704136904055</v>
+        <v>0.134421035088611</v>
       </c>
       <c r="AK13">
-        <v>-0.2972563031996797</v>
+        <v>0.2552760933541732</v>
       </c>
       <c r="AL13">
-        <v>1.71</v>
+        <v>351</v>
       </c>
       <c r="AM13">
-        <v>1.71</v>
+        <v>351</v>
       </c>
       <c r="AN13">
-        <v>0.6160287081339713</v>
+        <v>1.373587038432555</v>
       </c>
       <c r="AO13">
-        <v>23.91812865497076</v>
+        <v>12.44444444444444</v>
       </c>
       <c r="AP13">
-        <v>-1.929162611818451</v>
+        <v>1.285487728059872</v>
       </c>
       <c r="AQ13">
-        <v>23.91812865497076</v>
+        <v>12.44444444444444</v>
       </c>
     </row>
     <row r="14">
@@ -2169,7 +2187,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Erie Indemnity Company (NasdaqGS:ERIE)</t>
+          <t>Old Republic International Corporation (NYSE:ORI)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2177,119 +2195,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D14">
+        <v>0.06809999999999999</v>
+      </c>
       <c r="E14">
-        <v>0.0949</v>
+        <v>0.153</v>
       </c>
       <c r="G14">
-        <v>0.1378437464043263</v>
+        <v>0.2370931703453249</v>
       </c>
       <c r="H14">
-        <v>0.1378437464043263</v>
+        <v>0.2370931703453249</v>
       </c>
       <c r="I14">
-        <v>0.1256049141042695</v>
+        <v>0.1270274176904367</v>
       </c>
       <c r="J14">
-        <v>0.09975275922625973</v>
+        <v>0.1020114950845329</v>
       </c>
       <c r="K14">
-        <v>305.6</v>
+        <v>801.3</v>
       </c>
       <c r="L14">
-        <v>0.1172093736815863</v>
+        <v>0.09473086880962794</v>
       </c>
       <c r="M14">
-        <v>189.6</v>
+        <v>366.1</v>
       </c>
       <c r="N14">
-        <v>0.02130624353845462</v>
+        <v>0.05099453978159127</v>
       </c>
       <c r="O14">
-        <v>0.6204188481675392</v>
+        <v>0.4568825658305254</v>
       </c>
       <c r="P14">
-        <v>189.6</v>
+        <v>261.3</v>
       </c>
       <c r="Q14">
-        <v>0.02130624353845462</v>
+        <v>0.03639681301537776</v>
       </c>
       <c r="R14">
-        <v>0.6204188481675392</v>
+        <v>0.3260950954698615</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>104.8</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>0.2862605845397432</v>
       </c>
       <c r="U14">
-        <v>236</v>
+        <v>102.4</v>
       </c>
       <c r="V14">
-        <v>0.02652042972086124</v>
+        <v>0.01426342767996434</v>
       </c>
       <c r="W14">
-        <v>0.2450288646568313</v>
+        <v>0.1265996776945682</v>
       </c>
       <c r="X14">
-        <v>0.04813066463988988</v>
+        <v>0.08770725284284012</v>
       </c>
       <c r="Y14">
-        <v>0.1968982000169414</v>
+        <v>0.03889242485172809</v>
       </c>
       <c r="Z14">
-        <v>2.284597141673789</v>
+        <v>1.051846086389647</v>
       </c>
       <c r="AA14">
-        <v>0.2278948686023866</v>
+        <v>0.1073003918714226</v>
       </c>
       <c r="AB14">
-        <v>0.04775669148822175</v>
+        <v>0.07698619232289282</v>
       </c>
       <c r="AC14">
-        <v>0.1801381771141649</v>
+        <v>0.03031419954852974</v>
       </c>
       <c r="AD14">
-        <v>94.3</v>
+        <v>1596.6</v>
       </c>
       <c r="AE14">
-        <v>14.05153727969126</v>
+        <v>257.5659099095169</v>
       </c>
       <c r="AF14">
-        <v>108.3515372796913</v>
+        <v>1854.165909909517</v>
       </c>
       <c r="AG14">
-        <v>-127.6484627203087</v>
+        <v>1751.765909909517</v>
       </c>
       <c r="AH14">
-        <v>0.01202950087286032</v>
+        <v>0.2052574785967116</v>
       </c>
       <c r="AI14">
-        <v>0.07765735022298791</v>
+        <v>0.2461630978096723</v>
       </c>
       <c r="AJ14">
-        <v>-0.01455321598056645</v>
+        <v>0.1961451793210646</v>
       </c>
       <c r="AK14">
-        <v>-0.1101128259185661</v>
+        <v>0.2357735565016207</v>
       </c>
       <c r="AL14">
-        <v>3.81</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AM14">
-        <v>-55.19</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="AN14">
-        <v>0.2657835400225479</v>
+        <v>1.38425524536154</v>
       </c>
       <c r="AO14">
-        <v>83.85826771653544</v>
+        <v>16.03012048192771</v>
       </c>
       <c r="AP14">
-        <v>-0.3597758250290551</v>
+        <v>1.518784385217199</v>
       </c>
       <c r="AQ14">
-        <v>-5.789092226852691</v>
+        <v>16.03012048192771</v>
       </c>
     </row>
     <row r="15">
@@ -2300,7 +2321,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The Allstate Corporation (NYSE:ALL)</t>
+          <t>AMERISAFE, Inc. (NasdaqGS:AMSF)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2309,124 +2330,118 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0742</v>
+        <v>-0.0499</v>
       </c>
       <c r="E15">
-        <v>0.174</v>
+        <v>-0.09910000000000001</v>
       </c>
       <c r="F15">
-        <v>-0.0139</v>
+        <v>0.05</v>
       </c>
       <c r="G15">
-        <v>0.1790513603391611</v>
+        <v>0.2744630071599045</v>
       </c>
       <c r="H15">
-        <v>0.1790513603391611</v>
+        <v>0.2744630071599045</v>
       </c>
       <c r="I15">
-        <v>0.1691578555657496</v>
+        <v>0.1499624332379154</v>
       </c>
       <c r="J15">
-        <v>0.1353933108441067</v>
+        <v>0.1309694690282842</v>
       </c>
       <c r="K15">
-        <v>3406</v>
+        <v>38.4</v>
       </c>
       <c r="L15">
-        <v>0.06623752941405263</v>
+        <v>0.1309239686327992</v>
       </c>
       <c r="M15">
-        <v>3075</v>
+        <v>35.7</v>
       </c>
       <c r="N15">
-        <v>0.09117216269264752</v>
+        <v>0.03587218649517685</v>
       </c>
       <c r="O15">
-        <v>0.9028185554903112</v>
+        <v>0.9296875000000001</v>
       </c>
       <c r="P15">
-        <v>818</v>
+        <v>23.5</v>
       </c>
       <c r="Q15">
-        <v>0.02425327775043436</v>
+        <v>0.02361334405144695</v>
       </c>
       <c r="R15">
-        <v>0.2401644157369348</v>
+        <v>0.6119791666666667</v>
       </c>
       <c r="S15">
-        <v>2257</v>
+        <v>12.2</v>
       </c>
       <c r="T15">
-        <v>0.7339837398373984</v>
+        <v>0.3417366946778712</v>
       </c>
       <c r="U15">
-        <v>690</v>
+        <v>91</v>
       </c>
       <c r="V15">
-        <v>0.02045814382371603</v>
+        <v>0.09143890675241158</v>
       </c>
       <c r="W15">
-        <v>0.1346617641244613</v>
+        <v>0.07996668054977092</v>
       </c>
       <c r="X15">
-        <v>0.05385916262929531</v>
+        <v>0.07977694787474857</v>
       </c>
       <c r="Y15">
-        <v>0.08080260149516601</v>
+        <v>0.0001897326750223555</v>
       </c>
       <c r="Z15">
-        <v>1.632533477656651</v>
+        <v>0.8209015778749892</v>
       </c>
       <c r="AA15">
-        <v>0.2210341126037774</v>
+        <v>0.1075130437787681</v>
       </c>
       <c r="AB15">
-        <v>0.04645204100460967</v>
+        <v>0.0797684874422683</v>
       </c>
       <c r="AC15">
-        <v>0.1745820715991677</v>
+        <v>0.02774455633649975</v>
       </c>
       <c r="AD15">
-        <v>7981</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>513.6695447679505</v>
+        <v>0.1900916565970358</v>
       </c>
       <c r="AF15">
-        <v>8494.66954476795</v>
+        <v>0.1900916565970358</v>
       </c>
       <c r="AG15">
-        <v>7804.66954476795</v>
+        <v>-90.80990834340297</v>
       </c>
       <c r="AH15">
-        <v>0.2011902693628287</v>
+        <v>0.0001909720201058784</v>
       </c>
       <c r="AI15">
-        <v>0.2413143937381947</v>
+        <v>0.00050936951662681</v>
       </c>
       <c r="AJ15">
-        <v>0.187919109986927</v>
+        <v>-0.1004101097315915</v>
       </c>
       <c r="AK15">
-        <v>0.2261458123503375</v>
+        <v>-0.3218040286613303</v>
       </c>
       <c r="AL15">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>0.8139724630290668</v>
-      </c>
-      <c r="AO15">
-        <v>26.62883435582822</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>0.7959887348055024</v>
-      </c>
-      <c r="AQ15">
-        <v>26.62883435582822</v>
+        <v>-2.008091379050085</v>
       </c>
     </row>
     <row r="16">
@@ -2437,7 +2452,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RLI Corp. (NYSE:RLI)</t>
+          <t>Trean Insurance Group, Inc. (NasdaqGS:TIG)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2445,122 +2460,116 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.0742</v>
-      </c>
-      <c r="E16">
-        <v>0.181</v>
-      </c>
       <c r="G16">
-        <v>0.1590967853141429</v>
+        <v>0.1121597096188748</v>
       </c>
       <c r="H16">
-        <v>0.1590967853141429</v>
+        <v>0.1121597096188748</v>
       </c>
       <c r="I16">
-        <v>0.2659668498034096</v>
+        <v>0.08158870902362893</v>
       </c>
       <c r="J16">
-        <v>0.2158513149419371</v>
+        <v>0.06442360673942925</v>
       </c>
       <c r="K16">
-        <v>267.9</v>
+        <v>26.6</v>
       </c>
       <c r="L16">
-        <v>0.2308885633025941</v>
+        <v>0.09655172413793103</v>
       </c>
       <c r="M16">
-        <v>44.3</v>
+        <v>0.023</v>
       </c>
       <c r="N16">
-        <v>0.00873439933752637</v>
+        <v>7.484542792059876e-05</v>
       </c>
       <c r="O16">
-        <v>0.1653602090332214</v>
+        <v>0.0008646616541353383</v>
       </c>
       <c r="P16">
-        <v>44.3</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.00873439933752637</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.1653602090332214</v>
+        <v>-0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>89.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="V16">
-        <v>0.01766596344565153</v>
+        <v>0.2652131467621217</v>
       </c>
       <c r="W16">
-        <v>0.243700536705176</v>
+        <v>0.06298839687426</v>
       </c>
       <c r="X16">
-        <v>0.04863387413713293</v>
+        <v>0.08799678114042855</v>
       </c>
       <c r="Y16">
-        <v>0.1950666625680431</v>
+        <v>-0.02500838426616855</v>
       </c>
       <c r="Z16">
-        <v>1.008129574206525</v>
+        <v>1.521581997660034</v>
       </c>
       <c r="AA16">
-        <v>0.2176060942243335</v>
+        <v>0.0980258002390452</v>
       </c>
       <c r="AB16">
-        <v>0.04761783647913753</v>
+        <v>0.08051696001039566</v>
       </c>
       <c r="AC16">
-        <v>0.1699882577451959</v>
+        <v>0.01750884022864954</v>
       </c>
       <c r="AD16">
-        <v>149.6</v>
+        <v>77.5</v>
       </c>
       <c r="AE16">
-        <v>18.94332086551947</v>
+        <v>4.761553319951138</v>
       </c>
       <c r="AF16">
-        <v>168.5433208655195</v>
+        <v>82.26155331995113</v>
       </c>
       <c r="AG16">
-        <v>78.94332086551947</v>
+        <v>0.7615533199511333</v>
       </c>
       <c r="AH16">
-        <v>0.03216203487869851</v>
+        <v>0.2111644555754937</v>
       </c>
       <c r="AI16">
-        <v>0.1187892407758632</v>
+        <v>0.1694851039545033</v>
       </c>
       <c r="AJ16">
-        <v>0.01532629046310309</v>
+        <v>0.002472081672457802</v>
       </c>
       <c r="AK16">
-        <v>0.05938966901418512</v>
+        <v>0.001885679173198762</v>
       </c>
       <c r="AL16">
-        <v>7.61</v>
+        <v>2.22</v>
       </c>
       <c r="AM16">
-        <v>7.61</v>
+        <v>2.22</v>
       </c>
       <c r="AN16">
-        <v>0.4678069983426623</v>
+        <v>2.563678465100893</v>
       </c>
       <c r="AO16">
-        <v>40.2628120893561</v>
+        <v>9.459459459459458</v>
       </c>
       <c r="AP16">
-        <v>0.2468598795006706</v>
+        <v>0.02519197221141691</v>
       </c>
       <c r="AQ16">
-        <v>40.2628120893561</v>
+        <v>9.459459459459458</v>
       </c>
     </row>
     <row r="17">
@@ -2571,7 +2580,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mercury General Corporation (NYSE:MCY)</t>
+          <t>The Hanover Insurance Group, Inc. (NYSE:THG)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2580,121 +2589,124 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0415</v>
+        <v>0.0392</v>
       </c>
       <c r="E17">
-        <v>0.257</v>
+        <v>0.192</v>
+      </c>
+      <c r="F17">
+        <v>0.161</v>
       </c>
       <c r="G17">
-        <v>0.1354682869736285</v>
+        <v>0.1065866924968333</v>
       </c>
       <c r="H17">
-        <v>0.1354682869736285</v>
+        <v>0.1065866924968333</v>
       </c>
       <c r="I17">
-        <v>0.1233521789175701</v>
+        <v>0.07404440801728635</v>
       </c>
       <c r="J17">
-        <v>0.1005179015225237</v>
+        <v>0.05937811537012096</v>
       </c>
       <c r="K17">
-        <v>384.2</v>
+        <v>291.1</v>
       </c>
       <c r="L17">
-        <v>0.09567447767512513</v>
+        <v>0.05422472244989197</v>
       </c>
       <c r="M17">
-        <v>140.1</v>
+        <v>157.5</v>
       </c>
       <c r="N17">
-        <v>0.04768550034036759</v>
+        <v>0.03277494537509104</v>
       </c>
       <c r="O17">
-        <v>0.3646538261322228</v>
+        <v>0.5410511851597389</v>
       </c>
       <c r="P17">
-        <v>140.1</v>
+        <v>106.7</v>
       </c>
       <c r="Q17">
-        <v>0.04768550034036759</v>
+        <v>0.02220372489855374</v>
       </c>
       <c r="R17">
-        <v>0.3646538261322228</v>
+        <v>0.3665407076605977</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>50.8</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.3225396825396825</v>
       </c>
       <c r="U17">
-        <v>341.6</v>
+        <v>164.8</v>
       </c>
       <c r="V17">
-        <v>0.1162695711368278</v>
+        <v>0.03429403808136511</v>
       </c>
       <c r="W17">
-        <v>0.2021254208754209</v>
+        <v>0.09383360732359862</v>
       </c>
       <c r="X17">
-        <v>0.0512283868920003</v>
+        <v>0.08477278138998874</v>
       </c>
       <c r="Y17">
-        <v>0.1508970339834206</v>
+        <v>0.009060825933609878</v>
       </c>
       <c r="Z17">
-        <v>2.057146137999544</v>
+        <v>1.519200837648923</v>
       </c>
       <c r="AA17">
-        <v>0.2067800129168782</v>
+        <v>0.09020728260830216</v>
       </c>
       <c r="AB17">
-        <v>0.04698317949436519</v>
+        <v>0.07787178015455212</v>
       </c>
       <c r="AC17">
-        <v>0.159796833422513</v>
+        <v>0.01233550245375004</v>
       </c>
       <c r="AD17">
-        <v>372.8</v>
+        <v>782.2</v>
       </c>
       <c r="AE17">
-        <v>43.77327560356854</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>416.5732756035686</v>
+        <v>782.2</v>
       </c>
       <c r="AG17">
-        <v>74.97327560356854</v>
+        <v>617.4000000000001</v>
       </c>
       <c r="AH17">
-        <v>0.1241807053770847</v>
+        <v>0.1399860407681157</v>
       </c>
       <c r="AI17">
-        <v>0.1626303422999446</v>
+        <v>0.2541177999415223</v>
       </c>
       <c r="AJ17">
-        <v>0.0248834850978058</v>
+        <v>0.1138505227830128</v>
       </c>
       <c r="AK17">
-        <v>0.03377367367206301</v>
+        <v>0.2119246215631758</v>
       </c>
       <c r="AL17">
-        <v>17.1</v>
+        <v>34</v>
       </c>
       <c r="AM17">
-        <v>17.1</v>
+        <v>34</v>
       </c>
       <c r="AN17">
-        <v>0.6440912232204562</v>
+        <v>1.89900461277009</v>
       </c>
       <c r="AO17">
-        <v>28.57894736842105</v>
+        <v>11.69117647058824</v>
       </c>
       <c r="AP17">
-        <v>0.1295322660738918</v>
+        <v>1.498907501820831</v>
       </c>
       <c r="AQ17">
-        <v>28.57894736842105</v>
+        <v>11.69117647058824</v>
       </c>
     </row>
     <row r="18">
@@ -2705,7 +2717,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Old Republic International Corporation (NYSE:ORI)</t>
+          <t>United Fire Group, Inc. (NasdaqGS:UFCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2714,49 +2726,46 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.0917</v>
+        <v>-0.0141</v>
       </c>
       <c r="E18">
-        <v>0.274</v>
-      </c>
-      <c r="F18">
-        <v>0.1</v>
+        <v>0.253</v>
       </c>
       <c r="G18">
-        <v>0.08393224386899892</v>
+        <v>0.1096031256426074</v>
       </c>
       <c r="H18">
-        <v>0.08393224386899892</v>
+        <v>0.1096031256426074</v>
       </c>
       <c r="I18">
-        <v>0.2034459626530649</v>
+        <v>0.06954082303996571</v>
       </c>
       <c r="J18">
-        <v>0.1626610201176175</v>
+        <v>0.05930693854721225</v>
       </c>
       <c r="K18">
-        <v>1427</v>
+        <v>52.6</v>
       </c>
       <c r="L18">
-        <v>0.1577806771190376</v>
+        <v>0.05408184248406334</v>
       </c>
       <c r="M18">
-        <v>259.9</v>
+        <v>15.6</v>
       </c>
       <c r="N18">
-        <v>0.03521441636745477</v>
+        <v>0.0226283724978242</v>
       </c>
       <c r="O18">
-        <v>0.1821303433777155</v>
+        <v>0.2965779467680608</v>
       </c>
       <c r="P18">
-        <v>259.9</v>
+        <v>15.6</v>
       </c>
       <c r="Q18">
-        <v>0.03521441636745477</v>
+        <v>0.0226283724978242</v>
       </c>
       <c r="R18">
-        <v>0.1821303433777155</v>
+        <v>0.2965779467680608</v>
       </c>
       <c r="S18">
         <v>0</v>
@@ -2765,73 +2774,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>133.4</v>
+        <v>53</v>
       </c>
       <c r="V18">
-        <v>0.01807465618860511</v>
+        <v>0.07687844502465913</v>
       </c>
       <c r="W18">
-        <v>0.2349125868369934</v>
+        <v>0.06457949662369553</v>
       </c>
       <c r="X18">
-        <v>0.0539167985629968</v>
+        <v>0.08323984626457742</v>
       </c>
       <c r="Y18">
-        <v>0.1809957882739966</v>
+        <v>-0.0186603496408819</v>
       </c>
       <c r="Z18">
-        <v>1.250188318433605</v>
+        <v>1.28054058763148</v>
       </c>
       <c r="AA18">
-        <v>0.2033569072155389</v>
+        <v>0.07594494193787128</v>
       </c>
       <c r="AB18">
-        <v>0.04644144821587828</v>
+        <v>0.07898062181608391</v>
       </c>
       <c r="AC18">
-        <v>0.1569154589996606</v>
+        <v>-0.003035679878212627</v>
       </c>
       <c r="AD18">
-        <v>1588.2</v>
+        <v>50</v>
       </c>
       <c r="AE18">
-        <v>288.4701228657509</v>
+        <v>27.8229775566467</v>
       </c>
       <c r="AF18">
-        <v>1876.670122865751</v>
+        <v>77.82297755664669</v>
       </c>
       <c r="AG18">
-        <v>1743.270122865751</v>
+        <v>24.82297755664669</v>
       </c>
       <c r="AH18">
-        <v>0.2027261136997219</v>
+        <v>0.1014346283064766</v>
       </c>
       <c r="AI18">
-        <v>0.2286929181407451</v>
+        <v>0.09994950033565492</v>
       </c>
       <c r="AJ18">
-        <v>0.1910690536247525</v>
+        <v>0.03475522117975814</v>
       </c>
       <c r="AK18">
-        <v>0.215947152098778</v>
+        <v>0.03420919447759474</v>
       </c>
       <c r="AL18">
-        <v>51.6</v>
+        <v>3.19</v>
       </c>
       <c r="AM18">
-        <v>51.6</v>
+        <v>3.19</v>
       </c>
       <c r="AN18">
-        <v>0.825167558580558</v>
+        <v>0.6024096385542169</v>
       </c>
       <c r="AO18">
-        <v>35.58914728682171</v>
+        <v>20.3448275862069</v>
       </c>
       <c r="AP18">
-        <v>0.9057360226870426</v>
+        <v>0.2990720187547794</v>
       </c>
       <c r="AQ18">
-        <v>35.58914728682171</v>
+        <v>20.3448275862069</v>
       </c>
     </row>
     <row r="19">
@@ -2842,7 +2851,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Progressive Corporation (NYSE:PGR)</t>
+          <t>Selective Insurance Group, Inc. (NasdaqGS:SIGI)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2851,124 +2860,124 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.155</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="E19">
-        <v>0.33</v>
+        <v>0.0593</v>
       </c>
       <c r="F19">
-        <v>-0.0482</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G19">
-        <v>0.1657021095796934</v>
+        <v>0.1696110024168489</v>
       </c>
       <c r="H19">
-        <v>0.1657021095796934</v>
+        <v>0.1696110024168489</v>
       </c>
       <c r="I19">
-        <v>0.1154263177606914</v>
+        <v>0.09299982307996543</v>
       </c>
       <c r="J19">
-        <v>0.09195858020998771</v>
+        <v>0.07451285183659734</v>
       </c>
       <c r="K19">
-        <v>4072.9</v>
+        <v>237.4</v>
       </c>
       <c r="L19">
-        <v>0.087398099210973</v>
+        <v>0.06830475313614916</v>
       </c>
       <c r="M19">
-        <v>3074.4</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="N19">
-        <v>0.05130233233378555</v>
+        <v>0.01570866878861637</v>
       </c>
       <c r="O19">
-        <v>0.754842986569766</v>
+        <v>0.3534119629317607</v>
       </c>
       <c r="P19">
-        <v>2870.1</v>
+        <v>65.7</v>
       </c>
       <c r="Q19">
-        <v>0.04789319022612474</v>
+        <v>0.01230106721587718</v>
       </c>
       <c r="R19">
-        <v>0.7046821674973606</v>
+        <v>0.2767481044650379</v>
       </c>
       <c r="S19">
-        <v>204.3000000000002</v>
+        <v>18.2</v>
       </c>
       <c r="T19">
-        <v>0.06645199063231856</v>
+        <v>0.2169249106078665</v>
       </c>
       <c r="U19">
-        <v>270.6</v>
+        <v>0.538</v>
       </c>
       <c r="V19">
-        <v>0.004515486315873787</v>
+        <v>0.0001007302003370156</v>
       </c>
       <c r="W19">
-        <v>0.2315029016727959</v>
+        <v>0.08721207890966534</v>
       </c>
       <c r="X19">
-        <v>0.04986361109106109</v>
+        <v>0.08293681966422747</v>
       </c>
       <c r="Y19">
-        <v>0.1816392905817348</v>
+        <v>0.004275259245437868</v>
       </c>
       <c r="Z19">
-        <v>2.015950794187164</v>
+        <v>1.004589364446524</v>
       </c>
       <c r="AA19">
-        <v>0.1853839728066487</v>
+        <v>0.07485481846962531</v>
       </c>
       <c r="AB19">
-        <v>0.04730118785914222</v>
+        <v>0.07850383405883657</v>
       </c>
       <c r="AC19">
-        <v>0.1380827849475065</v>
+        <v>-0.003649015589211255</v>
       </c>
       <c r="AD19">
-        <v>4898.2</v>
+        <v>505.2</v>
       </c>
       <c r="AE19">
-        <v>176.686838057929</v>
+        <v>45.04907451636089</v>
       </c>
       <c r="AF19">
-        <v>5074.886838057929</v>
+        <v>550.2490745163609</v>
       </c>
       <c r="AG19">
-        <v>4804.286838057928</v>
+        <v>549.7110745163609</v>
       </c>
       <c r="AH19">
-        <v>0.07807279569317165</v>
+        <v>0.09340108821685379</v>
       </c>
       <c r="AI19">
-        <v>0.2147374292057518</v>
+        <v>0.184786918154187</v>
       </c>
       <c r="AJ19">
-        <v>0.07421881521057284</v>
+        <v>0.09331828832930722</v>
       </c>
       <c r="AK19">
-        <v>0.2056419522268856</v>
+        <v>0.1846396042328506</v>
       </c>
       <c r="AL19">
-        <v>223.2</v>
+        <v>28.8</v>
       </c>
       <c r="AM19">
-        <v>223.2</v>
+        <v>28.8</v>
       </c>
       <c r="AN19">
-        <v>0.8519794058303763</v>
+        <v>1.325845055637203</v>
       </c>
       <c r="AO19">
-        <v>23.90456989247312</v>
+        <v>11.28472222222222</v>
       </c>
       <c r="AP19">
-        <v>0.8356444093191973</v>
+        <v>1.442659758860909</v>
       </c>
       <c r="AQ19">
-        <v>23.90456989247312</v>
+        <v>11.28472222222222</v>
       </c>
     </row>
     <row r="20">
@@ -2979,7 +2988,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation (NYSE:WRB)</t>
+          <t>CNA Financial Corporation (NYSE:CNA)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2988,124 +2997,124 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0417</v>
+        <v>0.0451</v>
       </c>
       <c r="E20">
-        <v>0.132</v>
+        <v>-0.00109</v>
       </c>
       <c r="F20">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="G20">
-        <v>0.1087304264557058</v>
+        <v>0.1396548807308408</v>
       </c>
       <c r="H20">
-        <v>0.1087304264557058</v>
+        <v>0.1396548807308408</v>
       </c>
       <c r="I20">
-        <v>0.1634400589729499</v>
+        <v>0.1034868581368291</v>
       </c>
       <c r="J20">
-        <v>0.1291566693337494</v>
+        <v>0.08449419393087571</v>
       </c>
       <c r="K20">
-        <v>1040.2</v>
+        <v>912</v>
       </c>
       <c r="L20">
-        <v>0.1131919431537482</v>
+        <v>0.07714430722382</v>
       </c>
       <c r="M20">
-        <v>245.6</v>
+        <v>264.6</v>
       </c>
       <c r="N20">
-        <v>0.01687578160429865</v>
+        <v>0.0231023102310231</v>
       </c>
       <c r="O20">
-        <v>0.2361084406844838</v>
+        <v>0.2901315789473685</v>
       </c>
       <c r="P20">
-        <v>88.7</v>
+        <v>225.6</v>
       </c>
       <c r="Q20">
-        <v>0.006094795717839131</v>
+        <v>0.0196972078160197</v>
       </c>
       <c r="R20">
-        <v>0.08527206306479523</v>
+        <v>0.2473684210526316</v>
       </c>
       <c r="S20">
-        <v>156.9</v>
+        <v>39.00000000000003</v>
       </c>
       <c r="T20">
-        <v>0.6388436482084692</v>
+        <v>0.1473922902494332</v>
       </c>
       <c r="U20">
-        <v>2069</v>
+        <v>503</v>
       </c>
       <c r="V20">
-        <v>0.1421660917723694</v>
+        <v>0.04391709012171058</v>
       </c>
       <c r="W20">
-        <v>0.1735083651648847</v>
+        <v>0.07201516108654453</v>
       </c>
       <c r="X20">
-        <v>0.05356244182150843</v>
+        <v>0.08786777572092243</v>
       </c>
       <c r="Y20">
-        <v>0.1199459233433762</v>
+        <v>-0.0158526146343779</v>
       </c>
       <c r="Z20">
-        <v>1.403977674926973</v>
+        <v>0.7930560002912364</v>
       </c>
       <c r="AA20">
-        <v>0.1813330803125094</v>
+        <v>0.06700862748665234</v>
       </c>
       <c r="AB20">
-        <v>0.04650722705635853</v>
+        <v>0.076941610244011</v>
       </c>
       <c r="AC20">
-        <v>0.1348258532561508</v>
+        <v>-0.009932982757358655</v>
       </c>
       <c r="AD20">
-        <v>3266.1</v>
+        <v>2780</v>
       </c>
       <c r="AE20">
-        <v>218.6744502814088</v>
+        <v>237.8918155320311</v>
       </c>
       <c r="AF20">
-        <v>3484.774450281409</v>
+        <v>3017.891815532031</v>
       </c>
       <c r="AG20">
-        <v>1415.774450281409</v>
+        <v>2514.891815532031</v>
       </c>
       <c r="AH20">
-        <v>0.193188865086458</v>
+        <v>0.2085433597775238</v>
       </c>
       <c r="AI20">
-        <v>0.343379142092118</v>
+        <v>0.2715911804787073</v>
       </c>
       <c r="AJ20">
-        <v>0.08865670887930341</v>
+        <v>0.1800429035091892</v>
       </c>
       <c r="AK20">
-        <v>0.1752310077831978</v>
+        <v>0.2370550910746478</v>
       </c>
       <c r="AL20">
-        <v>145.5</v>
+        <v>112</v>
       </c>
       <c r="AM20">
-        <v>145.5</v>
+        <v>112</v>
       </c>
       <c r="AN20">
-        <v>1.937303517409099</v>
+        <v>2.102874432677761</v>
       </c>
       <c r="AO20">
-        <v>10.29690721649485</v>
+        <v>10.97321428571429</v>
       </c>
       <c r="AP20">
-        <v>0.8397736818799507</v>
+        <v>1.902338740947074</v>
       </c>
       <c r="AQ20">
-        <v>10.29690721649485</v>
+        <v>10.97321428571429</v>
       </c>
     </row>
     <row r="21">
@@ -3116,7 +3125,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Safety Insurance Group, Inc. (NasdaqGS:SAFT)</t>
+          <t>Tiptree Inc. (NasdaqCM:TIPT)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3125,121 +3134,118 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.0188</v>
-      </c>
-      <c r="E21">
-        <v>0.192</v>
+        <v>0.179</v>
       </c>
       <c r="G21">
-        <v>0.204476776720761</v>
+        <v>0.09740308618742943</v>
       </c>
       <c r="H21">
-        <v>0.204476776720761</v>
+        <v>0.09740308618742943</v>
       </c>
       <c r="I21">
-        <v>0.2141629433270439</v>
+        <v>0.04349661009611804</v>
       </c>
       <c r="J21">
-        <v>0.1693641221094411</v>
+        <v>0.02174830504805902</v>
       </c>
       <c r="K21">
-        <v>151.6</v>
+        <v>-9.57</v>
       </c>
       <c r="L21">
-        <v>0.1696698377168439</v>
+        <v>-0.007203613097478359</v>
       </c>
       <c r="M21">
-        <v>53.9</v>
+        <v>13.01</v>
       </c>
       <c r="N21">
-        <v>0.04231101342334562</v>
+        <v>0.02593183177197528</v>
       </c>
       <c r="O21">
-        <v>0.3555408970976253</v>
+        <v>-1.359456635318704</v>
       </c>
       <c r="P21">
-        <v>53.9</v>
+        <v>6.09</v>
       </c>
       <c r="Q21">
-        <v>0.04231101342334562</v>
+        <v>0.01213872832369942</v>
       </c>
       <c r="R21">
-        <v>0.3555408970976253</v>
+        <v>-0.6363636363636364</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.5318985395849347</v>
       </c>
       <c r="U21">
-        <v>44.7</v>
+        <v>503.5</v>
       </c>
       <c r="V21">
-        <v>0.03508909647539053</v>
+        <v>1.003587801474985</v>
       </c>
       <c r="W21">
-        <v>0.1809285117555794</v>
+        <v>-0.02484423676012461</v>
       </c>
       <c r="X21">
-        <v>0.04895552309345364</v>
+        <v>0.1001804922039535</v>
       </c>
       <c r="Y21">
-        <v>0.1319729886621258</v>
+        <v>-0.1250247289640781</v>
       </c>
       <c r="Z21">
-        <v>1.066640179849531</v>
+        <v>2.570508718260785</v>
       </c>
       <c r="AA21">
-        <v>0.1806505776668722</v>
+        <v>0.05590420773343074</v>
       </c>
       <c r="AB21">
-        <v>0.04753200763705114</v>
+        <v>0.07666093102367669</v>
       </c>
       <c r="AC21">
-        <v>0.1331185700298211</v>
+        <v>-0.02075672329024594</v>
       </c>
       <c r="AD21">
-        <v>30</v>
+        <v>295.3</v>
       </c>
       <c r="AE21">
-        <v>29.47705068643128</v>
+        <v>37.92376743653597</v>
       </c>
       <c r="AF21">
-        <v>59.47705068643128</v>
+        <v>333.223767436536</v>
       </c>
       <c r="AG21">
-        <v>14.77705068643128</v>
+        <v>-170.276232563464</v>
       </c>
       <c r="AH21">
-        <v>0.04460632546196299</v>
+        <v>0.399106817212345</v>
       </c>
       <c r="AI21">
-        <v>0.06022522561160246</v>
+        <v>0.3907299258768996</v>
       </c>
       <c r="AJ21">
-        <v>0.01146683777643133</v>
+        <v>-0.5137719418269242</v>
       </c>
       <c r="AK21">
-        <v>0.01567229860528828</v>
+        <v>-0.4874453113024989</v>
       </c>
       <c r="AL21">
-        <v>0.522</v>
+        <v>35.6</v>
       </c>
       <c r="AM21">
-        <v>0.522</v>
+        <v>35.6</v>
       </c>
       <c r="AN21">
-        <v>0.1467351430667645</v>
+        <v>3.307942197826818</v>
       </c>
       <c r="AO21">
-        <v>368.3908045977012</v>
+        <v>1.603932584269663</v>
       </c>
       <c r="AP21">
-        <v>0.07227708821927749</v>
+        <v>-1.907429512304963</v>
       </c>
       <c r="AQ21">
-        <v>368.3908045977012</v>
+        <v>1.603932584269663</v>
       </c>
     </row>
     <row r="22">
@@ -3250,7 +3256,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tiptree Inc. (NasdaqCM:TIPT)</t>
+          <t>Kingsway Financial Services Inc. (NYSE:KFS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3258,122 +3264,116 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.155</v>
-      </c>
-      <c r="E22">
-        <v>0.305</v>
-      </c>
       <c r="G22">
-        <v>0.01407342657342658</v>
+        <v>0.1162377994676131</v>
       </c>
       <c r="H22">
-        <v>0.01407342657342658</v>
+        <v>0.1162377994676131</v>
       </c>
       <c r="I22">
-        <v>0.105022212408363</v>
+        <v>0.07704389032252755</v>
       </c>
       <c r="J22">
-        <v>0.07870018955158342</v>
+        <v>0.06914926946231793</v>
       </c>
       <c r="K22">
-        <v>52.8</v>
+        <v>33.7</v>
       </c>
       <c r="L22">
-        <v>0.04615384615384615</v>
+        <v>0.2990239574090506</v>
       </c>
       <c r="M22">
-        <v>13</v>
+        <v>0.328</v>
       </c>
       <c r="N22">
-        <v>0.02773037542662116</v>
+        <v>0.001725407680168333</v>
       </c>
       <c r="O22">
-        <v>0.2462121212121212</v>
+        <v>0.009732937685459941</v>
       </c>
       <c r="P22">
-        <v>5.39</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.01149744027303754</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.1020833333333333</v>
+        <v>-0</v>
       </c>
       <c r="S22">
-        <v>7.61</v>
+        <v>0.328</v>
       </c>
       <c r="T22">
-        <v>0.5853846153846154</v>
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>150.5</v>
+        <v>48.6</v>
       </c>
       <c r="V22">
-        <v>0.3210324232081911</v>
+        <v>0.2556549184639664</v>
       </c>
       <c r="W22">
-        <v>0.1518550474547023</v>
+        <v>-4.970501474926253</v>
       </c>
       <c r="X22">
-        <v>0.07174587882220945</v>
+        <v>0.126008336301855</v>
       </c>
       <c r="Y22">
-        <v>0.08010916863249287</v>
+        <v>-5.096509811228109</v>
       </c>
       <c r="Z22">
-        <v>1.946164248408122</v>
+        <v>0.7328853018259091</v>
       </c>
       <c r="AA22">
-        <v>0.1531634952482341</v>
+        <v>0.050678483220932</v>
       </c>
       <c r="AB22">
-        <v>0.04607641089277995</v>
+        <v>0.07162020677225467</v>
       </c>
       <c r="AC22">
-        <v>0.1070870843554541</v>
+        <v>-0.02094172355132267</v>
       </c>
       <c r="AD22">
-        <v>423.3</v>
+        <v>283.6</v>
       </c>
       <c r="AE22">
-        <v>45.62294502416349</v>
+        <v>2.445767803255718</v>
       </c>
       <c r="AF22">
-        <v>468.9229450241635</v>
+        <v>286.0457678032557</v>
       </c>
       <c r="AG22">
-        <v>318.4229450241635</v>
+        <v>237.4457678032557</v>
       </c>
       <c r="AH22">
-        <v>0.5000655550900274</v>
+        <v>0.600752515606629</v>
       </c>
       <c r="AI22">
-        <v>0.5383588890544724</v>
+        <v>0.8537513238227991</v>
       </c>
       <c r="AJ22">
-        <v>0.4044889024600136</v>
+        <v>0.5553692392355091</v>
       </c>
       <c r="AK22">
-        <v>0.4419331087554538</v>
+        <v>0.8289379508875987</v>
       </c>
       <c r="AL22">
-        <v>36</v>
+        <v>6.73</v>
       </c>
       <c r="AM22">
-        <v>36</v>
+        <v>6.73</v>
       </c>
       <c r="AN22">
-        <v>2.769019428272389</v>
+        <v>15.34465966886701</v>
       </c>
       <c r="AO22">
-        <v>3.35</v>
+        <v>1.216939078751857</v>
       </c>
       <c r="AP22">
-        <v>2.082965559129741</v>
+        <v>12.84740654708667</v>
       </c>
       <c r="AQ22">
-        <v>3.35</v>
+        <v>1.216939078751857</v>
       </c>
     </row>
     <row r="23">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Selective Insurance Group, Inc. (NasdaqGS:SIGI)</t>
+          <t>Safety Insurance Group, Inc. (NasdaqGS:SAFT)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3393,124 +3393,121 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.08039999999999999</v>
+        <v>-0.00859</v>
       </c>
       <c r="E23">
-        <v>0.213</v>
-      </c>
-      <c r="F23">
-        <v>0.117</v>
+        <v>-0.0305</v>
       </c>
       <c r="G23">
-        <v>0.1189576468454306</v>
+        <v>0.2153248056182593</v>
       </c>
       <c r="H23">
-        <v>0.1189576468454306</v>
+        <v>0.2153248056182593</v>
       </c>
       <c r="I23">
-        <v>0.1724693264292366</v>
+        <v>0.0861169086888393</v>
       </c>
       <c r="J23">
-        <v>0.1378159150504853</v>
+        <v>0.06816007897692272</v>
       </c>
       <c r="K23">
-        <v>431.9</v>
+        <v>54</v>
       </c>
       <c r="L23">
-        <v>0.1305662202605883</v>
+        <v>0.06772009029345373</v>
       </c>
       <c r="M23">
-        <v>67.28999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="N23">
-        <v>0.01365878412666193</v>
+        <v>0.06401997100982446</v>
       </c>
       <c r="O23">
-        <v>0.1557999536929845</v>
+        <v>1.472222222222222</v>
       </c>
       <c r="P23">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="Q23">
-        <v>0.01183395920024358</v>
+        <v>0.04292156546947978</v>
       </c>
       <c r="R23">
-        <v>0.1349849502199583</v>
+        <v>0.9870370370370369</v>
       </c>
       <c r="S23">
-        <v>8.989999999999995</v>
+        <v>26.2</v>
       </c>
       <c r="T23">
-        <v>0.1336008322187546</v>
+        <v>0.329559748427673</v>
       </c>
       <c r="U23">
-        <v>0.477</v>
+        <v>33.6</v>
       </c>
       <c r="V23">
-        <v>9.682330254744747e-05</v>
+        <v>0.02705749718151071</v>
       </c>
       <c r="W23">
-        <v>0.1804395053475936</v>
+        <v>0.05818338541105484</v>
       </c>
       <c r="X23">
-        <v>0.05046757996751439</v>
+        <v>0.08110364200947612</v>
       </c>
       <c r="Y23">
-        <v>0.1299719253800792</v>
+        <v>-0.02292025659842128</v>
       </c>
       <c r="Z23">
-        <v>1.052345738013344</v>
+        <v>0.8507851653464497</v>
       </c>
       <c r="AA23">
-        <v>0.1450299908337873</v>
+        <v>0.05798958406240828</v>
       </c>
       <c r="AB23">
-        <v>0.04715642008808393</v>
+        <v>0.07920715390710335</v>
       </c>
       <c r="AC23">
-        <v>0.09787357074570338</v>
+        <v>-0.02121756984469508</v>
       </c>
       <c r="AD23">
-        <v>500.9</v>
+        <v>30</v>
       </c>
       <c r="AE23">
-        <v>40.79357552364037</v>
+        <v>23.85188505759775</v>
       </c>
       <c r="AF23">
-        <v>541.6935755236403</v>
+        <v>53.85188505759775</v>
       </c>
       <c r="AG23">
-        <v>541.2165755236404</v>
+        <v>20.25188505759775</v>
       </c>
       <c r="AH23">
-        <v>0.09906261876835024</v>
+        <v>0.04156354471340409</v>
       </c>
       <c r="AI23">
-        <v>0.156387372316709</v>
+        <v>0.06424308255972189</v>
       </c>
       <c r="AJ23">
-        <v>0.09898402158341726</v>
+        <v>0.01604679276452528</v>
       </c>
       <c r="AK23">
-        <v>0.1562711821808581</v>
+        <v>0.02516850508111107</v>
       </c>
       <c r="AL23">
-        <v>29.5</v>
+        <v>0.524</v>
       </c>
       <c r="AM23">
-        <v>29.5</v>
+        <v>0.524</v>
       </c>
       <c r="AN23">
-        <v>0.7897267725101298</v>
+        <v>0.3734129947722181</v>
       </c>
       <c r="AO23">
-        <v>19.33220338983051</v>
+        <v>131.1068702290076</v>
       </c>
       <c r="AP23">
-        <v>0.8532905159059082</v>
+        <v>0.2520772349713437</v>
       </c>
       <c r="AQ23">
-        <v>19.33220338983051</v>
+        <v>131.1068702290076</v>
       </c>
     </row>
     <row r="24">
@@ -3521,7 +3518,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Employers Holdings, Inc. (NYSE:EIG)</t>
+          <t>Loews Corporation (NYSE:L)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3530,121 +3527,121 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.0207</v>
+        <v>0.005759999999999999</v>
       </c>
       <c r="E24">
-        <v>0.0559</v>
+        <v>0.00367</v>
       </c>
       <c r="G24">
-        <v>0.2262384792626728</v>
+        <v>0.2243387004025302</v>
       </c>
       <c r="H24">
-        <v>0.2262384792626728</v>
+        <v>0.2243387004025302</v>
       </c>
       <c r="I24">
-        <v>0.2364608665989049</v>
+        <v>0.1248034582131382</v>
       </c>
       <c r="J24">
-        <v>0.1911020211192407</v>
+        <v>0.09936697626060706</v>
       </c>
       <c r="K24">
-        <v>128.5</v>
+        <v>991</v>
       </c>
       <c r="L24">
-        <v>0.1850518433179724</v>
+        <v>0.07123346751006325</v>
       </c>
       <c r="M24">
-        <v>80.2</v>
+        <v>984</v>
       </c>
       <c r="N24">
-        <v>0.06930521949533357</v>
+        <v>0.07105154847607426</v>
       </c>
       <c r="O24">
-        <v>0.624124513618677</v>
+        <v>0.9929364278506559</v>
       </c>
       <c r="P24">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="Q24">
-        <v>0.02506049083995852</v>
+        <v>0.004476825208858337</v>
       </c>
       <c r="R24">
-        <v>0.2256809338521401</v>
+        <v>0.06256306760847628</v>
       </c>
       <c r="S24">
-        <v>51.2</v>
+        <v>922</v>
       </c>
       <c r="T24">
-        <v>0.6384039900249376</v>
+        <v>0.9369918699186992</v>
       </c>
       <c r="U24">
-        <v>95.59999999999999</v>
+        <v>886</v>
       </c>
       <c r="V24">
-        <v>0.08261320428620808</v>
+        <v>0.06397527637174978</v>
       </c>
       <c r="W24">
-        <v>0.1100736679801268</v>
+        <v>0.05562103608912836</v>
       </c>
       <c r="X24">
-        <v>0.04825495258003573</v>
+        <v>0.1012105621423872</v>
       </c>
       <c r="Y24">
-        <v>0.06181871540009104</v>
+        <v>-0.04558952605325885</v>
       </c>
       <c r="Z24">
-        <v>0.7317886394438168</v>
+        <v>0.5321364303543213</v>
       </c>
       <c r="AA24">
-        <v>0.1398462880298127</v>
+        <v>0.05287678804242203</v>
       </c>
       <c r="AB24">
-        <v>0.04772186117052324</v>
+        <v>0.07595201366349258</v>
       </c>
       <c r="AC24">
-        <v>0.09212442685928948</v>
+        <v>-0.02307522562107055</v>
       </c>
       <c r="AD24">
-        <v>0.6</v>
+        <v>9289</v>
       </c>
       <c r="AE24">
-        <v>19.50787116860211</v>
+        <v>373.6714466941096</v>
       </c>
       <c r="AF24">
-        <v>20.10787116860211</v>
+        <v>9662.67144669411</v>
       </c>
       <c r="AG24">
-        <v>-75.49212883139788</v>
+        <v>8776.67144669411</v>
       </c>
       <c r="AH24">
-        <v>0.01707953515051499</v>
+        <v>0.4109716474831052</v>
       </c>
       <c r="AI24">
-        <v>0.01661796724444637</v>
+        <v>0.3973845208378081</v>
       </c>
       <c r="AJ24">
-        <v>-0.06978975640608163</v>
+        <v>0.3879059534996092</v>
       </c>
       <c r="AK24">
-        <v>-0.0677419199778574</v>
+        <v>0.3745964371144643</v>
       </c>
       <c r="AL24">
-        <v>0.8</v>
+        <v>384</v>
       </c>
       <c r="AM24">
-        <v>0.8</v>
+        <v>384</v>
       </c>
       <c r="AN24">
-        <v>0.003414911781445646</v>
+        <v>3.959505541346974</v>
       </c>
       <c r="AO24">
-        <v>205</v>
+        <v>4.552083333333333</v>
       </c>
       <c r="AP24">
-        <v>-0.4296649335879219</v>
+        <v>3.741121673782656</v>
       </c>
       <c r="AQ24">
-        <v>205</v>
+        <v>4.552083333333333</v>
       </c>
     </row>
     <row r="25">
@@ -3655,7 +3652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group, Inc. (NYSE:THG)</t>
+          <t>Employers Holdings, Inc. (NYSE:EIG)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3664,124 +3661,121 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.0102</v>
+        <v>-0.0267</v>
       </c>
       <c r="E25">
-        <v>0.113</v>
-      </c>
-      <c r="F25">
-        <v>0.0688</v>
+        <v>-0.119</v>
       </c>
       <c r="G25">
-        <v>0.09830877070348149</v>
+        <v>0.2299349240780911</v>
       </c>
       <c r="H25">
-        <v>0.09830877070348149</v>
+        <v>0.2299349240780911</v>
       </c>
       <c r="I25">
-        <v>0.1096463683365771</v>
+        <v>0.1016376427905456</v>
       </c>
       <c r="J25">
-        <v>0.08861772386476749</v>
+        <v>0.0834827490563632</v>
       </c>
       <c r="K25">
-        <v>419.8</v>
+        <v>56.1</v>
       </c>
       <c r="L25">
-        <v>0.08151298033047902</v>
+        <v>0.08112798264642082</v>
       </c>
       <c r="M25">
-        <v>362.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="N25">
-        <v>0.07767365057579723</v>
+        <v>0.05703324808184144</v>
       </c>
       <c r="O25">
-        <v>0.8627918056217247</v>
+        <v>1.192513368983957</v>
       </c>
       <c r="P25">
-        <v>101.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q25">
-        <v>0.02168085608286333</v>
+        <v>0.02497868712702472</v>
       </c>
       <c r="R25">
-        <v>0.2408289661743687</v>
+        <v>0.5222816399286988</v>
       </c>
       <c r="S25">
-        <v>261.1</v>
+        <v>37.60000000000001</v>
       </c>
       <c r="T25">
-        <v>0.7208724461623413</v>
+        <v>0.5620328849028401</v>
       </c>
       <c r="U25">
-        <v>171.2</v>
+        <v>148.1</v>
       </c>
       <c r="V25">
-        <v>0.03671377409877549</v>
+        <v>0.1262574595055413</v>
       </c>
       <c r="W25">
-        <v>0.1330586370839937</v>
+        <v>0.04714681906042524</v>
       </c>
       <c r="X25">
-        <v>0.05201912035760373</v>
+        <v>0.08496025552434025</v>
       </c>
       <c r="Y25">
-        <v>0.08103951672638993</v>
+        <v>-0.03781343646391501</v>
       </c>
       <c r="Z25">
-        <v>1.44700231093314</v>
+        <v>0.6439819559950446</v>
       </c>
       <c r="AA25">
-        <v>0.1282300512219534</v>
+        <v>0.05376138402916024</v>
       </c>
       <c r="AB25">
-        <v>0.0468130734583453</v>
+        <v>0.0778108756536737</v>
       </c>
       <c r="AC25">
-        <v>0.08141697776360812</v>
+        <v>-0.02404949162451346</v>
       </c>
       <c r="AD25">
-        <v>781.4</v>
+        <v>183</v>
       </c>
       <c r="AE25">
-        <v>34.05119214897082</v>
+        <v>15.08785005168861</v>
       </c>
       <c r="AF25">
-        <v>815.4511921489708</v>
+        <v>198.0878500516886</v>
       </c>
       <c r="AG25">
-        <v>644.2511921489709</v>
+        <v>49.98785005168861</v>
       </c>
       <c r="AH25">
-        <v>0.1488443136786879</v>
+        <v>0.1444749510720418</v>
       </c>
       <c r="AI25">
-        <v>0.2081426696476042</v>
+        <v>0.1773252211475784</v>
       </c>
       <c r="AJ25">
-        <v>0.1213884608016886</v>
+        <v>0.04087354592245206</v>
       </c>
       <c r="AK25">
-        <v>0.1719584650275223</v>
+        <v>0.05158769539682269</v>
       </c>
       <c r="AL25">
-        <v>34</v>
+        <v>1.7</v>
       </c>
       <c r="AM25">
-        <v>34</v>
+        <v>1.7</v>
       </c>
       <c r="AN25">
-        <v>1.32823389427163</v>
+        <v>2.313527180783818</v>
       </c>
       <c r="AO25">
-        <v>16.39705882352941</v>
+        <v>41.1764705882353</v>
       </c>
       <c r="AP25">
-        <v>1.095106564931108</v>
+        <v>0.6319576491996032</v>
       </c>
       <c r="AQ25">
-        <v>16.39705882352941</v>
+        <v>41.1764705882353</v>
       </c>
     </row>
     <row r="26">
@@ -3792,7 +3786,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
+          <t>The Progressive Corporation (NYSE:PGR)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3801,124 +3795,124 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.0476</v>
+        <v>0.135</v>
       </c>
       <c r="E26">
-        <v>0.0438</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="F26">
-        <v>0.08199999999999999</v>
+        <v>0.294</v>
       </c>
       <c r="G26">
-        <v>0.1276241155487983</v>
+        <v>0.09804849347646302</v>
       </c>
       <c r="H26">
-        <v>0.1276241155487983</v>
+        <v>0.09804849347646302</v>
       </c>
       <c r="I26">
-        <v>0.1400666935841518</v>
+        <v>0.03283672143469016</v>
       </c>
       <c r="J26">
-        <v>0.115213087240671</v>
+        <v>0.02557845458172376</v>
       </c>
       <c r="K26">
-        <v>3639</v>
+        <v>857.4</v>
       </c>
       <c r="L26">
-        <v>0.1063972867083796</v>
+        <v>0.01763885402994532</v>
       </c>
       <c r="M26">
-        <v>2473</v>
+        <v>1244.9</v>
       </c>
       <c r="N26">
-        <v>0.06426197473696246</v>
+        <v>0.01640413549191323</v>
       </c>
       <c r="O26">
-        <v>0.679582302830448</v>
+        <v>1.451947749008631</v>
       </c>
       <c r="P26">
-        <v>873</v>
+        <v>1110.5</v>
       </c>
       <c r="Q26">
-        <v>0.02268528263055731</v>
+        <v>0.01463313717067206</v>
       </c>
       <c r="R26">
-        <v>0.2399010717230008</v>
+        <v>1.295194774900863</v>
       </c>
       <c r="S26">
-        <v>1600</v>
+        <v>134.4000000000001</v>
       </c>
       <c r="T26">
-        <v>0.646987464617873</v>
+        <v>0.1079604787533136</v>
       </c>
       <c r="U26">
-        <v>818</v>
+        <v>350.9</v>
       </c>
       <c r="V26">
-        <v>0.02125608383939963</v>
+        <v>0.004623834158657204</v>
       </c>
       <c r="W26">
-        <v>0.1306689647743186</v>
+        <v>0.04746404490650015</v>
       </c>
       <c r="X26">
-        <v>0.05258895420233552</v>
+        <v>0.08242572927933359</v>
       </c>
       <c r="Y26">
-        <v>0.07808001057198312</v>
+        <v>-0.03496168437283344</v>
       </c>
       <c r="Z26">
-        <v>1.113049442062232</v>
+        <v>2.122482726136397</v>
       </c>
       <c r="AA26">
-        <v>0.128237862471496</v>
+        <v>0.05428982801097305</v>
       </c>
       <c r="AB26">
-        <v>0.04707551283788499</v>
+        <v>0.07869215409437164</v>
       </c>
       <c r="AC26">
-        <v>0.08116234963361105</v>
+        <v>-0.02440232608339859</v>
       </c>
       <c r="AD26">
-        <v>7290</v>
+        <v>6387.4</v>
       </c>
       <c r="AE26">
-        <v>357.1947301742011</v>
+        <v>168.7647123486016</v>
       </c>
       <c r="AF26">
-        <v>7647.194730174201</v>
+        <v>6556.164712348601</v>
       </c>
       <c r="AG26">
-        <v>6829.194730174201</v>
+        <v>6205.264712348601</v>
       </c>
       <c r="AH26">
-        <v>0.1657738103540038</v>
+        <v>0.07952113294660502</v>
       </c>
       <c r="AI26">
-        <v>0.2117093520106089</v>
+        <v>0.3073341751256228</v>
       </c>
       <c r="AJ26">
-        <v>0.1507139457588876</v>
+        <v>0.07558669901498742</v>
       </c>
       <c r="AK26">
-        <v>0.1934440999566869</v>
+        <v>0.2957498343143081</v>
       </c>
       <c r="AL26">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="AM26">
-        <v>335</v>
+        <v>232</v>
       </c>
       <c r="AN26">
-        <v>1.27092050209205</v>
+        <v>3.236912785688947</v>
       </c>
       <c r="AO26">
-        <v>14.20597014925373</v>
+        <v>6.713362068965517</v>
       </c>
       <c r="AP26">
-        <v>1.19058485533023</v>
+        <v>3.144612938908732</v>
       </c>
       <c r="AQ26">
-        <v>14.20597014925373</v>
+        <v>6.713362068965517</v>
       </c>
     </row>
     <row r="27">
@@ -3929,7 +3923,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NI Holdings, Inc. (NasdaqCM:NODK)</t>
+          <t>Ambac Financial Group, Inc. (NYSE:AMBC)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3938,37 +3932,34 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.147</v>
-      </c>
-      <c r="E27">
-        <v>0.18</v>
+        <v>-0.179</v>
       </c>
       <c r="G27">
-        <v>0.1675457648153894</v>
+        <v>0.8980582524271845</v>
       </c>
       <c r="H27">
-        <v>0.1675457648153894</v>
+        <v>0.8980582524271845</v>
       </c>
       <c r="I27">
-        <v>0.09737291944263088</v>
+        <v>1.844702737771225</v>
       </c>
       <c r="J27">
-        <v>0.07604948265329525</v>
+        <v>1.805925202743001</v>
       </c>
       <c r="K27">
-        <v>23.9</v>
+        <v>325</v>
       </c>
       <c r="L27">
-        <v>0.07415451442755196</v>
+        <v>1.577669902912621</v>
       </c>
       <c r="M27">
-        <v>4.08</v>
+        <v>18</v>
       </c>
       <c r="N27">
-        <v>0.01016189290161893</v>
+        <v>0.02295040163202856</v>
       </c>
       <c r="O27">
-        <v>0.1707112970711297</v>
+        <v>0.05538461538461539</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3980,73 +3971,79 @@
         <v>-0</v>
       </c>
       <c r="S27">
-        <v>4.08</v>
+        <v>18</v>
       </c>
       <c r="T27">
         <v>1</v>
       </c>
       <c r="U27">
-        <v>47.7</v>
+        <v>29</v>
       </c>
       <c r="V27">
-        <v>0.1188044831880448</v>
+        <v>0.03697564707382379</v>
       </c>
       <c r="W27">
-        <v>0.07426973275326289</v>
+        <v>0.3063147973609802</v>
       </c>
       <c r="X27">
-        <v>0.0479782697197067</v>
+        <v>0.3200558825986622</v>
       </c>
       <c r="Y27">
-        <v>0.02629146303355619</v>
+        <v>-0.01374108523768197</v>
       </c>
       <c r="Z27">
-        <v>1.323893745999613</v>
+        <v>0.02175070775144478</v>
       </c>
       <c r="AA27">
-        <v>0.1006814344712036</v>
+        <v>0.03928015130583167</v>
       </c>
       <c r="AB27">
-        <v>0.0477998900312316</v>
+        <v>0.07286187731507546</v>
       </c>
       <c r="AC27">
-        <v>0.05288154443997202</v>
+        <v>-0.03358172600924379</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>6103</v>
       </c>
       <c r="AE27">
-        <v>2.328540318200328</v>
+        <v>29.95618009563825</v>
       </c>
       <c r="AF27">
-        <v>2.328540318200328</v>
+        <v>6132.956180095638</v>
       </c>
       <c r="AG27">
-        <v>-45.37145968179968</v>
+        <v>6103.956180095638</v>
       </c>
       <c r="AH27">
-        <v>0.005766160847288142</v>
+        <v>0.8866168926550937</v>
       </c>
       <c r="AI27">
-        <v>0.006723501089632715</v>
+        <v>0.849209830017886</v>
       </c>
       <c r="AJ27">
-        <v>-0.1274019196587287</v>
+        <v>0.8861395425062267</v>
       </c>
       <c r="AK27">
-        <v>-0.1519327644754069</v>
+        <v>0.8486018859654</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>14.09468822170901</v>
+      </c>
+      <c r="AO27">
+        <v>2.886363636363636</v>
       </c>
       <c r="AP27">
-        <v>-1.377020840747812</v>
+        <v>14.09689648982826</v>
+      </c>
+      <c r="AQ27">
+        <v>2.886363636363636</v>
       </c>
     </row>
     <row r="28">
@@ -4057,7 +4054,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNA Financial Corporation (NYSE:CNA)</t>
+          <t>ProAssurance Corporation (NYSE:PRA)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4066,124 +4063,124 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0498</v>
+        <v>0.0469</v>
       </c>
       <c r="E28">
-        <v>0.193</v>
+        <v>-0.342</v>
       </c>
       <c r="F28">
-        <v>0.05</v>
+        <v>0.273</v>
       </c>
       <c r="G28">
-        <v>0.08510818837505303</v>
+        <v>0.1387555555555555</v>
       </c>
       <c r="H28">
-        <v>0.08510818837505303</v>
+        <v>0.1387555555555555</v>
       </c>
       <c r="I28">
-        <v>0.146700719924795</v>
+        <v>0.04244352349727326</v>
       </c>
       <c r="J28">
-        <v>0.1189246644978577</v>
+        <v>0.04004063618816837</v>
       </c>
       <c r="K28">
-        <v>1323</v>
+        <v>17.8</v>
       </c>
       <c r="L28">
-        <v>0.1122613491726771</v>
+        <v>0.01582222222222222</v>
       </c>
       <c r="M28">
-        <v>431.1</v>
+        <v>22.3</v>
       </c>
       <c r="N28">
-        <v>0.03604063035572462</v>
+        <v>0.02365545772780312</v>
       </c>
       <c r="O28">
-        <v>0.3258503401360545</v>
+        <v>1.252808988764045</v>
       </c>
       <c r="P28">
-        <v>413.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q28">
-        <v>0.03453580236592401</v>
+        <v>0.0114564548636894</v>
       </c>
       <c r="R28">
-        <v>0.3122448979591837</v>
+        <v>0.6067415730337079</v>
       </c>
       <c r="S28">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="T28">
-        <v>0.04175365344467641</v>
+        <v>0.5156950672645739</v>
       </c>
       <c r="U28">
-        <v>625</v>
+        <v>41</v>
       </c>
       <c r="V28">
-        <v>0.05225097186807675</v>
+        <v>0.04349209716770977</v>
       </c>
       <c r="W28">
-        <v>0.1100573995507861</v>
+        <v>0.01250790527721172</v>
       </c>
       <c r="X28">
-        <v>0.05399104740739297</v>
+        <v>0.09429768297792443</v>
       </c>
       <c r="Y28">
-        <v>0.05606635214339316</v>
+        <v>-0.0817897777007127</v>
       </c>
       <c r="Z28">
-        <v>0.81221751138873</v>
+        <v>0.6932653881731694</v>
       </c>
       <c r="AA28">
-        <v>0.09659269504118963</v>
+        <v>0.0277587871896912</v>
       </c>
       <c r="AB28">
-        <v>0.04642786206242543</v>
+        <v>0.0754158912279891</v>
       </c>
       <c r="AC28">
-        <v>0.05016483297876419</v>
+        <v>-0.0476571040382979</v>
       </c>
       <c r="AD28">
-        <v>2778</v>
+        <v>426.4</v>
       </c>
       <c r="AE28">
-        <v>300.6600784314546</v>
+        <v>19.25518032783793</v>
       </c>
       <c r="AF28">
-        <v>3078.660078431455</v>
+        <v>445.6551803278379</v>
       </c>
       <c r="AG28">
-        <v>2453.660078431455</v>
+        <v>404.6551803278379</v>
       </c>
       <c r="AH28">
-        <v>0.2046959648286223</v>
+        <v>0.3209950786675522</v>
       </c>
       <c r="AI28">
-        <v>0.1955616181187469</v>
+        <v>0.2948127232502766</v>
       </c>
       <c r="AJ28">
-        <v>0.1702138627029692</v>
+        <v>0.3003329680518075</v>
       </c>
       <c r="AK28">
-        <v>0.1623042233852129</v>
+        <v>0.2751529969368022</v>
       </c>
       <c r="AL28">
-        <v>113</v>
+        <v>20.4</v>
       </c>
       <c r="AM28">
-        <v>113</v>
+        <v>20.4</v>
       </c>
       <c r="AN28">
-        <v>1.506507592190889</v>
+        <v>4.619718309859154</v>
       </c>
       <c r="AO28">
-        <v>15.44247787610619</v>
+        <v>2.264705882352942</v>
       </c>
       <c r="AP28">
-        <v>1.330618263791461</v>
+        <v>4.384129797701386</v>
       </c>
       <c r="AQ28">
-        <v>15.44247787610619</v>
+        <v>2.264705882352942</v>
       </c>
     </row>
     <row r="29">
@@ -4194,7 +4191,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>State Auto Financial Corporation (NasdaqGS:STFC)</t>
+          <t>Global Indemnity Group, LLC (NYSE:GBLI)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4203,118 +4200,121 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.0365</v>
+        <v>0.0432</v>
+      </c>
+      <c r="E29">
+        <v>-0.158</v>
       </c>
       <c r="G29">
-        <v>0.01790019286403086</v>
+        <v>0.09183027232425585</v>
       </c>
       <c r="H29">
-        <v>0.01790019286403086</v>
+        <v>0.09183027232425585</v>
       </c>
       <c r="I29">
-        <v>0.0545443587270974</v>
+        <v>0.02660702144557631</v>
       </c>
       <c r="J29">
-        <v>0.04542195726751316</v>
+        <v>0.01953842274820154</v>
       </c>
       <c r="K29">
-        <v>71.7</v>
+        <v>22</v>
       </c>
       <c r="L29">
-        <v>0.04321359691417551</v>
+        <v>0.03483217226092464</v>
       </c>
       <c r="M29">
-        <v>7.7</v>
+        <v>11.425</v>
       </c>
       <c r="N29">
-        <v>0.003346662030598053</v>
+        <v>0.03353390079248606</v>
       </c>
       <c r="O29">
-        <v>0.1073919107391911</v>
+        <v>0.5193181818181819</v>
       </c>
       <c r="P29">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="Q29">
-        <v>0.003172809457579972</v>
+        <v>0.03228646903434106</v>
       </c>
       <c r="R29">
-        <v>0.101813110181311</v>
+        <v>0.5</v>
       </c>
       <c r="S29">
-        <v>0.4000000000000004</v>
+        <v>0.4250000000000007</v>
       </c>
       <c r="T29">
-        <v>0.05194805194805199</v>
+        <v>0.03719912472647709</v>
       </c>
       <c r="U29">
-        <v>46.1</v>
+        <v>18.9</v>
       </c>
       <c r="V29">
-        <v>0.0200365090403338</v>
+        <v>0.0554740240680951</v>
       </c>
       <c r="W29">
-        <v>0.07594534477279949</v>
+        <v>0.0318287037037037</v>
       </c>
       <c r="X29">
-        <v>0.04910799402980482</v>
+        <v>0.08123895063579992</v>
       </c>
       <c r="Y29">
-        <v>0.02683735074299467</v>
+        <v>-0.04941024693209622</v>
       </c>
       <c r="Z29">
-        <v>1.775115010163689</v>
+        <v>0.787378972033734</v>
       </c>
       <c r="AA29">
-        <v>0.08062919813657628</v>
+        <v>0.01538414321863945</v>
       </c>
       <c r="AB29">
-        <v>0.04798063208074427</v>
+        <v>0.07915250356186374</v>
       </c>
       <c r="AC29">
-        <v>0.032648566055832</v>
+        <v>-0.06376836034322428</v>
       </c>
       <c r="AD29">
-        <v>122.1</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>16.27502627486999</v>
       </c>
       <c r="AF29">
-        <v>122.1</v>
+        <v>16.27502627486999</v>
       </c>
       <c r="AG29">
-        <v>76</v>
+        <v>-2.624973725130012</v>
       </c>
       <c r="AH29">
-        <v>0.05039415576375417</v>
+        <v>0.04559149821964928</v>
       </c>
       <c r="AI29">
-        <v>0.1133704735376044</v>
+        <v>0.02466380091203913</v>
       </c>
       <c r="AJ29">
-        <v>0.03197576573544261</v>
+        <v>-0.007764470963897203</v>
       </c>
       <c r="AK29">
-        <v>0.07372199049374333</v>
+        <v>-0.0040952823706494</v>
       </c>
       <c r="AL29">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AM29">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AN29">
-        <v>1.243380855397149</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>20.56818181818182</v>
+        <v>3.107142857142857</v>
       </c>
       <c r="AP29">
-        <v>0.7739307535641547</v>
+        <v>-0.08506071695171782</v>
       </c>
       <c r="AQ29">
-        <v>20.56818181818182</v>
+        <v>3.107142857142857</v>
       </c>
     </row>
     <row r="30">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Loews Corporation (NYSE:L)</t>
+          <t>The Allstate Corporation (NYSE:ALL)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4334,121 +4334,121 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0229</v>
-      </c>
-      <c r="E30">
-        <v>0.585</v>
+        <v>0.0562</v>
+      </c>
+      <c r="F30">
+        <v>0.0199</v>
       </c>
       <c r="G30">
-        <v>0.03823870220162225</v>
+        <v>0.1592287694974003</v>
       </c>
       <c r="H30">
-        <v>0.03823870220162225</v>
+        <v>0.1592287694974003</v>
       </c>
       <c r="I30">
-        <v>0.1806159646507177</v>
+        <v>0.007322527212873277</v>
       </c>
       <c r="J30">
-        <v>0.1406911675328576</v>
+        <v>0.007322527212873277</v>
       </c>
       <c r="K30">
-        <v>1632</v>
+        <v>-210</v>
       </c>
       <c r="L30">
-        <v>0.1112398609501738</v>
+        <v>-0.004135812194737671</v>
       </c>
       <c r="M30">
-        <v>1136</v>
+        <v>3946</v>
       </c>
       <c r="N30">
-        <v>0.0775278445075344</v>
+        <v>0.1097257135230129</v>
       </c>
       <c r="O30">
-        <v>0.696078431372549</v>
+        <v>-18.79047619047619</v>
       </c>
       <c r="P30">
-        <v>66</v>
+        <v>933</v>
       </c>
       <c r="Q30">
-        <v>0.004504258571740555</v>
+        <v>0.02594376348630792</v>
       </c>
       <c r="R30">
-        <v>0.04044117647058824</v>
+        <v>-4.442857142857143</v>
       </c>
       <c r="S30">
-        <v>1070</v>
+        <v>3013</v>
       </c>
       <c r="T30">
-        <v>0.9419014084507042</v>
+        <v>0.7635580334515966</v>
       </c>
       <c r="U30">
-        <v>811</v>
+        <v>786</v>
       </c>
       <c r="V30">
-        <v>0.05534778335881197</v>
+        <v>0.02185616087914043</v>
       </c>
       <c r="W30">
-        <v>0.09394427814874511</v>
+        <v>-0.008481764206955046</v>
       </c>
       <c r="X30">
-        <v>0.06365940858816804</v>
+        <v>0.08695189458381956</v>
       </c>
       <c r="Y30">
-        <v>0.03028486956057706</v>
+        <v>-0.09543365879077462</v>
       </c>
       <c r="Z30">
-        <v>0.5485323459363572</v>
+        <v>1.634405337518921</v>
       </c>
       <c r="AA30">
-        <v>0.07717365617932347</v>
+        <v>0.01196797756084763</v>
       </c>
       <c r="AB30">
-        <v>0.04600373664567785</v>
+        <v>0.07720104666400104</v>
       </c>
       <c r="AC30">
-        <v>0.03116991953364561</v>
+        <v>-0.06523306910315341</v>
       </c>
       <c r="AD30">
-        <v>9113</v>
+        <v>7968</v>
       </c>
       <c r="AE30">
-        <v>585.9159130465993</v>
+        <v>435.9567911957325</v>
       </c>
       <c r="AF30">
-        <v>9698.9159130466</v>
+        <v>8403.956791195733</v>
       </c>
       <c r="AG30">
-        <v>8887.9159130466</v>
+        <v>7617.956791195733</v>
       </c>
       <c r="AH30">
-        <v>0.3982847018944706</v>
+        <v>0.1894218367027029</v>
       </c>
       <c r="AI30">
-        <v>0.3364301294679392</v>
+        <v>0.3236653485995928</v>
       </c>
       <c r="AJ30">
-        <v>0.3775550389323882</v>
+        <v>0.1748025338042836</v>
       </c>
       <c r="AK30">
-        <v>0.3172225921667473</v>
+        <v>0.3025525185324392</v>
       </c>
       <c r="AL30">
-        <v>435</v>
+        <v>335</v>
       </c>
       <c r="AM30">
-        <v>435</v>
+        <v>335</v>
       </c>
       <c r="AN30">
-        <v>2.601484441906937</v>
+        <v>5.803350327749453</v>
       </c>
       <c r="AO30">
-        <v>6.156321839080459</v>
+        <v>1.086567164179104</v>
       </c>
       <c r="AP30">
-        <v>2.537229778203426</v>
+        <v>5.5484026155832</v>
       </c>
       <c r="AQ30">
-        <v>6.156321839080459</v>
+        <v>1.086567164179104</v>
       </c>
     </row>
     <row r="31">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc. (NasdaqGS:PLMR)</t>
+          <t>Markel Corporation (NYSE:MKL)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4467,32 +4467,35 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D31">
+        <v>0.14</v>
+      </c>
       <c r="G31">
-        <v>0.02978331028123559</v>
+        <v>0.3189874094469245</v>
       </c>
       <c r="H31">
-        <v>0.02978331028123559</v>
+        <v>0.3189874094469245</v>
       </c>
       <c r="I31">
-        <v>0.1548758005946767</v>
+        <v>0.002111592822543728</v>
       </c>
       <c r="J31">
-        <v>0.1271097786862617</v>
+        <v>0.001520441416456458</v>
       </c>
       <c r="K31">
-        <v>27.4</v>
+        <v>-32.7</v>
       </c>
       <c r="L31">
-        <v>0.1263254956201014</v>
+        <v>-0.002913737335935203</v>
       </c>
       <c r="M31">
-        <v>15.9</v>
+        <v>292.2</v>
       </c>
       <c r="N31">
-        <v>0.009659194459631858</v>
+        <v>0.01648909755767234</v>
       </c>
       <c r="O31">
-        <v>0.5802919708029197</v>
+        <v>-8.93577981651376</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -4501,76 +4504,82 @@
         <v>-0</v>
       </c>
       <c r="R31">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>15.9</v>
+        <v>292.2</v>
       </c>
       <c r="T31">
         <v>1</v>
       </c>
       <c r="U31">
-        <v>41.4</v>
+        <v>3540.7</v>
       </c>
       <c r="V31">
-        <v>0.02515035538545653</v>
+        <v>0.1998047492212541</v>
       </c>
       <c r="W31">
-        <v>0.07571152252003316</v>
+        <v>-0.002435772333499691</v>
       </c>
       <c r="X31">
-        <v>0.04788223243682169</v>
+        <v>0.08787367608116566</v>
       </c>
       <c r="Y31">
-        <v>0.02782929008321147</v>
+        <v>-0.09030944841466534</v>
       </c>
       <c r="Z31">
-        <v>0.6182442875875369</v>
+        <v>0.9204358104690255</v>
       </c>
       <c r="AA31">
-        <v>0.07858489456929733</v>
+        <v>0.001399468727426773</v>
       </c>
       <c r="AB31">
-        <v>0.04783338975682339</v>
+        <v>0.07693997855801052</v>
       </c>
       <c r="AC31">
-        <v>0.03075150481247394</v>
+        <v>-0.07554050983058375</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>4131.2</v>
       </c>
       <c r="AE31">
-        <v>2.932194255073116</v>
+        <v>541.5111361521925</v>
       </c>
       <c r="AF31">
-        <v>2.932194255073116</v>
+        <v>4672.711136152192</v>
       </c>
       <c r="AG31">
-        <v>-38.46780574492688</v>
+        <v>1132.011136152192</v>
       </c>
       <c r="AH31">
-        <v>0.001778130387804644</v>
+        <v>0.208663621695686</v>
       </c>
       <c r="AI31">
-        <v>0.007701461287796116</v>
+        <v>0.2663346444873925</v>
       </c>
       <c r="AJ31">
-        <v>-0.02392823799025229</v>
+        <v>0.06004468659750403</v>
       </c>
       <c r="AK31">
-        <v>-0.1133632658385811</v>
+        <v>0.08083593281473185</v>
       </c>
       <c r="AL31">
-        <v>0</v>
+        <v>195.3</v>
       </c>
       <c r="AM31">
-        <v>0</v>
+        <v>195.3</v>
       </c>
       <c r="AN31">
-        <v>0</v>
+        <v>8.060878048780488</v>
+      </c>
+      <c r="AO31">
+        <v>0.1464413722478239</v>
       </c>
       <c r="AP31">
-        <v>-1.099740008145656</v>
+        <v>2.208802216882326</v>
+      </c>
+      <c r="AQ31">
+        <v>0.1464413722478239</v>
       </c>
     </row>
     <row r="32">
@@ -4581,7 +4590,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kemper Corporation (NYSE:KMPR)</t>
+          <t>Donegal Group Inc. (NasdaqGS:DGIC.A)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4590,121 +4599,118 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.178</v>
-      </c>
-      <c r="F32">
-        <v>0.1</v>
+        <v>0.0285</v>
       </c>
       <c r="G32">
-        <v>0.1304938032191527</v>
+        <v>0.0444311377245509</v>
       </c>
       <c r="H32">
-        <v>0.1304938032191527</v>
+        <v>0.0444311377245509</v>
       </c>
       <c r="I32">
-        <v>0.05220674138579915</v>
+        <v>-0.0006958083832335329</v>
       </c>
       <c r="J32">
-        <v>0.05220674138579915</v>
+        <v>-0.0006958083832335329</v>
       </c>
       <c r="K32">
-        <v>82.8</v>
+        <v>-0.166</v>
       </c>
       <c r="L32">
-        <v>0.01459725331875959</v>
+        <v>-0.0001988023952095808</v>
       </c>
       <c r="M32">
-        <v>242.1</v>
+        <v>20.2</v>
       </c>
       <c r="N32">
-        <v>0.06469456469456469</v>
+        <v>0.04274227676682183</v>
       </c>
       <c r="O32">
-        <v>2.923913043478261</v>
+        <v>-121.6867469879518</v>
       </c>
       <c r="P32">
-        <v>80.40000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="Q32">
-        <v>0.02148468815135482</v>
+        <v>0.04274227676682183</v>
       </c>
       <c r="R32">
-        <v>0.9710144927536233</v>
+        <v>-121.6867469879518</v>
       </c>
       <c r="S32">
-        <v>161.7</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>0.667905824039653</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>119.8</v>
+        <v>26.7</v>
       </c>
       <c r="V32">
-        <v>0.03201325423547646</v>
+        <v>0.05649597968683876</v>
       </c>
       <c r="W32">
-        <v>0.01904542840713053</v>
+        <v>-0.0003084928451960602</v>
       </c>
       <c r="X32">
-        <v>0.05561495776200853</v>
+        <v>0.08204676790740262</v>
       </c>
       <c r="Y32">
-        <v>-0.036569529354878</v>
+        <v>-0.08235526075259868</v>
       </c>
       <c r="Z32">
-        <v>1.366839531303298</v>
+        <v>1.674789899111459</v>
       </c>
       <c r="AA32">
-        <v>0.07135823792663819</v>
+        <v>-0.001165332851956596</v>
       </c>
       <c r="AB32">
-        <v>0.0461466471805759</v>
+        <v>0.0788355545962145</v>
       </c>
       <c r="AC32">
-        <v>0.02521159074606229</v>
+        <v>-0.08000088744817109</v>
       </c>
       <c r="AD32">
-        <v>1122.1</v>
+        <v>35</v>
       </c>
       <c r="AE32">
-        <v>95.33850418665729</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1217.438504186657</v>
+        <v>35</v>
       </c>
       <c r="AG32">
-        <v>1097.638504186657</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AH32">
-        <v>0.2454692016684203</v>
+        <v>0.06895193065405832</v>
       </c>
       <c r="AI32">
-        <v>0.2267685751680347</v>
+        <v>0.06780317706315381</v>
       </c>
       <c r="AJ32">
-        <v>0.2267923822741514</v>
+        <v>0.01725930546891246</v>
       </c>
       <c r="AK32">
-        <v>0.2091202660000193</v>
+        <v>0.01695607763023493</v>
       </c>
       <c r="AL32">
-        <v>44.3</v>
+        <v>0.621</v>
       </c>
       <c r="AM32">
-        <v>44.3</v>
+        <v>0.621</v>
       </c>
       <c r="AN32">
-        <v>2.777475247524752</v>
+        <v>7.760532150776053</v>
       </c>
       <c r="AO32">
-        <v>6.645598194130925</v>
+        <v>-0.9355877616747181</v>
       </c>
       <c r="AP32">
-        <v>2.716926990561033</v>
+        <v>1.840354767184036</v>
       </c>
       <c r="AQ32">
-        <v>6.645598194130925</v>
+        <v>-0.9355877616747181</v>
       </c>
     </row>
     <row r="33">
@@ -4715,7 +4721,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ProAssurance Corporation (NYSE:PRA)</t>
+          <t>Cincinnati Financial Corporation (NasdaqGS:CINF)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4724,121 +4730,121 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.0493</v>
-      </c>
-      <c r="E33">
-        <v>-0.00757</v>
+        <v>0.0373</v>
+      </c>
+      <c r="F33">
+        <v>-0.0189</v>
       </c>
       <c r="G33">
-        <v>-0.01200883850513978</v>
+        <v>0.5639964528524978</v>
       </c>
       <c r="H33">
-        <v>-0.01200883850513978</v>
+        <v>0.5639964528524978</v>
       </c>
       <c r="I33">
-        <v>0.09772090016809064</v>
+        <v>-0.01154806908890322</v>
       </c>
       <c r="J33">
-        <v>0.09355720449754727</v>
+        <v>-0.01154806908890322</v>
       </c>
       <c r="K33">
-        <v>126.3</v>
+        <v>-29</v>
       </c>
       <c r="L33">
-        <v>0.1213373042559324</v>
+        <v>-0.004286136565178835</v>
       </c>
       <c r="M33">
-        <v>21.7</v>
+        <v>919</v>
       </c>
       <c r="N33">
-        <v>0.01588812417630693</v>
+        <v>0.05710167079861564</v>
       </c>
       <c r="O33">
-        <v>0.1718131433095804</v>
+        <v>-31.68965517241379</v>
       </c>
       <c r="P33">
-        <v>10.8</v>
+        <v>416</v>
       </c>
       <c r="Q33">
-        <v>0.007907453507102065</v>
+        <v>0.02584798155845931</v>
       </c>
       <c r="R33">
-        <v>0.08551068883610452</v>
+        <v>-14.3448275862069</v>
       </c>
       <c r="S33">
-        <v>10.9</v>
+        <v>503</v>
       </c>
       <c r="T33">
-        <v>0.5023041474654378</v>
+        <v>0.5473340587595212</v>
       </c>
       <c r="U33">
-        <v>194.8</v>
+        <v>1083</v>
       </c>
       <c r="V33">
-        <v>0.1426270317762484</v>
+        <v>0.06729174045146979</v>
       </c>
       <c r="W33">
-        <v>0.0949695465824498</v>
+        <v>-0.002449117473186386</v>
       </c>
       <c r="X33">
-        <v>0.05562598256782013</v>
+        <v>0.08138189169461321</v>
       </c>
       <c r="Y33">
-        <v>0.03934356401462967</v>
+        <v>-0.08383100916779959</v>
       </c>
       <c r="Z33">
-        <v>0.764770690071469</v>
+        <v>0.5825390918717258</v>
       </c>
       <c r="AA33">
-        <v>0.07154980784474678</v>
+        <v>-0.006727201679921631</v>
       </c>
       <c r="AB33">
-        <v>0.04697320084240665</v>
+        <v>0.07909526726476455</v>
       </c>
       <c r="AC33">
-        <v>0.02457660700234013</v>
+        <v>-0.08582246894468619</v>
       </c>
       <c r="AD33">
-        <v>424.8</v>
+        <v>833</v>
       </c>
       <c r="AE33">
-        <v>20.16157507517222</v>
+        <v>10.67117727759593</v>
       </c>
       <c r="AF33">
-        <v>444.9615750751722</v>
+        <v>843.6711772775959</v>
       </c>
       <c r="AG33">
-        <v>250.1615750751722</v>
+        <v>-239.3288227224041</v>
       </c>
       <c r="AH33">
-        <v>0.2457317303393187</v>
+        <v>0.04981004693282196</v>
       </c>
       <c r="AI33">
-        <v>0.2381942763622589</v>
+        <v>0.08211174476740161</v>
       </c>
       <c r="AJ33">
-        <v>0.1548066358344783</v>
+        <v>-0.01509506633974007</v>
       </c>
       <c r="AK33">
-        <v>0.1495053605494608</v>
+        <v>-0.02603757446350348</v>
       </c>
       <c r="AL33">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="AM33">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="AN33">
-        <v>3.088331515812432</v>
+        <v>28.72413793103448</v>
       </c>
       <c r="AO33">
-        <v>5.644444444444444</v>
+        <v>-1.481481481481481</v>
       </c>
       <c r="AP33">
-        <v>1.818695565795508</v>
+        <v>-8.252718024910486</v>
       </c>
       <c r="AQ33">
-        <v>5.644444444444444</v>
+        <v>-1.481481481481481</v>
       </c>
     </row>
     <row r="34">
@@ -4858,37 +4864,34 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.0623</v>
-      </c>
-      <c r="E34">
-        <v>0.239</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="G34">
-        <v>0.06458684654300169</v>
+        <v>0.08885542168674698</v>
       </c>
       <c r="H34">
-        <v>0.06458684654300169</v>
+        <v>0.08885542168674698</v>
       </c>
       <c r="I34">
-        <v>0.1174176256364688</v>
+        <v>-0.03328313253012048</v>
       </c>
       <c r="J34">
-        <v>0.09098108237939556</v>
+        <v>-0.03328313253012048</v>
       </c>
       <c r="K34">
-        <v>6.47</v>
+        <v>-1.67</v>
       </c>
       <c r="L34">
-        <v>0.109106239460371</v>
+        <v>-0.02515060240963855</v>
       </c>
       <c r="M34">
-        <v>0.145</v>
+        <v>2.51</v>
       </c>
       <c r="N34">
-        <v>0.002837573385518591</v>
+        <v>0.05421166306695464</v>
       </c>
       <c r="O34">
-        <v>0.02241112828438949</v>
+        <v>-1.502994011976048</v>
       </c>
       <c r="P34">
         <v>-0</v>
@@ -4897,82 +4900,82 @@
         <v>-0</v>
       </c>
       <c r="R34">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>0.145</v>
+        <v>2.51</v>
       </c>
       <c r="T34">
         <v>1</v>
       </c>
       <c r="U34">
-        <v>2.64</v>
+        <v>3.28</v>
       </c>
       <c r="V34">
-        <v>0.05166340508806262</v>
+        <v>0.07084233261339093</v>
       </c>
       <c r="W34">
-        <v>0.0951470588235294</v>
+        <v>-0.02275204359673024</v>
       </c>
       <c r="X34">
-        <v>0.05653469288839218</v>
+        <v>0.08972625416970324</v>
       </c>
       <c r="Y34">
-        <v>0.03861236593513722</v>
+        <v>-0.1124782977664335</v>
       </c>
       <c r="Z34">
-        <v>0.7742456999521788</v>
+        <v>0.743894241541564</v>
       </c>
       <c r="AA34">
-        <v>0.07044171180924197</v>
+        <v>-0.02475913062962133</v>
       </c>
       <c r="AB34">
-        <v>0.04599980457856467</v>
+        <v>0.07645106962573019</v>
       </c>
       <c r="AC34">
-        <v>0.0244419072306773</v>
+        <v>-0.1012102002553515</v>
       </c>
       <c r="AD34">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AE34">
-        <v>0.09067399878701521</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>18.59067399878701</v>
+        <v>15</v>
       </c>
       <c r="AG34">
-        <v>15.95067399878701</v>
+        <v>11.72</v>
       </c>
       <c r="AH34">
-        <v>0.2667598536801436</v>
+        <v>0.2446982055464927</v>
       </c>
       <c r="AI34">
-        <v>0.2020930295502797</v>
+        <v>0.2094972067039106</v>
       </c>
       <c r="AJ34">
-        <v>0.237889838349359</v>
+        <v>0.2019993105825578</v>
       </c>
       <c r="AK34">
-        <v>0.1785176684733632</v>
+        <v>0.1715456674473068</v>
       </c>
       <c r="AL34">
-        <v>0.231</v>
+        <v>0.211</v>
       </c>
       <c r="AM34">
-        <v>0.231</v>
+        <v>0.211</v>
       </c>
       <c r="AN34">
-        <v>2.421149064258605</v>
+        <v>-10.48951048951049</v>
       </c>
       <c r="AO34">
-        <v>30.04329004329004</v>
+        <v>-10.4739336492891</v>
       </c>
       <c r="AP34">
-        <v>2.08751132034904</v>
+        <v>-8.195804195804197</v>
       </c>
       <c r="AQ34">
-        <v>30.04329004329004</v>
+        <v>-10.4739336492891</v>
       </c>
     </row>
     <row r="35">
@@ -4983,7 +4986,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Donegal Group Inc. (NasdaqGS:DGIC.A)</t>
+          <t>Positive Physicians Holdings, Inc. (OTCPK:PPHI)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4991,122 +4994,113 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D35">
-        <v>0.0355</v>
-      </c>
-      <c r="E35">
-        <v>0.0488</v>
-      </c>
       <c r="G35">
-        <v>0.08859027000124424</v>
+        <v>-0.09103139013452914</v>
       </c>
       <c r="H35">
-        <v>0.08859027000124424</v>
+        <v>-0.09103139013452914</v>
       </c>
       <c r="I35">
-        <v>0.05387582431255443</v>
+        <v>-0.1415629432255728</v>
       </c>
       <c r="J35">
-        <v>0.04404316796047594</v>
+        <v>-0.1415629432255728</v>
       </c>
       <c r="K35">
-        <v>34.6</v>
+        <v>-2.52</v>
       </c>
       <c r="L35">
-        <v>0.04305088963543611</v>
+        <v>-0.1130044843049327</v>
       </c>
       <c r="M35">
-        <v>18.6</v>
+        <v>-0</v>
       </c>
       <c r="N35">
-        <v>0.04197698036560596</v>
+        <v>-0</v>
       </c>
       <c r="O35">
-        <v>0.5375722543352601</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>18.6</v>
+        <v>-0</v>
       </c>
       <c r="Q35">
-        <v>0.04197698036560596</v>
+        <v>-0</v>
       </c>
       <c r="R35">
-        <v>0.5375722543352601</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
       <c r="U35">
-        <v>68.90000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="V35">
-        <v>0.1554953735048522</v>
+        <v>0.6798418972332015</v>
       </c>
       <c r="W35">
-        <v>0.068637175163658</v>
+        <v>-0.0339622641509434</v>
       </c>
       <c r="X35">
-        <v>0.04972749137396734</v>
+        <v>0.08377822994517736</v>
       </c>
       <c r="Y35">
-        <v>0.01890968378969066</v>
+        <v>-0.1177404940961208</v>
       </c>
       <c r="Z35">
-        <v>1.605569650598318</v>
+        <v>0.3990032564446639</v>
       </c>
       <c r="AA35">
-        <v>0.07071437379354437</v>
+        <v>-0.05648407533889464</v>
       </c>
       <c r="AB35">
-        <v>0.047334751322286</v>
+        <v>0.08017856359225714</v>
       </c>
       <c r="AC35">
-        <v>0.02337962247125837</v>
+        <v>-0.1366626389311518</v>
       </c>
       <c r="AD35">
-        <v>35</v>
+        <v>2.71</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>0.5892681696513704</v>
       </c>
       <c r="AF35">
-        <v>35</v>
+        <v>3.29926816965137</v>
       </c>
       <c r="AG35">
-        <v>-33.90000000000001</v>
+        <v>-13.90073183034863</v>
       </c>
       <c r="AH35">
-        <v>0.07320644216691069</v>
+        <v>0.1153619788478521</v>
       </c>
       <c r="AI35">
-        <v>0.0610713662537079</v>
+        <v>0.04544492324552882</v>
       </c>
       <c r="AJ35">
-        <v>-0.08284457478005866</v>
+        <v>-1.219440724042003</v>
       </c>
       <c r="AK35">
-        <v>-0.06723522411741373</v>
+        <v>-0.2509190516340373</v>
       </c>
       <c r="AL35">
-        <v>1.06</v>
+        <v>0.016</v>
       </c>
       <c r="AM35">
-        <v>1.06</v>
+        <v>0.016</v>
       </c>
       <c r="AN35">
-        <v>0.708502024291498</v>
+        <v>-1.457772996234535</v>
       </c>
       <c r="AO35">
-        <v>40.84905660377358</v>
+        <v>-200.625</v>
       </c>
       <c r="AP35">
-        <v>-0.6862348178137653</v>
+        <v>7.477531915195605</v>
       </c>
       <c r="AQ35">
-        <v>40.84905660377358</v>
+        <v>-200.625</v>
       </c>
     </row>
     <row r="36">
@@ -5117,7 +5111,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Hallmark Financial Services, Inc. (NasdaqGM:HALL)</t>
+          <t>Kemper Corporation (NYSE:KMPR)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5126,118 +5120,118 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.03759999999999999</v>
-      </c>
-      <c r="E36">
-        <v>-0.139</v>
+        <v>0.163</v>
       </c>
       <c r="G36">
-        <v>-0.1290103931314957</v>
+        <v>0.005671010919337796</v>
       </c>
       <c r="H36">
-        <v>-0.1290103931314957</v>
+        <v>0.005671010919337796</v>
       </c>
       <c r="I36">
-        <v>0.009834267580876957</v>
+        <v>-0.04370571190147952</v>
       </c>
       <c r="J36">
-        <v>0.009834267580876957</v>
+        <v>-0.04370571190147952</v>
       </c>
       <c r="K36">
-        <v>6.46</v>
+        <v>-351.5</v>
       </c>
       <c r="L36">
-        <v>0.01459557162223226</v>
+        <v>-0.06190560056357872</v>
       </c>
       <c r="M36">
-        <v>-0</v>
+        <v>79.7</v>
       </c>
       <c r="N36">
-        <v>-0</v>
+        <v>0.02535713149438453</v>
       </c>
       <c r="O36">
-        <v>-0</v>
+        <v>-0.2267425320056899</v>
       </c>
       <c r="P36">
-        <v>-0</v>
+        <v>79.7</v>
       </c>
       <c r="Q36">
-        <v>-0</v>
+        <v>0.02535713149438453</v>
       </c>
       <c r="R36">
-        <v>-0</v>
+        <v>-0.2267425320056899</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
       <c r="U36">
-        <v>325.8</v>
+        <v>249.2</v>
       </c>
       <c r="V36">
-        <v>4.118836915297093</v>
+        <v>0.07928478253953103</v>
       </c>
       <c r="W36">
-        <v>0.03666288308740068</v>
+        <v>-0.0846743110425901</v>
       </c>
       <c r="X36">
-        <v>0.08504525652467378</v>
+        <v>0.09357252046874244</v>
       </c>
       <c r="Y36">
-        <v>-0.04838237343727309</v>
+        <v>-0.1782468315113325</v>
       </c>
       <c r="Z36">
-        <v>3.936434818980618</v>
+        <v>1.468395681644172</v>
       </c>
       <c r="AA36">
-        <v>0.03871195332453634</v>
+        <v>-0.06417727861931684</v>
       </c>
       <c r="AB36">
-        <v>0.04704694921430815</v>
+        <v>0.07556591720399825</v>
       </c>
       <c r="AC36">
-        <v>-0.008334995889771803</v>
+        <v>-0.1397431958233151</v>
       </c>
       <c r="AD36">
-        <v>105.2</v>
+        <v>1386.4</v>
       </c>
       <c r="AE36">
-        <v>17.93676584351929</v>
+        <v>25.3051608830038</v>
       </c>
       <c r="AF36">
-        <v>123.1367658435193</v>
+        <v>1411.705160883004</v>
       </c>
       <c r="AG36">
-        <v>-202.6632341564807</v>
+        <v>1162.505160883004</v>
       </c>
       <c r="AH36">
-        <v>0.6088742832190878</v>
+        <v>0.309937551886265</v>
       </c>
       <c r="AI36">
-        <v>0.4091782055887043</v>
+        <v>0.3667428540685427</v>
       </c>
       <c r="AJ36">
-        <v>1.640158057855847</v>
+        <v>0.2699980879446443</v>
       </c>
       <c r="AK36">
-        <v>8.15112116472811</v>
+        <v>0.3229086676451068</v>
       </c>
       <c r="AL36">
-        <v>5.01</v>
+        <v>51.6</v>
       </c>
       <c r="AM36">
-        <v>5.01</v>
+        <v>51.6</v>
       </c>
       <c r="AN36">
-        <v>8.766666666666667</v>
+        <v>-6.521166509877705</v>
       </c>
       <c r="AO36">
-        <v>1.584830339321357</v>
+        <v>-4.757751937984496</v>
       </c>
       <c r="AP36">
-        <v>-16.88860284637339</v>
+        <v>-5.468039326825042</v>
       </c>
       <c r="AQ36">
-        <v>1.584830339321357</v>
+        <v>-4.757751937984496</v>
       </c>
     </row>
     <row r="37">
@@ -5248,7 +5242,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Kingsway Financial Services Inc. (NYSE:KFS)</t>
+          <t>MBIA Inc. (NYSE:MBI)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5257,34 +5251,34 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.112</v>
+        <v>-0.181</v>
       </c>
       <c r="G37">
-        <v>0.1018973214285714</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>0.1018973214285714</v>
+        <v>0</v>
       </c>
       <c r="I37">
-        <v>0.04591042132163449</v>
+        <v>-13.86161171780009</v>
       </c>
       <c r="J37">
-        <v>0.04591042132163449</v>
+        <v>-13.86161171780009</v>
       </c>
       <c r="K37">
-        <v>-3.9</v>
+        <v>-298</v>
       </c>
       <c r="L37">
-        <v>-0.04352678571428572</v>
+        <v>-17.52941176470588</v>
       </c>
       <c r="M37">
-        <v>0.468</v>
+        <v>3</v>
       </c>
       <c r="N37">
-        <v>0.003591711435149655</v>
+        <v>0.004252906152537568</v>
       </c>
       <c r="O37">
-        <v>-0.12</v>
+        <v>-0.01006711409395973</v>
       </c>
       <c r="P37">
         <v>-0</v>
@@ -5296,79 +5290,79 @@
         <v>0</v>
       </c>
       <c r="S37">
-        <v>0.468</v>
+        <v>3</v>
       </c>
       <c r="T37">
         <v>1</v>
       </c>
       <c r="U37">
-        <v>18.1</v>
+        <v>111</v>
       </c>
       <c r="V37">
-        <v>0.1389102072141213</v>
+        <v>0.15735752764389</v>
       </c>
       <c r="W37">
-        <v>-0.6830122591943958</v>
+        <v>1.752941176470588</v>
       </c>
       <c r="X37">
-        <v>0.09827665170852999</v>
+        <v>0.2232731084716984</v>
       </c>
       <c r="Y37">
-        <v>-0.7812889109029257</v>
+        <v>1.52966806799889</v>
       </c>
       <c r="Z37">
-        <v>0.5587528244159022</v>
+        <v>0.005103209414504719</v>
       </c>
       <c r="AA37">
-        <v>0.02565257758358733</v>
+        <v>-0.07073870741848635</v>
       </c>
       <c r="AB37">
-        <v>0.04316007183292905</v>
+        <v>0.0733526885299664</v>
       </c>
       <c r="AC37">
-        <v>-0.01750749424934172</v>
+        <v>-0.1440913959484528</v>
       </c>
       <c r="AD37">
-        <v>271.6</v>
+        <v>3276</v>
       </c>
       <c r="AE37">
-        <v>3.377131247907748</v>
+        <v>18.23699601300778</v>
       </c>
       <c r="AF37">
-        <v>274.9771312479078</v>
+        <v>3294.236996013008</v>
       </c>
       <c r="AG37">
-        <v>256.8771312479078</v>
+        <v>3183.236996013008</v>
       </c>
       <c r="AH37">
-        <v>0.6784916049943722</v>
+        <v>0.8236339946092183</v>
       </c>
       <c r="AI37">
-        <v>0.9525421361201113</v>
+        <v>1.347205608856854</v>
       </c>
       <c r="AJ37">
-        <v>0.6634615283706684</v>
+        <v>0.8185996788275065</v>
       </c>
       <c r="AK37">
-        <v>0.9493674874265416</v>
+        <v>1.363716281358806</v>
       </c>
       <c r="AL37">
-        <v>6.4</v>
+        <v>96</v>
       </c>
       <c r="AM37">
-        <v>6.4</v>
+        <v>96</v>
       </c>
       <c r="AN37">
-        <v>20.92611141074043</v>
+        <v>1092</v>
       </c>
       <c r="AO37">
-        <v>0.5953125</v>
+        <v>-2.447916666666667</v>
       </c>
       <c r="AP37">
-        <v>19.7917506162191</v>
+        <v>1061.078998671003</v>
       </c>
       <c r="AQ37">
-        <v>0.5953125</v>
+        <v>-2.447916666666667</v>
       </c>
     </row>
     <row r="38">
@@ -5379,7 +5373,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United Fire Group, Inc. (NasdaqGS:UFCS)</t>
+          <t>FG Financial Group, Inc. (NasdaqGM:FGF)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5388,124 +5382,109 @@
         </is>
       </c>
       <c r="D38">
-        <v>0.0185</v>
-      </c>
-      <c r="E38">
-        <v>-0.273</v>
-      </c>
-      <c r="F38">
-        <v>0.06</v>
+        <v>-0.129</v>
       </c>
       <c r="G38">
-        <v>-0.133804091978997</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>-0.133804091978997</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>0.01486918586903755</v>
+        <v>-0.1308352294192396</v>
       </c>
       <c r="J38">
-        <v>0.01486918586903755</v>
+        <v>-0.1308352294192396</v>
       </c>
       <c r="K38">
-        <v>14</v>
+        <v>-2.4</v>
       </c>
       <c r="L38">
-        <v>0.01267427122940431</v>
+        <v>-0.1363636363636364</v>
       </c>
       <c r="M38">
-        <v>17.11</v>
+        <v>-0</v>
       </c>
       <c r="N38">
-        <v>0.02937339055793991</v>
+        <v>-0</v>
       </c>
       <c r="O38">
-        <v>1.222142857142857</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>15.1</v>
+        <v>-0</v>
       </c>
       <c r="Q38">
-        <v>0.02592274678111588</v>
+        <v>-0</v>
       </c>
       <c r="R38">
-        <v>1.078571428571429</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>2.01</v>
-      </c>
-      <c r="T38">
-        <v>0.1174751607247224</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>132.8</v>
+        <v>9.65</v>
       </c>
       <c r="V38">
-        <v>0.2279828326180258</v>
+        <v>0.3600746268656717</v>
       </c>
       <c r="W38">
-        <v>0.01706692673412166</v>
+        <v>-0.24</v>
       </c>
       <c r="X38">
-        <v>0.05068416347147075</v>
+        <v>0.07978082464208421</v>
       </c>
       <c r="Y38">
-        <v>-0.03361723673734909</v>
+        <v>-0.3197808246420842</v>
       </c>
       <c r="Z38">
-        <v>1.492647260044224</v>
+        <v>0.7496219885598139</v>
       </c>
       <c r="AA38">
-        <v>0.0221944495465072</v>
+        <v>-0.09807696485092986</v>
       </c>
       <c r="AB38">
-        <v>0.04710609907992098</v>
+        <v>0.07976951129940625</v>
       </c>
       <c r="AC38">
-        <v>-0.02491164953341378</v>
+        <v>-0.1778464761503361</v>
       </c>
       <c r="AD38">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>19.32748644530563</v>
+        <v>0.008500188893086513</v>
       </c>
       <c r="AF38">
-        <v>69.32748644530562</v>
+        <v>0.008500188893086513</v>
       </c>
       <c r="AG38">
-        <v>-63.47251355469439</v>
+        <v>-9.641499811106915</v>
       </c>
       <c r="AH38">
-        <v>0.1063586422588254</v>
+        <v>0.0003170706616630567</v>
       </c>
       <c r="AI38">
-        <v>0.07844006608590109</v>
+        <v>0.0002254183765067966</v>
       </c>
       <c r="AJ38">
-        <v>-0.1222912373859087</v>
+        <v>-0.5619080750045962</v>
       </c>
       <c r="AK38">
-        <v>-0.08451423509826074</v>
+        <v>-0.343621353465054</v>
       </c>
       <c r="AL38">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AM38">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AN38">
-        <v>1.859427296392711</v>
-      </c>
-      <c r="AO38">
-        <v>5.606694560669456</v>
+        <v>0</v>
       </c>
       <c r="AP38">
-        <v>-2.360450485485102</v>
-      </c>
-      <c r="AQ38">
-        <v>5.606694560669456</v>
+        <v>-1071.277756789657</v>
       </c>
     </row>
     <row r="39">
@@ -5516,7 +5495,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Global Indemnity Group, LLC (NasdaqGS:GBLI)</t>
+          <t>Conifer Holdings, Inc. (NasdaqGM:CNFR)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5525,124 +5504,118 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.0471</v>
-      </c>
-      <c r="E39">
-        <v>-0.327</v>
-      </c>
-      <c r="F39">
-        <v>0.1</v>
+        <v>0.0167</v>
       </c>
       <c r="G39">
-        <v>-0.005144446160976364</v>
+        <v>-0.09730250481695568</v>
       </c>
       <c r="H39">
-        <v>-0.005144446160976364</v>
+        <v>-0.09730250481695568</v>
       </c>
       <c r="I39">
-        <v>0.02004565694347053</v>
+        <v>-0.1048166700673065</v>
       </c>
       <c r="J39">
-        <v>0.02004565694347053</v>
+        <v>-0.1048166700673065</v>
       </c>
       <c r="K39">
-        <v>5.37</v>
+        <v>-13.6</v>
       </c>
       <c r="L39">
-        <v>0.008295998764097019</v>
+        <v>-0.1310211946050096</v>
       </c>
       <c r="M39">
-        <v>14.879</v>
+        <v>0.001</v>
       </c>
       <c r="N39">
-        <v>0.04088760648529816</v>
+        <v>5.208333333333334e-05</v>
       </c>
       <c r="O39">
-        <v>2.770763500931098</v>
+        <v>-7.352941176470589e-05</v>
       </c>
       <c r="P39">
-        <v>14.4</v>
+        <v>-0</v>
       </c>
       <c r="Q39">
-        <v>0.03957131079967025</v>
+        <v>-0</v>
       </c>
       <c r="R39">
-        <v>2.681564245810056</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>0.4789999999999992</v>
+        <v>0.001</v>
       </c>
       <c r="T39">
-        <v>0.03219302372471263</v>
+        <v>1</v>
       </c>
       <c r="U39">
-        <v>40.6</v>
+        <v>35.4</v>
       </c>
       <c r="V39">
-        <v>0.1115691123935147</v>
+        <v>1.84375</v>
       </c>
       <c r="W39">
-        <v>0.00749267475931352</v>
+        <v>-0.3230403800475059</v>
       </c>
       <c r="X39">
-        <v>0.0584020214703531</v>
+        <v>0.1596484400267948</v>
       </c>
       <c r="Y39">
-        <v>-0.05090934671103958</v>
+        <v>-0.4826888200743008</v>
       </c>
       <c r="Z39">
-        <v>0.766759404321081</v>
+        <v>1.468178467263576</v>
       </c>
       <c r="AA39">
-        <v>0.01537019597720021</v>
+        <v>-0.15388957800309</v>
       </c>
       <c r="AB39">
-        <v>0.04572578243307816</v>
+        <v>0.07414328497254802</v>
       </c>
       <c r="AC39">
-        <v>-0.03035558645587795</v>
+        <v>-0.228032862975638</v>
       </c>
       <c r="AD39">
-        <v>137.8</v>
+        <v>48.3</v>
       </c>
       <c r="AE39">
-        <v>23.02223130245763</v>
+        <v>1.609851764932061</v>
       </c>
       <c r="AF39">
-        <v>160.8222313024576</v>
+        <v>49.90985176493206</v>
       </c>
       <c r="AG39">
-        <v>120.2222313024576</v>
+        <v>14.50985176493206</v>
       </c>
       <c r="AH39">
-        <v>0.3064902184595211</v>
+        <v>0.7221814327527971</v>
       </c>
       <c r="AI39">
-        <v>0.1878715591974321</v>
+        <v>0.7549533153152026</v>
       </c>
       <c r="AJ39">
-        <v>0.2483303255440633</v>
+        <v>0.4304335677923828</v>
       </c>
       <c r="AK39">
-        <v>0.1474355575398393</v>
+        <v>0.472481986432153</v>
       </c>
       <c r="AL39">
-        <v>10.5</v>
+        <v>2.91</v>
       </c>
       <c r="AM39">
-        <v>10.5</v>
+        <v>2.91</v>
       </c>
       <c r="AN39">
-        <v>5.387021110242378</v>
+        <v>-4.754873006497341</v>
       </c>
       <c r="AO39">
-        <v>1.4</v>
+        <v>-3.883161512027491</v>
       </c>
       <c r="AP39">
-        <v>4.699852670150807</v>
+        <v>-1.428416200524912</v>
       </c>
       <c r="AQ39">
-        <v>1.4</v>
+        <v>-3.883161512027491</v>
       </c>
     </row>
     <row r="40">
@@ -5653,7 +5626,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ambac Financial Group, Inc. (NYSE:AMBC)</t>
+          <t>NI Holdings, Inc. (NasdaqCM:NODK)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5662,34 +5635,34 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.138</v>
+        <v>0.129</v>
       </c>
       <c r="G40">
-        <v>-0.5852713178294574</v>
+        <v>0.03949447077409163</v>
       </c>
       <c r="H40">
-        <v>-0.5852713178294574</v>
+        <v>0.03949447077409163</v>
       </c>
       <c r="I40">
-        <v>0.544442786165005</v>
+        <v>-0.1938901933687274</v>
       </c>
       <c r="J40">
-        <v>0.2722213930825025</v>
+        <v>-0.1938901933687274</v>
       </c>
       <c r="K40">
-        <v>-9</v>
+        <v>-47.9</v>
       </c>
       <c r="L40">
-        <v>-0.03488372093023256</v>
+        <v>-0.1513428120063191</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>3.98</v>
       </c>
       <c r="N40">
-        <v>0.008073196986006458</v>
+        <v>0.01419907242240457</v>
       </c>
       <c r="O40">
-        <v>-0.6666666666666666</v>
+        <v>-0.08308977035490606</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5701,79 +5674,73 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>6</v>
+        <v>3.98</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="U40">
-        <v>14</v>
+        <v>54.3</v>
       </c>
       <c r="V40">
-        <v>0.01883745963401507</v>
+        <v>0.1937210132001427</v>
       </c>
       <c r="W40">
-        <v>-0.008695652173913044</v>
+        <v>-0.1410067706800118</v>
       </c>
       <c r="X40">
-        <v>0.3189866926294703</v>
+        <v>0.07998224447641358</v>
       </c>
       <c r="Y40">
-        <v>-0.3276823448033833</v>
+        <v>-0.2209890151564254</v>
       </c>
       <c r="Z40">
-        <v>0.02622572533105144</v>
+        <v>1.112297284279664</v>
       </c>
       <c r="AA40">
-        <v>0.007139203484217897</v>
+        <v>-0.2156635355324943</v>
       </c>
       <c r="AB40">
-        <v>0.04459924709904908</v>
+        <v>0.07967847670118945</v>
       </c>
       <c r="AC40">
-        <v>-0.03746004361483118</v>
+        <v>-0.2953420122336838</v>
       </c>
       <c r="AD40">
-        <v>8394</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>37.66880584714358</v>
+        <v>1.926231006011135</v>
       </c>
       <c r="AF40">
-        <v>8431.668805847143</v>
+        <v>1.926231006011135</v>
       </c>
       <c r="AG40">
-        <v>8417.668805847143</v>
+        <v>-52.37376899398886</v>
       </c>
       <c r="AH40">
-        <v>0.9189961169225265</v>
+        <v>0.006825131027491589</v>
       </c>
       <c r="AI40">
-        <v>0.8808064894814852</v>
+        <v>0.007621808778390397</v>
       </c>
       <c r="AJ40">
-        <v>0.9188723236025784</v>
+        <v>-0.2297838592900156</v>
       </c>
       <c r="AK40">
-        <v>0.8806319140064736</v>
+        <v>-0.2639457934994605</v>
       </c>
       <c r="AL40">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="AM40">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="AN40">
-        <v>40.16267942583732</v>
-      </c>
-      <c r="AO40">
-        <v>0.8461538461538461</v>
+        <v>-0</v>
       </c>
       <c r="AP40">
-        <v>40.27592730070403</v>
-      </c>
-      <c r="AQ40">
-        <v>0.8461538461538461</v>
+        <v>0.876093892607833</v>
       </c>
     </row>
     <row r="41">
@@ -5784,7 +5751,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MBIA Inc. (NYSE:MBI)</t>
+          <t>Kingstone Companies, Inc. (NasdaqCM:KINS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5793,118 +5760,118 @@
         </is>
       </c>
       <c r="D41">
-        <v>-0.22</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>-0.0314977973568282</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>-0.0314977973568282</v>
       </c>
       <c r="I41">
-        <v>-1.180686180504954</v>
+        <v>-0.1327690513324486</v>
       </c>
       <c r="J41">
-        <v>-1.180686180504954</v>
+        <v>-0.1327690513324486</v>
       </c>
       <c r="K41">
-        <v>-371</v>
+        <v>-16.3</v>
       </c>
       <c r="L41">
-        <v>-1.809756097560976</v>
+        <v>-0.1196769456681351</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>2.094</v>
       </c>
       <c r="N41">
-        <v>0.001164008846467233</v>
+        <v>0.1454166666666667</v>
       </c>
       <c r="O41">
-        <v>-0.002695417789757413</v>
+        <v>-0.1284662576687116</v>
       </c>
       <c r="P41">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="Q41">
-        <v>-0</v>
+        <v>0.1180555555555556</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>-0.1042944785276074</v>
       </c>
       <c r="S41">
-        <v>1</v>
+        <v>0.3939999999999999</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>0.1881566380133715</v>
       </c>
       <c r="U41">
-        <v>112</v>
+        <v>15.1</v>
       </c>
       <c r="V41">
-        <v>0.1303689908043301</v>
+        <v>1.048611111111111</v>
       </c>
       <c r="W41">
-        <v>-1.61304347826087</v>
+        <v>-0.2095115681233933</v>
       </c>
       <c r="X41">
-        <v>0.1485528289973025</v>
+        <v>0.1454650531494729</v>
       </c>
       <c r="Y41">
-        <v>-1.761596307258172</v>
+        <v>-0.3549766212728663</v>
       </c>
       <c r="Z41">
-        <v>0.04263546811903922</v>
+        <v>1.884189471219395</v>
       </c>
       <c r="AA41">
-        <v>-0.05033910800750914</v>
+        <v>-0.2501620486243871</v>
       </c>
       <c r="AB41">
-        <v>0.04498989416291202</v>
+        <v>0.07446174552315049</v>
       </c>
       <c r="AC41">
-        <v>-0.09532900217042116</v>
+        <v>-0.3246237941475376</v>
       </c>
       <c r="AD41">
-        <v>3595</v>
+        <v>30</v>
       </c>
       <c r="AE41">
-        <v>25.2033350175776</v>
+        <v>0.7857239573975107</v>
       </c>
       <c r="AF41">
-        <v>3620.203335017578</v>
+        <v>30.78572395739751</v>
       </c>
       <c r="AG41">
-        <v>3508.203335017578</v>
+        <v>15.68572395739751</v>
       </c>
       <c r="AH41">
-        <v>0.8082067822279715</v>
+        <v>0.6813152752941003</v>
       </c>
       <c r="AI41">
-        <v>1.045333751677969</v>
+        <v>0.4417794952696253</v>
       </c>
       <c r="AJ41">
-        <v>0.8032882229380245</v>
+        <v>0.5213676752339107</v>
       </c>
       <c r="AK41">
-        <v>1.046848843327251</v>
+        <v>0.2873594562864045</v>
       </c>
       <c r="AL41">
-        <v>158</v>
+        <v>1.83</v>
       </c>
       <c r="AM41">
-        <v>158</v>
+        <v>1.83</v>
       </c>
       <c r="AN41">
-        <v>1198.333333333333</v>
+        <v>-2.05114180226993</v>
       </c>
       <c r="AO41">
-        <v>-1.518987341772152</v>
+        <v>-9.94535519125683</v>
       </c>
       <c r="AP41">
-        <v>1169.401111672526</v>
+        <v>-1.072454803596165</v>
       </c>
       <c r="AQ41">
-        <v>-1.518987341772152</v>
+        <v>-9.94535519125683</v>
       </c>
     </row>
     <row r="42">
@@ -5915,7 +5882,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Conifer Holdings, Inc. (NasdaqGM:CNFR)</t>
+          <t>Mercury General Corporation (NYSE:MCY)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5924,118 +5891,118 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.0391</v>
+        <v>0.0146</v>
       </c>
       <c r="G42">
-        <v>0.02677902621722847</v>
+        <v>0.1117042309213128</v>
       </c>
       <c r="H42">
-        <v>0.02677902621722847</v>
+        <v>0.1117042309213128</v>
       </c>
       <c r="I42">
-        <v>-0.05904219127113235</v>
+        <v>-0.1675336116401723</v>
       </c>
       <c r="J42">
-        <v>-0.05561513663583634</v>
+        <v>-0.1675336116401723</v>
       </c>
       <c r="K42">
-        <v>2.98</v>
+        <v>-475.4</v>
       </c>
       <c r="L42">
-        <v>0.02790262172284644</v>
+        <v>-0.1342710275094617</v>
       </c>
       <c r="M42">
-        <v>0.012</v>
+        <v>123.1</v>
       </c>
       <c r="N42">
-        <v>0.0005333333333333334</v>
+        <v>0.06500501663410255</v>
       </c>
       <c r="O42">
-        <v>0.004026845637583893</v>
+        <v>-0.2589398401346235</v>
       </c>
       <c r="P42">
-        <v>-0</v>
+        <v>123.1</v>
       </c>
       <c r="Q42">
-        <v>-0</v>
+        <v>0.06500501663410255</v>
       </c>
       <c r="R42">
-        <v>-0</v>
+        <v>-0.2589398401346235</v>
       </c>
       <c r="S42">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="T42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>7.51</v>
+        <v>335.9</v>
       </c>
       <c r="V42">
-        <v>0.3337777777777778</v>
+        <v>0.1773776205312351</v>
       </c>
       <c r="W42">
-        <v>0.06995305164319249</v>
+        <v>-0.2216420345936873</v>
       </c>
       <c r="X42">
-        <v>0.08711368505679962</v>
+        <v>0.08635984854703414</v>
       </c>
       <c r="Y42">
-        <v>-0.01716063341360713</v>
+        <v>-0.3080018831407215</v>
       </c>
       <c r="Z42">
-        <v>1.361836170993553</v>
+        <v>1.634514711526882</v>
       </c>
       <c r="AA42">
-        <v>-0.07573870472543062</v>
+        <v>-0.2738361529010929</v>
       </c>
       <c r="AB42">
-        <v>0.04564759257533422</v>
+        <v>0.07737552889189801</v>
       </c>
       <c r="AC42">
-        <v>-0.1213862973007648</v>
+        <v>-0.3512116817929909</v>
       </c>
       <c r="AD42">
-        <v>34.5</v>
+        <v>373.2</v>
       </c>
       <c r="AE42">
-        <v>2.47353013878467</v>
+        <v>32.84752686596998</v>
       </c>
       <c r="AF42">
-        <v>36.97353013878467</v>
+        <v>406.04752686597</v>
       </c>
       <c r="AG42">
-        <v>29.46353013878467</v>
+        <v>70.14752686597001</v>
       </c>
       <c r="AH42">
-        <v>0.621680435859532</v>
+        <v>0.1765617843360918</v>
       </c>
       <c r="AI42">
-        <v>0.4675841596282745</v>
+        <v>0.2079578198630156</v>
       </c>
       <c r="AJ42">
-        <v>0.5670040133934936</v>
+        <v>0.0357194364156752</v>
       </c>
       <c r="AK42">
-        <v>0.411711525153181</v>
+        <v>0.04339073650887765</v>
       </c>
       <c r="AL42">
-        <v>2.89</v>
+        <v>17.1</v>
       </c>
       <c r="AM42">
-        <v>2.89</v>
+        <v>17.1</v>
       </c>
       <c r="AN42">
-        <v>-6.399554813578185</v>
+        <v>-0.7466986794717887</v>
       </c>
       <c r="AO42">
-        <v>-2.304498269896194</v>
+        <v>-35.16959064327485</v>
       </c>
       <c r="AP42">
-        <v>-5.465318148541026</v>
+        <v>-0.1403511942096239</v>
       </c>
       <c r="AQ42">
-        <v>-2.304498269896194</v>
+        <v>-35.16959064327485</v>
       </c>
     </row>
     <row r="43">
@@ -6046,7 +6013,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The National Security Group, Inc. (NasdaqGM:NSEC)</t>
+          <t>Unico American Corporation (NasdaqGM:UNAM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6055,118 +6022,109 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.00092</v>
+        <v>-0.05980000000000001</v>
       </c>
       <c r="G43">
-        <v>-0.1493957703927492</v>
+        <v>-0.3135338345864662</v>
       </c>
       <c r="H43">
-        <v>-0.1493957703927492</v>
+        <v>-0.3135338345864662</v>
       </c>
       <c r="I43">
-        <v>-0.05256797583081571</v>
+        <v>-0.3469924812030075</v>
       </c>
       <c r="J43">
-        <v>-0.05256797583081571</v>
+        <v>-0.3469924812030075</v>
       </c>
       <c r="K43">
-        <v>-3.22</v>
+        <v>-10.3</v>
       </c>
       <c r="L43">
-        <v>-0.0486404833836858</v>
+        <v>-0.387218045112782</v>
       </c>
       <c r="M43">
-        <v>0.608</v>
+        <v>-0</v>
       </c>
       <c r="N43">
-        <v>0.02609442060085837</v>
+        <v>-0</v>
       </c>
       <c r="O43">
-        <v>-0.1888198757763975</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>0.608</v>
+        <v>-0</v>
       </c>
       <c r="Q43">
-        <v>0.02609442060085837</v>
+        <v>-0</v>
       </c>
       <c r="R43">
-        <v>-0.1888198757763975</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
       <c r="U43">
-        <v>9.289999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="V43">
-        <v>0.3987124463519313</v>
+        <v>1.351981351981352</v>
       </c>
       <c r="W43">
-        <v>-0.06836518046709129</v>
+        <v>-0.2942857142857143</v>
       </c>
       <c r="X43">
-        <v>0.0618924206537298</v>
+        <v>0.07977107850664222</v>
       </c>
       <c r="Y43">
-        <v>-0.1302576011208211</v>
+        <v>-0.3740567927923565</v>
       </c>
       <c r="Z43">
-        <v>1.408510638297872</v>
+        <v>0.8031400966183576</v>
       </c>
       <c r="AA43">
-        <v>-0.07404255319148936</v>
+        <v>-0.2786835748792271</v>
       </c>
       <c r="AB43">
-        <v>0.04735759438701183</v>
+        <v>0.07977107850664222</v>
       </c>
       <c r="AC43">
-        <v>-0.1214001475785012</v>
+        <v>-0.3584546533858693</v>
       </c>
       <c r="AD43">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="AE43">
         <v>0</v>
       </c>
       <c r="AF43">
-        <v>13.7</v>
+        <v>0</v>
       </c>
       <c r="AG43">
-        <v>4.41</v>
+        <v>-11.6</v>
       </c>
       <c r="AH43">
-        <v>0.3702702702702703</v>
+        <v>0</v>
       </c>
       <c r="AI43">
-        <v>0.2416225749559083</v>
+        <v>0</v>
       </c>
       <c r="AJ43">
-        <v>0.1591483219054493</v>
+        <v>3.841059602649007</v>
       </c>
       <c r="AK43">
-        <v>0.09301835055895381</v>
+        <v>-1.288888888888889</v>
       </c>
       <c r="AL43">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="AM43">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="AN43">
-        <v>-4.202453987730062</v>
-      </c>
-      <c r="AO43">
-        <v>-5.225225225225225</v>
+        <v>-0</v>
       </c>
       <c r="AP43">
-        <v>-1.352760736196319</v>
-      </c>
-      <c r="AQ43">
-        <v>-5.225225225225225</v>
+        <v>1.355140186915888</v>
       </c>
     </row>
     <row r="44">
@@ -6177,7 +6135,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kingstone Companies, Inc. (NasdaqCM:KINS)</t>
+          <t>Lemonade, Inc. (NYSE:LMND)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6185,119 +6143,107 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D44">
-        <v>0.156</v>
-      </c>
       <c r="G44">
-        <v>0.02212101496421601</v>
+        <v>-1.09842331581462</v>
       </c>
       <c r="H44">
-        <v>0.02212101496421601</v>
+        <v>-1.09842331581462</v>
       </c>
       <c r="I44">
-        <v>-0.05459375847617059</v>
+        <v>-1.406637976255382</v>
       </c>
       <c r="J44">
-        <v>-0.05459375847617059</v>
+        <v>-1.406637976255382</v>
       </c>
       <c r="K44">
-        <v>-6.57</v>
+        <v>-304.4</v>
       </c>
       <c r="L44">
-        <v>-0.04274560832791152</v>
+        <v>-1.45437171524128</v>
       </c>
       <c r="M44">
-        <v>3.94</v>
+        <v>-0</v>
       </c>
       <c r="N44">
-        <v>0.07519083969465649</v>
+        <v>-0</v>
       </c>
       <c r="O44">
-        <v>-0.5996955859969559</v>
+        <v>0</v>
       </c>
       <c r="P44">
-        <v>1.7</v>
+        <v>-0</v>
       </c>
       <c r="Q44">
-        <v>0.03244274809160305</v>
+        <v>-0</v>
       </c>
       <c r="R44">
-        <v>-0.258751902587519</v>
+        <v>0</v>
       </c>
       <c r="S44">
-        <v>2.24</v>
-      </c>
-      <c r="T44">
-        <v>0.5685279187817259</v>
+        <v>0</v>
       </c>
       <c r="U44">
-        <v>36.1</v>
+        <v>225</v>
       </c>
       <c r="V44">
-        <v>0.6889312977099237</v>
+        <v>0.2377932783766645</v>
       </c>
       <c r="W44">
-        <v>-0.07357222844344906</v>
+        <v>-0.2904580152671756</v>
       </c>
       <c r="X44">
-        <v>0.06192434941973617</v>
+        <v>0.08045457852874144</v>
       </c>
       <c r="Y44">
-        <v>-0.1354965778631852</v>
+        <v>-0.370912593795917</v>
       </c>
       <c r="Z44">
-        <v>1.608071899233895</v>
+        <v>0.2791982091714209</v>
       </c>
       <c r="AA44">
-        <v>-0.08779068887909221</v>
+        <v>-0.3927308039230143</v>
       </c>
       <c r="AB44">
-        <v>0.04528223766636956</v>
+        <v>0.07966352713449473</v>
       </c>
       <c r="AC44">
-        <v>-0.1330729265454618</v>
+        <v>-0.4723943310575091</v>
       </c>
       <c r="AD44">
-        <v>29.8</v>
+        <v>0</v>
       </c>
       <c r="AE44">
-        <v>1.080303388937095</v>
+        <v>21.04664215125731</v>
       </c>
       <c r="AF44">
-        <v>30.8803033889371</v>
+        <v>21.04664215125731</v>
       </c>
       <c r="AG44">
-        <v>-5.219696611062904</v>
+        <v>-203.9533578487427</v>
       </c>
       <c r="AH44">
-        <v>0.3707996024548491</v>
+        <v>0.02175933338413807</v>
       </c>
       <c r="AI44">
-        <v>0.2841389140995028</v>
+        <v>0.02268331984524905</v>
       </c>
       <c r="AJ44">
-        <v>-0.1106329598611023</v>
+        <v>-0.2747784176666985</v>
       </c>
       <c r="AK44">
-        <v>-0.07191615861802123</v>
+        <v>-0.2901818769802852</v>
       </c>
       <c r="AL44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM44">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN44">
-        <v>-6.075433231396534</v>
-      </c>
-      <c r="AO44">
-        <v>-4.612021857923497</v>
+        <v>-0</v>
       </c>
       <c r="AP44">
-        <v>1.064158330491927</v>
-      </c>
-      <c r="AQ44">
-        <v>-4.612021857923497</v>
+        <v>0.7227262857857641</v>
       </c>
     </row>
     <row r="45">
@@ -6308,7 +6254,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FG Financial Group, Inc. (NasdaqGM:FGF)</t>
+          <t>Universal Insurance Holdings, Inc. (NYSE:UVE)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6317,109 +6263,118 @@
         </is>
       </c>
       <c r="D45">
-        <v>-0.311</v>
+        <v>0.102</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>0.03037974683544304</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>0.03037974683544304</v>
       </c>
       <c r="I45">
-        <v>-1.230397657487309</v>
+        <v>-0.10042194092827</v>
       </c>
       <c r="J45">
-        <v>-1.230397657487309</v>
+        <v>-0.10042194092827</v>
       </c>
       <c r="K45">
-        <v>-7.15</v>
+        <v>-95.5</v>
       </c>
       <c r="L45">
-        <v>-1.453252032520325</v>
+        <v>-0.08059071729957806</v>
       </c>
       <c r="M45">
-        <v>-0</v>
+        <v>31.1</v>
       </c>
       <c r="N45">
-        <v>-0</v>
+        <v>0.09625502940266172</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>-0.3256544502617801</v>
       </c>
       <c r="P45">
-        <v>-0</v>
+        <v>20.8</v>
       </c>
       <c r="Q45">
-        <v>-0</v>
+        <v>0.06437635406994738</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>-0.2178010471204189</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>10.3</v>
+      </c>
+      <c r="T45">
+        <v>0.3311897106109325</v>
       </c>
       <c r="U45">
-        <v>8.93</v>
+        <v>307.4</v>
       </c>
       <c r="V45">
-        <v>0.4096330275229357</v>
+        <v>0.95140823274528</v>
       </c>
       <c r="W45">
-        <v>-0.3783068783068784</v>
+        <v>-0.1932025085980174</v>
       </c>
       <c r="X45">
-        <v>0.0478481915417784</v>
+        <v>0.08986168071080829</v>
       </c>
       <c r="Y45">
-        <v>-0.4261550698486568</v>
+        <v>-0.2830641893088257</v>
       </c>
       <c r="Z45">
-        <v>0.2319903096510544</v>
+        <v>4.280296189272168</v>
       </c>
       <c r="AA45">
-        <v>-0.2854403335544127</v>
+        <v>-0.4298356510745891</v>
       </c>
       <c r="AB45">
-        <v>0.04783840119793618</v>
+        <v>0.07784467389949246</v>
       </c>
       <c r="AC45">
-        <v>-0.3332787347523489</v>
+        <v>-0.5076803249740816</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>106.1</v>
       </c>
       <c r="AE45">
-        <v>0.007782374187797358</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>0.007782374187797358</v>
+        <v>106.1</v>
       </c>
       <c r="AG45">
-        <v>-8.922217625812202</v>
+        <v>-201.3</v>
       </c>
       <c r="AH45">
-        <v>0.0003568622455169379</v>
+        <v>0.2472041006523765</v>
       </c>
       <c r="AI45">
-        <v>0.0002058405359715188</v>
+        <v>0.28933733296973</v>
       </c>
       <c r="AJ45">
-        <v>-0.6928380497946508</v>
+        <v>-1.652709359605911</v>
       </c>
       <c r="AK45">
-        <v>-0.308964778188344</v>
+        <v>-3.394603709949407</v>
       </c>
       <c r="AL45">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AM45">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AN45">
-        <v>0</v>
+        <v>-0.9464763603925067</v>
+      </c>
+      <c r="AO45">
+        <v>-21.48014440433213</v>
       </c>
       <c r="AP45">
-        <v>-1115.277203226525</v>
+        <v>1.7957181088314</v>
+      </c>
+      <c r="AQ45">
+        <v>-21.48014440433213</v>
       </c>
     </row>
     <row r="46">
@@ -6430,7 +6385,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Unico American Corporation (NasdaqGM:UNAM)</t>
+          <t>United Insurance Holdings Corp. (NasdaqCM:UIHC)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6439,112 +6394,118 @@
         </is>
       </c>
       <c r="D46">
-        <v>-0.0112</v>
+        <v>-0.0382</v>
       </c>
       <c r="G46">
-        <v>-0.5323076923076924</v>
+        <v>-0.1272910372608258</v>
       </c>
       <c r="H46">
-        <v>-0.5323076923076924</v>
+        <v>-0.1272910372608258</v>
       </c>
       <c r="I46">
-        <v>-0.5846153846153846</v>
+        <v>-0.2672564979915143</v>
       </c>
       <c r="J46">
-        <v>-0.5846153846153846</v>
+        <v>-0.2672564979915143</v>
       </c>
       <c r="K46">
-        <v>-19.2</v>
+        <v>-175.4</v>
       </c>
       <c r="L46">
-        <v>-0.5907692307692307</v>
+        <v>-0.3532729103726083</v>
       </c>
       <c r="M46">
-        <v>0.005</v>
+        <v>5.202999999999999</v>
       </c>
       <c r="N46">
-        <v>0.0002747252747252747</v>
+        <v>0.113355119825708</v>
       </c>
       <c r="O46">
-        <v>-0.0002604166666666667</v>
+        <v>-0.02966362599771949</v>
       </c>
       <c r="P46">
-        <v>-0</v>
+        <v>5.18</v>
       </c>
       <c r="Q46">
-        <v>-0</v>
+        <v>0.1128540305010893</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>-0.02953249714937286</v>
       </c>
       <c r="S46">
-        <v>0.005</v>
+        <v>0.02299999999999969</v>
       </c>
       <c r="T46">
-        <v>1</v>
+        <v>0.004420526619258061</v>
       </c>
       <c r="U46">
-        <v>1.88</v>
+        <v>180.9</v>
       </c>
       <c r="V46">
-        <v>0.1032967032967033</v>
+        <v>3.941176470588236</v>
       </c>
       <c r="W46">
-        <v>-0.3490909090909091</v>
+        <v>-0.5474406991260924</v>
       </c>
       <c r="X46">
-        <v>0.04783965950667861</v>
+        <v>0.183768165417518</v>
       </c>
       <c r="Y46">
-        <v>-0.3969305685975877</v>
+        <v>-0.7312088645436104</v>
       </c>
       <c r="Z46">
-        <v>0.645866454689984</v>
+        <v>2.267700502731966</v>
       </c>
       <c r="AA46">
-        <v>-0.37758346581876</v>
+        <v>-0.6060576948537417</v>
       </c>
       <c r="AB46">
-        <v>0.04783965950667861</v>
+        <v>0.07595566093501958</v>
       </c>
       <c r="AC46">
-        <v>-0.4254231253254386</v>
+        <v>-0.6820133557887613</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>152.7</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>2.644256263934239</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>155.3442562639342</v>
       </c>
       <c r="AG46">
-        <v>-1.88</v>
+        <v>-25.55574373606578</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>0.7719189563363159</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>0.6589524543495733</v>
       </c>
       <c r="AJ46">
-        <v>-0.1151960784313725</v>
+        <v>-1.256165052411886</v>
       </c>
       <c r="AK46">
-        <v>-0.05676328502415459</v>
+        <v>-0.4659693735854583</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AM46">
-        <v>0</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN46">
-        <v>-0</v>
+        <v>-1.248936727082379</v>
+      </c>
+      <c r="AO46">
+        <v>-13.90575916230367</v>
       </c>
       <c r="AP46">
-        <v>0.1021739130434783</v>
+        <v>0.2090210015709103</v>
+      </c>
+      <c r="AQ46">
+        <v>-13.90575916230367</v>
       </c>
     </row>
     <row r="47">
@@ -6555,7 +6516,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HCI Group, Inc. (NYSE:HCI)</t>
+          <t>FedNat Holding Company (OTCPK:FNHC.Q)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6564,121 +6525,115 @@
         </is>
       </c>
       <c r="D47">
-        <v>0.0764</v>
-      </c>
-      <c r="E47">
-        <v>-0.337</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="G47">
-        <v>0.04454769062585406</v>
+        <v>-0.3863829787234043</v>
       </c>
       <c r="H47">
-        <v>0.04454769062585406</v>
+        <v>-0.3863829787234043</v>
       </c>
       <c r="I47">
-        <v>0.0612850700542241</v>
+        <v>-0.4814402186362228</v>
       </c>
       <c r="J47">
-        <v>0.04495999535874545</v>
+        <v>-0.4814402186362228</v>
       </c>
       <c r="K47">
-        <v>4.54</v>
+        <v>-127.6</v>
       </c>
       <c r="L47">
-        <v>0.01240776168352009</v>
+        <v>-0.5429787234042553</v>
       </c>
       <c r="M47">
-        <v>14.62</v>
+        <v>-0</v>
       </c>
       <c r="N47">
-        <v>0.01707345556463856</v>
+        <v>-0</v>
       </c>
       <c r="O47">
-        <v>3.220264317180617</v>
+        <v>0</v>
       </c>
       <c r="P47">
-        <v>13.1</v>
+        <v>-0</v>
       </c>
       <c r="Q47">
-        <v>0.01529837673712484</v>
+        <v>-0</v>
       </c>
       <c r="R47">
-        <v>2.885462555066079</v>
+        <v>0</v>
       </c>
       <c r="S47">
-        <v>1.52</v>
-      </c>
-      <c r="T47">
-        <v>0.1039671682626539</v>
+        <v>0</v>
       </c>
       <c r="U47">
-        <v>569.1</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="V47">
-        <v>0.6646035268013547</v>
+        <v>3121.428571428572</v>
       </c>
       <c r="W47">
-        <v>0.02273410115172759</v>
+        <v>-0.86743711760707</v>
       </c>
       <c r="X47">
-        <v>0.05013054268063728</v>
+        <v>137.3609678085887</v>
       </c>
       <c r="Y47">
-        <v>-0.02739644152890969</v>
+        <v>-138.2284049261957</v>
       </c>
       <c r="Z47">
-        <v>-8.584962666857864</v>
+        <v>1.289138683120573</v>
       </c>
       <c r="AA47">
-        <v>-0.3859798816569325</v>
+        <v>-0.620643209453981</v>
       </c>
       <c r="AB47">
-        <v>0.04723638258162199</v>
+        <v>0.07482941499623297</v>
       </c>
       <c r="AC47">
-        <v>-0.4332162642385545</v>
+        <v>-0.695472624450214</v>
       </c>
       <c r="AD47">
-        <v>78.09999999999999</v>
+        <v>118.9</v>
       </c>
       <c r="AE47">
-        <v>3.978964335797007</v>
+        <v>6.192256897561787</v>
       </c>
       <c r="AF47">
-        <v>82.078964335797</v>
+        <v>125.0922568975618</v>
       </c>
       <c r="AG47">
-        <v>-487.0210356642031</v>
+        <v>37.69225689756179</v>
       </c>
       <c r="AH47">
-        <v>0.08746888778980047</v>
+        <v>0.9997762152932365</v>
       </c>
       <c r="AI47">
-        <v>0.1775144863125481</v>
+        <v>0.8987012617348616</v>
       </c>
       <c r="AJ47">
-        <v>-1.3188431584241</v>
+        <v>0.9992576932846444</v>
       </c>
       <c r="AK47">
-        <v>4.563496152685504</v>
+        <v>0.7277585329427152</v>
       </c>
       <c r="AL47">
-        <v>8.630000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AM47">
-        <v>8.630000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="AN47">
-        <v>3.084518167456556</v>
+        <v>-1.079927338782925</v>
       </c>
       <c r="AO47">
-        <v>2.491309385863267</v>
+        <v>-12.37677984665936</v>
       </c>
       <c r="AP47">
-        <v>-19.2346380594077</v>
+        <v>-0.3423456575618691</v>
       </c>
       <c r="AQ47">
-        <v>2.491309385863267</v>
+        <v>-12.37677984665936</v>
       </c>
     </row>
     <row r="48">
@@ -6689,7 +6644,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FedNat Holding Company (NasdaqGM:FNHC)</t>
+          <t>Heritage Insurance Holdings, Inc. (NYSE:HRTG)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6698,118 +6653,118 @@
         </is>
       </c>
       <c r="D48">
-        <v>-0.0145</v>
+        <v>0.103</v>
       </c>
       <c r="G48">
-        <v>-0.3433345993163692</v>
+        <v>0.001351970669110907</v>
       </c>
       <c r="H48">
-        <v>-0.3433345993163692</v>
+        <v>0.001351970669110907</v>
       </c>
       <c r="I48">
-        <v>-0.4591616538775852</v>
+        <v>-0.09767579923723847</v>
       </c>
       <c r="J48">
-        <v>-0.4591616538775852</v>
+        <v>-0.09767579923723847</v>
       </c>
       <c r="K48">
-        <v>-132.6</v>
+        <v>-216.1</v>
       </c>
       <c r="L48">
-        <v>-0.5036080516521079</v>
+        <v>-0.3301252673388329</v>
       </c>
       <c r="M48">
-        <v>1.26</v>
+        <v>20.45</v>
       </c>
       <c r="N48">
-        <v>0.05121951219512195</v>
+        <v>0.4504405286343612</v>
       </c>
       <c r="O48">
-        <v>-0.009502262443438915</v>
+        <v>-0.0946321147616844</v>
       </c>
       <c r="P48">
-        <v>1.26</v>
+        <v>6.45</v>
       </c>
       <c r="Q48">
-        <v>0.05121951219512195</v>
+        <v>0.1420704845814978</v>
       </c>
       <c r="R48">
-        <v>-0.009502262443438915</v>
+        <v>-0.02984729291994447</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>0.684596577017115</v>
       </c>
       <c r="U48">
-        <v>166.9</v>
+        <v>297.5</v>
       </c>
       <c r="V48">
-        <v>6.784552845528455</v>
+        <v>6.552863436123348</v>
       </c>
       <c r="W48">
-        <v>-0.6580645161290323</v>
+        <v>-0.5335802469135802</v>
       </c>
       <c r="X48">
-        <v>0.1708722544135016</v>
+        <v>0.1971632971127908</v>
       </c>
       <c r="Y48">
-        <v>-0.8289367705425339</v>
+        <v>-0.730743544026371</v>
       </c>
       <c r="Z48">
-        <v>1.063252768572292</v>
+        <v>18.84126458614309</v>
       </c>
       <c r="AA48">
-        <v>-0.4882048997075751</v>
+        <v>-1.840335577091803</v>
       </c>
       <c r="AB48">
-        <v>0.04488716710251614</v>
+        <v>0.07359495605362198</v>
       </c>
       <c r="AC48">
-        <v>-0.5330920668100912</v>
+        <v>-1.913930533145425</v>
       </c>
       <c r="AD48">
-        <v>118.8</v>
+        <v>144.4</v>
       </c>
       <c r="AE48">
-        <v>7.836317329840817</v>
+        <v>29.04289090348152</v>
       </c>
       <c r="AF48">
-        <v>126.6363173298408</v>
+        <v>173.4428909034815</v>
       </c>
       <c r="AG48">
-        <v>-40.2636826701592</v>
+        <v>-124.0571090965185</v>
       </c>
       <c r="AH48">
-        <v>0.8373406570966132</v>
+        <v>0.7925452373044038</v>
       </c>
       <c r="AI48">
-        <v>0.6401065236101597</v>
+        <v>0.5957311558089206</v>
       </c>
       <c r="AJ48">
-        <v>2.570511898001186</v>
+        <v>1.577188769349388</v>
       </c>
       <c r="AK48">
-        <v>-1.301502122598197</v>
+        <v>19.51470506687694</v>
       </c>
       <c r="AL48">
-        <v>8.369999999999999</v>
+        <v>7.77</v>
       </c>
       <c r="AM48">
-        <v>8.369999999999999</v>
+        <v>7.77</v>
       </c>
       <c r="AN48">
-        <v>-1.011666524738142</v>
+        <v>-2.903679871305048</v>
       </c>
       <c r="AO48">
-        <v>-14.3847072879331</v>
+        <v>-8.069498069498071</v>
       </c>
       <c r="AP48">
-        <v>0.3428739050511726</v>
+        <v>2.494613092630575</v>
       </c>
       <c r="AQ48">
-        <v>-14.3847072879331</v>
+        <v>-8.069498069498071</v>
       </c>
     </row>
     <row r="49">
@@ -6820,7 +6775,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>United Insurance Holdings Corp. (NasdaqCM:UIHC)</t>
+          <t>Atlas Financial Holdings, Inc. (OTCPK:AFHI.F)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6829,118 +6784,115 @@
         </is>
       </c>
       <c r="D49">
-        <v>0.09619999999999999</v>
+        <v>-0.491</v>
       </c>
       <c r="G49">
-        <v>-0.151275651691625</v>
+        <v>-0.9845938375350141</v>
       </c>
       <c r="H49">
-        <v>-0.151275651691625</v>
+        <v>-0.9845938375350141</v>
       </c>
       <c r="I49">
-        <v>-0.1538738246852451</v>
+        <v>-1.744946096816675</v>
       </c>
       <c r="J49">
-        <v>-0.1538738246852451</v>
+        <v>-1.744946096816675</v>
       </c>
       <c r="K49">
-        <v>-89.5</v>
+        <v>-12.6</v>
       </c>
       <c r="L49">
-        <v>-0.1240987243483084</v>
+        <v>-1.764705882352941</v>
       </c>
       <c r="M49">
-        <v>10.342</v>
+        <v>-0</v>
       </c>
       <c r="N49">
-        <v>0.05515733333333334</v>
+        <v>-0</v>
       </c>
       <c r="O49">
-        <v>-0.1155530726256983</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>10.3</v>
+        <v>-0</v>
       </c>
       <c r="Q49">
-        <v>0.05493333333333333</v>
+        <v>-0</v>
       </c>
       <c r="R49">
-        <v>-0.1150837988826816</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>0.04199999999999982</v>
-      </c>
-      <c r="T49">
-        <v>0.004061110036743358</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>188.3</v>
+        <v>0.082</v>
       </c>
       <c r="V49">
-        <v>1.004266666666667</v>
+        <v>0.354978354978355</v>
       </c>
       <c r="W49">
-        <v>-0.1971799955937431</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="X49">
-        <v>0.06831318794774061</v>
+        <v>4.907118653796467</v>
       </c>
       <c r="Y49">
-        <v>-0.2654931835414838</v>
+        <v>-4.42063216730998</v>
       </c>
       <c r="Z49">
-        <v>3.291362050358835</v>
+        <v>1.157291910772673</v>
       </c>
       <c r="AA49">
-        <v>-0.5064544671125844</v>
+        <v>-2.019412002580287</v>
       </c>
       <c r="AB49">
-        <v>0.04621277839230382</v>
+        <v>0.07485957289384888</v>
       </c>
       <c r="AC49">
-        <v>-0.5526672455048882</v>
+        <v>-2.094271575474136</v>
       </c>
       <c r="AD49">
-        <v>157.2</v>
+        <v>36.1</v>
       </c>
       <c r="AE49">
-        <v>3.419011814993856</v>
+        <v>0.1895756563553068</v>
       </c>
       <c r="AF49">
-        <v>160.6190118149939</v>
+        <v>36.28957565635531</v>
       </c>
       <c r="AG49">
-        <v>-27.68098818500616</v>
+        <v>36.20757565635531</v>
       </c>
       <c r="AH49">
-        <v>0.4613910943202207</v>
+        <v>0.9936747984978763</v>
       </c>
       <c r="AI49">
-        <v>0.3203928198004757</v>
+        <v>9.096099129877823</v>
       </c>
       <c r="AJ49">
-        <v>-0.1732020982400367</v>
+        <v>0.9936605645023419</v>
       </c>
       <c r="AK49">
-        <v>-0.08843229050051016</v>
+        <v>9.265994785658728</v>
       </c>
       <c r="AL49">
-        <v>9.4</v>
+        <v>2.77</v>
       </c>
       <c r="AM49">
-        <v>9.4</v>
+        <v>2.77</v>
       </c>
       <c r="AN49">
-        <v>-1.597723345868483</v>
+        <v>-2.978302120287105</v>
       </c>
       <c r="AO49">
-        <v>-11.79787234042553</v>
+        <v>-4.548736462093863</v>
       </c>
       <c r="AP49">
-        <v>0.2813394469458904</v>
+        <v>-2.98717726725149</v>
       </c>
       <c r="AQ49">
-        <v>-11.79787234042553</v>
+        <v>-4.548736462093863</v>
       </c>
     </row>
     <row r="50">
@@ -6951,7 +6903,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Atlas Financial Holdings, Inc. (OTCPK:AFHI.F)</t>
+          <t>Root, Inc. (NasdaqGS:ROOT)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6959,26 +6911,23 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D50">
-        <v>-0.442</v>
-      </c>
       <c r="G50">
-        <v>-1.305732484076433</v>
+        <v>-1.419597234746018</v>
       </c>
       <c r="H50">
-        <v>-1.305732484076433</v>
+        <v>-1.419597234746018</v>
       </c>
       <c r="I50">
-        <v>-1.009738519842667</v>
+        <v>-0.8671306664394877</v>
       </c>
       <c r="J50">
-        <v>-1.009738519842667</v>
+        <v>-0.8671306664394877</v>
       </c>
       <c r="K50">
-        <v>-7.13</v>
+        <v>-340.2</v>
       </c>
       <c r="L50">
-        <v>-0.756900212314225</v>
+        <v>-1.022542831379621</v>
       </c>
       <c r="M50">
         <v>-0</v>
@@ -7002,73 +6951,73 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>1.52</v>
+        <v>819.7</v>
       </c>
       <c r="V50">
-        <v>0.2851782363977486</v>
+        <v>12.94944707740916</v>
       </c>
       <c r="W50">
-        <v>0.3656410256410256</v>
+        <v>-0.5349056603773584</v>
       </c>
       <c r="X50">
-        <v>0.2021745343708613</v>
+        <v>0.2297096255795503</v>
       </c>
       <c r="Y50">
-        <v>0.1634664912701644</v>
+        <v>-0.7646152859569088</v>
       </c>
       <c r="Z50">
-        <v>0.6352552808605911</v>
+        <v>17.91419573016451</v>
       </c>
       <c r="AA50">
-        <v>-0.6414417270184108</v>
+        <v>-15.53394848222498</v>
       </c>
       <c r="AB50">
-        <v>0.06583323981520996</v>
+        <v>0.07566898854427065</v>
       </c>
       <c r="AC50">
-        <v>-0.7072749668336208</v>
+        <v>-15.60961747076925</v>
       </c>
       <c r="AD50">
-        <v>33.4</v>
+        <v>293.9</v>
       </c>
       <c r="AE50">
-        <v>1.018684284589601</v>
+        <v>14.97186362208761</v>
       </c>
       <c r="AF50">
-        <v>34.4186842845896</v>
+        <v>308.8718636220876</v>
       </c>
       <c r="AG50">
-        <v>32.8986842845896</v>
+        <v>-510.8281363779125</v>
       </c>
       <c r="AH50">
-        <v>0.8659075112565068</v>
+        <v>0.8299172877177078</v>
       </c>
       <c r="AI50">
-        <v>4.040375618433634</v>
+        <v>0.4108585045121563</v>
       </c>
       <c r="AJ50">
-        <v>0.8605758973988916</v>
+        <v>1.141443620757169</v>
       </c>
       <c r="AK50">
-        <v>4.700695580314888</v>
+        <v>7.520125880326864</v>
       </c>
       <c r="AL50">
-        <v>2.21</v>
+        <v>26.1</v>
       </c>
       <c r="AM50">
-        <v>2.21</v>
+        <v>26.1</v>
       </c>
       <c r="AN50">
-        <v>-4.074164430348866</v>
+        <v>-1.066787658802178</v>
       </c>
       <c r="AO50">
-        <v>-4.615384615384615</v>
+        <v>-11.10344827586207</v>
       </c>
       <c r="AP50">
-        <v>-4.013013452621322</v>
+        <v>1.854185612986978</v>
       </c>
       <c r="AQ50">
-        <v>-4.615384615384615</v>
+        <v>-11.10344827586207</v>
       </c>
     </row>
     <row r="51">
@@ -7079,7 +7028,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Metromile, Inc. (NasdaqCM:MILE)</t>
+          <t>HCI Group, Inc. (NYSE:HCI)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7087,113 +7036,113 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D51">
+        <v>0.14</v>
+      </c>
+      <c r="F51">
+        <v>0.25</v>
+      </c>
       <c r="G51">
-        <v>-0.4703832752613241</v>
+        <v>0.04879040455377109</v>
       </c>
       <c r="H51">
-        <v>-0.4703832752613241</v>
+        <v>0.04879040455377109</v>
       </c>
       <c r="I51">
-        <v>-1.864309396131826</v>
+        <v>-0.1252220374048718</v>
       </c>
       <c r="J51">
-        <v>-1.864309396131826</v>
+        <v>-0.1252220374048718</v>
       </c>
       <c r="K51">
-        <v>-255.3</v>
+        <v>-60</v>
       </c>
       <c r="L51">
-        <v>-2.965156794425087</v>
+        <v>-0.1219760113844277</v>
       </c>
       <c r="M51">
-        <v>-0</v>
+        <v>92.10000000000001</v>
       </c>
       <c r="N51">
-        <v>-0</v>
+        <v>0.2656475338909721</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>-1.535</v>
       </c>
       <c r="P51">
-        <v>-0</v>
+        <v>15.9</v>
       </c>
       <c r="Q51">
-        <v>-0</v>
+        <v>0.04586097490625902</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>-0.265</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>76.2</v>
+      </c>
+      <c r="T51">
+        <v>0.8273615635179152</v>
       </c>
       <c r="U51">
-        <v>159.2</v>
+        <v>355.7</v>
       </c>
       <c r="V51">
-        <v>0.5689778413152251</v>
+        <v>1.025959042399769</v>
       </c>
       <c r="W51">
-        <v>0.9170258620689656</v>
+        <v>-0.2058319039451115</v>
       </c>
       <c r="X51">
-        <v>0.04954675454187159</v>
+        <v>0.09871889657678715</v>
       </c>
       <c r="Y51">
-        <v>0.867479107527094</v>
-      </c>
-      <c r="Z51">
-        <v>1.207824429154279</v>
-      </c>
-      <c r="AA51">
-        <v>-2.251758432149883</v>
+        <v>-0.3045508005218986</v>
       </c>
       <c r="AB51">
-        <v>0.04922496095800453</v>
-      </c>
-      <c r="AC51">
-        <v>-2.300983393107887</v>
+        <v>0.07679870545314799</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>211.7</v>
       </c>
       <c r="AE51">
-        <v>19.9851950347513</v>
+        <v>2.083600997282181</v>
       </c>
       <c r="AF51">
-        <v>19.9851950347513</v>
+        <v>213.7836009972822</v>
       </c>
       <c r="AG51">
-        <v>-139.2148049652487</v>
+        <v>-141.9163990027178</v>
       </c>
       <c r="AH51">
-        <v>0.06666505006171035</v>
+        <v>0.3814270401790379</v>
       </c>
       <c r="AI51">
-        <v>0.08429541554385936</v>
+        <v>0.4470743048306612</v>
       </c>
       <c r="AJ51">
-        <v>-0.9902522447746798</v>
+        <v>-0.6930066583046427</v>
       </c>
       <c r="AK51">
-        <v>-1.787436044849511</v>
+        <v>-1.158656324987268</v>
       </c>
       <c r="AL51">
-        <v>18.6</v>
+        <v>5.59</v>
       </c>
       <c r="AM51">
-        <v>18.6</v>
+        <v>5.59</v>
       </c>
       <c r="AN51">
-        <v>-0</v>
+        <v>-3.843500363108206</v>
       </c>
       <c r="AO51">
-        <v>-8.591397849462366</v>
+        <v>-11.19856887298748</v>
       </c>
       <c r="AP51">
-        <v>0.9157663791951629</v>
+        <v>2.576550453934601</v>
       </c>
       <c r="AQ51">
-        <v>-8.591397849462366</v>
+        <v>-11.19856887298748</v>
       </c>
     </row>
     <row r="52">
@@ -7204,7 +7153,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lemonade, Inc. (NYSE:LMND)</t>
+          <t>Hallmark Financial Services, Inc. (NasdaqGM:HALL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7212,23 +7161,26 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D52">
+        <v>-0.0186</v>
+      </c>
       <c r="G52">
-        <v>-1.103799814643188</v>
+        <v>0.0567113137646053</v>
       </c>
       <c r="H52">
-        <v>-1.103799814643188</v>
+        <v>0.0567113137646053</v>
       </c>
       <c r="I52">
-        <v>-1.829081758238015</v>
+        <v>-0.2326234236343938</v>
       </c>
       <c r="J52">
-        <v>-1.829081758238015</v>
+        <v>-0.2326234236343938</v>
       </c>
       <c r="K52">
-        <v>-204.9</v>
+        <v>-103.4</v>
       </c>
       <c r="L52">
-        <v>-1.898980537534754</v>
+        <v>-0.2946708463949844</v>
       </c>
       <c r="M52">
         <v>-0</v>
@@ -7252,195 +7204,64 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>319.4</v>
+        <v>129.5</v>
       </c>
       <c r="V52">
-        <v>0.123078108743401</v>
+        <v>12.21698113207547</v>
       </c>
       <c r="W52">
-        <v>-0.3601054481546573</v>
+        <v>-0.5815523059617548</v>
       </c>
       <c r="X52">
-        <v>0.04800349549794803</v>
+        <v>0.4429675047269</v>
       </c>
       <c r="Y52">
-        <v>-0.4081089436526053</v>
-      </c>
-      <c r="Z52">
-        <v>9.473547694150048</v>
-      </c>
-      <c r="AA52">
-        <v>-17.32789327316766</v>
+        <v>-1.024519810688655</v>
       </c>
       <c r="AB52">
-        <v>0.04785870533153587</v>
-      </c>
-      <c r="AC52">
-        <v>-17.3757519784992</v>
+        <v>0.07258618802739705</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>105.3</v>
       </c>
       <c r="AE52">
-        <v>17.78960856940937</v>
+        <v>19.98779676654398</v>
       </c>
       <c r="AF52">
-        <v>17.78960856940937</v>
+        <v>125.287796766544</v>
       </c>
       <c r="AG52">
-        <v>-301.6103914305906</v>
+        <v>-4.212203233456023</v>
       </c>
       <c r="AH52">
-        <v>0.006808404193987137</v>
+        <v>0.921994467110164</v>
       </c>
       <c r="AI52">
-        <v>0.01669148247118683</v>
+        <v>0.6556556665918899</v>
       </c>
       <c r="AJ52">
-        <v>-0.131507197723352</v>
+        <v>-0.6594140965031005</v>
       </c>
       <c r="AK52">
-        <v>-0.4040924310410503</v>
+        <v>-0.06839347167139119</v>
       </c>
       <c r="AL52">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AM52">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="AN52">
-        <v>-0</v>
+        <v>-1.416655455401588</v>
+      </c>
+      <c r="AO52">
+        <v>-14.75046210720887</v>
       </c>
       <c r="AP52">
-        <v>1.581596179499689</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Root, Inc. (NasdaqGS:ROOT)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="F53">
-        <v>0.333</v>
-      </c>
-      <c r="G53">
-        <v>-0.8977235235895744</v>
-      </c>
-      <c r="H53">
-        <v>-0.8977235235895744</v>
-      </c>
-      <c r="I53">
-        <v>-1.589343773367077</v>
-      </c>
-      <c r="J53">
-        <v>-1.589343773367077</v>
-      </c>
-      <c r="K53">
-        <v>-544.5</v>
-      </c>
-      <c r="L53">
-        <v>-1.796436819531508</v>
-      </c>
-      <c r="M53">
-        <v>-0</v>
-      </c>
-      <c r="N53">
-        <v>-0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>-0</v>
-      </c>
-      <c r="Q53">
-        <v>-0</v>
-      </c>
-      <c r="R53">
-        <v>0</v>
-      </c>
-      <c r="S53">
-        <v>0</v>
-      </c>
-      <c r="U53">
-        <v>834.1</v>
-      </c>
-      <c r="V53">
-        <v>1.065533980582524</v>
-      </c>
-      <c r="W53">
-        <v>0.954593267882188</v>
-      </c>
-      <c r="X53">
-        <v>0.05458252607735605</v>
-      </c>
-      <c r="Y53">
-        <v>0.900010741804832</v>
-      </c>
-      <c r="Z53">
-        <v>26.70369640834918</v>
-      </c>
-      <c r="AA53">
-        <v>-42.44135361249456</v>
-      </c>
-      <c r="AB53">
-        <v>0.04845521940563379</v>
-      </c>
-      <c r="AC53">
-        <v>-42.48980883190019</v>
-      </c>
-      <c r="AD53">
-        <v>201.7</v>
-      </c>
-      <c r="AE53">
-        <v>19.15048853780531</v>
-      </c>
-      <c r="AF53">
-        <v>220.8504885378053</v>
-      </c>
-      <c r="AG53">
-        <v>-613.2495114621947</v>
-      </c>
-      <c r="AH53">
-        <v>0.2200472087245802</v>
-      </c>
-      <c r="AI53">
-        <v>0.2577468198853237</v>
-      </c>
-      <c r="AJ53">
-        <v>-3.616913857051237</v>
-      </c>
-      <c r="AK53">
-        <v>-26.95544363555697</v>
-      </c>
-      <c r="AL53">
-        <v>62.7</v>
-      </c>
-      <c r="AM53">
-        <v>62.7</v>
-      </c>
-      <c r="AN53">
-        <v>-0.4344174025414602</v>
-      </c>
-      <c r="AO53">
-        <v>-7.684210526315789</v>
-      </c>
-      <c r="AP53">
-        <v>1.320804461473605</v>
-      </c>
-      <c r="AQ53">
-        <v>-7.684210526315789</v>
+        <v>0.05666895242104161</v>
+      </c>
+      <c r="AQ52">
+        <v>-14.75046210720887</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ52"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04805</v>
+        <v>0.05905</v>
       </c>
       <c r="E2">
-        <v>0.06795</v>
+        <v>0.0345</v>
       </c>
       <c r="F2">
-        <v>0.1136</v>
+        <v>0.17</v>
       </c>
       <c r="G2">
-        <v>0.1687657367886011</v>
+        <v>0.06298988144289665</v>
       </c>
       <c r="H2">
-        <v>0.1687657367886011</v>
+        <v>0.06298988144289665</v>
       </c>
       <c r="I2">
-        <v>0.06492359510899157</v>
+        <v>0.07491728052428291</v>
       </c>
       <c r="J2">
-        <v>0.05768945288318047</v>
+        <v>0.06522469293479601</v>
       </c>
       <c r="K2">
-        <v>10805.474</v>
+        <v>15963.52</v>
       </c>
       <c r="L2">
-        <v>0.0405396257176756</v>
+        <v>0.0500380374494127</v>
       </c>
       <c r="M2">
-        <v>16682.03</v>
+        <v>12367.4075</v>
       </c>
       <c r="N2">
-        <v>0.05180692892298094</v>
+        <v>0.03256708665948671</v>
       </c>
       <c r="O2">
-        <v>1.54384990422447</v>
+        <v>0.7747293516718117</v>
       </c>
       <c r="P2">
-        <v>7922.51</v>
+        <v>5608.5325</v>
       </c>
       <c r="Q2">
-        <v>0.02460377498791249</v>
+        <v>0.01476894522639831</v>
       </c>
       <c r="R2">
-        <v>0.7331941199432807</v>
+        <v>0.3513343235075973</v>
       </c>
       <c r="S2">
-        <v>8759.52</v>
+        <v>6758.875</v>
       </c>
       <c r="T2">
-        <v>0.5250871746424147</v>
+        <v>0.546507018548552</v>
       </c>
       <c r="U2">
-        <v>20176.55</v>
+        <v>20288.809</v>
       </c>
       <c r="V2">
-        <v>0.06265934612040448</v>
+        <v>0.05342650841906633</v>
       </c>
       <c r="W2">
-        <v>0.03948776138206447</v>
+        <v>0.110216780242265</v>
       </c>
       <c r="X2">
-        <v>0.08732957371332983</v>
+        <v>0.0734601362503027</v>
       </c>
       <c r="Y2">
-        <v>-0.04784181233126536</v>
+        <v>0.03675664399196234</v>
       </c>
       <c r="Z2">
-        <v>1.223591749574505</v>
+        <v>1.69459365934776</v>
       </c>
       <c r="AA2">
-        <v>0.03351946924776143</v>
+        <v>0.1205716302049778</v>
       </c>
       <c r="AB2">
-        <v>0.07759320227278585</v>
+        <v>0.06747495306225802</v>
       </c>
       <c r="AC2">
-        <v>-0.04061941502377084</v>
+        <v>0.05205325052795332</v>
       </c>
       <c r="AD2">
-        <v>65237.41</v>
+        <v>69844.81200000001</v>
       </c>
       <c r="AE2">
-        <v>3889.822195552394</v>
+        <v>3775.121520416151</v>
       </c>
       <c r="AF2">
-        <v>69127.23219555239</v>
+        <v>73619.93352041615</v>
       </c>
       <c r="AG2">
-        <v>48950.68219555239</v>
+        <v>53331.12452041615</v>
       </c>
       <c r="AH2">
-        <v>0.1767367444991122</v>
+        <v>0.1623831823735074</v>
       </c>
       <c r="AI2">
-        <v>0.3206831148242104</v>
+        <v>0.3082349485801537</v>
       </c>
       <c r="AJ2">
-        <v>0.1319587156878122</v>
+        <v>0.1231430059254448</v>
       </c>
       <c r="AK2">
-        <v>0.2505333632373704</v>
+        <v>0.2440172241388336</v>
       </c>
       <c r="AL2">
-        <v>2699.037</v>
+        <v>3199.655</v>
       </c>
       <c r="AM2">
-        <v>2661.837</v>
+        <v>3165.355</v>
       </c>
       <c r="AN2">
-        <v>2.838654382631688</v>
+        <v>2.368384569857547</v>
       </c>
       <c r="AO2">
-        <v>6.329683142543062</v>
+        <v>7.390379900333005</v>
       </c>
       <c r="AP2">
-        <v>2.129975248055</v>
+        <v>1.808417959623186</v>
       </c>
       <c r="AQ2">
-        <v>6.418142433214354</v>
+        <v>7.470462554752943</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stewart Information Services Corporation (NYSE:STC)</t>
+          <t>Heritage Insurance Holdings, Inc. (NYSE:HRTG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,121 +725,112 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.115</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="E3">
-        <v>0.361</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1405884962294839</v>
+        <v>-0.07882727147005947</v>
       </c>
       <c r="H3">
-        <v>0.1405884962294839</v>
+        <v>-0.07882727147005947</v>
       </c>
       <c r="I3">
-        <v>0.1094071368956501</v>
+        <v>0.0589525886182732</v>
       </c>
       <c r="J3">
-        <v>0.08531071840145475</v>
+        <v>0.05161711993678123</v>
       </c>
       <c r="K3">
-        <v>234.5</v>
+        <v>26.9</v>
       </c>
       <c r="L3">
-        <v>0.0693479225195919</v>
+        <v>0.03720094039551929</v>
       </c>
       <c r="M3">
-        <v>45.78</v>
+        <v>0.668</v>
       </c>
       <c r="N3">
-        <v>0.03949616081442499</v>
+        <v>0.003383991894630193</v>
       </c>
       <c r="O3">
-        <v>0.1952238805970149</v>
+        <v>0.02483271375464684</v>
       </c>
       <c r="P3">
-        <v>42.5</v>
+        <v>0.01</v>
       </c>
       <c r="Q3">
-        <v>0.03666637908722285</v>
+        <v>5.065856129685917e-05</v>
       </c>
       <c r="R3">
-        <v>0.1812366737739872</v>
+        <v>0.0003717472118959108</v>
       </c>
       <c r="S3">
-        <v>3.280000000000001</v>
+        <v>0.658</v>
       </c>
       <c r="T3">
-        <v>0.07164700742682396</v>
+        <v>0.9850299401197604</v>
       </c>
       <c r="U3">
-        <v>310.4</v>
+        <v>228.8</v>
       </c>
       <c r="V3">
-        <v>0.2677939780864464</v>
+        <v>1.159067882472138</v>
       </c>
       <c r="W3">
-        <v>0.1941385876314264</v>
+        <v>0.2285471537807986</v>
       </c>
       <c r="X3">
-        <v>0.09556069537062159</v>
+        <v>0.08663723379582475</v>
       </c>
       <c r="Y3">
-        <v>0.09857789226080485</v>
-      </c>
-      <c r="Z3">
-        <v>6.596776626717255</v>
-      </c>
-      <c r="AA3">
-        <v>0.5627757531591744</v>
+        <v>0.1419099199849739</v>
       </c>
       <c r="AB3">
-        <v>0.07516575957469225</v>
-      </c>
-      <c r="AC3">
-        <v>0.4876099935844821</v>
+        <v>0.06646298774359594</v>
       </c>
       <c r="AD3">
-        <v>446.4</v>
+        <v>143</v>
       </c>
       <c r="AE3">
-        <v>149.1988329367962</v>
+        <v>8.306915850633278</v>
       </c>
       <c r="AF3">
-        <v>595.5988329367962</v>
+        <v>151.3069158506333</v>
       </c>
       <c r="AG3">
-        <v>285.1988329367962</v>
+        <v>-77.49308414936672</v>
       </c>
       <c r="AH3">
-        <v>0.3394308024585377</v>
+        <v>0.4339085603780934</v>
       </c>
       <c r="AI3">
-        <v>0.3049506880515709</v>
+        <v>0.4998462470718497</v>
       </c>
       <c r="AJ3">
-        <v>0.1974652519498898</v>
+        <v>-0.6462770191328997</v>
       </c>
       <c r="AK3">
-        <v>0.1736160196978538</v>
+        <v>-1.048522770263897</v>
       </c>
       <c r="AL3">
-        <v>16.5</v>
+        <v>11.3</v>
       </c>
       <c r="AM3">
-        <v>16.5</v>
+        <v>11.3</v>
       </c>
       <c r="AN3">
-        <v>0.9791620969510858</v>
+        <v>2.703724711665721</v>
       </c>
       <c r="AO3">
-        <v>21.14545454545454</v>
+        <v>3.778761061946903</v>
       </c>
       <c r="AP3">
-        <v>0.6255732242526787</v>
+        <v>-1.465174591593245</v>
       </c>
       <c r="AQ3">
-        <v>21.14545454545454</v>
+        <v>3.778761061946903</v>
       </c>
     </row>
     <row r="4">
@@ -850,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fidelity National Financial, Inc. (NYSE:FNF)</t>
+          <t>HCI Group, Inc. (NYSE:HCI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -859,121 +850,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.158</v>
+        <v>0.16</v>
       </c>
       <c r="E4">
-        <v>0.162</v>
+        <v>0.021</v>
+      </c>
+      <c r="F4">
+        <v>0.25</v>
       </c>
       <c r="G4">
-        <v>0.2783848324770244</v>
+        <v>-0.10756735340729</v>
       </c>
       <c r="H4">
-        <v>0.2783848324770244</v>
+        <v>-0.10756735340729</v>
       </c>
       <c r="I4">
-        <v>0.1720419029121613</v>
+        <v>0.1514919981183617</v>
       </c>
       <c r="J4">
-        <v>0.1259981386608053</v>
+        <v>0.1167083369189796</v>
       </c>
       <c r="K4">
-        <v>1601</v>
+        <v>42.5</v>
       </c>
       <c r="L4">
-        <v>0.1158549822707866</v>
+        <v>0.0841917591125198</v>
       </c>
       <c r="M4">
-        <v>1114</v>
+        <v>26.7</v>
       </c>
       <c r="N4">
-        <v>0.1088145659138861</v>
+        <v>0.03137116672541417</v>
       </c>
       <c r="O4">
-        <v>0.6958151155527795</v>
+        <v>0.6282352941176471</v>
       </c>
       <c r="P4">
-        <v>491</v>
+        <v>13.8</v>
       </c>
       <c r="Q4">
-        <v>0.04796045948269125</v>
+        <v>0.0162143108917871</v>
       </c>
       <c r="R4">
-        <v>0.306683322923173</v>
+        <v>0.3247058823529412</v>
       </c>
       <c r="S4">
-        <v>623</v>
+        <v>12.9</v>
       </c>
       <c r="T4">
-        <v>0.559245960502693</v>
+        <v>0.4831460674157304</v>
       </c>
       <c r="U4">
-        <v>2051</v>
+        <v>324</v>
       </c>
       <c r="V4">
-        <v>0.2003399234195515</v>
+        <v>0.3806838209376102</v>
       </c>
       <c r="W4">
-        <v>0.1715602228889841</v>
+        <v>0.2439724454649828</v>
       </c>
       <c r="X4">
-        <v>0.08903304726830386</v>
+        <v>0.07476916571585022</v>
       </c>
       <c r="Y4">
-        <v>0.08252717562068029</v>
+        <v>0.1692032797491326</v>
       </c>
       <c r="Z4">
-        <v>3.586774955246717</v>
+        <v>16.34492889999405</v>
       </c>
       <c r="AA4">
-        <v>0.4519269681562796</v>
+        <v>1.907589468977272</v>
       </c>
       <c r="AB4">
-        <v>0.07662870826421379</v>
+        <v>0.06754836611526251</v>
       </c>
       <c r="AC4">
-        <v>0.3752982598920658</v>
+        <v>1.840041102862009</v>
       </c>
       <c r="AD4">
-        <v>2693</v>
+        <v>208.3</v>
       </c>
       <c r="AE4">
-        <v>392.7647182842155</v>
+        <v>0.6841967492549954</v>
       </c>
       <c r="AF4">
-        <v>3085.764718284216</v>
+        <v>208.984196749255</v>
       </c>
       <c r="AG4">
-        <v>1034.764718284216</v>
+        <v>-115.015803250745</v>
       </c>
       <c r="AH4">
-        <v>0.2316055128363701</v>
+        <v>0.1971392436469711</v>
       </c>
       <c r="AI4">
-        <v>0.3473096717951271</v>
+        <v>0.4147464796425251</v>
       </c>
       <c r="AJ4">
-        <v>0.09179659673411621</v>
+        <v>-0.1562535967470645</v>
       </c>
       <c r="AK4">
-        <v>0.1514194241302499</v>
+        <v>-0.6393880359099491</v>
       </c>
       <c r="AL4">
-        <v>120</v>
+        <v>11.1</v>
       </c>
       <c r="AM4">
-        <v>120</v>
+        <v>11.1</v>
       </c>
       <c r="AN4">
-        <v>0.8873146622734761</v>
+        <v>2.467717095130909</v>
       </c>
       <c r="AO4">
-        <v>19.25833333333333</v>
+        <v>6.891891891891892</v>
       </c>
       <c r="AP4">
-        <v>0.3409438939980941</v>
+        <v>-1.362585040288414</v>
       </c>
       <c r="AQ4">
-        <v>19.25833333333333</v>
+        <v>6.891891891891892</v>
       </c>
     </row>
     <row r="5">
@@ -984,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RLI Corp. (NYSE:RLI)</t>
+          <t>Universal Insurance Holdings, Inc. (NYSE:UVE)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -993,121 +987,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.157</v>
+        <v>0.107</v>
       </c>
       <c r="E5">
-        <v>0.487</v>
+        <v>-0.148</v>
       </c>
       <c r="G5">
-        <v>0.1940631021194605</v>
+        <v>-0.00987746008169328</v>
       </c>
       <c r="H5">
-        <v>0.1940631021194605</v>
+        <v>-0.00987746008169328</v>
       </c>
       <c r="I5">
-        <v>0.4354795017166902</v>
+        <v>0.07560341626438916</v>
       </c>
       <c r="J5">
-        <v>0.3495509776802893</v>
+        <v>0.05703972328866296</v>
       </c>
       <c r="K5">
-        <v>580.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L5">
-        <v>0.3497711946050096</v>
+        <v>0.05339769773486818</v>
       </c>
       <c r="M5">
-        <v>91.5</v>
+        <v>44.40000000000001</v>
       </c>
       <c r="N5">
-        <v>0.01536059629331184</v>
+        <v>0.09519725557461409</v>
       </c>
       <c r="O5">
-        <v>0.1575142021001894</v>
+        <v>0.6175243393602226</v>
       </c>
       <c r="P5">
-        <v>91.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q5">
-        <v>0.01536059629331184</v>
+        <v>0.05060034305317325</v>
       </c>
       <c r="R5">
-        <v>0.1575142021001894</v>
+        <v>0.3282336578581363</v>
       </c>
       <c r="S5">
+        <v>20.8</v>
+      </c>
+      <c r="T5">
+        <v>0.4684684684684685</v>
+      </c>
+      <c r="U5">
+        <v>343.5</v>
+      </c>
+      <c r="V5">
+        <v>0.7364922813036021</v>
+      </c>
+      <c r="W5">
+        <v>0.2759017651573292</v>
+      </c>
+      <c r="X5">
+        <v>0.07476317472654087</v>
+      </c>
+      <c r="Y5">
+        <v>0.2011385904307884</v>
+      </c>
+      <c r="Z5">
+        <v>22.70657672849913</v>
+      </c>
+      <c r="AA5">
+        <v>1.295176853426384</v>
+      </c>
+      <c r="AB5">
+        <v>0.06754976531070706</v>
+      </c>
+      <c r="AC5">
+        <v>1.227627088115677</v>
+      </c>
+      <c r="AD5">
+        <v>114.4</v>
+      </c>
+      <c r="AE5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>723.5</v>
-      </c>
-      <c r="V5">
-        <v>0.1214578297072254</v>
-      </c>
-      <c r="W5">
-        <v>0.4646084939614493</v>
-      </c>
-      <c r="X5">
-        <v>0.08088185475990441</v>
-      </c>
-      <c r="Y5">
-        <v>0.3837266392015449</v>
-      </c>
-      <c r="Z5">
-        <v>1.297775556537307</v>
-      </c>
-      <c r="AA5">
-        <v>0.4536387145971971</v>
-      </c>
-      <c r="AB5">
-        <v>0.07929773713241754</v>
-      </c>
-      <c r="AC5">
-        <v>0.3743409774647796</v>
-      </c>
-      <c r="AD5">
-        <v>199.8</v>
-      </c>
-      <c r="AE5">
-        <v>15.52821774460456</v>
-      </c>
       <c r="AF5">
-        <v>215.3282177446046</v>
+        <v>114.4</v>
       </c>
       <c r="AG5">
-        <v>-508.1717822553954</v>
+        <v>-229.1</v>
       </c>
       <c r="AH5">
-        <v>0.03488719128120915</v>
+        <v>0.196969696969697</v>
       </c>
       <c r="AI5">
-        <v>0.1338000635112063</v>
+        <v>0.2750661216638615</v>
       </c>
       <c r="AJ5">
-        <v>-0.0932660042027509</v>
+        <v>-0.9654445849136115</v>
       </c>
       <c r="AK5">
-        <v>-0.5736685421347774</v>
+        <v>-3.164364640883977</v>
       </c>
       <c r="AL5">
-        <v>8</v>
+        <v>6.54</v>
       </c>
       <c r="AM5">
-        <v>8</v>
+        <v>6.54</v>
       </c>
       <c r="AN5">
-        <v>0.2703470671808403</v>
+        <v>1.048579285059579</v>
       </c>
       <c r="AO5">
-        <v>90.125</v>
+        <v>15.56574923547401</v>
       </c>
       <c r="AP5">
-        <v>-0.6876013561401737</v>
+        <v>-2.099908340971586</v>
       </c>
       <c r="AQ5">
-        <v>90.125</v>
+        <v>15.56574923547401</v>
       </c>
     </row>
     <row r="6">
@@ -1118,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erie Indemnity Company (NasdaqGS:ERIE)</t>
+          <t>Tiptree Inc. (NasdaqCM:TIPT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1127,121 +1121,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.107</v>
+        <v>0.205</v>
       </c>
       <c r="E6">
-        <v>0.0646</v>
+        <v>-0.251</v>
       </c>
       <c r="G6">
-        <v>0.1265403185126468</v>
+        <v>0.06504781077000504</v>
       </c>
       <c r="H6">
-        <v>0.1265403185126468</v>
+        <v>0.06504781077000504</v>
       </c>
       <c r="I6">
-        <v>0.1297470634863443</v>
+        <v>0.07535560363626731</v>
       </c>
       <c r="J6">
-        <v>0.1026080949503591</v>
+        <v>0.03767780181813365</v>
       </c>
       <c r="K6">
-        <v>288.1</v>
+        <v>7.95</v>
       </c>
       <c r="L6">
-        <v>0.1038048569575557</v>
+        <v>0.005001258178158028</v>
       </c>
       <c r="M6">
-        <v>203.3</v>
+        <v>13.473</v>
       </c>
       <c r="N6">
-        <v>0.0156318480642805</v>
+        <v>0.01933553386911596</v>
       </c>
       <c r="O6">
-        <v>0.7056577577230129</v>
+        <v>1.694716981132075</v>
       </c>
       <c r="P6">
-        <v>203.3</v>
+        <v>13.4</v>
       </c>
       <c r="Q6">
-        <v>0.0156318480642805</v>
+        <v>0.01923076923076923</v>
       </c>
       <c r="R6">
-        <v>0.7056577577230129</v>
+        <v>1.685534591194969</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.0730000000000004</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.005418243895197832</v>
       </c>
       <c r="U6">
-        <v>97.7</v>
+        <v>514.7</v>
       </c>
       <c r="V6">
-        <v>0.007512206374226289</v>
+        <v>0.7386624569460392</v>
       </c>
       <c r="W6">
-        <v>0.2238713186727795</v>
+        <v>0.02052672347017816</v>
       </c>
       <c r="X6">
-        <v>0.07977107850664222</v>
+        <v>0.08261670983013009</v>
       </c>
       <c r="Y6">
-        <v>0.1441002401661373</v>
+        <v>-0.06208998635995193</v>
       </c>
       <c r="Z6">
-        <v>2.423506811037373</v>
+        <v>34.021305732188</v>
       </c>
       <c r="AA6">
-        <v>0.2486714169797647</v>
+        <v>1.281848014971514</v>
       </c>
       <c r="AB6">
-        <v>0.07977107850664222</v>
+        <v>0.06449542345007928</v>
       </c>
       <c r="AC6">
-        <v>0.1689003384731224</v>
+        <v>1.217352591521435</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>357.6</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>53.52366229894751</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>411.1236622989475</v>
       </c>
       <c r="AG6">
-        <v>-97.7</v>
+        <v>-103.5763377010525</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.3710758026828886</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.4306205853419128</v>
       </c>
       <c r="AJ6">
-        <v>-0.007569066765831513</v>
+        <v>-0.1745991339921579</v>
       </c>
       <c r="AK6">
-        <v>-0.07760743506235604</v>
+        <v>-0.2353881088119389</v>
       </c>
       <c r="AL6">
-        <v>3.06</v>
+        <v>25.6</v>
       </c>
       <c r="AM6">
-        <v>-34.14</v>
+        <v>25.6</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>2.33283319198904</v>
       </c>
       <c r="AO6">
-        <v>117.6797385620915</v>
+        <v>4.7265625</v>
       </c>
       <c r="AP6">
-        <v>-0.238700219887613</v>
+        <v>-0.6756888101053722</v>
       </c>
       <c r="AQ6">
-        <v>-10.5477445811365</v>
+        <v>4.7265625</v>
       </c>
     </row>
     <row r="7">
@@ -1252,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Financial Group, Inc. (NYSE:AFG)</t>
+          <t>Kinsale Capital Group, Inc. (NYSE:KNSL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1261,121 +1255,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.00199</v>
+        <v>0.385</v>
       </c>
       <c r="E7">
-        <v>0.0708</v>
+        <v>0.505</v>
       </c>
       <c r="G7">
-        <v>0.2429277054333184</v>
+        <v>0.1838642345040385</v>
       </c>
       <c r="H7">
-        <v>0.2429277054333184</v>
+        <v>0.1838642345040385</v>
       </c>
       <c r="I7">
-        <v>0.1995252945301436</v>
+        <v>0.3158181323169071</v>
       </c>
       <c r="J7">
-        <v>0.1595222690310559</v>
+        <v>0.2539809233273205</v>
       </c>
       <c r="K7">
-        <v>977</v>
+        <v>272</v>
       </c>
       <c r="L7">
-        <v>0.1462355934740308</v>
+        <v>0.2468463562936745</v>
       </c>
       <c r="M7">
-        <v>2282</v>
+        <v>16.97</v>
       </c>
       <c r="N7">
-        <v>0.1952346323309236</v>
+        <v>0.002186573895116609</v>
       </c>
       <c r="O7">
-        <v>2.335721596724667</v>
+        <v>0.06238970588235294</v>
       </c>
       <c r="P7">
-        <v>2271</v>
+        <v>12.7</v>
       </c>
       <c r="Q7">
-        <v>0.1942935363819139</v>
+        <v>0.001636387063522742</v>
       </c>
       <c r="R7">
-        <v>2.32446264073695</v>
+        <v>0.04669117647058824</v>
       </c>
       <c r="S7">
-        <v>11</v>
+        <v>4.27</v>
       </c>
       <c r="T7">
-        <v>0.004820333041191937</v>
+        <v>0.2516205067766647</v>
       </c>
       <c r="U7">
-        <v>794</v>
+        <v>162.9</v>
       </c>
       <c r="V7">
-        <v>0.06793001668306455</v>
+        <v>0.02098956320061848</v>
       </c>
       <c r="W7">
-        <v>0.1864503816793893</v>
+        <v>0.4390637610976594</v>
       </c>
       <c r="X7">
-        <v>0.08423989378875284</v>
+        <v>0.06971479319675931</v>
       </c>
       <c r="Y7">
-        <v>0.1022104878906365</v>
+        <v>0.3693489679009</v>
       </c>
       <c r="Z7">
-        <v>1.544790769186458</v>
+        <v>1.78734793187348</v>
       </c>
       <c r="AA7">
-        <v>0.246428528678854</v>
+        <v>0.453952278044403</v>
       </c>
       <c r="AB7">
-        <v>0.0780484418510862</v>
+        <v>0.06888350714304313</v>
       </c>
       <c r="AC7">
-        <v>0.1683800868277678</v>
+        <v>0.3850687709013598</v>
       </c>
       <c r="AD7">
-        <v>1570</v>
+        <v>183.8</v>
       </c>
       <c r="AE7">
-        <v>129.8575362205534</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>1699.857536220553</v>
+        <v>183.8</v>
       </c>
       <c r="AG7">
-        <v>905.8575362205534</v>
+        <v>20.90000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.126965352667181</v>
+        <v>0.02313462893968382</v>
       </c>
       <c r="AI7">
-        <v>0.3018289303818753</v>
+        <v>0.1659443842542434</v>
       </c>
       <c r="AJ7">
-        <v>0.07192566461729913</v>
+        <v>0.002685719425847159</v>
       </c>
       <c r="AK7">
-        <v>0.1872435327908044</v>
+        <v>0.02212342542606119</v>
       </c>
       <c r="AL7">
-        <v>88</v>
+        <v>9.85</v>
       </c>
       <c r="AM7">
-        <v>88</v>
+        <v>9.85</v>
       </c>
       <c r="AN7">
-        <v>1.072404371584699</v>
+        <v>0.5236467236467237</v>
       </c>
       <c r="AO7">
-        <v>15.01136363636364</v>
+        <v>35.32994923857868</v>
       </c>
       <c r="AP7">
-        <v>0.6187551476916348</v>
+        <v>0.05954415954415956</v>
       </c>
       <c r="AQ7">
-        <v>15.01136363636364</v>
+        <v>35.32994923857868</v>
       </c>
     </row>
     <row r="8">
@@ -1386,7 +1380,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kinsale Capital Group, Inc. (NYSE:KNSL)</t>
+          <t>Fidelity National Financial, Inc. (NYSE:FNF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,121 +1389,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.339</v>
+        <v>0.068</v>
       </c>
       <c r="E8">
-        <v>0.402</v>
+        <v>-0.124</v>
       </c>
       <c r="G8">
-        <v>0.2515135561989997</v>
+        <v>0.1965381445187288</v>
       </c>
       <c r="H8">
-        <v>0.2515135561989997</v>
+        <v>0.1965381445187288</v>
       </c>
       <c r="I8">
-        <v>0.2276914977625691</v>
+        <v>0.09111661594745681</v>
       </c>
       <c r="J8">
-        <v>0.1861361398618787</v>
+        <v>0.06925449714524898</v>
       </c>
       <c r="K8">
-        <v>140.2</v>
+        <v>423</v>
       </c>
       <c r="L8">
-        <v>0.1845222426954462</v>
+        <v>0.03873981133803462</v>
       </c>
       <c r="M8">
-        <v>13.28</v>
+        <v>578</v>
       </c>
       <c r="N8">
-        <v>0.002200168988883182</v>
+        <v>0.04162615678225487</v>
       </c>
       <c r="O8">
-        <v>0.09472182596291014</v>
+        <v>1.366430260047281</v>
       </c>
       <c r="P8">
-        <v>10</v>
+        <v>490</v>
       </c>
       <c r="Q8">
-        <v>0.001656753756689143</v>
+        <v>0.03528861042094271</v>
       </c>
       <c r="R8">
-        <v>0.07132667617689016</v>
+        <v>1.15839243498818</v>
       </c>
       <c r="S8">
-        <v>3.279999999999999</v>
+        <v>88</v>
       </c>
       <c r="T8">
-        <v>0.2469879518072289</v>
+        <v>0.1522491349480969</v>
       </c>
       <c r="U8">
-        <v>126.2</v>
+        <v>2813</v>
       </c>
       <c r="V8">
-        <v>0.02090823240941699</v>
+        <v>0.2025854308451262</v>
       </c>
       <c r="W8">
-        <v>0.2126820388349514</v>
+        <v>0.0740546218487395</v>
       </c>
       <c r="X8">
-        <v>0.08039828035790116</v>
+        <v>0.07592084596010071</v>
       </c>
       <c r="Y8">
-        <v>0.1322837584770503</v>
+        <v>-0.001866224111361212</v>
       </c>
       <c r="Z8">
-        <v>1.24170616113744</v>
+        <v>5.089284212635008</v>
       </c>
       <c r="AA8">
-        <v>0.231126391676835</v>
+        <v>0.3524558189752919</v>
       </c>
       <c r="AB8">
-        <v>0.07949968346223565</v>
+        <v>0.06629410491419298</v>
       </c>
       <c r="AC8">
-        <v>0.1516267082145994</v>
+        <v>0.2861617140610989</v>
       </c>
       <c r="AD8">
-        <v>123.2</v>
+        <v>3711</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>400.4883523485952</v>
       </c>
       <c r="AF8">
-        <v>123.2</v>
+        <v>4111.488352348595</v>
       </c>
       <c r="AG8">
-        <v>-3</v>
+        <v>1298.488352348595</v>
       </c>
       <c r="AH8">
-        <v>0.02000292250491143</v>
+        <v>0.2284542431129622</v>
       </c>
       <c r="AI8">
-        <v>0.1658812441093308</v>
+        <v>0.3844133355019515</v>
       </c>
       <c r="AJ8">
-        <v>-0.0004972732848215619</v>
+        <v>0.085516948657811</v>
       </c>
       <c r="AK8">
-        <v>-0.004866180048661801</v>
+        <v>0.1647307670250739</v>
       </c>
       <c r="AL8">
-        <v>1.55</v>
+        <v>155</v>
       </c>
       <c r="AM8">
-        <v>1.55</v>
+        <v>155</v>
       </c>
       <c r="AN8">
-        <v>0.7003979533826038</v>
+        <v>2.251820388349515</v>
       </c>
       <c r="AO8">
-        <v>111.6129032258064</v>
+        <v>5.987096774193549</v>
       </c>
       <c r="AP8">
-        <v>-0.01705514496873223</v>
+        <v>0.7879176895319144</v>
       </c>
       <c r="AQ8">
-        <v>111.6129032258064</v>
+        <v>5.987096774193549</v>
       </c>
     </row>
     <row r="9">
@@ -1520,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Investors Title Company (NasdaqGS:ITIC)</t>
+          <t>RLI Corp. (NYSE:RLI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1529,115 +1523,121 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.141</v>
+        <v>0.11</v>
       </c>
       <c r="E9">
-        <v>0.108</v>
+        <v>0.152</v>
       </c>
       <c r="G9">
-        <v>0.2699902881191324</v>
+        <v>0.5051073587658954</v>
       </c>
       <c r="H9">
-        <v>0.2699902881191324</v>
+        <v>0.5051073587658954</v>
       </c>
       <c r="I9">
-        <v>0.1469887548193473</v>
+        <v>0.2395091276744503</v>
       </c>
       <c r="J9">
-        <v>0.1159468343384829</v>
+        <v>0.1981907042688522</v>
       </c>
       <c r="K9">
-        <v>35.3</v>
+        <v>287.8</v>
       </c>
       <c r="L9">
-        <v>0.1142764648753642</v>
+        <v>0.1999861024251268</v>
       </c>
       <c r="M9">
-        <v>3.576</v>
+        <v>49.2</v>
       </c>
       <c r="N9">
-        <v>0.01277599142550911</v>
+        <v>0.00810049887218664</v>
       </c>
       <c r="O9">
-        <v>0.1013031161473088</v>
+        <v>0.1709520500347463</v>
       </c>
       <c r="P9">
-        <v>3.49</v>
+        <v>48.4</v>
       </c>
       <c r="Q9">
-        <v>0.01246873883529832</v>
+        <v>0.007968783443370597</v>
       </c>
       <c r="R9">
-        <v>0.09886685552407934</v>
+        <v>0.1681723419041</v>
       </c>
       <c r="S9">
-        <v>0.08599999999999985</v>
+        <v>0.7999999999999972</v>
       </c>
       <c r="T9">
-        <v>0.02404921700223709</v>
+        <v>0.01626016260162596</v>
       </c>
       <c r="U9">
-        <v>41.4</v>
+        <v>18.4</v>
       </c>
       <c r="V9">
-        <v>0.1479099678456592</v>
+        <v>0.003029454862768987</v>
       </c>
       <c r="W9">
-        <v>0.1439054219323277</v>
+        <v>0.2064562410329986</v>
       </c>
       <c r="X9">
-        <v>0.08033381255723088</v>
+        <v>0.06960103626225839</v>
       </c>
       <c r="Y9">
-        <v>0.06357160937509687</v>
+        <v>0.1368552047707402</v>
       </c>
       <c r="Z9">
-        <v>1.563450045003499</v>
+        <v>1.717893353113585</v>
       </c>
       <c r="AA9">
-        <v>0.1812770833645143</v>
+        <v>0.3404704935123614</v>
       </c>
       <c r="AB9">
-        <v>0.07952707750046276</v>
+        <v>0.06894389624645515</v>
       </c>
       <c r="AC9">
-        <v>0.1017500058640515</v>
+        <v>0.2715265972659063</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE9">
-        <v>5.125868181518174</v>
+        <v>13.5120718184933</v>
       </c>
       <c r="AF9">
-        <v>5.125868181518174</v>
+        <v>113.5120718184933</v>
       </c>
       <c r="AG9">
-        <v>-36.27413181848183</v>
+        <v>95.11207181849329</v>
       </c>
       <c r="AH9">
-        <v>0.01798387007544794</v>
+        <v>0.01834623906549413</v>
       </c>
       <c r="AI9">
-        <v>0.02099682520209972</v>
+        <v>0.08035615303242183</v>
       </c>
       <c r="AJ9">
-        <v>-0.1488927759980524</v>
+        <v>0.01541821516220308</v>
       </c>
       <c r="AK9">
-        <v>-0.1789319347543868</v>
+        <v>0.06821922843806472</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>7.94</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>7.94</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.2810725729383327</v>
+      </c>
+      <c r="AO9">
+        <v>43.04785894206549</v>
       </c>
       <c r="AP9">
-        <v>-0.7279576925242189</v>
+        <v>0.267333947435194</v>
+      </c>
+      <c r="AQ9">
+        <v>43.04785894206549</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation (NYSE:WRB)</t>
+          <t>Erie Indemnity Company (NasdaqGS:ERIE)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1657,124 +1657,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.068</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="E10">
-        <v>0.188</v>
-      </c>
-      <c r="F10">
-        <v>0.21</v>
+        <v>0.092</v>
       </c>
       <c r="G10">
-        <v>0.1440326533655145</v>
+        <v>0.1359180177036073</v>
       </c>
       <c r="H10">
-        <v>0.1440326533655145</v>
+        <v>0.1359180177036073</v>
       </c>
       <c r="I10">
-        <v>0.1532279447045706</v>
+        <v>0.1587931089184302</v>
       </c>
       <c r="J10">
-        <v>0.1245583135943602</v>
+        <v>0.1262153163347681</v>
       </c>
       <c r="K10">
-        <v>1293.3</v>
+        <v>400.6</v>
       </c>
       <c r="L10">
-        <v>0.1205211119291019</v>
+        <v>0.1270979409245217</v>
       </c>
       <c r="M10">
-        <v>122.87</v>
+        <v>217.9</v>
       </c>
       <c r="N10">
-        <v>0.006377688730171914</v>
+        <v>0.01244225685066437</v>
       </c>
       <c r="O10">
-        <v>0.09500502590272945</v>
+        <v>0.5439340988517224</v>
       </c>
       <c r="P10">
-        <v>116.3</v>
+        <v>217.9</v>
       </c>
       <c r="Q10">
-        <v>0.006036666389834732</v>
+        <v>0.01244225685066437</v>
       </c>
       <c r="R10">
-        <v>0.08992499806696048</v>
+        <v>0.5439340988517224</v>
       </c>
       <c r="S10">
-        <v>6.570000000000007</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.05347114836819408</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>1130.8</v>
+        <v>102.9</v>
       </c>
       <c r="V10">
-        <v>0.05869529108878</v>
+        <v>0.00587566879271851</v>
       </c>
       <c r="W10">
-        <v>0.1945280067384634</v>
+        <v>0.295297066194899</v>
       </c>
       <c r="X10">
-        <v>0.08463040423811169</v>
+        <v>0.06917527108377156</v>
       </c>
       <c r="Y10">
-        <v>0.1098976025003517</v>
+        <v>0.2261217951111275</v>
       </c>
       <c r="Z10">
-        <v>1.361801222880259</v>
+        <v>2.503693700849949</v>
       </c>
       <c r="AA10">
-        <v>0.1696236637727025</v>
+        <v>0.3160044924581425</v>
       </c>
       <c r="AB10">
-        <v>0.07791846276566047</v>
+        <v>0.06917527108377156</v>
       </c>
       <c r="AC10">
-        <v>0.09170520100704205</v>
+        <v>0.2468292213743709</v>
       </c>
       <c r="AD10">
-        <v>2842.5</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>204.1312408486151</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>3046.631240848615</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1915.831240848615</v>
+        <v>-102.9</v>
       </c>
       <c r="AH10">
-        <v>0.1365453417886297</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.3235372781332421</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.0904486207312523</v>
+        <v>-0.005910396323951752</v>
       </c>
       <c r="AK10">
-        <v>0.231217748124496</v>
+        <v>-0.06819085487077535</v>
       </c>
       <c r="AL10">
-        <v>135.8</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>135.8</v>
+        <v>-34.3</v>
       </c>
       <c r="AN10">
-        <v>1.615515771526002</v>
-      </c>
-      <c r="AO10">
-        <v>12.07731958762886</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.088849810087306</v>
+        <v>-0.1859414528370076</v>
       </c>
       <c r="AQ10">
-        <v>12.07731958762886</v>
+        <v>-14.59183673469388</v>
       </c>
     </row>
     <row r="11">
@@ -1785,7 +1779,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc. (NasdaqGS:PLMR)</t>
+          <t>AMERISAFE, Inc. (NasdaqGS:AMSF)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1793,119 +1787,119 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="E11">
+        <v>0.0356</v>
+      </c>
       <c r="F11">
-        <v>1.192</v>
+        <v>0.1</v>
       </c>
       <c r="G11">
-        <v>0.1880616174582798</v>
+        <v>0.2250489236790607</v>
       </c>
       <c r="H11">
-        <v>0.1880616174582798</v>
+        <v>0.2250489236790607</v>
       </c>
       <c r="I11">
-        <v>0.208588954202991</v>
+        <v>0.2582227550960651</v>
       </c>
       <c r="J11">
-        <v>0.1632860407120289</v>
+        <v>0.2079492983516984</v>
       </c>
       <c r="K11">
-        <v>50</v>
+        <v>63.7</v>
       </c>
       <c r="L11">
-        <v>0.1604621309370988</v>
+        <v>0.2077625570776256</v>
       </c>
       <c r="M11">
-        <v>23.3</v>
+        <v>103.3</v>
       </c>
       <c r="N11">
-        <v>0.02044756472136902</v>
+        <v>0.1151873327386262</v>
       </c>
       <c r="O11">
-        <v>0.466</v>
+        <v>1.621664050235479</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>102.2</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.1139607493309545</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>1.604395604395604</v>
       </c>
       <c r="S11">
-        <v>23.3</v>
+        <v>1.099999999999994</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.01064859632139394</v>
       </c>
       <c r="U11">
-        <v>29.5</v>
+        <v>59.2</v>
       </c>
       <c r="V11">
-        <v>0.02588854760860026</v>
+        <v>0.06601248884924175</v>
       </c>
       <c r="W11">
-        <v>0.1323451561672843</v>
+        <v>0.1707774798927614</v>
       </c>
       <c r="X11">
-        <v>0.08053796242644531</v>
+        <v>0.0691779261198405</v>
       </c>
       <c r="Y11">
-        <v>0.05180719374083895</v>
+        <v>0.1015995537729209</v>
       </c>
       <c r="Z11">
-        <v>0.9206992805481284</v>
+        <v>1.086831235003197</v>
       </c>
       <c r="AA11">
-        <v>0.1503373402071174</v>
+        <v>0.2260057927456246</v>
       </c>
       <c r="AB11">
-        <v>0.07958133051064149</v>
+        <v>0.06917380145560773</v>
       </c>
       <c r="AC11">
-        <v>0.07075600969647593</v>
+        <v>0.1568319912900168</v>
       </c>
       <c r="AD11">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>2.038409351739969</v>
+        <v>0.1045164377321857</v>
       </c>
       <c r="AF11">
-        <v>28.43840935173997</v>
+        <v>0.1045164377321857</v>
       </c>
       <c r="AG11">
-        <v>-1.061590648260033</v>
+        <v>-59.09548356226782</v>
       </c>
       <c r="AH11">
-        <v>0.02434923718924922</v>
+        <v>0.0001165301721829849</v>
       </c>
       <c r="AI11">
-        <v>0.07177095576944752</v>
+        <v>0.0003110566454292127</v>
       </c>
       <c r="AJ11">
-        <v>-0.0009324972168362922</v>
+        <v>-0.07054454452933641</v>
       </c>
       <c r="AK11">
-        <v>-0.002894680843865083</v>
+        <v>-0.2134917606214763</v>
       </c>
       <c r="AL11">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.515</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>0.3934191702432046</v>
-      </c>
-      <c r="AO11">
-        <v>125.2427184466019</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>-0.01582007999910636</v>
-      </c>
-      <c r="AQ11">
-        <v>125.2427184466019</v>
+        <v>-0.7332673660198011</v>
       </c>
     </row>
     <row r="12">
@@ -1916,7 +1910,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>First American Financial Corporation (NYSE:FAF)</t>
+          <t>Markel Group Inc. (NYSE:MKL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1925,121 +1919,121 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0741</v>
+        <v>0.156</v>
       </c>
       <c r="E12">
-        <v>0.106</v>
+        <v>0.127</v>
       </c>
       <c r="G12">
-        <v>0.2250784455708424</v>
+        <v>0.0230290334961846</v>
       </c>
       <c r="H12">
-        <v>0.2250784455708424</v>
+        <v>0.0230290334961846</v>
       </c>
       <c r="I12">
-        <v>0.08605628708355248</v>
+        <v>0.190415875735048</v>
       </c>
       <c r="J12">
-        <v>0.06758497088758197</v>
+        <v>0.1506787907651204</v>
       </c>
       <c r="K12">
-        <v>469</v>
+        <v>1920.6</v>
       </c>
       <c r="L12">
-        <v>0.05660149650012068</v>
+        <v>0.1249422647818422</v>
       </c>
       <c r="M12">
-        <v>647</v>
+        <v>352.3</v>
       </c>
       <c r="N12">
-        <v>0.1193859098793224</v>
+        <v>0.01877031274974693</v>
       </c>
       <c r="O12">
-        <v>1.37953091684435</v>
+        <v>0.1834322607518484</v>
       </c>
       <c r="P12">
-        <v>220</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.04059489980440639</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4690831556503198</v>
+        <v>-0</v>
       </c>
       <c r="S12">
-        <v>427</v>
+        <v>352.3</v>
       </c>
       <c r="T12">
-        <v>0.6599690880989181</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>2361</v>
+        <v>4354.9</v>
       </c>
       <c r="V12">
-        <v>0.4356570838100159</v>
+        <v>0.2320262134370504</v>
       </c>
       <c r="W12">
-        <v>0.08379339300709296</v>
+        <v>0.1641257904631687</v>
       </c>
       <c r="X12">
-        <v>0.09251559855179675</v>
+        <v>0.07440415535716313</v>
       </c>
       <c r="Y12">
-        <v>-0.008722205544703793</v>
+        <v>0.08972163510600556</v>
       </c>
       <c r="Z12">
-        <v>1.752171913783354</v>
+        <v>1.44666752824163</v>
       </c>
       <c r="AA12">
-        <v>0.1184204877830868</v>
+        <v>0.2179821137946146</v>
       </c>
       <c r="AB12">
-        <v>0.07579354319894951</v>
+        <v>0.06682098212965569</v>
       </c>
       <c r="AC12">
-        <v>0.04262694458413725</v>
+        <v>0.1511611316649589</v>
       </c>
       <c r="AD12">
-        <v>1988</v>
+        <v>3769.2</v>
       </c>
       <c r="AE12">
-        <v>259.6880261284208</v>
+        <v>538.7309989420769</v>
       </c>
       <c r="AF12">
-        <v>2247.688026128421</v>
+        <v>4307.930998942076</v>
       </c>
       <c r="AG12">
-        <v>-113.3119738715791</v>
+        <v>-46.96900105792338</v>
       </c>
       <c r="AH12">
-        <v>0.2931605869749503</v>
+        <v>0.1866769458702965</v>
       </c>
       <c r="AI12">
-        <v>0.3315815711631392</v>
+        <v>0.228773739794385</v>
       </c>
       <c r="AJ12">
-        <v>-0.02135508746059326</v>
+        <v>-0.002508755650526241</v>
       </c>
       <c r="AK12">
-        <v>-0.02564960975093653</v>
+        <v>-0.003244694553305207</v>
       </c>
       <c r="AL12">
-        <v>83</v>
+        <v>190.2</v>
       </c>
       <c r="AM12">
-        <v>83</v>
+        <v>190.2</v>
       </c>
       <c r="AN12">
-        <v>2.139935414424112</v>
+        <v>1.10549934007919</v>
       </c>
       <c r="AO12">
-        <v>8.156626506024097</v>
+        <v>15.42534174553102</v>
       </c>
       <c r="AP12">
-        <v>-0.1219719847917966</v>
+        <v>-0.01377592053319354</v>
       </c>
       <c r="AQ12">
-        <v>8.156626506024097</v>
+        <v>15.42534174553102</v>
       </c>
     </row>
     <row r="13">
@@ -2050,7 +2044,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
+          <t>American Financial Group, Inc. (NYSE:AFG)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2059,124 +2053,121 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0492</v>
+        <v>0.0062</v>
       </c>
       <c r="E13">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="F13">
-        <v>0.06269999999999999</v>
+        <v>0.0359</v>
       </c>
       <c r="G13">
-        <v>0.1563198102540059</v>
+        <v>0.1829402084476138</v>
       </c>
       <c r="H13">
-        <v>0.1563198102540059</v>
+        <v>0.1829402084476138</v>
       </c>
       <c r="I13">
-        <v>0.1213471476844822</v>
+        <v>0.1651642196730004</v>
       </c>
       <c r="J13">
-        <v>0.1013793944807374</v>
+        <v>0.1317961716025326</v>
       </c>
       <c r="K13">
-        <v>3356</v>
+        <v>865</v>
       </c>
       <c r="L13">
-        <v>0.09255633084199785</v>
+        <v>0.1186231486560614</v>
       </c>
       <c r="M13">
-        <v>3231</v>
+        <v>195</v>
       </c>
       <c r="N13">
-        <v>0.07353577102176258</v>
+        <v>0.0195777235625433</v>
       </c>
       <c r="O13">
-        <v>0.9627532777115614</v>
+        <v>0.2254335260115607</v>
       </c>
       <c r="P13">
-        <v>870</v>
+        <v>41</v>
       </c>
       <c r="Q13">
-        <v>0.01980071828812548</v>
+        <v>0.004116341877252693</v>
       </c>
       <c r="R13">
-        <v>0.2592371871275328</v>
+        <v>0.04739884393063584</v>
       </c>
       <c r="S13">
-        <v>2361</v>
+        <v>154</v>
       </c>
       <c r="T13">
-        <v>0.7307335190343547</v>
+        <v>0.7897435897435897</v>
       </c>
       <c r="U13">
-        <v>773</v>
+        <v>1221</v>
       </c>
       <c r="V13">
-        <v>0.01759305199623103</v>
+        <v>0.1225866690762327</v>
       </c>
       <c r="W13">
-        <v>0.1178619091100653</v>
+        <v>0.2199898270600203</v>
       </c>
       <c r="X13">
-        <v>0.08508366968583198</v>
+        <v>0.07290370626834819</v>
       </c>
       <c r="Y13">
-        <v>0.03277823942423334</v>
+        <v>0.1470861207916722</v>
       </c>
       <c r="Z13">
-        <v>1.160422837028855</v>
+        <v>1.593840570949146</v>
       </c>
       <c r="AA13">
-        <v>0.1176429645596048</v>
+        <v>0.2100620853958922</v>
       </c>
       <c r="AB13">
-        <v>0.07840128236204577</v>
+        <v>0.06740154000925354</v>
       </c>
       <c r="AC13">
-        <v>0.03924168219755905</v>
+        <v>0.1426605453866387</v>
       </c>
       <c r="AD13">
-        <v>7291</v>
+        <v>1517</v>
       </c>
       <c r="AE13">
-        <v>305.3688605417994</v>
+        <v>113.1125507224046</v>
       </c>
       <c r="AF13">
-        <v>7596.368860541799</v>
+        <v>1630.112550722405</v>
       </c>
       <c r="AG13">
-        <v>6823.368860541799</v>
+        <v>409.1125507224046</v>
       </c>
       <c r="AH13">
-        <v>0.1474045090568661</v>
+        <v>0.1406431862186651</v>
       </c>
       <c r="AI13">
-        <v>0.276207802282823</v>
+        <v>0.2905150335137254</v>
       </c>
       <c r="AJ13">
-        <v>0.134421035088611</v>
+        <v>0.03945378281761035</v>
       </c>
       <c r="AK13">
-        <v>0.2552760933541732</v>
+        <v>0.09318953580246687</v>
       </c>
       <c r="AL13">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AM13">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AN13">
-        <v>1.373587038432555</v>
+        <v>1.158899923605806</v>
       </c>
       <c r="AO13">
-        <v>12.44444444444444</v>
+        <v>15.46753246753247</v>
       </c>
       <c r="AP13">
-        <v>1.285487728059872</v>
+        <v>0.3125382358459928</v>
       </c>
       <c r="AQ13">
-        <v>12.44444444444444</v>
+        <v>15.46753246753247</v>
       </c>
     </row>
     <row r="14">
@@ -2187,7 +2178,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Old Republic International Corporation (NYSE:ORI)</t>
+          <t>Palomar Holdings, Inc. (NasdaqGS:PLMR)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2195,122 +2186,119 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.06809999999999999</v>
-      </c>
-      <c r="E14">
-        <v>0.153</v>
+      <c r="F14">
+        <v>0.199</v>
       </c>
       <c r="G14">
-        <v>0.2370931703453249</v>
+        <v>0.1945991091314031</v>
       </c>
       <c r="H14">
-        <v>0.2370931703453249</v>
+        <v>0.1945991091314031</v>
       </c>
       <c r="I14">
-        <v>0.1270274176904367</v>
+        <v>0.2758114007262883</v>
       </c>
       <c r="J14">
-        <v>0.1020114950845329</v>
+        <v>0.2088865755500566</v>
       </c>
       <c r="K14">
-        <v>801.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="L14">
-        <v>0.09473086880962794</v>
+        <v>0.2007238307349666</v>
       </c>
       <c r="M14">
-        <v>366.1</v>
+        <v>33.3</v>
       </c>
       <c r="N14">
-        <v>0.05099453978159127</v>
+        <v>0.02426052746612269</v>
       </c>
       <c r="O14">
-        <v>0.4568825658305254</v>
+        <v>0.4618585298196949</v>
       </c>
       <c r="P14">
-        <v>261.3</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.03639681301537776</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.3260950954698615</v>
+        <v>-0</v>
       </c>
       <c r="S14">
-        <v>104.8</v>
+        <v>33.3</v>
       </c>
       <c r="T14">
-        <v>0.2862605845397432</v>
+        <v>1</v>
       </c>
       <c r="U14">
-        <v>102.4</v>
+        <v>53</v>
       </c>
       <c r="V14">
-        <v>0.01426342767996434</v>
+        <v>0.03861285152265773</v>
       </c>
       <c r="W14">
-        <v>0.1265996776945682</v>
+        <v>0.1960304513322458</v>
       </c>
       <c r="X14">
-        <v>0.08770725284284012</v>
+        <v>0.07008103093419686</v>
       </c>
       <c r="Y14">
-        <v>0.03889242485172809</v>
+        <v>0.1259494203980489</v>
       </c>
       <c r="Z14">
-        <v>1.051846086389647</v>
+        <v>0.9796201795212828</v>
       </c>
       <c r="AA14">
-        <v>0.1073003918714226</v>
+        <v>0.2046295046399324</v>
       </c>
       <c r="AB14">
-        <v>0.07698619232289282</v>
+        <v>0.06885970654275457</v>
       </c>
       <c r="AC14">
-        <v>0.03031419954852974</v>
+        <v>0.1357697980971779</v>
       </c>
       <c r="AD14">
-        <v>1596.6</v>
+        <v>52.6</v>
       </c>
       <c r="AE14">
-        <v>257.5659099095169</v>
+        <v>1.972724295586228</v>
       </c>
       <c r="AF14">
-        <v>1854.165909909517</v>
+        <v>54.57272429558623</v>
       </c>
       <c r="AG14">
-        <v>1751.765909909517</v>
+        <v>1.572724295586227</v>
       </c>
       <c r="AH14">
-        <v>0.2052574785967116</v>
+        <v>0.03823834590345176</v>
       </c>
       <c r="AI14">
-        <v>0.2461630978096723</v>
+        <v>0.1146792440696572</v>
       </c>
       <c r="AJ14">
-        <v>0.1961451793210646</v>
+        <v>0.001144488074737781</v>
       </c>
       <c r="AK14">
-        <v>0.2357735565016207</v>
+        <v>0.003719143385769424</v>
       </c>
       <c r="AL14">
-        <v>66.40000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AM14">
-        <v>66.40000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AN14">
-        <v>1.38425524536154</v>
+        <v>0.5199375284186387</v>
       </c>
       <c r="AO14">
-        <v>16.03012048192771</v>
+        <v>29.40298507462687</v>
       </c>
       <c r="AP14">
-        <v>1.518784385217199</v>
+        <v>0.01554597686560926</v>
       </c>
       <c r="AQ14">
-        <v>16.03012048192771</v>
+        <v>29.40298507462687</v>
       </c>
     </row>
     <row r="15">
@@ -2321,7 +2309,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMERISAFE, Inc. (NasdaqGS:AMSF)</t>
+          <t>Cincinnati Financial Corporation (NasdaqGS:CINF)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2330,118 +2318,124 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0499</v>
+        <v>0.0984</v>
       </c>
       <c r="E15">
-        <v>-0.09910000000000001</v>
+        <v>0.0392</v>
       </c>
       <c r="F15">
-        <v>0.05</v>
+        <v>0.182</v>
       </c>
       <c r="G15">
-        <v>0.2744630071599045</v>
+        <v>-0.05252918287937743</v>
       </c>
       <c r="H15">
-        <v>0.2744630071599045</v>
+        <v>-0.05252918287937743</v>
       </c>
       <c r="I15">
-        <v>0.1499624332379154</v>
+        <v>0.2178403276036816</v>
       </c>
       <c r="J15">
-        <v>0.1309694690282842</v>
+        <v>0.1758267639385549</v>
       </c>
       <c r="K15">
-        <v>38.4</v>
+        <v>1674</v>
       </c>
       <c r="L15">
-        <v>0.1309239686327992</v>
+        <v>0.1714110178169158</v>
       </c>
       <c r="M15">
-        <v>35.7</v>
+        <v>523</v>
       </c>
       <c r="N15">
-        <v>0.03587218649517685</v>
+        <v>0.0322169314450803</v>
       </c>
       <c r="O15">
-        <v>0.9296875000000001</v>
+        <v>0.3124253285543608</v>
       </c>
       <c r="P15">
-        <v>23.5</v>
+        <v>445</v>
       </c>
       <c r="Q15">
-        <v>0.02361334405144695</v>
+        <v>0.02741211184141631</v>
       </c>
       <c r="R15">
-        <v>0.6119791666666667</v>
+        <v>0.2658303464755077</v>
       </c>
       <c r="S15">
-        <v>12.2</v>
+        <v>78</v>
       </c>
       <c r="T15">
-        <v>0.3417366946778712</v>
+        <v>0.1491395793499044</v>
       </c>
       <c r="U15">
-        <v>91</v>
+        <v>899</v>
       </c>
       <c r="V15">
-        <v>0.09143890675241158</v>
+        <v>0.05537862594479386</v>
       </c>
       <c r="W15">
-        <v>0.07996668054977092</v>
+        <v>0.1774997349167639</v>
       </c>
       <c r="X15">
-        <v>0.07977694787474857</v>
+        <v>0.07033002162389763</v>
       </c>
       <c r="Y15">
-        <v>0.0001897326750223555</v>
+        <v>0.1071697132928662</v>
       </c>
       <c r="Z15">
-        <v>0.8209015778749892</v>
+        <v>1.062809031553555</v>
       </c>
       <c r="AA15">
-        <v>0.1075130437787681</v>
+        <v>0.186870272702731</v>
       </c>
       <c r="AB15">
-        <v>0.0797684874422683</v>
+        <v>0.06856685319157789</v>
       </c>
       <c r="AC15">
-        <v>0.02774455633649975</v>
+        <v>0.1183034195111532</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="AE15">
-        <v>0.1900916565970358</v>
+        <v>7.856803112228564</v>
       </c>
       <c r="AF15">
-        <v>0.1900916565970358</v>
+        <v>822.8568031122286</v>
       </c>
       <c r="AG15">
-        <v>-90.80990834340297</v>
+        <v>-76.14319688777141</v>
       </c>
       <c r="AH15">
-        <v>0.0001909720201058784</v>
+        <v>0.0482428436530687</v>
       </c>
       <c r="AI15">
-        <v>0.00050936951662681</v>
+        <v>0.0718849564789267</v>
       </c>
       <c r="AJ15">
-        <v>-0.1004101097315915</v>
+        <v>-0.004712543970330025</v>
       </c>
       <c r="AK15">
-        <v>-0.3218040286613303</v>
+        <v>-0.007218831115085366</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AN15">
-        <v>0</v>
+        <v>0.3635147190008921</v>
+      </c>
+      <c r="AO15">
+        <v>40.13207547169812</v>
       </c>
       <c r="AP15">
-        <v>-2.008091379050085</v>
+        <v>-0.03396217523986236</v>
+      </c>
+      <c r="AQ15">
+        <v>40.13207547169812</v>
       </c>
     </row>
     <row r="16">
@@ -2452,7 +2446,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trean Insurance Group, Inc. (NasdaqGS:TIG)</t>
+          <t>W. R. Berkley Corporation (NYSE:WRB)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2460,116 +2454,125 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.09230000000000001</v>
+      </c>
+      <c r="E16">
+        <v>0.156</v>
+      </c>
+      <c r="F16">
+        <v>0.17</v>
+      </c>
       <c r="G16">
-        <v>0.1121597096188748</v>
+        <v>0.1554200110595372</v>
       </c>
       <c r="H16">
-        <v>0.1121597096188748</v>
+        <v>0.1554200110595372</v>
       </c>
       <c r="I16">
-        <v>0.08158870902362893</v>
+        <v>0.1591211990661379</v>
       </c>
       <c r="J16">
-        <v>0.06442360673942925</v>
+        <v>0.1255987842940617</v>
       </c>
       <c r="K16">
-        <v>26.6</v>
+        <v>1366.2</v>
       </c>
       <c r="L16">
-        <v>0.09655172413793103</v>
+        <v>0.1144662097625551</v>
       </c>
       <c r="M16">
-        <v>0.023</v>
+        <v>625.9</v>
       </c>
       <c r="N16">
-        <v>7.484542792059876e-05</v>
+        <v>0.03432090235623769</v>
       </c>
       <c r="O16">
-        <v>0.0008646616541353383</v>
+        <v>0.4581320450885668</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>107.8</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.005911157172076088</v>
       </c>
       <c r="R16">
-        <v>-0</v>
+        <v>0.0789049919484702</v>
       </c>
       <c r="S16">
-        <v>0.023</v>
+        <v>518.1</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0.827768014059754</v>
       </c>
       <c r="U16">
-        <v>81.5</v>
+        <v>1646.1</v>
       </c>
       <c r="V16">
-        <v>0.2652131467621217</v>
+        <v>0.09026304101070917</v>
       </c>
       <c r="W16">
-        <v>0.06298839687426</v>
+        <v>0.2152818266336805</v>
       </c>
       <c r="X16">
-        <v>0.08799678114042855</v>
+        <v>0.07296490233047911</v>
       </c>
       <c r="Y16">
-        <v>-0.02500838426616855</v>
+        <v>0.1423169243032014</v>
       </c>
       <c r="Z16">
-        <v>1.521581997660034</v>
+        <v>1.476290309950687</v>
       </c>
       <c r="AA16">
-        <v>0.0980258002390452</v>
+        <v>0.1854202681949098</v>
       </c>
       <c r="AB16">
-        <v>0.08051696001039566</v>
+        <v>0.0673765793070905</v>
       </c>
       <c r="AC16">
-        <v>0.01750884022864954</v>
+        <v>0.1180436888878193</v>
       </c>
       <c r="AD16">
-        <v>77.5</v>
+        <v>2837</v>
       </c>
       <c r="AE16">
-        <v>4.761553319951138</v>
+        <v>196.6242033300905</v>
       </c>
       <c r="AF16">
-        <v>82.26155331995113</v>
+        <v>3033.62420333009</v>
       </c>
       <c r="AG16">
-        <v>0.7615533199511333</v>
+        <v>1387.524203330091</v>
       </c>
       <c r="AH16">
-        <v>0.2111644555754937</v>
+        <v>0.1426223772769361</v>
       </c>
       <c r="AI16">
-        <v>0.1694851039545033</v>
+        <v>0.3044730098930425</v>
       </c>
       <c r="AJ16">
-        <v>0.002472081672457802</v>
+        <v>0.07070466526236679</v>
       </c>
       <c r="AK16">
-        <v>0.001885679173198762</v>
+        <v>0.166821382366738</v>
       </c>
       <c r="AL16">
-        <v>2.22</v>
+        <v>127.5</v>
       </c>
       <c r="AM16">
-        <v>2.22</v>
+        <v>127.5</v>
       </c>
       <c r="AN16">
-        <v>2.563678465100893</v>
+        <v>1.453679032588645</v>
       </c>
       <c r="AO16">
-        <v>9.459459459459458</v>
+        <v>14.83529411764706</v>
       </c>
       <c r="AP16">
-        <v>0.02519197221141691</v>
+        <v>0.7109675155411409</v>
       </c>
       <c r="AQ16">
-        <v>9.459459459459458</v>
+        <v>14.83529411764706</v>
       </c>
     </row>
     <row r="17">
@@ -2580,7 +2583,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Hanover Insurance Group, Inc. (NYSE:THG)</t>
+          <t>Skyward Specialty Insurance Group, Inc. (NasdaqGS:SKWD)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2588,125 +2591,113 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D17">
-        <v>0.0392</v>
-      </c>
-      <c r="E17">
-        <v>0.192</v>
-      </c>
-      <c r="F17">
-        <v>0.161</v>
-      </c>
       <c r="G17">
-        <v>0.1065866924968333</v>
+        <v>0.07291414752116082</v>
       </c>
       <c r="H17">
-        <v>0.1065866924968333</v>
+        <v>0.07291414752116082</v>
       </c>
       <c r="I17">
-        <v>0.07404440801728635</v>
+        <v>0.1312519766748878</v>
       </c>
       <c r="J17">
-        <v>0.05937811537012096</v>
+        <v>0.1027363187983132</v>
       </c>
       <c r="K17">
-        <v>291.1</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="L17">
-        <v>0.05422472244989197</v>
+        <v>0.0932285368802902</v>
       </c>
       <c r="M17">
-        <v>157.5</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.03277494537509104</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.5410511851597389</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>106.7</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.02220372489855374</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.3665407076605977</v>
+        <v>-0</v>
       </c>
       <c r="S17">
-        <v>50.8</v>
-      </c>
-      <c r="T17">
-        <v>0.3225396825396825</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>164.8</v>
+        <v>53.7</v>
       </c>
       <c r="V17">
-        <v>0.03429403808136511</v>
+        <v>0.03979546465095598</v>
       </c>
       <c r="W17">
-        <v>0.09383360732359862</v>
+        <v>0.1928464232116058</v>
       </c>
       <c r="X17">
-        <v>0.08477278138998874</v>
+        <v>0.0714801429470103</v>
       </c>
       <c r="Y17">
-        <v>0.009060825933609878</v>
+        <v>0.1213662802645955</v>
       </c>
       <c r="Z17">
-        <v>1.519200837648923</v>
+        <v>1.635864555417118</v>
       </c>
       <c r="AA17">
-        <v>0.09020728260830216</v>
+        <v>0.1680627024761939</v>
       </c>
       <c r="AB17">
-        <v>0.07787178015455212</v>
+        <v>0.06860096082105425</v>
       </c>
       <c r="AC17">
-        <v>0.01233550245375004</v>
+        <v>0.09946174165513964</v>
       </c>
       <c r="AD17">
-        <v>782.2</v>
+        <v>128.7</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>7.823076449338978</v>
       </c>
       <c r="AF17">
-        <v>782.2</v>
+        <v>136.523076449339</v>
       </c>
       <c r="AG17">
-        <v>617.4000000000001</v>
+        <v>82.82307644933896</v>
       </c>
       <c r="AH17">
-        <v>0.1399860407681157</v>
+        <v>0.09187762045903831</v>
       </c>
       <c r="AI17">
-        <v>0.2541177999415223</v>
+        <v>0.2031825981789039</v>
       </c>
       <c r="AJ17">
-        <v>0.1138505227830128</v>
+        <v>0.05782833541173472</v>
       </c>
       <c r="AK17">
-        <v>0.2119246215631758</v>
+        <v>0.133969564716056</v>
       </c>
       <c r="AL17">
-        <v>34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AM17">
-        <v>34</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AN17">
-        <v>1.89900461277009</v>
+        <v>1.125885749278278</v>
       </c>
       <c r="AO17">
-        <v>11.69117647058824</v>
+        <v>11.50319829424307</v>
       </c>
       <c r="AP17">
-        <v>1.498907501820831</v>
+        <v>0.7245479524918115</v>
       </c>
       <c r="AQ17">
-        <v>11.69117647058824</v>
+        <v>11.50319829424307</v>
       </c>
     </row>
     <row r="18">
@@ -2717,7 +2708,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>United Fire Group, Inc. (NasdaqGS:UFCS)</t>
+          <t>The Hartford Financial Services Group, Inc. (NYSE:HIG)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2726,121 +2717,121 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.0141</v>
-      </c>
-      <c r="E18">
-        <v>0.253</v>
+        <v>0.0507</v>
+      </c>
+      <c r="F18">
+        <v>0.07000000000000001</v>
       </c>
       <c r="G18">
-        <v>0.1096031256426074</v>
+        <v>0.1243276789408358</v>
       </c>
       <c r="H18">
-        <v>0.1096031256426074</v>
+        <v>0.1243276789408358</v>
       </c>
       <c r="I18">
-        <v>0.06954082303996571</v>
+        <v>0.1283693480689792</v>
       </c>
       <c r="J18">
-        <v>0.05930693854721225</v>
+        <v>0.1038498629724994</v>
       </c>
       <c r="K18">
-        <v>52.6</v>
+        <v>2321</v>
       </c>
       <c r="L18">
-        <v>0.05408184248406334</v>
+        <v>0.09602813405047579</v>
       </c>
       <c r="M18">
-        <v>15.6</v>
+        <v>1932</v>
       </c>
       <c r="N18">
-        <v>0.0226283724978242</v>
+        <v>0.07991429481425717</v>
       </c>
       <c r="O18">
-        <v>0.2965779467680608</v>
+        <v>0.8323998276604911</v>
       </c>
       <c r="P18">
-        <v>15.6</v>
+        <v>522</v>
       </c>
       <c r="Q18">
-        <v>0.0226283724978242</v>
+        <v>0.02159175046223719</v>
       </c>
       <c r="R18">
-        <v>0.2965779467680608</v>
+        <v>0.2249030590262818</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>0.7298136645962733</v>
       </c>
       <c r="U18">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="V18">
-        <v>0.07687844502465913</v>
+        <v>0.00459134923622285</v>
       </c>
       <c r="W18">
-        <v>0.06457949662369553</v>
+        <v>0.1838998494572538</v>
       </c>
       <c r="X18">
-        <v>0.08323984626457742</v>
+        <v>0.0734039962301663</v>
       </c>
       <c r="Y18">
-        <v>-0.0186603496408819</v>
+        <v>0.1104958532270875</v>
       </c>
       <c r="Z18">
-        <v>1.28054058763148</v>
+        <v>1.573509901732149</v>
       </c>
       <c r="AA18">
-        <v>0.07594494193787128</v>
+        <v>0.1634087876807547</v>
       </c>
       <c r="AB18">
-        <v>0.07898062181608391</v>
+        <v>0.06720079861410758</v>
       </c>
       <c r="AC18">
-        <v>-0.003035679878212627</v>
+        <v>0.09620798906664713</v>
       </c>
       <c r="AD18">
-        <v>50</v>
+        <v>4361</v>
       </c>
       <c r="AE18">
-        <v>27.8229775566467</v>
+        <v>126.5642858638576</v>
       </c>
       <c r="AF18">
-        <v>77.82297755664669</v>
+        <v>4487.564285863858</v>
       </c>
       <c r="AG18">
-        <v>24.82297755664669</v>
+        <v>4376.564285863858</v>
       </c>
       <c r="AH18">
-        <v>0.1014346283064766</v>
+        <v>0.1565604297201793</v>
       </c>
       <c r="AI18">
-        <v>0.09994950033565492</v>
+        <v>0.2470232794296616</v>
       </c>
       <c r="AJ18">
-        <v>0.03475522117975814</v>
+        <v>0.1532814905938142</v>
       </c>
       <c r="AK18">
-        <v>0.03420919447759474</v>
+        <v>0.2423942124750084</v>
       </c>
       <c r="AL18">
-        <v>3.19</v>
+        <v>227</v>
       </c>
       <c r="AM18">
-        <v>3.19</v>
+        <v>227</v>
       </c>
       <c r="AN18">
-        <v>0.6024096385542169</v>
+        <v>1.222596019063639</v>
       </c>
       <c r="AO18">
-        <v>20.3448275862069</v>
+        <v>13.61674008810573</v>
       </c>
       <c r="AP18">
-        <v>0.2990720187547794</v>
+        <v>1.226959429734751</v>
       </c>
       <c r="AQ18">
-        <v>20.3448275862069</v>
+        <v>13.61674008810573</v>
       </c>
     </row>
     <row r="19">
@@ -2851,7 +2842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Selective Insurance Group, Inc. (NasdaqGS:SIGI)</t>
+          <t>FG Financial Group, Inc. (NasdaqGM:FGF)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2860,124 +2851,112 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.07519999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="E19">
-        <v>0.0593</v>
-      </c>
-      <c r="F19">
-        <v>0.06619999999999999</v>
+        <v>0.252</v>
       </c>
       <c r="G19">
-        <v>0.1696110024168489</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>0.1696110024168489</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>0.09299982307996543</v>
+        <v>0.1693379297516437</v>
       </c>
       <c r="J19">
-        <v>0.07451285183659734</v>
+        <v>0.1693379297516437</v>
       </c>
       <c r="K19">
-        <v>237.4</v>
+        <v>4.19</v>
       </c>
       <c r="L19">
-        <v>0.06830475313614916</v>
+        <v>0.1689516129032258</v>
       </c>
       <c r="M19">
-        <v>83.90000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.01570866878861637</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>0.3534119629317607</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>65.7</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.01230106721587718</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.2767481044650379</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>18.2</v>
-      </c>
-      <c r="T19">
-        <v>0.2169249106078665</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>0.538</v>
+        <v>5.53</v>
       </c>
       <c r="V19">
-        <v>0.0001007302003370156</v>
+        <v>0.3272189349112427</v>
       </c>
       <c r="W19">
-        <v>0.08721207890966534</v>
+        <v>0.2738562091503268</v>
       </c>
       <c r="X19">
-        <v>0.08293681966422747</v>
+        <v>0.06925223830574312</v>
       </c>
       <c r="Y19">
-        <v>0.004275259245437868</v>
+        <v>0.2046039708445837</v>
       </c>
       <c r="Z19">
-        <v>1.004589364446524</v>
+        <v>0.8823394410022469</v>
       </c>
       <c r="AA19">
-        <v>0.07485481846962531</v>
+        <v>0.1494135342775431</v>
       </c>
       <c r="AB19">
-        <v>0.07850383405883657</v>
+        <v>0.06914748363386905</v>
       </c>
       <c r="AC19">
-        <v>-0.003649015589211255</v>
+        <v>0.08026605064367401</v>
       </c>
       <c r="AD19">
-        <v>505.2</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>45.04907451636089</v>
+        <v>0.05709671079618284</v>
       </c>
       <c r="AF19">
-        <v>550.2490745163609</v>
+        <v>0.05709671079618284</v>
       </c>
       <c r="AG19">
-        <v>549.7110745163609</v>
+        <v>-5.472903289203817</v>
       </c>
       <c r="AH19">
-        <v>0.09340108821685379</v>
+        <v>0.003367127744210523</v>
       </c>
       <c r="AI19">
-        <v>0.184786918154187</v>
+        <v>0.001335373895528456</v>
       </c>
       <c r="AJ19">
-        <v>0.09331828832930722</v>
+        <v>-0.4789408392801195</v>
       </c>
       <c r="AK19">
-        <v>0.1846396042328506</v>
+        <v>-0.147013970273342</v>
       </c>
       <c r="AL19">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1.325845055637203</v>
-      </c>
-      <c r="AO19">
-        <v>11.28472222222222</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.442659758860909</v>
-      </c>
-      <c r="AQ19">
-        <v>11.28472222222222</v>
+        <v>-260.6144423430389</v>
       </c>
     </row>
     <row r="20">
@@ -2988,7 +2967,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CNA Financial Corporation (NYSE:CNA)</t>
+          <t>First American Financial Corporation (NYSE:FAF)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2997,124 +2976,121 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0451</v>
+        <v>0.0149</v>
       </c>
       <c r="E20">
-        <v>-0.00109</v>
-      </c>
-      <c r="F20">
-        <v>0.05</v>
+        <v>-0.171</v>
       </c>
       <c r="G20">
-        <v>0.1396548807308408</v>
+        <v>0.09362966750283605</v>
       </c>
       <c r="H20">
-        <v>0.1396548807308408</v>
+        <v>0.09362966750283605</v>
       </c>
       <c r="I20">
-        <v>0.1034868581368291</v>
+        <v>0.07310081703518938</v>
       </c>
       <c r="J20">
-        <v>0.08449419393087571</v>
+        <v>0.05855524629859557</v>
       </c>
       <c r="K20">
-        <v>912</v>
+        <v>237</v>
       </c>
       <c r="L20">
-        <v>0.07714430722382</v>
+        <v>0.03786728873408216</v>
       </c>
       <c r="M20">
-        <v>264.6</v>
+        <v>304.7</v>
       </c>
       <c r="N20">
-        <v>0.0231023102310231</v>
+        <v>0.04582644006617536</v>
       </c>
       <c r="O20">
-        <v>0.2901315789473685</v>
+        <v>1.285654008438819</v>
       </c>
       <c r="P20">
-        <v>225.6</v>
+        <v>215.4</v>
       </c>
       <c r="Q20">
-        <v>0.0196972078160197</v>
+        <v>0.0323958489998496</v>
       </c>
       <c r="R20">
-        <v>0.2473684210526316</v>
+        <v>0.908860759493671</v>
       </c>
       <c r="S20">
-        <v>39.00000000000003</v>
+        <v>89.29999999999998</v>
       </c>
       <c r="T20">
-        <v>0.1473922902494332</v>
+        <v>0.2930751558910403</v>
       </c>
       <c r="U20">
-        <v>503</v>
+        <v>1579.1</v>
       </c>
       <c r="V20">
-        <v>0.04391709012171058</v>
+        <v>0.2374943600541435</v>
       </c>
       <c r="W20">
-        <v>0.07201516108654453</v>
+        <v>0.0525732031943212</v>
       </c>
       <c r="X20">
-        <v>0.08786777572092243</v>
+        <v>0.07664124083524734</v>
       </c>
       <c r="Y20">
-        <v>-0.0158526146343779</v>
+        <v>-0.02406803764092614</v>
       </c>
       <c r="Z20">
-        <v>0.7930560002912364</v>
+        <v>2.425458263994407</v>
       </c>
       <c r="AA20">
-        <v>0.06700862748665234</v>
+        <v>0.1420233060351566</v>
       </c>
       <c r="AB20">
-        <v>0.076941610244011</v>
+        <v>0.06606235851279411</v>
       </c>
       <c r="AC20">
-        <v>-0.009932982757358655</v>
+        <v>0.07596094752236245</v>
       </c>
       <c r="AD20">
-        <v>2780</v>
+        <v>1922.6</v>
       </c>
       <c r="AE20">
-        <v>237.8918155320311</v>
+        <v>256.4195821093014</v>
       </c>
       <c r="AF20">
-        <v>3017.891815532031</v>
+        <v>2179.019582109301</v>
       </c>
       <c r="AG20">
-        <v>2514.891815532031</v>
+        <v>599.9195821093012</v>
       </c>
       <c r="AH20">
-        <v>0.2085433597775238</v>
+        <v>0.2468299443428129</v>
       </c>
       <c r="AI20">
-        <v>0.2715911804787073</v>
+        <v>0.3242096761493805</v>
       </c>
       <c r="AJ20">
-        <v>0.1800429035091892</v>
+        <v>0.08275986170269194</v>
       </c>
       <c r="AK20">
-        <v>0.2370550910746478</v>
+        <v>0.1166722996206806</v>
       </c>
       <c r="AL20">
-        <v>112</v>
+        <v>128.8</v>
       </c>
       <c r="AM20">
-        <v>112</v>
+        <v>128.8</v>
       </c>
       <c r="AN20">
-        <v>2.102874432677761</v>
+        <v>2.783552917330244</v>
       </c>
       <c r="AO20">
-        <v>10.97321428571429</v>
+        <v>3.282608695652174</v>
       </c>
       <c r="AP20">
-        <v>1.902338740947074</v>
+        <v>0.8685675142743611</v>
       </c>
       <c r="AQ20">
-        <v>10.97321428571429</v>
+        <v>3.282608695652174</v>
       </c>
     </row>
     <row r="21">
@@ -3125,7 +3101,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tiptree Inc. (NasdaqCM:TIPT)</t>
+          <t>The Progressive Corporation (NYSE:PGR)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3134,118 +3110,124 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.179</v>
+        <v>0.136</v>
+      </c>
+      <c r="E21">
+        <v>-0.013</v>
+      </c>
+      <c r="F21">
+        <v>0.401</v>
       </c>
       <c r="G21">
-        <v>0.09740308618742943</v>
+        <v>0.0294401429219214</v>
       </c>
       <c r="H21">
-        <v>0.09740308618742943</v>
+        <v>0.0294401429219214</v>
       </c>
       <c r="I21">
-        <v>0.04349661009611804</v>
+        <v>0.06359108005969151</v>
       </c>
       <c r="J21">
-        <v>0.02174830504805902</v>
+        <v>0.05088251706084027</v>
       </c>
       <c r="K21">
-        <v>-9.57</v>
+        <v>2741</v>
       </c>
       <c r="L21">
-        <v>-0.007203613097478359</v>
+        <v>0.0467257856102991</v>
       </c>
       <c r="M21">
-        <v>13.01</v>
+        <v>334.2</v>
       </c>
       <c r="N21">
-        <v>0.02593183177197528</v>
+        <v>0.00358688757543787</v>
       </c>
       <c r="O21">
-        <v>-1.359456635318704</v>
+        <v>0.1219263042685151</v>
       </c>
       <c r="P21">
-        <v>6.09</v>
+        <v>234</v>
       </c>
       <c r="Q21">
-        <v>0.01213872832369942</v>
+        <v>0.002511465268259909</v>
       </c>
       <c r="R21">
-        <v>-0.6363636363636364</v>
+        <v>0.08537030280919372</v>
       </c>
       <c r="S21">
-        <v>6.92</v>
+        <v>100.2</v>
       </c>
       <c r="T21">
-        <v>0.5318985395849347</v>
+        <v>0.2998204667863554</v>
       </c>
       <c r="U21">
-        <v>503.5</v>
+        <v>123.5</v>
       </c>
       <c r="V21">
-        <v>1.003587801474985</v>
+        <v>0.001325495558248285</v>
       </c>
       <c r="W21">
-        <v>-0.02484423676012461</v>
+        <v>0.1919158678924263</v>
       </c>
       <c r="X21">
-        <v>0.1001804922039535</v>
+        <v>0.07089120029924745</v>
       </c>
       <c r="Y21">
-        <v>-0.1250247289640781</v>
+        <v>0.1210246675931788</v>
       </c>
       <c r="Z21">
-        <v>2.570508718260785</v>
+        <v>2.831819554681899</v>
       </c>
       <c r="AA21">
-        <v>0.05590420773343074</v>
+        <v>0.1440901068043228</v>
       </c>
       <c r="AB21">
-        <v>0.07666093102367669</v>
+        <v>0.06829188864215309</v>
       </c>
       <c r="AC21">
-        <v>-0.02075672329024594</v>
+        <v>0.07579821816216974</v>
       </c>
       <c r="AD21">
-        <v>295.3</v>
+        <v>6887.6</v>
       </c>
       <c r="AE21">
-        <v>37.92376743653597</v>
+        <v>130.2910809320637</v>
       </c>
       <c r="AF21">
-        <v>333.223767436536</v>
+        <v>7017.891080932064</v>
       </c>
       <c r="AG21">
-        <v>-170.276232563464</v>
+        <v>6894.391080932064</v>
       </c>
       <c r="AH21">
-        <v>0.399106817212345</v>
+        <v>0.0700454105042972</v>
       </c>
       <c r="AI21">
-        <v>0.3907299258768996</v>
+        <v>0.2874630791880948</v>
       </c>
       <c r="AJ21">
-        <v>-0.5137719418269242</v>
+        <v>0.06889768660663906</v>
       </c>
       <c r="AK21">
-        <v>-0.4874453113024989</v>
+        <v>0.2838402126219016</v>
       </c>
       <c r="AL21">
-        <v>35.6</v>
+        <v>261.8</v>
       </c>
       <c r="AM21">
-        <v>35.6</v>
+        <v>261.8</v>
       </c>
       <c r="AN21">
-        <v>3.307942197826818</v>
+        <v>1.695033715607619</v>
       </c>
       <c r="AO21">
-        <v>1.603932584269663</v>
+        <v>14.08479755538579</v>
       </c>
       <c r="AP21">
-        <v>-1.907429512304963</v>
+        <v>1.696704996045692</v>
       </c>
       <c r="AQ21">
-        <v>1.603932584269663</v>
+        <v>14.08479755538579</v>
       </c>
     </row>
     <row r="22">
@@ -3256,7 +3238,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kingsway Financial Services Inc. (NYSE:KFS)</t>
+          <t>Employers Holdings, Inc. (NYSE:EIG)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3264,116 +3246,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D22">
+        <v>0.00601</v>
+      </c>
+      <c r="E22">
+        <v>-0.0404</v>
+      </c>
       <c r="G22">
-        <v>0.1162377994676131</v>
+        <v>0.07626918536009444</v>
       </c>
       <c r="H22">
-        <v>0.1162377994676131</v>
+        <v>0.07626918536009444</v>
       </c>
       <c r="I22">
-        <v>0.07704389032252755</v>
+        <v>0.1929966381749073</v>
       </c>
       <c r="J22">
-        <v>0.06914926946231793</v>
+        <v>0.1578823387532073</v>
       </c>
       <c r="K22">
-        <v>33.7</v>
+        <v>119.6</v>
       </c>
       <c r="L22">
-        <v>0.2990239574090506</v>
+        <v>0.1412042502951594</v>
       </c>
       <c r="M22">
-        <v>0.328</v>
+        <v>92.7</v>
       </c>
       <c r="N22">
-        <v>0.001725407680168333</v>
+        <v>0.09147424511545293</v>
       </c>
       <c r="O22">
-        <v>0.009732937685459941</v>
+        <v>0.7750836120401339</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>29.5</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.02910992697848826</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0.2466555183946488</v>
       </c>
       <c r="S22">
-        <v>0.328</v>
+        <v>63.2</v>
       </c>
       <c r="T22">
-        <v>1</v>
+        <v>0.6817691477885652</v>
       </c>
       <c r="U22">
-        <v>48.6</v>
+        <v>108.8</v>
       </c>
       <c r="V22">
-        <v>0.2556549184639664</v>
+        <v>0.1073613578054075</v>
       </c>
       <c r="W22">
-        <v>-4.970501474926253</v>
+        <v>0.1301414581066376</v>
       </c>
       <c r="X22">
-        <v>0.126008336301855</v>
+        <v>0.07037255037002928</v>
       </c>
       <c r="Y22">
-        <v>-5.096509811228109</v>
+        <v>0.05976890773660835</v>
       </c>
       <c r="Z22">
-        <v>0.7328853018259091</v>
+        <v>0.9104010214714883</v>
       </c>
       <c r="AA22">
-        <v>0.050678483220932</v>
+        <v>0.1437362424732275</v>
       </c>
       <c r="AB22">
-        <v>0.07162020677225467</v>
+        <v>0.06854556437191804</v>
       </c>
       <c r="AC22">
-        <v>-0.02094172355132267</v>
+        <v>0.07519067810130946</v>
       </c>
       <c r="AD22">
-        <v>283.6</v>
+        <v>40.6</v>
       </c>
       <c r="AE22">
-        <v>2.445767803255718</v>
+        <v>12.6592373292676</v>
       </c>
       <c r="AF22">
-        <v>286.0457678032557</v>
+        <v>53.2592373292676</v>
       </c>
       <c r="AG22">
-        <v>237.4457678032557</v>
+        <v>-55.5407626707324</v>
       </c>
       <c r="AH22">
-        <v>0.600752515606629</v>
+        <v>0.04993088276497715</v>
       </c>
       <c r="AI22">
-        <v>0.8537513238227991</v>
+        <v>0.0547788442468978</v>
       </c>
       <c r="AJ22">
-        <v>0.5553692392355091</v>
+        <v>-0.05798426376885277</v>
       </c>
       <c r="AK22">
-        <v>0.8289379508875987</v>
+        <v>-0.06432354912609817</v>
       </c>
       <c r="AL22">
-        <v>6.73</v>
+        <v>7.1</v>
       </c>
       <c r="AM22">
-        <v>6.73</v>
+        <v>7.1</v>
       </c>
       <c r="AN22">
-        <v>15.34465966886701</v>
+        <v>0.2375658279695728</v>
       </c>
       <c r="AO22">
-        <v>1.216939078751857</v>
+        <v>22.91549295774648</v>
       </c>
       <c r="AP22">
-        <v>12.84740654708667</v>
+        <v>-0.3249898342348297</v>
       </c>
       <c r="AQ22">
-        <v>1.216939078751857</v>
+        <v>22.91549295774648</v>
       </c>
     </row>
     <row r="23">
@@ -3384,7 +3372,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Safety Insurance Group, Inc. (NasdaqGS:SAFT)</t>
+          <t>CNA Financial Corporation (NYSE:CNA)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3393,121 +3381,124 @@
         </is>
       </c>
       <c r="D23">
-        <v>-0.00859</v>
+        <v>0.0486</v>
       </c>
       <c r="E23">
-        <v>-0.0305</v>
+        <v>0.0285</v>
+      </c>
+      <c r="F23">
+        <v>0.05</v>
       </c>
       <c r="G23">
-        <v>0.2153248056182593</v>
+        <v>0.09641168720452607</v>
       </c>
       <c r="H23">
-        <v>0.2153248056182593</v>
+        <v>0.09641168720452607</v>
       </c>
       <c r="I23">
-        <v>0.0861169086888393</v>
+        <v>0.1337356172531197</v>
       </c>
       <c r="J23">
-        <v>0.06816007897692272</v>
+        <v>0.1072047329846215</v>
       </c>
       <c r="K23">
-        <v>54</v>
+        <v>1289</v>
       </c>
       <c r="L23">
-        <v>0.06772009029345373</v>
+        <v>0.09989924823684415</v>
       </c>
       <c r="M23">
-        <v>79.5</v>
+        <v>476.7</v>
       </c>
       <c r="N23">
-        <v>0.06401997100982446</v>
+        <v>0.04159504384625452</v>
       </c>
       <c r="O23">
-        <v>1.472222222222222</v>
+        <v>0.3698215671062839</v>
       </c>
       <c r="P23">
-        <v>53.3</v>
+        <v>452.7</v>
       </c>
       <c r="Q23">
-        <v>0.04292156546947978</v>
+        <v>0.03950089437633611</v>
       </c>
       <c r="R23">
-        <v>0.9870370370370369</v>
+        <v>0.3512024825446082</v>
       </c>
       <c r="S23">
-        <v>26.2</v>
+        <v>24</v>
       </c>
       <c r="T23">
-        <v>0.329559748427673</v>
+        <v>0.05034612964128383</v>
       </c>
       <c r="U23">
-        <v>33.6</v>
+        <v>485</v>
       </c>
       <c r="V23">
-        <v>0.02705749718151071</v>
+        <v>0.04231927053793465</v>
       </c>
       <c r="W23">
-        <v>0.05818338541105484</v>
+        <v>0.1592537682233753</v>
       </c>
       <c r="X23">
-        <v>0.08110364200947612</v>
+        <v>0.07610292935491264</v>
       </c>
       <c r="Y23">
-        <v>-0.02292025659842128</v>
+        <v>0.0831508388684627</v>
       </c>
       <c r="Z23">
-        <v>0.8507851653464497</v>
+        <v>1.23579564663641</v>
       </c>
       <c r="AA23">
-        <v>0.05798958406240828</v>
+        <v>0.132483142321214</v>
       </c>
       <c r="AB23">
-        <v>0.07920715390710335</v>
+        <v>0.06623446851101571</v>
       </c>
       <c r="AC23">
-        <v>-0.02121756984469508</v>
+        <v>0.06624867381019826</v>
       </c>
       <c r="AD23">
-        <v>30</v>
+        <v>3273</v>
       </c>
       <c r="AE23">
-        <v>23.85188505759775</v>
+        <v>212.0466529149828</v>
       </c>
       <c r="AF23">
-        <v>53.85188505759775</v>
+        <v>3485.046652914983</v>
       </c>
       <c r="AG23">
-        <v>20.25188505759775</v>
+        <v>3000.046652914983</v>
       </c>
       <c r="AH23">
-        <v>0.04156354471340409</v>
+        <v>0.2331829496671678</v>
       </c>
       <c r="AI23">
-        <v>0.06424308255972189</v>
+        <v>0.2892623803105699</v>
       </c>
       <c r="AJ23">
-        <v>0.01604679276452528</v>
+        <v>0.2074642629302142</v>
       </c>
       <c r="AK23">
-        <v>0.02516850508111107</v>
+        <v>0.2594512279476696</v>
       </c>
       <c r="AL23">
-        <v>0.524</v>
+        <v>121</v>
       </c>
       <c r="AM23">
-        <v>0.524</v>
+        <v>121</v>
       </c>
       <c r="AN23">
-        <v>0.3734129947722181</v>
+        <v>1.793424657534247</v>
       </c>
       <c r="AO23">
-        <v>131.1068702290076</v>
+        <v>14.28925619834711</v>
       </c>
       <c r="AP23">
-        <v>0.2520772349713437</v>
+        <v>1.643861179679442</v>
       </c>
       <c r="AQ23">
-        <v>131.1068702290076</v>
+        <v>14.28925619834711</v>
       </c>
     </row>
     <row r="24">
@@ -3518,7 +3509,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Loews Corporation (NYSE:L)</t>
+          <t>Old Republic International Corporation (NYSE:ORI)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3527,121 +3518,124 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.005759999999999999</v>
+        <v>0.0345</v>
       </c>
       <c r="E24">
-        <v>0.00367</v>
+        <v>0.0345</v>
+      </c>
+      <c r="F24">
+        <v>0.1</v>
       </c>
       <c r="G24">
-        <v>0.2243387004025302</v>
+        <v>0.124292015764884</v>
       </c>
       <c r="H24">
-        <v>0.2243387004025302</v>
+        <v>0.124292015764884</v>
       </c>
       <c r="I24">
-        <v>0.1248034582131382</v>
+        <v>0.1619319212258765</v>
       </c>
       <c r="J24">
-        <v>0.09936697626060706</v>
+        <v>0.1285646395029157</v>
       </c>
       <c r="K24">
-        <v>991</v>
+        <v>920.1</v>
       </c>
       <c r="L24">
-        <v>0.07123346751006325</v>
+        <v>0.1200767363558061</v>
       </c>
       <c r="M24">
-        <v>984</v>
+        <v>918.8625</v>
       </c>
       <c r="N24">
-        <v>0.07105154847607426</v>
+        <v>0.1147000998626888</v>
       </c>
       <c r="O24">
-        <v>0.9929364278506559</v>
+        <v>0.9986550374959243</v>
       </c>
       <c r="P24">
-        <v>62</v>
+        <v>262.9625</v>
       </c>
       <c r="Q24">
-        <v>0.004476825208858337</v>
+        <v>0.03282517788041443</v>
       </c>
       <c r="R24">
-        <v>0.06256306760847628</v>
+        <v>0.2857977393761547</v>
       </c>
       <c r="S24">
-        <v>922</v>
+        <v>655.9</v>
       </c>
       <c r="T24">
-        <v>0.9369918699186992</v>
+        <v>0.7138173556979418</v>
       </c>
       <c r="U24">
-        <v>886</v>
+        <v>152.1</v>
       </c>
       <c r="V24">
-        <v>0.06397527637174978</v>
+        <v>0.0189863937086506</v>
       </c>
       <c r="W24">
-        <v>0.05562103608912836</v>
+        <v>0.1620436413589053</v>
       </c>
       <c r="X24">
-        <v>0.1012105621423872</v>
+        <v>0.07438023256711182</v>
       </c>
       <c r="Y24">
-        <v>-0.04558952605325885</v>
+        <v>0.08766340879179343</v>
       </c>
       <c r="Z24">
-        <v>0.5321364303543213</v>
+        <v>1.033851561719746</v>
       </c>
       <c r="AA24">
-        <v>0.05287678804242203</v>
+        <v>0.1329167533320255</v>
       </c>
       <c r="AB24">
-        <v>0.07595201366349258</v>
+        <v>0.06682975005257186</v>
       </c>
       <c r="AC24">
-        <v>-0.02307522562107055</v>
+        <v>0.06608700327945363</v>
       </c>
       <c r="AD24">
-        <v>9289</v>
+        <v>1590.9</v>
       </c>
       <c r="AE24">
-        <v>373.6714466941096</v>
+        <v>239.4023020729933</v>
       </c>
       <c r="AF24">
-        <v>9662.67144669411</v>
+        <v>1830.302302072993</v>
       </c>
       <c r="AG24">
-        <v>8776.67144669411</v>
+        <v>1678.202302072993</v>
       </c>
       <c r="AH24">
-        <v>0.4109716474831052</v>
+        <v>0.1859817172456388</v>
       </c>
       <c r="AI24">
-        <v>0.3973845208378081</v>
+        <v>0.2362929753946367</v>
       </c>
       <c r="AJ24">
-        <v>0.3879059534996092</v>
+        <v>0.1732033504671426</v>
       </c>
       <c r="AK24">
-        <v>0.3745964371144643</v>
+        <v>0.220996311902256</v>
       </c>
       <c r="AL24">
-        <v>384</v>
+        <v>70.8</v>
       </c>
       <c r="AM24">
-        <v>384</v>
+        <v>70.8</v>
       </c>
       <c r="AN24">
-        <v>3.959505541346974</v>
+        <v>1.207239338291091</v>
       </c>
       <c r="AO24">
-        <v>4.552083333333333</v>
+        <v>17.37146892655367</v>
       </c>
       <c r="AP24">
-        <v>3.741121673782656</v>
+        <v>1.273487860125204</v>
       </c>
       <c r="AQ24">
-        <v>4.552083333333333</v>
+        <v>17.37146892655367</v>
       </c>
     </row>
     <row r="25">
@@ -3652,7 +3646,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Employers Holdings, Inc. (NYSE:EIG)</t>
+          <t>Stewart Information Services Corporation (NYSE:STC)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3661,121 +3655,121 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.0267</v>
+        <v>0.0352</v>
       </c>
       <c r="E25">
-        <v>-0.119</v>
+        <v>-0.0736</v>
       </c>
       <c r="G25">
-        <v>0.2299349240780911</v>
+        <v>0.1327164460437819</v>
       </c>
       <c r="H25">
-        <v>0.2299349240780911</v>
+        <v>0.1327164460437819</v>
       </c>
       <c r="I25">
-        <v>0.1016376427905456</v>
+        <v>0.0441115129570154</v>
       </c>
       <c r="J25">
-        <v>0.0834827490563632</v>
+        <v>0.03561232017389619</v>
       </c>
       <c r="K25">
-        <v>56.1</v>
+        <v>34.9</v>
       </c>
       <c r="L25">
-        <v>0.08112798264642082</v>
+        <v>0.01495094889260164</v>
       </c>
       <c r="M25">
-        <v>66.90000000000001</v>
+        <v>51.37</v>
       </c>
       <c r="N25">
-        <v>0.05703324808184144</v>
+        <v>0.03195645412130638</v>
       </c>
       <c r="O25">
-        <v>1.192513368983957</v>
+        <v>1.471919770773639</v>
       </c>
       <c r="P25">
-        <v>29.3</v>
+        <v>49.7</v>
       </c>
       <c r="Q25">
-        <v>0.02497868712702472</v>
+        <v>0.03091757387247279</v>
       </c>
       <c r="R25">
-        <v>0.5222816399286988</v>
+        <v>1.424068767908309</v>
       </c>
       <c r="S25">
-        <v>37.60000000000001</v>
+        <v>1.670000000000002</v>
       </c>
       <c r="T25">
-        <v>0.5620328849028401</v>
+        <v>0.03250924664200899</v>
       </c>
       <c r="U25">
-        <v>148.1</v>
+        <v>192</v>
       </c>
       <c r="V25">
-        <v>0.1262574595055413</v>
+        <v>0.1194401244167963</v>
       </c>
       <c r="W25">
-        <v>0.04714681906042524</v>
+        <v>0.02594795539033457</v>
       </c>
       <c r="X25">
-        <v>0.08496025552434025</v>
+        <v>0.07762676477078875</v>
       </c>
       <c r="Y25">
-        <v>-0.03781343646391501</v>
+        <v>-0.05167880938045418</v>
       </c>
       <c r="Z25">
-        <v>0.6439819559950446</v>
+        <v>3.48167854060082</v>
       </c>
       <c r="AA25">
-        <v>0.05376138402916024</v>
+        <v>0.12399065093046</v>
       </c>
       <c r="AB25">
-        <v>0.0778108756536737</v>
+        <v>0.06576263809079656</v>
       </c>
       <c r="AC25">
-        <v>-0.02404949162451346</v>
+        <v>0.05822801283966347</v>
       </c>
       <c r="AD25">
-        <v>183</v>
+        <v>445.2</v>
       </c>
       <c r="AE25">
-        <v>15.08785005168861</v>
+        <v>151.1524765221947</v>
       </c>
       <c r="AF25">
-        <v>198.0878500516886</v>
+        <v>596.3524765221947</v>
       </c>
       <c r="AG25">
-        <v>49.98785005168861</v>
+        <v>404.3524765221947</v>
       </c>
       <c r="AH25">
-        <v>0.1444749510720418</v>
+        <v>0.2705954608464869</v>
       </c>
       <c r="AI25">
-        <v>0.1773252211475784</v>
+        <v>0.3049534510997953</v>
       </c>
       <c r="AJ25">
-        <v>0.04087354592245206</v>
+        <v>0.2009851523612616</v>
       </c>
       <c r="AK25">
-        <v>0.05158769539682269</v>
+        <v>0.2292829285803823</v>
       </c>
       <c r="AL25">
-        <v>1.7</v>
+        <v>19.7</v>
       </c>
       <c r="AM25">
-        <v>1.7</v>
+        <v>19.7</v>
       </c>
       <c r="AN25">
-        <v>2.313527180783818</v>
+        <v>2.280737704918033</v>
       </c>
       <c r="AO25">
-        <v>41.1764705882353</v>
+        <v>4.3502538071066</v>
       </c>
       <c r="AP25">
-        <v>0.6319576491996032</v>
+        <v>2.071477851035834</v>
       </c>
       <c r="AQ25">
-        <v>41.1764705882353</v>
+        <v>4.3502538071066</v>
       </c>
     </row>
     <row r="26">
@@ -3786,7 +3780,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Progressive Corporation (NYSE:PGR)</t>
+          <t>Investors Title Company (NasdaqGS:ITIC)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3795,124 +3789,115 @@
         </is>
       </c>
       <c r="D26">
-        <v>0.135</v>
+        <v>0.07519999999999999</v>
       </c>
       <c r="E26">
-        <v>-0.09329999999999999</v>
-      </c>
-      <c r="F26">
-        <v>0.294</v>
+        <v>-0.0572</v>
       </c>
       <c r="G26">
-        <v>0.09804849347646302</v>
+        <v>0.1420718816067653</v>
       </c>
       <c r="H26">
-        <v>0.09804849347646302</v>
+        <v>0.1420718816067653</v>
       </c>
       <c r="I26">
-        <v>0.03283672143469016</v>
+        <v>0.1265264288512837</v>
       </c>
       <c r="J26">
-        <v>0.02557845458172376</v>
+        <v>0.1009620445919117</v>
       </c>
       <c r="K26">
-        <v>857.4</v>
+        <v>23.4</v>
       </c>
       <c r="L26">
-        <v>0.01763885402994532</v>
+        <v>0.0989429175475687</v>
       </c>
       <c r="M26">
-        <v>1244.9</v>
+        <v>4.5</v>
       </c>
       <c r="N26">
-        <v>0.01640413549191323</v>
+        <v>0.01468189233278956</v>
       </c>
       <c r="O26">
-        <v>1.451947749008631</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="P26">
-        <v>1110.5</v>
+        <v>3.49</v>
       </c>
       <c r="Q26">
-        <v>0.01463313717067206</v>
+        <v>0.01138662316476346</v>
       </c>
       <c r="R26">
-        <v>1.295194774900863</v>
+        <v>0.1491452991452992</v>
       </c>
       <c r="S26">
-        <v>134.4000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="T26">
-        <v>0.1079604787533136</v>
+        <v>0.2244444444444444</v>
       </c>
       <c r="U26">
-        <v>350.9</v>
+        <v>30.4</v>
       </c>
       <c r="V26">
-        <v>0.004623834158657204</v>
+        <v>0.09918433931484502</v>
       </c>
       <c r="W26">
-        <v>0.04746404490650015</v>
+        <v>0.09790794979079498</v>
       </c>
       <c r="X26">
-        <v>0.08242572927933359</v>
+        <v>0.06965055968079825</v>
       </c>
       <c r="Y26">
-        <v>-0.03496168437283344</v>
+        <v>0.02825739010999673</v>
       </c>
       <c r="Z26">
-        <v>2.122482726136397</v>
+        <v>1.22006269307524</v>
       </c>
       <c r="AA26">
-        <v>0.05428982801097305</v>
+        <v>0.1231800240231902</v>
       </c>
       <c r="AB26">
-        <v>0.07869215409437164</v>
+        <v>0.06891753359090209</v>
       </c>
       <c r="AC26">
-        <v>-0.02440232608339859</v>
+        <v>0.05426249043228813</v>
       </c>
       <c r="AD26">
-        <v>6387.4</v>
+        <v>0.512</v>
       </c>
       <c r="AE26">
-        <v>168.7647123486016</v>
+        <v>5.882497883357028</v>
       </c>
       <c r="AF26">
-        <v>6556.164712348601</v>
+        <v>6.394497883357028</v>
       </c>
       <c r="AG26">
-        <v>6205.264712348601</v>
+        <v>-24.00550211664297</v>
       </c>
       <c r="AH26">
-        <v>0.07952113294660502</v>
+        <v>0.02043659420863582</v>
       </c>
       <c r="AI26">
-        <v>0.3073341751256228</v>
+        <v>0.02468017628933131</v>
       </c>
       <c r="AJ26">
-        <v>0.07558669901498742</v>
+        <v>-0.08497688378537881</v>
       </c>
       <c r="AK26">
-        <v>0.2957498343143081</v>
+        <v>-0.1049675542648459</v>
       </c>
       <c r="AL26">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>3.236912785688947</v>
-      </c>
-      <c r="AO26">
-        <v>6.713362068965517</v>
+        <v>0.01462857142857143</v>
       </c>
       <c r="AP26">
-        <v>3.144612938908732</v>
-      </c>
-      <c r="AQ26">
-        <v>6.713362068965517</v>
+        <v>-0.6858714890469421</v>
       </c>
     </row>
     <row r="27">
@@ -3923,7 +3908,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ambac Financial Group, Inc. (NYSE:AMBC)</t>
+          <t>Selective Insurance Group, Inc. (NasdaqGS:SIGI)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3932,118 +3917,124 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.179</v>
+        <v>0.0959</v>
+      </c>
+      <c r="E27">
+        <v>0.149</v>
+      </c>
+      <c r="F27">
+        <v>0.228</v>
       </c>
       <c r="G27">
-        <v>0.8980582524271845</v>
+        <v>0.08626276512175962</v>
       </c>
       <c r="H27">
-        <v>0.8980582524271845</v>
+        <v>0.08626276512175962</v>
       </c>
       <c r="I27">
-        <v>1.844702737771225</v>
+        <v>0.1076773512719094</v>
       </c>
       <c r="J27">
-        <v>1.805925202743001</v>
+        <v>0.08602083609674287</v>
       </c>
       <c r="K27">
-        <v>325</v>
+        <v>326.9</v>
       </c>
       <c r="L27">
-        <v>1.577669902912621</v>
+        <v>0.08024842890809111</v>
       </c>
       <c r="M27">
-        <v>18</v>
+        <v>78.77000000000001</v>
       </c>
       <c r="N27">
-        <v>0.02295040163202856</v>
+        <v>0.01306886997494732</v>
       </c>
       <c r="O27">
-        <v>0.05538461538461539</v>
+        <v>0.2409605383909453</v>
       </c>
       <c r="P27">
-        <v>-0</v>
+        <v>70.7</v>
       </c>
       <c r="Q27">
-        <v>-0</v>
+        <v>0.0117299620062051</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0.2162740899357602</v>
       </c>
       <c r="S27">
-        <v>18</v>
+        <v>8.070000000000007</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>0.1024501713850452</v>
       </c>
       <c r="U27">
-        <v>29</v>
+        <v>0.109</v>
       </c>
       <c r="V27">
-        <v>0.03697564707382379</v>
+        <v>1.80843827252667e-05</v>
       </c>
       <c r="W27">
-        <v>0.3063147973609802</v>
+        <v>0.1467564534231201</v>
       </c>
       <c r="X27">
-        <v>0.3200558825986622</v>
+        <v>0.0712572407455916</v>
       </c>
       <c r="Y27">
-        <v>-0.01374108523768197</v>
+        <v>0.07549921267752847</v>
       </c>
       <c r="Z27">
-        <v>0.02175070775144478</v>
+        <v>1.371333292483912</v>
       </c>
       <c r="AA27">
-        <v>0.03928015130583167</v>
+        <v>0.1179632363867654</v>
       </c>
       <c r="AB27">
-        <v>0.07286187731507546</v>
+        <v>0.06811922576314686</v>
       </c>
       <c r="AC27">
-        <v>-0.03358172600924379</v>
+        <v>0.0498440106236185</v>
       </c>
       <c r="AD27">
-        <v>6103</v>
+        <v>504.6</v>
       </c>
       <c r="AE27">
-        <v>29.95618009563825</v>
+        <v>46.22770929374926</v>
       </c>
       <c r="AF27">
-        <v>6132.956180095638</v>
+        <v>550.8277092937493</v>
       </c>
       <c r="AG27">
-        <v>6103.956180095638</v>
+        <v>550.7187092937493</v>
       </c>
       <c r="AH27">
-        <v>0.8866168926550937</v>
+        <v>0.08373624435955015</v>
       </c>
       <c r="AI27">
-        <v>0.849209830017886</v>
+        <v>0.1723907525249587</v>
       </c>
       <c r="AJ27">
-        <v>0.8861395425062267</v>
+        <v>0.08372106155850038</v>
       </c>
       <c r="AK27">
-        <v>0.8486018859654</v>
+        <v>0.1723625190174798</v>
       </c>
       <c r="AL27">
-        <v>132</v>
+        <v>28.9</v>
       </c>
       <c r="AM27">
-        <v>132</v>
+        <v>28.9</v>
       </c>
       <c r="AN27">
-        <v>14.09468822170901</v>
+        <v>1.052829243865799</v>
       </c>
       <c r="AO27">
-        <v>2.886363636363636</v>
+        <v>15.15916955017301</v>
       </c>
       <c r="AP27">
-        <v>14.09689648982826</v>
+        <v>1.149054225700529</v>
       </c>
       <c r="AQ27">
-        <v>2.886363636363636</v>
+        <v>15.15916955017301</v>
       </c>
     </row>
     <row r="28">
@@ -4054,7 +4045,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ProAssurance Corporation (NYSE:PRA)</t>
+          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4063,124 +4054,124 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0469</v>
+        <v>0.0601</v>
       </c>
       <c r="E28">
-        <v>-0.342</v>
+        <v>-0.023</v>
       </c>
       <c r="F28">
-        <v>0.273</v>
+        <v>0.164</v>
       </c>
       <c r="G28">
-        <v>0.1387555555555555</v>
+        <v>0.1130686497142715</v>
       </c>
       <c r="H28">
-        <v>0.1387555555555555</v>
+        <v>0.1130686497142715</v>
       </c>
       <c r="I28">
-        <v>0.04244352349727326</v>
+        <v>0.06835320603518626</v>
       </c>
       <c r="J28">
-        <v>0.04004063618816837</v>
+        <v>0.06382360067586439</v>
       </c>
       <c r="K28">
-        <v>17.8</v>
+        <v>2184</v>
       </c>
       <c r="L28">
-        <v>0.01582222222222222</v>
+        <v>0.05450053652084945</v>
       </c>
       <c r="M28">
-        <v>22.3</v>
+        <v>2353</v>
       </c>
       <c r="N28">
-        <v>0.02365545772780312</v>
+        <v>0.05408225651492376</v>
       </c>
       <c r="O28">
-        <v>1.252808988764045</v>
+        <v>1.077380952380952</v>
       </c>
       <c r="P28">
-        <v>10.8</v>
+        <v>895</v>
       </c>
       <c r="Q28">
-        <v>0.0114564548636894</v>
+        <v>0.02057102404626297</v>
       </c>
       <c r="R28">
-        <v>0.6067415730337079</v>
+        <v>0.4097985347985348</v>
       </c>
       <c r="S28">
-        <v>11.5</v>
+        <v>1458</v>
       </c>
       <c r="T28">
-        <v>0.5156950672645739</v>
+        <v>0.6196345091372716</v>
       </c>
       <c r="U28">
-        <v>41</v>
+        <v>593</v>
       </c>
       <c r="V28">
-        <v>0.04349209716770977</v>
+        <v>0.01362973995467479</v>
       </c>
       <c r="W28">
-        <v>0.01250790527721172</v>
+        <v>0.1097156636190093</v>
       </c>
       <c r="X28">
-        <v>0.09429768297792443</v>
+        <v>0.07351627627043909</v>
       </c>
       <c r="Y28">
-        <v>-0.0817897777007127</v>
+        <v>0.03619938734857026</v>
       </c>
       <c r="Z28">
-        <v>0.6932653881731694</v>
+        <v>1.760567566948391</v>
       </c>
       <c r="AA28">
-        <v>0.0277587871896912</v>
+        <v>0.1123657613557923</v>
       </c>
       <c r="AB28">
-        <v>0.0754158912279891</v>
+        <v>0.06769417854413746</v>
       </c>
       <c r="AC28">
-        <v>-0.0476571040382979</v>
+        <v>0.0446715828116548</v>
       </c>
       <c r="AD28">
-        <v>426.4</v>
+        <v>8031</v>
       </c>
       <c r="AE28">
-        <v>19.25518032783793</v>
+        <v>259.4098727599035</v>
       </c>
       <c r="AF28">
-        <v>445.6551803278379</v>
+        <v>8290.409872759903</v>
       </c>
       <c r="AG28">
-        <v>404.6551803278379</v>
+        <v>7697.409872759903</v>
       </c>
       <c r="AH28">
-        <v>0.3209950786675522</v>
+        <v>0.1600520537895989</v>
       </c>
       <c r="AI28">
-        <v>0.2948127232502766</v>
+        <v>0.2932747158427448</v>
       </c>
       <c r="AJ28">
-        <v>0.3003329680518075</v>
+        <v>0.1503247402341917</v>
       </c>
       <c r="AK28">
-        <v>0.2751529969368022</v>
+        <v>0.2781317389028532</v>
       </c>
       <c r="AL28">
-        <v>20.4</v>
+        <v>366</v>
       </c>
       <c r="AM28">
-        <v>20.4</v>
+        <v>366</v>
       </c>
       <c r="AN28">
-        <v>4.619718309859154</v>
+        <v>2.275070821529745</v>
       </c>
       <c r="AO28">
-        <v>2.264705882352942</v>
+        <v>7.390710382513661</v>
       </c>
       <c r="AP28">
-        <v>4.384129797701386</v>
+        <v>2.180569369053797</v>
       </c>
       <c r="AQ28">
-        <v>2.264705882352942</v>
+        <v>7.390710382513661</v>
       </c>
     </row>
     <row r="29">
@@ -4191,7 +4182,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Global Indemnity Group, LLC (NYSE:GBLI)</t>
+          <t>Loews Corporation (NYSE:L)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4200,121 +4191,121 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.0432</v>
+        <v>0.0149</v>
       </c>
       <c r="E29">
-        <v>-0.158</v>
+        <v>0.0364</v>
       </c>
       <c r="G29">
-        <v>0.09183027232425585</v>
+        <v>0.1397382741642913</v>
       </c>
       <c r="H29">
-        <v>0.09183027232425585</v>
+        <v>0.1397382741642913</v>
       </c>
       <c r="I29">
-        <v>0.02660702144557631</v>
+        <v>0.1536039405923466</v>
       </c>
       <c r="J29">
-        <v>0.01953842274820154</v>
+        <v>0.1204864952447768</v>
       </c>
       <c r="K29">
-        <v>22</v>
+        <v>1533</v>
       </c>
       <c r="L29">
-        <v>0.03483217226092464</v>
+        <v>0.09931329359937807</v>
       </c>
       <c r="M29">
-        <v>11.425</v>
+        <v>885</v>
       </c>
       <c r="N29">
-        <v>0.03353390079248606</v>
+        <v>0.05696446961894953</v>
       </c>
       <c r="O29">
-        <v>0.5193181818181819</v>
+        <v>0.5772994129158513</v>
       </c>
       <c r="P29">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="Q29">
-        <v>0.03228646903434106</v>
+        <v>0.003733264675592173</v>
       </c>
       <c r="R29">
-        <v>0.5</v>
+        <v>0.03783431180691454</v>
       </c>
       <c r="S29">
-        <v>0.4250000000000007</v>
+        <v>827</v>
       </c>
       <c r="T29">
-        <v>0.03719912472647709</v>
+        <v>0.9344632768361582</v>
       </c>
       <c r="U29">
-        <v>18.9</v>
+        <v>762</v>
       </c>
       <c r="V29">
-        <v>0.0554740240680951</v>
+        <v>0.04904737384140062</v>
       </c>
       <c r="W29">
-        <v>0.0318287037037037</v>
+        <v>0.1107178968655207</v>
       </c>
       <c r="X29">
-        <v>0.08123895063579992</v>
+        <v>0.08327561796853242</v>
       </c>
       <c r="Y29">
-        <v>-0.04941024693209622</v>
+        <v>0.02744227889698832</v>
       </c>
       <c r="Z29">
-        <v>0.787378972033734</v>
+        <v>0.6911173110846194</v>
       </c>
       <c r="AA29">
-        <v>0.01538414321863945</v>
+        <v>0.08327030261557994</v>
       </c>
       <c r="AB29">
-        <v>0.07915250356186374</v>
+        <v>0.06563742748938034</v>
       </c>
       <c r="AC29">
-        <v>-0.06376836034322428</v>
+        <v>0.0176328751261996</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>9186</v>
       </c>
       <c r="AE29">
-        <v>16.27502627486999</v>
+        <v>429.8478650826905</v>
       </c>
       <c r="AF29">
-        <v>16.27502627486999</v>
+        <v>9615.847865082691</v>
       </c>
       <c r="AG29">
-        <v>-2.624973725130012</v>
+        <v>8853.847865082691</v>
       </c>
       <c r="AH29">
-        <v>0.04559149821964928</v>
+        <v>0.3823117854665458</v>
       </c>
       <c r="AI29">
-        <v>0.02466380091203913</v>
+        <v>0.3881451084002043</v>
       </c>
       <c r="AJ29">
-        <v>-0.007764470963897203</v>
+        <v>0.3630136569141192</v>
       </c>
       <c r="AK29">
-        <v>-0.0040952823706494</v>
+        <v>0.3687283009133875</v>
       </c>
       <c r="AL29">
-        <v>5.6</v>
+        <v>374</v>
       </c>
       <c r="AM29">
-        <v>5.6</v>
+        <v>374</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>3.080482897384306</v>
       </c>
       <c r="AO29">
-        <v>3.107142857142857</v>
+        <v>6.409090909090909</v>
       </c>
       <c r="AP29">
-        <v>-0.08506071695171782</v>
+        <v>2.969097204923773</v>
       </c>
       <c r="AQ29">
-        <v>3.107142857142857</v>
+        <v>6.409090909090909</v>
       </c>
     </row>
     <row r="30">
@@ -4325,7 +4316,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Allstate Corporation (NYSE:ALL)</t>
+          <t>ICC Holdings, Inc. (NasdaqCM:ICCH)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4334,121 +4325,121 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0562</v>
-      </c>
-      <c r="F30">
-        <v>0.0199</v>
+        <v>0.09609999999999999</v>
+      </c>
+      <c r="E30">
+        <v>0.449</v>
       </c>
       <c r="G30">
-        <v>0.1592287694974003</v>
+        <v>0.002059186189889026</v>
       </c>
       <c r="H30">
-        <v>0.1592287694974003</v>
+        <v>0.002059186189889026</v>
       </c>
       <c r="I30">
-        <v>0.007322527212873277</v>
+        <v>0.07225647348951912</v>
       </c>
       <c r="J30">
-        <v>0.007322527212873277</v>
+        <v>0.05699102134384607</v>
       </c>
       <c r="K30">
-        <v>-210</v>
+        <v>4.47</v>
       </c>
       <c r="L30">
-        <v>-0.004135812194737671</v>
+        <v>0.05511713933415537</v>
       </c>
       <c r="M30">
-        <v>3946</v>
+        <v>0.436</v>
       </c>
       <c r="N30">
-        <v>0.1097257135230129</v>
+        <v>0.00966740576496674</v>
       </c>
       <c r="O30">
-        <v>-18.79047619047619</v>
+        <v>0.09753914988814318</v>
       </c>
       <c r="P30">
-        <v>933</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.02594376348630792</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>-4.442857142857143</v>
+        <v>-0</v>
       </c>
       <c r="S30">
-        <v>3013</v>
+        <v>0.436</v>
       </c>
       <c r="T30">
-        <v>0.7635580334515966</v>
+        <v>1</v>
       </c>
       <c r="U30">
-        <v>786</v>
+        <v>2.67</v>
       </c>
       <c r="V30">
-        <v>0.02185616087914043</v>
+        <v>0.05920177383592017</v>
       </c>
       <c r="W30">
-        <v>-0.008481764206955046</v>
+        <v>0.07897526501766784</v>
       </c>
       <c r="X30">
-        <v>0.08695189458381956</v>
+        <v>0.07675225112129773</v>
       </c>
       <c r="Y30">
-        <v>-0.09543365879077462</v>
+        <v>0.002223013896370113</v>
       </c>
       <c r="Z30">
-        <v>1.634405337518921</v>
+        <v>1.187060889929742</v>
       </c>
       <c r="AA30">
-        <v>0.01196797756084763</v>
+        <v>0.06765181251443086</v>
       </c>
       <c r="AB30">
-        <v>0.07720104666400104</v>
+        <v>0.06602762521747967</v>
       </c>
       <c r="AC30">
-        <v>-0.06523306910315341</v>
+        <v>0.001624187296951199</v>
       </c>
       <c r="AD30">
-        <v>7968</v>
+        <v>15</v>
       </c>
       <c r="AE30">
-        <v>435.9567911957325</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>8403.956791195733</v>
+        <v>15</v>
       </c>
       <c r="AG30">
-        <v>7617.956791195733</v>
+        <v>12.33</v>
       </c>
       <c r="AH30">
-        <v>0.1894218367027029</v>
+        <v>0.2495840266222962</v>
       </c>
       <c r="AI30">
-        <v>0.3236653485995928</v>
+        <v>0.2010723860589813</v>
       </c>
       <c r="AJ30">
-        <v>0.1748025338042836</v>
+        <v>0.214696151837019</v>
       </c>
       <c r="AK30">
-        <v>0.3025525185324392</v>
+        <v>0.1714166550813291</v>
       </c>
       <c r="AL30">
-        <v>335</v>
+        <v>0.184</v>
       </c>
       <c r="AM30">
-        <v>335</v>
+        <v>0.184</v>
       </c>
       <c r="AN30">
-        <v>5.803350327749453</v>
+        <v>2.293577981651376</v>
       </c>
       <c r="AO30">
-        <v>1.086567164179104</v>
+        <v>31.84782608695652</v>
       </c>
       <c r="AP30">
-        <v>5.5484026155832</v>
+        <v>1.885321100917431</v>
       </c>
       <c r="AQ30">
-        <v>1.086567164179104</v>
+        <v>31.84782608695652</v>
       </c>
     </row>
     <row r="31">
@@ -4459,7 +4450,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Markel Corporation (NYSE:MKL)</t>
+          <t>Safety Insurance Group, Inc. (NasdaqGS:SAFT)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4468,118 +4459,121 @@
         </is>
       </c>
       <c r="D31">
-        <v>0.14</v>
+        <v>0.012</v>
+      </c>
+      <c r="E31">
+        <v>-0.163</v>
       </c>
       <c r="G31">
-        <v>0.3189874094469245</v>
+        <v>0.07417704626334519</v>
       </c>
       <c r="H31">
-        <v>0.3189874094469245</v>
+        <v>0.07417704626334519</v>
       </c>
       <c r="I31">
-        <v>0.002111592822543728</v>
+        <v>0.04634500640202049</v>
       </c>
       <c r="J31">
-        <v>0.001520441416456458</v>
+        <v>0.03579119306294652</v>
       </c>
       <c r="K31">
-        <v>-32.7</v>
+        <v>31.2</v>
       </c>
       <c r="L31">
-        <v>-0.002913737335935203</v>
+        <v>0.03469750889679715</v>
       </c>
       <c r="M31">
-        <v>292.2</v>
+        <v>58.54</v>
       </c>
       <c r="N31">
-        <v>0.01648909755767234</v>
+        <v>0.05208185053380783</v>
       </c>
       <c r="O31">
-        <v>-8.93577981651376</v>
+        <v>1.876282051282051</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>53.3</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.04741992882562277</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.708333333333333</v>
       </c>
       <c r="S31">
-        <v>292.2</v>
+        <v>5.240000000000002</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>0.0895114451656987</v>
       </c>
       <c r="U31">
-        <v>3540.7</v>
+        <v>30.9</v>
       </c>
       <c r="V31">
-        <v>0.1998047492212541</v>
+        <v>0.02749110320284697</v>
       </c>
       <c r="W31">
-        <v>-0.002435772333499691</v>
+        <v>0.03977562468128506</v>
       </c>
       <c r="X31">
-        <v>0.08787367608116566</v>
+        <v>0.07020353450140121</v>
       </c>
       <c r="Y31">
-        <v>-0.09030944841466534</v>
+        <v>-0.03042790982011615</v>
       </c>
       <c r="Z31">
-        <v>0.9204358104690255</v>
+        <v>1.121850462691893</v>
       </c>
       <c r="AA31">
-        <v>0.001399468727426773</v>
+        <v>0.04015236649796142</v>
       </c>
       <c r="AB31">
-        <v>0.07693997855801052</v>
+        <v>0.068630618918245</v>
       </c>
       <c r="AC31">
-        <v>-0.07554050983058375</v>
+        <v>-0.02847825242028358</v>
       </c>
       <c r="AD31">
-        <v>4131.2</v>
+        <v>30</v>
       </c>
       <c r="AE31">
-        <v>541.5111361521925</v>
+        <v>20.73285121651579</v>
       </c>
       <c r="AF31">
-        <v>4672.711136152192</v>
+        <v>50.73285121651578</v>
       </c>
       <c r="AG31">
-        <v>1132.011136152192</v>
+        <v>19.83285121651578</v>
       </c>
       <c r="AH31">
-        <v>0.208663621695686</v>
+        <v>0.04318671361235745</v>
       </c>
       <c r="AI31">
-        <v>0.2663346444873925</v>
+        <v>0.06183668918338713</v>
       </c>
       <c r="AJ31">
-        <v>0.06004468659750403</v>
+        <v>0.01733894178281616</v>
       </c>
       <c r="AK31">
-        <v>0.08083593281473185</v>
+        <v>0.02511972894599286</v>
       </c>
       <c r="AL31">
-        <v>195.3</v>
+        <v>0.829</v>
       </c>
       <c r="AM31">
-        <v>195.3</v>
+        <v>0.829</v>
       </c>
       <c r="AN31">
-        <v>8.060878048780488</v>
+        <v>0.5712109672505713</v>
       </c>
       <c r="AO31">
-        <v>0.1464413722478239</v>
+        <v>49.81905910735826</v>
       </c>
       <c r="AP31">
-        <v>2.208802216882326</v>
+        <v>0.3776247375574217</v>
       </c>
       <c r="AQ31">
-        <v>0.1464413722478239</v>
+        <v>49.81905910735826</v>
       </c>
     </row>
     <row r="32">
@@ -4590,7 +4584,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Donegal Group Inc. (NasdaqGS:DGIC.A)</t>
+          <t>Global Indemnity Group, LLC (NYSE:GBLI)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4599,118 +4593,118 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.0285</v>
+        <v>0.0239</v>
       </c>
       <c r="G32">
-        <v>0.0444311377245509</v>
+        <v>-0.01489028213166144</v>
       </c>
       <c r="H32">
-        <v>0.0444311377245509</v>
+        <v>-0.01489028213166144</v>
       </c>
       <c r="I32">
-        <v>-0.0006958083832335329</v>
+        <v>0.05042149173060382</v>
       </c>
       <c r="J32">
-        <v>-0.0006958083832335329</v>
+        <v>0.04241223169801175</v>
       </c>
       <c r="K32">
-        <v>-0.166</v>
+        <v>21.9</v>
       </c>
       <c r="L32">
-        <v>-0.0001988023952095808</v>
+        <v>0.03814002089864158</v>
       </c>
       <c r="M32">
-        <v>20.2</v>
+        <v>49.1</v>
       </c>
       <c r="N32">
-        <v>0.04274227676682183</v>
+        <v>0.1124599175446633</v>
       </c>
       <c r="O32">
-        <v>-121.6867469879518</v>
+        <v>2.242009132420092</v>
       </c>
       <c r="P32">
-        <v>20.2</v>
+        <v>14.5</v>
       </c>
       <c r="Q32">
-        <v>0.04274227676682183</v>
+        <v>0.03321117727897389</v>
       </c>
       <c r="R32">
-        <v>-121.6867469879518</v>
+        <v>0.6621004566210046</v>
       </c>
       <c r="S32">
+        <v>34.6</v>
+      </c>
+      <c r="T32">
+        <v>0.7046843177189409</v>
+      </c>
+      <c r="U32">
+        <v>46.5</v>
+      </c>
+      <c r="V32">
+        <v>0.1065048098946404</v>
+      </c>
+      <c r="W32">
+        <v>0.03424015009380862</v>
+      </c>
+      <c r="X32">
+        <v>0.06989220838915142</v>
+      </c>
+      <c r="Y32">
+        <v>-0.03565205829534279</v>
+      </c>
+      <c r="Z32">
+        <v>0.9062215414949401</v>
+      </c>
+      <c r="AA32">
+        <v>0.03843487798761276</v>
+      </c>
+      <c r="AB32">
+        <v>0.06879049139561245</v>
+      </c>
+      <c r="AC32">
+        <v>-0.03035561340799969</v>
+      </c>
+      <c r="AD32">
         <v>0</v>
       </c>
-      <c r="T32">
+      <c r="AE32">
+        <v>13.73989724143642</v>
+      </c>
+      <c r="AF32">
+        <v>13.73989724143642</v>
+      </c>
+      <c r="AG32">
+        <v>-32.76010275856358</v>
+      </c>
+      <c r="AH32">
+        <v>0.03051005990275425</v>
+      </c>
+      <c r="AI32">
+        <v>0.02132068064105105</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.08112151122844083</v>
+      </c>
+      <c r="AK32">
+        <v>-0.05478828709992517</v>
+      </c>
+      <c r="AL32">
+        <v>0.012</v>
+      </c>
+      <c r="AM32">
+        <v>0.012</v>
+      </c>
+      <c r="AN32">
         <v>0</v>
       </c>
-      <c r="U32">
-        <v>26.7</v>
-      </c>
-      <c r="V32">
-        <v>0.05649597968683876</v>
-      </c>
-      <c r="W32">
-        <v>-0.0003084928451960602</v>
-      </c>
-      <c r="X32">
-        <v>0.08204676790740262</v>
-      </c>
-      <c r="Y32">
-        <v>-0.08235526075259868</v>
-      </c>
-      <c r="Z32">
-        <v>1.674789899111459</v>
-      </c>
-      <c r="AA32">
-        <v>-0.001165332851956596</v>
-      </c>
-      <c r="AB32">
-        <v>0.0788355545962145</v>
-      </c>
-      <c r="AC32">
-        <v>-0.08000088744817109</v>
-      </c>
-      <c r="AD32">
-        <v>35</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>35</v>
-      </c>
-      <c r="AG32">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AH32">
-        <v>0.06895193065405832</v>
-      </c>
-      <c r="AI32">
-        <v>0.06780317706315381</v>
-      </c>
-      <c r="AJ32">
-        <v>0.01725930546891246</v>
-      </c>
-      <c r="AK32">
-        <v>0.01695607763023493</v>
-      </c>
-      <c r="AL32">
-        <v>0.621</v>
-      </c>
-      <c r="AM32">
-        <v>0.621</v>
-      </c>
-      <c r="AN32">
-        <v>7.760532150776053</v>
-      </c>
       <c r="AO32">
-        <v>-0.9355877616747181</v>
+        <v>2391.666666666667</v>
       </c>
       <c r="AP32">
-        <v>1.840354767184036</v>
+        <v>-0.8531276760042599</v>
       </c>
       <c r="AQ32">
-        <v>-0.9355877616747181</v>
+        <v>2391.666666666667</v>
       </c>
     </row>
     <row r="33">
@@ -4721,7 +4715,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cincinnati Financial Corporation (NasdaqGS:CINF)</t>
+          <t>Ambac Financial Group, Inc. (NYSE:AMBC)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4730,121 +4724,121 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.0373</v>
-      </c>
-      <c r="F33">
-        <v>-0.0189</v>
+        <v>-0.124</v>
+      </c>
+      <c r="E33">
+        <v>0.00771</v>
       </c>
       <c r="G33">
-        <v>0.5639964528524978</v>
+        <v>1.643076923076923</v>
       </c>
       <c r="H33">
-        <v>0.5639964528524978</v>
+        <v>1.643076923076923</v>
       </c>
       <c r="I33">
-        <v>-0.01154806908890322</v>
+        <v>0.5808000369004194</v>
       </c>
       <c r="J33">
-        <v>-0.01154806908890322</v>
+        <v>0.5662800359779089</v>
       </c>
       <c r="K33">
-        <v>-29</v>
+        <v>194</v>
       </c>
       <c r="L33">
-        <v>-0.004286136565178835</v>
+        <v>0.5969230769230769</v>
       </c>
       <c r="M33">
-        <v>919</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>0.05710167079861564</v>
+        <v>0.01342642320085929</v>
       </c>
       <c r="O33">
-        <v>-31.68965517241379</v>
+        <v>0.05154639175257732</v>
       </c>
       <c r="P33">
-        <v>416</v>
+        <v>-0</v>
       </c>
       <c r="Q33">
-        <v>0.02584798155845931</v>
+        <v>-0</v>
       </c>
       <c r="R33">
-        <v>-14.3448275862069</v>
+        <v>-0</v>
       </c>
       <c r="S33">
-        <v>503</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>0.5473340587595212</v>
+        <v>1</v>
       </c>
       <c r="U33">
-        <v>1083</v>
+        <v>33</v>
       </c>
       <c r="V33">
-        <v>0.06729174045146979</v>
+        <v>0.04430719656283566</v>
       </c>
       <c r="W33">
-        <v>-0.002449117473186386</v>
+        <v>0.1922695738354807</v>
       </c>
       <c r="X33">
-        <v>0.08138189169461321</v>
+        <v>0.2004010896077366</v>
       </c>
       <c r="Y33">
-        <v>-0.08383100916779959</v>
+        <v>-0.008131515772255904</v>
       </c>
       <c r="Z33">
-        <v>0.5825390918717258</v>
+        <v>0.04601313891141327</v>
       </c>
       <c r="AA33">
-        <v>-0.006727201679921631</v>
+        <v>0.02605632195821162</v>
       </c>
       <c r="AB33">
-        <v>0.07909526726476455</v>
+        <v>0.06214346052216309</v>
       </c>
       <c r="AC33">
-        <v>-0.08582246894468619</v>
+        <v>-0.03608713856395147</v>
       </c>
       <c r="AD33">
-        <v>833</v>
+        <v>4264</v>
       </c>
       <c r="AE33">
-        <v>10.67117727759593</v>
+        <v>26.19994003681857</v>
       </c>
       <c r="AF33">
-        <v>843.6711772775959</v>
+        <v>4290.199940036819</v>
       </c>
       <c r="AG33">
-        <v>-239.3288227224041</v>
+        <v>4257.199940036819</v>
       </c>
       <c r="AH33">
-        <v>0.04981004693282196</v>
+        <v>0.8520754699364398</v>
       </c>
       <c r="AI33">
-        <v>0.08211174476740161</v>
+        <v>0.7621331602602053</v>
       </c>
       <c r="AJ33">
-        <v>-0.01509506633974007</v>
+        <v>0.8510995583909348</v>
       </c>
       <c r="AK33">
-        <v>-0.02603757446350348</v>
+        <v>0.7607304931297378</v>
       </c>
       <c r="AL33">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="AM33">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="AN33">
-        <v>28.72413793103448</v>
+        <v>18.53913043478261</v>
       </c>
       <c r="AO33">
-        <v>-1.481481481481481</v>
+        <v>1.359712230215827</v>
       </c>
       <c r="AP33">
-        <v>-8.252718024910486</v>
+        <v>18.50956495668182</v>
       </c>
       <c r="AQ33">
-        <v>-1.481481481481481</v>
+        <v>1.359712230215827</v>
       </c>
     </row>
     <row r="34">
@@ -4855,7 +4849,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ICC Holdings, Inc. (NasdaqCM:ICCH)</t>
+          <t>ProAssurance Corporation (NYSE:PRA)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4864,118 +4858,118 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.07240000000000001</v>
+        <v>0.04389999999999999</v>
       </c>
       <c r="G34">
-        <v>0.08885542168674698</v>
+        <v>0.04757709251101322</v>
       </c>
       <c r="H34">
-        <v>0.08885542168674698</v>
+        <v>0.04757709251101322</v>
       </c>
       <c r="I34">
-        <v>-0.03328313253012048</v>
+        <v>0.02556682674236213</v>
       </c>
       <c r="J34">
-        <v>-0.03328313253012048</v>
+        <v>0.02556682674236213</v>
       </c>
       <c r="K34">
-        <v>-1.67</v>
+        <v>-31</v>
       </c>
       <c r="L34">
-        <v>-0.02515060240963855</v>
+        <v>-0.02731277533039648</v>
       </c>
       <c r="M34">
-        <v>2.51</v>
+        <v>60.47</v>
       </c>
       <c r="N34">
-        <v>0.05421166306695464</v>
+        <v>0.08602930715606773</v>
       </c>
       <c r="O34">
-        <v>-1.502994011976048</v>
+        <v>-1.950645161290323</v>
       </c>
       <c r="P34">
-        <v>-0</v>
+        <v>8.07</v>
       </c>
       <c r="Q34">
-        <v>-0</v>
+        <v>0.01148100725565514</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>-0.2603225806451613</v>
       </c>
       <c r="S34">
-        <v>2.51</v>
+        <v>52.4</v>
       </c>
       <c r="T34">
-        <v>1</v>
+        <v>0.8665453944104514</v>
       </c>
       <c r="U34">
-        <v>3.28</v>
+        <v>62.1</v>
       </c>
       <c r="V34">
-        <v>0.07084233261339093</v>
+        <v>0.088348271446863</v>
       </c>
       <c r="W34">
-        <v>-0.02275204359673024</v>
+        <v>-0.02908067542213884</v>
       </c>
       <c r="X34">
-        <v>0.08972625416970324</v>
+        <v>0.08360962642238456</v>
       </c>
       <c r="Y34">
-        <v>-0.1124782977664335</v>
+        <v>-0.1126903018445234</v>
       </c>
       <c r="Z34">
-        <v>0.743894241541564</v>
+        <v>0.7989816633134981</v>
       </c>
       <c r="AA34">
-        <v>-0.02475913062962133</v>
+        <v>0.02042742575626052</v>
       </c>
       <c r="AB34">
-        <v>0.07645106962573019</v>
+        <v>0.06428380540885502</v>
       </c>
       <c r="AC34">
-        <v>-0.1012102002553515</v>
+        <v>-0.0438563796525945</v>
       </c>
       <c r="AD34">
-        <v>15</v>
+        <v>426.6</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>18.7582582370949</v>
       </c>
       <c r="AF34">
-        <v>15</v>
+        <v>445.3582582370949</v>
       </c>
       <c r="AG34">
-        <v>11.72</v>
+        <v>383.2582582370949</v>
       </c>
       <c r="AH34">
-        <v>0.2446982055464927</v>
+        <v>0.3878554802826738</v>
       </c>
       <c r="AI34">
-        <v>0.2094972067039106</v>
+        <v>0.3056347899890435</v>
       </c>
       <c r="AJ34">
-        <v>0.2019993105825578</v>
+        <v>0.3528567364199282</v>
       </c>
       <c r="AK34">
-        <v>0.1715456674473068</v>
+        <v>0.2747256295385184</v>
       </c>
       <c r="AL34">
-        <v>0.211</v>
+        <v>22</v>
       </c>
       <c r="AM34">
-        <v>0.211</v>
+        <v>22</v>
       </c>
       <c r="AN34">
-        <v>-10.48951048951049</v>
+        <v>7.008378511582061</v>
       </c>
       <c r="AO34">
-        <v>-10.4739336492891</v>
+        <v>1.281818181818182</v>
       </c>
       <c r="AP34">
-        <v>-8.195804195804197</v>
+        <v>6.296340697175865</v>
       </c>
       <c r="AQ34">
-        <v>-10.4739336492891</v>
+        <v>1.281818181818182</v>
       </c>
     </row>
     <row r="35">
@@ -4986,7 +4980,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Positive Physicians Holdings, Inc. (OTCPK:PPHI)</t>
+          <t>Donegal Group Inc. (NasdaqGS:DGIC.A)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4994,113 +4988,119 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D35">
+        <v>0.0327</v>
+      </c>
       <c r="G35">
-        <v>-0.09103139013452914</v>
+        <v>0.001997146932952925</v>
       </c>
       <c r="H35">
-        <v>-0.09103139013452914</v>
+        <v>0.001997146932952925</v>
       </c>
       <c r="I35">
-        <v>-0.1415629432255728</v>
+        <v>0.01338746845166246</v>
       </c>
       <c r="J35">
-        <v>-0.1415629432255728</v>
+        <v>0.01136780726283407</v>
       </c>
       <c r="K35">
-        <v>-2.52</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L35">
-        <v>-0.1130044843049327</v>
+        <v>0.0108416547788873</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>21.6</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.04614398632770775</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.186234817813765</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>21.6</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.04614398632770775</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.186234817813765</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
       <c r="U35">
-        <v>17.2</v>
+        <v>23.7</v>
       </c>
       <c r="V35">
-        <v>0.6798418972332015</v>
+        <v>0.05063020722067934</v>
       </c>
       <c r="W35">
-        <v>-0.0339622641509434</v>
+        <v>0.02053200332502078</v>
       </c>
       <c r="X35">
-        <v>0.08377822994517736</v>
+        <v>0.0708786482808427</v>
       </c>
       <c r="Y35">
-        <v>-0.1177404940961208</v>
+        <v>-0.05034664495582192</v>
       </c>
       <c r="Z35">
-        <v>0.3990032564446639</v>
+        <v>1.883357100047533</v>
       </c>
       <c r="AA35">
-        <v>-0.05648407533889464</v>
+        <v>0.02140964052043046</v>
       </c>
       <c r="AB35">
-        <v>0.08017856359225714</v>
+        <v>0.06829790103411343</v>
       </c>
       <c r="AC35">
-        <v>-0.1366626389311518</v>
+        <v>-0.04688826051368297</v>
       </c>
       <c r="AD35">
-        <v>2.71</v>
+        <v>35</v>
       </c>
       <c r="AE35">
-        <v>0.5892681696513704</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>3.29926816965137</v>
+        <v>35</v>
       </c>
       <c r="AG35">
-        <v>-13.90073183034863</v>
+        <v>11.3</v>
       </c>
       <c r="AH35">
-        <v>0.1153619788478521</v>
+        <v>0.06956867421983701</v>
       </c>
       <c r="AI35">
-        <v>0.04544492324552882</v>
+        <v>0.06885697422781821</v>
       </c>
       <c r="AJ35">
-        <v>-1.219440724042003</v>
+        <v>0.02357113057989153</v>
       </c>
       <c r="AK35">
-        <v>-0.2509190516340373</v>
+        <v>0.02331820057779612</v>
       </c>
       <c r="AL35">
-        <v>0.016</v>
+        <v>0.62</v>
       </c>
       <c r="AM35">
-        <v>0.016</v>
+        <v>0.62</v>
       </c>
       <c r="AN35">
-        <v>-1.457772996234535</v>
+        <v>2.108433734939759</v>
       </c>
       <c r="AO35">
-        <v>-200.625</v>
+        <v>19.67741935483871</v>
       </c>
       <c r="AP35">
-        <v>7.477531915195605</v>
+        <v>0.6807228915662651</v>
       </c>
       <c r="AQ35">
-        <v>-200.625</v>
+        <v>19.67741935483871</v>
       </c>
     </row>
     <row r="36">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kemper Corporation (NYSE:KMPR)</t>
+          <t>Kingsway Financial Services Inc. (NYSE:KFS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5120,118 +5120,118 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.163</v>
+        <v>0.139</v>
       </c>
       <c r="G36">
-        <v>0.005671010919337796</v>
+        <v>0.06190028222013171</v>
       </c>
       <c r="H36">
-        <v>0.005671010919337796</v>
+        <v>0.06190028222013171</v>
       </c>
       <c r="I36">
-        <v>-0.04370571190147952</v>
+        <v>0.008541037006789152</v>
       </c>
       <c r="J36">
-        <v>-0.04370571190147952</v>
+        <v>0.008535585281040137</v>
       </c>
       <c r="K36">
-        <v>-351.5</v>
+        <v>17.1</v>
       </c>
       <c r="L36">
-        <v>-0.06190560056357872</v>
+        <v>0.160865475070555</v>
       </c>
       <c r="M36">
-        <v>79.7</v>
+        <v>1.29</v>
       </c>
       <c r="N36">
-        <v>0.02535713149438453</v>
+        <v>0.005496378355347252</v>
       </c>
       <c r="O36">
-        <v>-0.2267425320056899</v>
+        <v>0.07543859649122807</v>
       </c>
       <c r="P36">
-        <v>79.7</v>
+        <v>-0</v>
       </c>
       <c r="Q36">
-        <v>0.02535713149438453</v>
+        <v>-0</v>
       </c>
       <c r="R36">
-        <v>-0.2267425320056899</v>
+        <v>-0</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36">
-        <v>249.2</v>
+        <v>20.2</v>
       </c>
       <c r="V36">
-        <v>0.07928478253953103</v>
+        <v>0.08606731998295697</v>
       </c>
       <c r="W36">
-        <v>-0.0846743110425901</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="X36">
-        <v>0.09357252046874244</v>
+        <v>0.07326471558856465</v>
       </c>
       <c r="Y36">
-        <v>-0.1782468315113325</v>
+        <v>0.5267352844114355</v>
       </c>
       <c r="Z36">
-        <v>1.468395681644172</v>
+        <v>0.6257710330978963</v>
       </c>
       <c r="AA36">
-        <v>-0.06417727861931684</v>
+        <v>0.005341322019411684</v>
       </c>
       <c r="AB36">
-        <v>0.07556591720399825</v>
+        <v>0.06725593415399149</v>
       </c>
       <c r="AC36">
-        <v>-0.1397431958233151</v>
+        <v>-0.06191461213457981</v>
       </c>
       <c r="AD36">
-        <v>1386.4</v>
+        <v>40.9</v>
       </c>
       <c r="AE36">
-        <v>25.3051608830038</v>
+        <v>1.230438830891565</v>
       </c>
       <c r="AF36">
-        <v>1411.705160883004</v>
+        <v>42.13043883089156</v>
       </c>
       <c r="AG36">
-        <v>1162.505160883004</v>
+        <v>21.93043883089156</v>
       </c>
       <c r="AH36">
-        <v>0.309937551886265</v>
+        <v>0.1521886068917007</v>
       </c>
       <c r="AI36">
-        <v>0.3667428540685427</v>
+        <v>0.5998885886550956</v>
       </c>
       <c r="AJ36">
-        <v>0.2699980879446443</v>
+        <v>0.08545532997098128</v>
       </c>
       <c r="AK36">
-        <v>0.3229086676451068</v>
+        <v>0.4383419243037</v>
       </c>
       <c r="AL36">
-        <v>51.6</v>
+        <v>8</v>
       </c>
       <c r="AM36">
-        <v>51.6</v>
+        <v>8</v>
       </c>
       <c r="AN36">
-        <v>-6.521166509877705</v>
+        <v>5.361824855794441</v>
       </c>
       <c r="AO36">
-        <v>-4.757751937984496</v>
+        <v>0.0895</v>
       </c>
       <c r="AP36">
-        <v>-5.468039326825042</v>
+        <v>2.87499198097687</v>
       </c>
       <c r="AQ36">
-        <v>-4.757751937984496</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="37">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MBIA Inc. (NYSE:MBI)</t>
+          <t>The Hanover Insurance Group, Inc. (NYSE:THG)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5251,118 +5251,121 @@
         </is>
       </c>
       <c r="D37">
-        <v>-0.181</v>
+        <v>0.058</v>
+      </c>
+      <c r="F37">
+        <v>0.364</v>
       </c>
       <c r="G37">
+        <v>0.03213648753238887</v>
+      </c>
+      <c r="H37">
+        <v>0.03213648753238887</v>
+      </c>
+      <c r="I37">
+        <v>-0.01507554598378033</v>
+      </c>
+      <c r="J37">
+        <v>-0.01507554598378033</v>
+      </c>
+      <c r="K37">
+        <v>-84.7</v>
+      </c>
+      <c r="L37">
+        <v>-0.01425110206279234</v>
+      </c>
+      <c r="M37">
+        <v>115.7</v>
+      </c>
+      <c r="N37">
+        <v>0.02664486562420837</v>
+      </c>
+      <c r="O37">
+        <v>-1.365997638724912</v>
+      </c>
+      <c r="P37">
+        <v>115.7</v>
+      </c>
+      <c r="Q37">
+        <v>0.02664486562420837</v>
+      </c>
+      <c r="R37">
+        <v>-1.365997638724912</v>
+      </c>
+      <c r="S37">
         <v>0</v>
       </c>
-      <c r="H37">
+      <c r="T37">
         <v>0</v>
       </c>
-      <c r="I37">
-        <v>-13.86161171780009</v>
-      </c>
-      <c r="J37">
-        <v>-13.86161171780009</v>
-      </c>
-      <c r="K37">
-        <v>-298</v>
-      </c>
-      <c r="L37">
-        <v>-17.52941176470588</v>
-      </c>
-      <c r="M37">
-        <v>3</v>
-      </c>
-      <c r="N37">
-        <v>0.004252906152537568</v>
-      </c>
-      <c r="O37">
-        <v>-0.01006711409395973</v>
-      </c>
-      <c r="P37">
-        <v>-0</v>
-      </c>
-      <c r="Q37">
-        <v>-0</v>
-      </c>
-      <c r="R37">
+      <c r="U37">
+        <v>294.5</v>
+      </c>
+      <c r="V37">
+        <v>0.06782120074614835</v>
+      </c>
+      <c r="W37">
+        <v>-0.03689185069036108</v>
+      </c>
+      <c r="X37">
+        <v>0.07328320419386181</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1101750548842229</v>
+      </c>
+      <c r="Z37">
+        <v>2.17348692631194</v>
+      </c>
+      <c r="AA37">
+        <v>-0.03276650210276102</v>
+      </c>
+      <c r="AB37">
+        <v>0.06724858238951986</v>
+      </c>
+      <c r="AC37">
+        <v>-0.1000150844922809</v>
+      </c>
+      <c r="AD37">
+        <v>783</v>
+      </c>
+      <c r="AE37">
         <v>0</v>
       </c>
-      <c r="S37">
-        <v>3</v>
-      </c>
-      <c r="T37">
-        <v>1</v>
-      </c>
-      <c r="U37">
-        <v>111</v>
-      </c>
-      <c r="V37">
-        <v>0.15735752764389</v>
-      </c>
-      <c r="W37">
-        <v>1.752941176470588</v>
-      </c>
-      <c r="X37">
-        <v>0.2232731084716984</v>
-      </c>
-      <c r="Y37">
-        <v>1.52966806799889</v>
-      </c>
-      <c r="Z37">
-        <v>0.005103209414504719</v>
-      </c>
-      <c r="AA37">
-        <v>-0.07073870741848635</v>
-      </c>
-      <c r="AB37">
-        <v>0.0733526885299664</v>
-      </c>
-      <c r="AC37">
-        <v>-0.1440913959484528</v>
-      </c>
-      <c r="AD37">
-        <v>3276</v>
-      </c>
-      <c r="AE37">
-        <v>18.23699601300778</v>
-      </c>
       <c r="AF37">
-        <v>3294.236996013008</v>
+        <v>783</v>
       </c>
       <c r="AG37">
-        <v>3183.236996013008</v>
+        <v>488.5</v>
       </c>
       <c r="AH37">
-        <v>0.8236339946092183</v>
+        <v>0.152771545080288</v>
       </c>
       <c r="AI37">
-        <v>1.347205608856854</v>
+        <v>0.2700651881488635</v>
       </c>
       <c r="AJ37">
-        <v>0.8185996788275065</v>
+        <v>0.101121967376004</v>
       </c>
       <c r="AK37">
-        <v>1.363716281358806</v>
+        <v>0.1875383906633906</v>
       </c>
       <c r="AL37">
-        <v>96</v>
+        <v>34.2</v>
       </c>
       <c r="AM37">
-        <v>96</v>
+        <v>34.2</v>
       </c>
       <c r="AN37">
-        <v>1092</v>
+        <v>-9.642857142857142</v>
       </c>
       <c r="AO37">
-        <v>-2.447916666666667</v>
+        <v>-2.619883040935672</v>
       </c>
       <c r="AP37">
-        <v>1061.078998671003</v>
+        <v>-6.016009852216748</v>
       </c>
       <c r="AQ37">
-        <v>-2.447916666666667</v>
+        <v>-2.619883040935672</v>
       </c>
     </row>
     <row r="38">
@@ -5373,7 +5376,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FG Financial Group, Inc. (NasdaqGM:FGF)</t>
+          <t>United Fire Group, Inc. (NasdaqGS:UFCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5382,109 +5385,118 @@
         </is>
       </c>
       <c r="D38">
-        <v>-0.129</v>
+        <v>-0.00058</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>0.02104199209776716</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>0.02104199209776716</v>
       </c>
       <c r="I38">
-        <v>-0.1308352294192396</v>
+        <v>-0.03178049273348642</v>
       </c>
       <c r="J38">
-        <v>-0.1308352294192396</v>
+        <v>-0.03178049273348642</v>
       </c>
       <c r="K38">
-        <v>-2.4</v>
+        <v>-29.2</v>
       </c>
       <c r="L38">
-        <v>-0.1363636363636364</v>
+        <v>-0.02683083708536249</v>
       </c>
       <c r="M38">
-        <v>-0</v>
+        <v>17.046</v>
       </c>
       <c r="N38">
-        <v>-0</v>
+        <v>0.03353531379106826</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>-0.5837671232876712</v>
       </c>
       <c r="P38">
-        <v>-0</v>
+        <v>16.2</v>
       </c>
       <c r="Q38">
-        <v>-0</v>
+        <v>0.03187094235687586</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>-0.5547945205479452</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>0.8460000000000001</v>
+      </c>
+      <c r="T38">
+        <v>0.04963041182682155</v>
       </c>
       <c r="U38">
-        <v>9.65</v>
+        <v>69.2</v>
       </c>
       <c r="V38">
-        <v>0.3600746268656717</v>
+        <v>0.1361400747590006</v>
       </c>
       <c r="W38">
-        <v>-0.24</v>
+        <v>-0.04166666666666667</v>
       </c>
       <c r="X38">
-        <v>0.07978082464208421</v>
+        <v>0.07254491610003472</v>
       </c>
       <c r="Y38">
-        <v>-0.3197808246420842</v>
+        <v>-0.1142115827667014</v>
       </c>
       <c r="Z38">
-        <v>0.7496219885598139</v>
+        <v>1.505290124761073</v>
       </c>
       <c r="AA38">
-        <v>-0.09807696485092986</v>
+        <v>-0.04783886187175814</v>
       </c>
       <c r="AB38">
-        <v>0.07976951129940625</v>
+        <v>0.06811190374406038</v>
       </c>
       <c r="AC38">
-        <v>-0.1778464761503361</v>
+        <v>-0.1159507656158185</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AE38">
-        <v>0.008500188893086513</v>
+        <v>25.18355120926634</v>
       </c>
       <c r="AF38">
-        <v>0.008500188893086513</v>
+        <v>75.18355120926634</v>
       </c>
       <c r="AG38">
-        <v>-9.641499811106915</v>
+        <v>5.983551209266338</v>
       </c>
       <c r="AH38">
-        <v>0.0003170706616630567</v>
+        <v>0.1288529060561328</v>
       </c>
       <c r="AI38">
-        <v>0.0002254183765067966</v>
+        <v>0.1044094828759905</v>
       </c>
       <c r="AJ38">
-        <v>-0.5619080750045962</v>
+        <v>0.01163473184237926</v>
       </c>
       <c r="AK38">
-        <v>-0.343621353465054</v>
+        <v>0.009192967310588187</v>
       </c>
       <c r="AL38">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AM38">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AN38">
-        <v>0</v>
+        <v>-2.257336343115124</v>
+      </c>
+      <c r="AO38">
+        <v>-11.91222570532915</v>
       </c>
       <c r="AP38">
-        <v>-1071.277756789657</v>
+        <v>-0.2701377521113471</v>
+      </c>
+      <c r="AQ38">
+        <v>-11.91222570532915</v>
       </c>
     </row>
     <row r="39">
@@ -5495,7 +5507,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Conifer Holdings, Inc. (NasdaqGM:CNFR)</t>
+          <t>Kemper Corporation (NYSE:KMPR)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5504,118 +5516,118 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.0167</v>
+        <v>0.0951</v>
       </c>
       <c r="G39">
-        <v>-0.09730250481695568</v>
+        <v>-0.01128254580520733</v>
       </c>
       <c r="H39">
-        <v>-0.09730250481695568</v>
+        <v>-0.01128254580520733</v>
       </c>
       <c r="I39">
-        <v>-0.1048166700673065</v>
+        <v>-0.02383526589121706</v>
       </c>
       <c r="J39">
-        <v>-0.1048166700673065</v>
+        <v>-0.02383526589121706</v>
       </c>
       <c r="K39">
-        <v>-13.6</v>
+        <v>-391.4</v>
       </c>
       <c r="L39">
-        <v>-0.1310211946050096</v>
+        <v>-0.07548698167791706</v>
       </c>
       <c r="M39">
-        <v>0.001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N39">
-        <v>5.208333333333334e-05</v>
+        <v>0.025520182103812</v>
       </c>
       <c r="O39">
-        <v>-7.352941176470589e-05</v>
+        <v>-0.2033725089422586</v>
       </c>
       <c r="P39">
-        <v>-0</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Q39">
-        <v>-0</v>
+        <v>0.025520182103812</v>
       </c>
       <c r="R39">
+        <v>-0.2033725089422586</v>
+      </c>
+      <c r="S39">
         <v>0</v>
       </c>
-      <c r="S39">
-        <v>0.001</v>
-      </c>
       <c r="T39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>35.4</v>
+        <v>112.4</v>
       </c>
       <c r="V39">
-        <v>1.84375</v>
+        <v>0.03603603603603604</v>
       </c>
       <c r="W39">
-        <v>-0.3230403800475059</v>
+        <v>-0.1605677715786019</v>
       </c>
       <c r="X39">
-        <v>0.1596484400267948</v>
+        <v>0.07949217967188393</v>
       </c>
       <c r="Y39">
-        <v>-0.4826888200743008</v>
+        <v>-0.2400599512504858</v>
       </c>
       <c r="Z39">
-        <v>1.468178467263576</v>
+        <v>2.254417156050527</v>
       </c>
       <c r="AA39">
-        <v>-0.15388957800309</v>
+        <v>-0.05373463234418568</v>
       </c>
       <c r="AB39">
-        <v>0.07414328497254802</v>
+        <v>0.0652441885656998</v>
       </c>
       <c r="AC39">
-        <v>-0.228032862975638</v>
+        <v>-0.1189788209098855</v>
       </c>
       <c r="AD39">
-        <v>48.3</v>
+        <v>1388.6</v>
       </c>
       <c r="AE39">
-        <v>1.609851764932061</v>
+        <v>23.92926822980222</v>
       </c>
       <c r="AF39">
-        <v>49.90985176493206</v>
+        <v>1412.529268229802</v>
       </c>
       <c r="AG39">
-        <v>14.50985176493206</v>
+        <v>1300.129268229802</v>
       </c>
       <c r="AH39">
-        <v>0.7221814327527971</v>
+        <v>0.3117045072801334</v>
       </c>
       <c r="AI39">
-        <v>0.7549533153152026</v>
+        <v>0.3743059366027064</v>
       </c>
       <c r="AJ39">
-        <v>0.4304335677923828</v>
+        <v>0.2941981936933069</v>
       </c>
       <c r="AK39">
-        <v>0.472481986432153</v>
+        <v>0.3550976088141876</v>
       </c>
       <c r="AL39">
-        <v>2.91</v>
+        <v>55.9</v>
       </c>
       <c r="AM39">
-        <v>2.91</v>
+        <v>55.9</v>
       </c>
       <c r="AN39">
-        <v>-4.754873006497341</v>
+        <v>-25.29326047358834</v>
       </c>
       <c r="AO39">
-        <v>-3.883161512027491</v>
+        <v>-2.168157423971377</v>
       </c>
       <c r="AP39">
-        <v>-1.428416200524912</v>
+        <v>-23.68177173460477</v>
       </c>
       <c r="AQ39">
-        <v>-3.883161512027491</v>
+        <v>-2.168157423971377</v>
       </c>
     </row>
     <row r="40">
@@ -5626,7 +5638,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NI Holdings, Inc. (NasdaqCM:NODK)</t>
+          <t>MBIA Inc. (NYSE:MBI)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5635,34 +5647,34 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.129</v>
+        <v>-0.275</v>
       </c>
       <c r="G40">
-        <v>0.03949447077409163</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>0.03949447077409163</v>
+        <v>0</v>
       </c>
       <c r="I40">
-        <v>-0.1938901933687274</v>
+        <v>-1.618405358211408</v>
       </c>
       <c r="J40">
-        <v>-0.1938901933687274</v>
+        <v>-1.618405358211408</v>
       </c>
       <c r="K40">
-        <v>-47.9</v>
+        <v>-405</v>
       </c>
       <c r="L40">
-        <v>-0.1513428120063191</v>
+        <v>-4.450549450549451</v>
       </c>
       <c r="M40">
-        <v>3.98</v>
+        <v>35</v>
       </c>
       <c r="N40">
-        <v>0.01419907242240457</v>
+        <v>0.1118210862619808</v>
       </c>
       <c r="O40">
-        <v>-0.08308977035490606</v>
+        <v>-0.08641975308641975</v>
       </c>
       <c r="P40">
         <v>-0</v>
@@ -5674,73 +5686,79 @@
         <v>0</v>
       </c>
       <c r="S40">
-        <v>3.98</v>
+        <v>35</v>
       </c>
       <c r="T40">
         <v>1</v>
       </c>
       <c r="U40">
-        <v>54.3</v>
+        <v>74</v>
       </c>
       <c r="V40">
-        <v>0.1937210132001427</v>
+        <v>0.2364217252396166</v>
       </c>
       <c r="W40">
-        <v>-0.1410067706800118</v>
+        <v>0.4692931633835458</v>
       </c>
       <c r="X40">
-        <v>0.07998224447641358</v>
+        <v>0.3156498115270266</v>
       </c>
       <c r="Y40">
-        <v>-0.2209890151564254</v>
+        <v>0.1536433518565192</v>
       </c>
       <c r="Z40">
-        <v>1.112297284279664</v>
+        <v>0.03925164050680498</v>
       </c>
       <c r="AA40">
-        <v>-0.2156635355324943</v>
+        <v>-0.06352506531480114</v>
       </c>
       <c r="AB40">
-        <v>0.07967847670118945</v>
+        <v>0.0634533281253416</v>
       </c>
       <c r="AC40">
-        <v>-0.2953420122336838</v>
+        <v>-0.1269783934401427</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>3370</v>
       </c>
       <c r="AE40">
-        <v>1.926231006011135</v>
+        <v>16.37443798619081</v>
       </c>
       <c r="AF40">
-        <v>1.926231006011135</v>
+        <v>3386.374437986191</v>
       </c>
       <c r="AG40">
-        <v>-52.37376899398886</v>
+        <v>3312.374437986191</v>
       </c>
       <c r="AH40">
-        <v>0.006825131027491589</v>
+        <v>0.9153911005098511</v>
       </c>
       <c r="AI40">
-        <v>0.007621808778390397</v>
+        <v>1.568946693580077</v>
       </c>
       <c r="AJ40">
-        <v>-0.2297838592900156</v>
+        <v>0.9136640903294215</v>
       </c>
       <c r="AK40">
-        <v>-0.2639457934994605</v>
+        <v>1.589145586138749</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="AN40">
-        <v>-0</v>
+        <v>1123.333333333333</v>
+      </c>
+      <c r="AO40">
+        <v>-0.7903225806451613</v>
       </c>
       <c r="AP40">
-        <v>0.876093892607833</v>
+        <v>1104.124812662064</v>
+      </c>
+      <c r="AQ40">
+        <v>-0.7903225806451613</v>
       </c>
     </row>
     <row r="41">
@@ -5751,7 +5769,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kingstone Companies, Inc. (NasdaqCM:KINS)</t>
+          <t>NI Holdings, Inc. (NasdaqCM:NODK)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5760,118 +5778,112 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.09329999999999999</v>
+        <v>0.127</v>
       </c>
       <c r="G41">
-        <v>-0.0314977973568282</v>
+        <v>-0.185957213384531</v>
       </c>
       <c r="H41">
-        <v>-0.0314977973568282</v>
+        <v>-0.185957213384531</v>
       </c>
       <c r="I41">
-        <v>-0.1327690513324486</v>
+        <v>-0.04137066045403525</v>
       </c>
       <c r="J41">
-        <v>-0.1327690513324486</v>
+        <v>-0.04137066045403525</v>
       </c>
       <c r="K41">
-        <v>-16.3</v>
+        <v>-11.2</v>
       </c>
       <c r="L41">
-        <v>-0.1196769456681351</v>
+        <v>-0.03071859572133845</v>
       </c>
       <c r="M41">
-        <v>2.094</v>
+        <v>8.59</v>
       </c>
       <c r="N41">
-        <v>0.1454166666666667</v>
+        <v>0.03213617658062103</v>
       </c>
       <c r="O41">
-        <v>-0.1284662576687116</v>
+        <v>-0.7669642857142858</v>
       </c>
       <c r="P41">
-        <v>1.7</v>
+        <v>-0</v>
       </c>
       <c r="Q41">
-        <v>0.1180555555555556</v>
+        <v>-0</v>
       </c>
       <c r="R41">
-        <v>-0.1042944785276074</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>0.3939999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="T41">
-        <v>0.1881566380133715</v>
+        <v>1</v>
       </c>
       <c r="U41">
-        <v>15.1</v>
+        <v>34.5</v>
       </c>
       <c r="V41">
-        <v>1.048611111111111</v>
+        <v>0.1290684624017957</v>
       </c>
       <c r="W41">
-        <v>-0.2095115681233933</v>
+        <v>-0.045016077170418</v>
       </c>
       <c r="X41">
-        <v>0.1454650531494729</v>
+        <v>0.06932132755836229</v>
       </c>
       <c r="Y41">
-        <v>-0.3549766212728663</v>
+        <v>-0.1143374047287803</v>
       </c>
       <c r="Z41">
-        <v>1.884189471219395</v>
+        <v>1.9514679239581</v>
       </c>
       <c r="AA41">
-        <v>-0.2501620486243871</v>
+        <v>-0.08073351686901166</v>
       </c>
       <c r="AB41">
-        <v>0.07446174552315049</v>
+        <v>0.06909493086606956</v>
       </c>
       <c r="AC41">
-        <v>-0.3246237941475376</v>
+        <v>-0.1498284477350812</v>
       </c>
       <c r="AD41">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>0.7857239573975107</v>
+        <v>1.713714007706272</v>
       </c>
       <c r="AF41">
-        <v>30.78572395739751</v>
+        <v>1.713714007706272</v>
       </c>
       <c r="AG41">
-        <v>15.68572395739751</v>
+        <v>-32.78628599229373</v>
       </c>
       <c r="AH41">
-        <v>0.6813152752941003</v>
+        <v>0.006370359273420462</v>
       </c>
       <c r="AI41">
-        <v>0.4417794952696253</v>
+        <v>0.007399017864932009</v>
       </c>
       <c r="AJ41">
-        <v>0.5213676752339107</v>
+        <v>-0.1398054102337757</v>
       </c>
       <c r="AK41">
-        <v>0.2873594562864045</v>
+        <v>-0.1663318362060386</v>
       </c>
       <c r="AL41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>-2.05114180226993</v>
-      </c>
-      <c r="AO41">
-        <v>-9.94535519125683</v>
+        <v>-0</v>
       </c>
       <c r="AP41">
-        <v>-1.072454803596165</v>
-      </c>
-      <c r="AQ41">
-        <v>-9.94535519125683</v>
+        <v>2.42126031993898</v>
       </c>
     </row>
     <row r="42">
@@ -5891,43 +5903,43 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.0146</v>
+        <v>0.0517</v>
       </c>
       <c r="G42">
-        <v>0.1117042309213128</v>
+        <v>-0.129777757578512</v>
       </c>
       <c r="H42">
-        <v>0.1117042309213128</v>
+        <v>-0.129777757578512</v>
       </c>
       <c r="I42">
-        <v>-0.1675336116401723</v>
+        <v>-0.03066906011321069</v>
       </c>
       <c r="J42">
-        <v>-0.1675336116401723</v>
+        <v>-0.03066906011321069</v>
       </c>
       <c r="K42">
-        <v>-475.4</v>
+        <v>-101.8</v>
       </c>
       <c r="L42">
-        <v>-0.1342710275094617</v>
+        <v>-0.02313320910784893</v>
       </c>
       <c r="M42">
-        <v>123.1</v>
+        <v>70.3</v>
       </c>
       <c r="N42">
-        <v>0.06500501663410255</v>
+        <v>0.03402875260177162</v>
       </c>
       <c r="O42">
-        <v>-0.2589398401346235</v>
+        <v>-0.6905697445972495</v>
       </c>
       <c r="P42">
-        <v>123.1</v>
+        <v>70.3</v>
       </c>
       <c r="Q42">
-        <v>0.06500501663410255</v>
+        <v>0.03402875260177162</v>
       </c>
       <c r="R42">
-        <v>-0.2589398401346235</v>
+        <v>-0.6905697445972495</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -5936,73 +5948,73 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>335.9</v>
+        <v>453.9</v>
       </c>
       <c r="V42">
-        <v>0.1773776205312351</v>
+        <v>0.2197105377801442</v>
       </c>
       <c r="W42">
-        <v>-0.2216420345936873</v>
+        <v>-0.06582605884254769</v>
       </c>
       <c r="X42">
-        <v>0.08635984854703414</v>
+        <v>0.075730067518989</v>
       </c>
       <c r="Y42">
-        <v>-0.3080018831407215</v>
+        <v>-0.1415561263615367</v>
       </c>
       <c r="Z42">
-        <v>1.634514711526882</v>
+        <v>2.81762586581253</v>
       </c>
       <c r="AA42">
-        <v>-0.2738361529010929</v>
+        <v>-0.0864139370551418</v>
       </c>
       <c r="AB42">
-        <v>0.07737552889189801</v>
+        <v>0.06733134412409023</v>
       </c>
       <c r="AC42">
-        <v>-0.3512116817929909</v>
+        <v>-0.153745281179232</v>
       </c>
       <c r="AD42">
-        <v>373.2</v>
+        <v>573.6</v>
       </c>
       <c r="AE42">
-        <v>32.84752686596998</v>
+        <v>20.8113296709751</v>
       </c>
       <c r="AF42">
-        <v>406.04752686597</v>
+        <v>594.4113296709751</v>
       </c>
       <c r="AG42">
-        <v>70.14752686597001</v>
+        <v>140.5113296709751</v>
       </c>
       <c r="AH42">
-        <v>0.1765617843360918</v>
+        <v>0.2234367545788302</v>
       </c>
       <c r="AI42">
-        <v>0.2079578198630156</v>
+        <v>0.3019291455849534</v>
       </c>
       <c r="AJ42">
-        <v>0.0357194364156752</v>
+        <v>0.06368319804264623</v>
       </c>
       <c r="AK42">
-        <v>0.04339073650887765</v>
+        <v>0.09275830390144685</v>
       </c>
       <c r="AL42">
-        <v>17.1</v>
+        <v>20.8</v>
       </c>
       <c r="AM42">
-        <v>17.1</v>
+        <v>20.8</v>
       </c>
       <c r="AN42">
-        <v>-0.7466986794717887</v>
+        <v>-9.738539898132428</v>
       </c>
       <c r="AO42">
-        <v>-35.16959064327485</v>
+        <v>-6.788461538461537</v>
       </c>
       <c r="AP42">
-        <v>-0.1403511942096239</v>
+        <v>-2.385591335670206</v>
       </c>
       <c r="AQ42">
-        <v>-35.16959064327485</v>
+        <v>-6.788461538461537</v>
       </c>
     </row>
     <row r="43">
@@ -6013,7 +6025,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Unico American Corporation (NasdaqGM:UNAM)</t>
+          <t>The Allstate Corporation (NYSE:ALL)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6022,109 +6034,121 @@
         </is>
       </c>
       <c r="D43">
-        <v>-0.05980000000000001</v>
+        <v>0.0672</v>
+      </c>
+      <c r="F43">
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G43">
-        <v>-0.3135338345864662</v>
+        <v>-0.01117848008441988</v>
       </c>
       <c r="H43">
-        <v>-0.3135338345864662</v>
+        <v>-0.01117848008441988</v>
       </c>
       <c r="I43">
-        <v>-0.3469924812030075</v>
+        <v>-0.03679042785054717</v>
       </c>
       <c r="J43">
-        <v>-0.3469924812030075</v>
+        <v>-0.03679042785054717</v>
       </c>
       <c r="K43">
-        <v>-10.3</v>
+        <v>-1976</v>
       </c>
       <c r="L43">
-        <v>-0.387218045112782</v>
+        <v>-0.0353418826349019</v>
       </c>
       <c r="M43">
-        <v>-0</v>
+        <v>1625</v>
       </c>
       <c r="N43">
-        <v>-0</v>
+        <v>0.04436133329693429</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>-0.8223684210526315</v>
       </c>
       <c r="P43">
-        <v>-0</v>
+        <v>920</v>
       </c>
       <c r="Q43">
-        <v>-0</v>
+        <v>0.02511533946657203</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>-0.465587044534413</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>705</v>
+      </c>
+      <c r="T43">
+        <v>0.4338461538461538</v>
       </c>
       <c r="U43">
-        <v>11.6</v>
+        <v>860</v>
       </c>
       <c r="V43">
-        <v>1.351981351981352</v>
+        <v>0.02347738254483907</v>
       </c>
       <c r="W43">
-        <v>-0.2942857142857143</v>
+        <v>-0.125835827548876</v>
       </c>
       <c r="X43">
-        <v>0.07977107850664222</v>
+        <v>0.07432036076020163</v>
       </c>
       <c r="Y43">
-        <v>-0.3740567927923565</v>
+        <v>-0.2001561883090776</v>
       </c>
       <c r="Z43">
-        <v>0.8031400966183576</v>
+        <v>2.579164773853512</v>
       </c>
       <c r="AA43">
-        <v>-0.2786835748792271</v>
+        <v>-0.09488857552713043</v>
       </c>
       <c r="AB43">
-        <v>0.07977107850664222</v>
+        <v>0.066851759463775</v>
       </c>
       <c r="AC43">
-        <v>-0.3584546533858693</v>
+        <v>-0.1617403349909054</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>7948</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>324.9480577597141</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>8272.948057759713</v>
       </c>
       <c r="AG43">
-        <v>-11.6</v>
+        <v>7412.948057759713</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>0.1842365407851947</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>0.3641270674003232</v>
       </c>
       <c r="AJ43">
-        <v>3.841059602649007</v>
+        <v>0.1683079829273773</v>
       </c>
       <c r="AK43">
-        <v>-1.288888888888889</v>
+        <v>0.3391109639498118</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="AN43">
-        <v>-0</v>
+        <v>-6.348242811501597</v>
+      </c>
+      <c r="AO43">
+        <v>-5.876404494382022</v>
       </c>
       <c r="AP43">
-        <v>1.355140186915888</v>
+        <v>-5.920885030159515</v>
+      </c>
+      <c r="AQ43">
+        <v>-5.876404494382022</v>
       </c>
     </row>
     <row r="44">
@@ -6135,7 +6159,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lemonade, Inc. (NYSE:LMND)</t>
+          <t>Trupanion, Inc. (NasdaqGM:TRUP)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6143,32 +6167,35 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D44">
+        <v>0.298</v>
+      </c>
       <c r="G44">
-        <v>-1.09842331581462</v>
+        <v>-0.0297506611258028</v>
       </c>
       <c r="H44">
-        <v>-1.09842331581462</v>
+        <v>-0.0297506611258028</v>
       </c>
       <c r="I44">
-        <v>-1.406637976255382</v>
+        <v>-0.04316207026822819</v>
       </c>
       <c r="J44">
-        <v>-1.406637976255382</v>
+        <v>-0.04316207026822819</v>
       </c>
       <c r="K44">
-        <v>-304.4</v>
+        <v>-51.8</v>
       </c>
       <c r="L44">
-        <v>-1.45437171524128</v>
+        <v>-0.0489233094068757</v>
       </c>
       <c r="M44">
-        <v>-0</v>
+        <v>1.88</v>
       </c>
       <c r="N44">
-        <v>-0</v>
+        <v>0.001483234714003945</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>-0.03629343629343629</v>
       </c>
       <c r="P44">
         <v>-0</v>
@@ -6180,70 +6207,79 @@
         <v>0</v>
       </c>
       <c r="S44">
+        <v>1.88</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="U44">
+        <v>150.3</v>
+      </c>
+      <c r="V44">
+        <v>0.1185798816568047</v>
+      </c>
+      <c r="W44">
+        <v>-0.1694471704285247</v>
+      </c>
+      <c r="X44">
+        <v>0.07149205951140361</v>
+      </c>
+      <c r="Y44">
+        <v>-0.2409392299399283</v>
+      </c>
+      <c r="Z44">
+        <v>4.323397305022459</v>
+      </c>
+      <c r="AA44">
+        <v>-0.1866067782768477</v>
+      </c>
+      <c r="AB44">
+        <v>0.06859826563356064</v>
+      </c>
+      <c r="AC44">
+        <v>-0.2552050439104083</v>
+      </c>
+      <c r="AD44">
+        <v>128.9</v>
+      </c>
+      <c r="AE44">
         <v>0</v>
       </c>
-      <c r="U44">
-        <v>225</v>
-      </c>
-      <c r="V44">
-        <v>0.2377932783766645</v>
-      </c>
-      <c r="W44">
-        <v>-0.2904580152671756</v>
-      </c>
-      <c r="X44">
-        <v>0.08045457852874144</v>
-      </c>
-      <c r="Y44">
-        <v>-0.370912593795917</v>
-      </c>
-      <c r="Z44">
-        <v>0.2791982091714209</v>
-      </c>
-      <c r="AA44">
-        <v>-0.3927308039230143</v>
-      </c>
-      <c r="AB44">
-        <v>0.07966352713449473</v>
-      </c>
-      <c r="AC44">
-        <v>-0.4723943310575091</v>
-      </c>
-      <c r="AD44">
-        <v>0</v>
-      </c>
-      <c r="AE44">
-        <v>21.04664215125731</v>
-      </c>
       <c r="AF44">
-        <v>21.04664215125731</v>
+        <v>128.9</v>
       </c>
       <c r="AG44">
-        <v>-203.9533578487427</v>
+        <v>-21.40000000000001</v>
       </c>
       <c r="AH44">
-        <v>0.02175933338413807</v>
+        <v>0.09230879404182182</v>
       </c>
       <c r="AI44">
-        <v>0.02268331984524905</v>
+        <v>0.3080783938814532</v>
       </c>
       <c r="AJ44">
-        <v>-0.2747784176666985</v>
+        <v>-0.01717358157451249</v>
       </c>
       <c r="AK44">
-        <v>-0.2901818769802852</v>
+        <v>-0.07982096232748975</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AN44">
-        <v>-0</v>
+        <v>-3.870870870870871</v>
+      </c>
+      <c r="AO44">
+        <v>-4.583751253761283</v>
       </c>
       <c r="AP44">
-        <v>0.7227262857857641</v>
+        <v>0.6426426426426428</v>
+      </c>
+      <c r="AQ44">
+        <v>-4.583751253761283</v>
       </c>
     </row>
     <row r="45">
@@ -6254,7 +6290,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Universal Insurance Holdings, Inc. (NYSE:UVE)</t>
+          <t>Kingstone Companies, Inc. (NasdaqCM:KINS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6263,118 +6299,118 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.102</v>
+        <v>0.0565</v>
       </c>
       <c r="G45">
-        <v>0.03037974683544304</v>
+        <v>-0.1561852107809261</v>
       </c>
       <c r="H45">
-        <v>0.03037974683544304</v>
+        <v>-0.1561852107809261</v>
       </c>
       <c r="I45">
-        <v>-0.10042194092827</v>
+        <v>-0.08535485928081059</v>
       </c>
       <c r="J45">
-        <v>-0.10042194092827</v>
+        <v>-0.08535485928081059</v>
       </c>
       <c r="K45">
-        <v>-95.5</v>
+        <v>-13.1</v>
       </c>
       <c r="L45">
-        <v>-0.08059071729957806</v>
+        <v>-0.09053213545266069</v>
       </c>
       <c r="M45">
-        <v>31.1</v>
+        <v>0.014</v>
       </c>
       <c r="N45">
-        <v>0.09625502940266172</v>
+        <v>0.000611353711790393</v>
       </c>
       <c r="O45">
-        <v>-0.3256544502617801</v>
+        <v>-0.001068702290076336</v>
       </c>
       <c r="P45">
-        <v>20.8</v>
+        <v>-0</v>
       </c>
       <c r="Q45">
-        <v>0.06437635406994738</v>
+        <v>-0</v>
       </c>
       <c r="R45">
-        <v>-0.2178010471204189</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>10.3</v>
+        <v>0.014</v>
       </c>
       <c r="T45">
-        <v>0.3311897106109325</v>
+        <v>1</v>
       </c>
       <c r="U45">
-        <v>307.4</v>
+        <v>15.1</v>
       </c>
       <c r="V45">
-        <v>0.95140823274528</v>
+        <v>0.6593886462882096</v>
       </c>
       <c r="W45">
-        <v>-0.1932025085980174</v>
+        <v>-0.3367609254498715</v>
       </c>
       <c r="X45">
-        <v>0.08986168071080829</v>
+        <v>0.09447287193758463</v>
       </c>
       <c r="Y45">
-        <v>-0.2830641893088257</v>
+        <v>-0.4312337973874561</v>
       </c>
       <c r="Z45">
-        <v>4.280296189272168</v>
+        <v>2.67817941086992</v>
       </c>
       <c r="AA45">
-        <v>-0.4298356510745891</v>
+        <v>-0.2285956267435661</v>
       </c>
       <c r="AB45">
-        <v>0.07784467389949246</v>
+        <v>0.06588629845899499</v>
       </c>
       <c r="AC45">
-        <v>-0.5076803249740816</v>
+        <v>-0.2944819252025611</v>
       </c>
       <c r="AD45">
-        <v>106.1</v>
+        <v>25.2</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>0.2292406896664539</v>
       </c>
       <c r="AF45">
-        <v>106.1</v>
+        <v>25.42924068966645</v>
       </c>
       <c r="AG45">
-        <v>-201.3</v>
+        <v>10.32924068966645</v>
       </c>
       <c r="AH45">
-        <v>0.2472041006523765</v>
+        <v>0.5261667745403587</v>
       </c>
       <c r="AI45">
-        <v>0.28933733296973</v>
+        <v>0.4896902082900413</v>
       </c>
       <c r="AJ45">
-        <v>-1.652709359605911</v>
+        <v>0.3108479301749021</v>
       </c>
       <c r="AK45">
-        <v>-3.394603709949407</v>
+        <v>0.280463036876148</v>
       </c>
       <c r="AL45">
-        <v>5.54</v>
+        <v>3.65</v>
       </c>
       <c r="AM45">
-        <v>5.54</v>
+        <v>3.65</v>
       </c>
       <c r="AN45">
-        <v>-0.9464763603925067</v>
+        <v>-2.740619902120718</v>
       </c>
       <c r="AO45">
-        <v>-21.48014440433213</v>
+        <v>-3.424657534246575</v>
       </c>
       <c r="AP45">
-        <v>1.7957181088314</v>
+        <v>-1.123354071741866</v>
       </c>
       <c r="AQ45">
-        <v>-21.48014440433213</v>
+        <v>-3.424657534246575</v>
       </c>
     </row>
     <row r="46">
@@ -6385,7 +6421,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>United Insurance Holdings Corp. (NasdaqCM:UIHC)</t>
+          <t>Lemonade, Inc. (NYSE:LMND)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6393,119 +6429,107 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D46">
-        <v>-0.0382</v>
-      </c>
       <c r="G46">
-        <v>-0.1272910372608258</v>
+        <v>-0.6797223599405057</v>
       </c>
       <c r="H46">
-        <v>-0.1272910372608258</v>
+        <v>-0.6797223599405057</v>
       </c>
       <c r="I46">
-        <v>-0.2672564979915143</v>
+        <v>-0.6175074755522675</v>
       </c>
       <c r="J46">
-        <v>-0.2672564979915143</v>
+        <v>-0.6175074755522675</v>
       </c>
       <c r="K46">
-        <v>-175.4</v>
+        <v>-258.2</v>
       </c>
       <c r="L46">
-        <v>-0.3532729103726083</v>
+        <v>-0.6400594942984631</v>
       </c>
       <c r="M46">
-        <v>5.202999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N46">
-        <v>0.113355119825708</v>
+        <v>-0</v>
       </c>
       <c r="O46">
-        <v>-0.02966362599771949</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>5.18</v>
+        <v>-0</v>
       </c>
       <c r="Q46">
-        <v>0.1128540305010893</v>
+        <v>-0</v>
       </c>
       <c r="R46">
-        <v>-0.02953249714937286</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>0.02299999999999969</v>
-      </c>
-      <c r="T46">
-        <v>0.004420526619258061</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>180.9</v>
+        <v>231.7</v>
       </c>
       <c r="V46">
-        <v>3.941176470588236</v>
+        <v>0.2054260129444099</v>
       </c>
       <c r="W46">
-        <v>-0.5474406991260924</v>
+        <v>-0.2847375385972651</v>
       </c>
       <c r="X46">
-        <v>0.183768165417518</v>
+        <v>0.07003798462742038</v>
       </c>
       <c r="Y46">
-        <v>-0.7312088645436104</v>
+        <v>-0.3547755232246855</v>
       </c>
       <c r="Z46">
-        <v>2.267700502731966</v>
+        <v>0.5714588639785336</v>
       </c>
       <c r="AA46">
-        <v>-0.6060576948537417</v>
+        <v>-0.3528801204773509</v>
       </c>
       <c r="AB46">
-        <v>0.07595566093501958</v>
+        <v>0.06894719516201855</v>
       </c>
       <c r="AC46">
-        <v>-0.6820133557887613</v>
+        <v>-0.4218273156393695</v>
       </c>
       <c r="AD46">
-        <v>152.7</v>
+        <v>7.7</v>
       </c>
       <c r="AE46">
-        <v>2.644256263934239</v>
+        <v>35.01257818892336</v>
       </c>
       <c r="AF46">
-        <v>155.3442562639342</v>
+        <v>42.71257818892336</v>
       </c>
       <c r="AG46">
-        <v>-25.55574373606578</v>
+        <v>-188.9874218110766</v>
       </c>
       <c r="AH46">
-        <v>0.7719189563363159</v>
+        <v>0.03648737335028877</v>
       </c>
       <c r="AI46">
-        <v>0.6589524543495733</v>
+        <v>0.05549880472254748</v>
       </c>
       <c r="AJ46">
-        <v>-1.256165052411886</v>
+        <v>-0.2012832996396918</v>
       </c>
       <c r="AK46">
-        <v>-0.4659693735854583</v>
+        <v>-0.3513348255349799</v>
       </c>
       <c r="AL46">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="AM46">
-        <v>9.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN46">
-        <v>-1.248936727082379</v>
-      </c>
-      <c r="AO46">
-        <v>-13.90575916230367</v>
+        <v>-0.03476297968397291</v>
       </c>
       <c r="AP46">
-        <v>0.2090210015709103</v>
-      </c>
-      <c r="AQ46">
-        <v>-13.90575916230367</v>
+        <v>0.8532163512915423</v>
       </c>
     </row>
     <row r="47">
@@ -6516,7 +6540,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FedNat Holding Company (OTCPK:FNHC.Q)</t>
+          <t>Conifer Holdings, Inc. (NasdaqGM:CNFR)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6525,34 +6549,34 @@
         </is>
       </c>
       <c r="D47">
-        <v>-0.06809999999999999</v>
+        <v>0.00464</v>
       </c>
       <c r="G47">
-        <v>-0.3863829787234043</v>
+        <v>-0.1647398843930636</v>
       </c>
       <c r="H47">
-        <v>-0.3863829787234043</v>
+        <v>-0.1647398843930636</v>
       </c>
       <c r="I47">
-        <v>-0.4814402186362228</v>
+        <v>-0.123736597525165</v>
       </c>
       <c r="J47">
-        <v>-0.4814402186362228</v>
+        <v>-0.123736597525165</v>
       </c>
       <c r="K47">
-        <v>-127.6</v>
+        <v>-4.33</v>
       </c>
       <c r="L47">
-        <v>-0.5429787234042553</v>
+        <v>-0.04171483622350675</v>
       </c>
       <c r="M47">
-        <v>-0</v>
+        <v>0.003</v>
       </c>
       <c r="N47">
-        <v>-0</v>
+        <v>0.0002238805970149254</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>-0.0006928406466512702</v>
       </c>
       <c r="P47">
         <v>-0</v>
@@ -6564,76 +6588,79 @@
         <v>0</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>0.003</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
       </c>
       <c r="U47">
-        <v>87.40000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="V47">
-        <v>3121.428571428572</v>
+        <v>1.074626865671642</v>
       </c>
       <c r="W47">
-        <v>-0.86743711760707</v>
+        <v>-0.267283950617284</v>
       </c>
       <c r="X47">
-        <v>137.3609678085887</v>
+        <v>0.114498962445459</v>
       </c>
       <c r="Y47">
-        <v>-138.2284049261957</v>
+        <v>-0.381782913062743</v>
       </c>
       <c r="Z47">
-        <v>1.289138683120573</v>
+        <v>3.407826839525218</v>
       </c>
       <c r="AA47">
-        <v>-0.620643209453981</v>
+        <v>-0.4216728980777869</v>
       </c>
       <c r="AB47">
-        <v>0.07482941499623297</v>
+        <v>0.06368322145405272</v>
       </c>
       <c r="AC47">
-        <v>-0.695472624450214</v>
+        <v>-0.4853561195318395</v>
       </c>
       <c r="AD47">
-        <v>118.9</v>
+        <v>25.3</v>
       </c>
       <c r="AE47">
-        <v>6.192256897561787</v>
+        <v>1.359294115560607</v>
       </c>
       <c r="AF47">
-        <v>125.0922568975618</v>
+        <v>26.65929411556061</v>
       </c>
       <c r="AG47">
-        <v>37.69225689756179</v>
+        <v>12.25929411556061</v>
       </c>
       <c r="AH47">
-        <v>0.9997762152932365</v>
+        <v>0.6654958531884136</v>
       </c>
       <c r="AI47">
-        <v>0.8987012617348616</v>
+        <v>0.6931820962562668</v>
       </c>
       <c r="AJ47">
-        <v>0.9992576932846444</v>
+        <v>0.477772071996563</v>
       </c>
       <c r="AK47">
-        <v>0.7277585329427152</v>
+        <v>0.5095450455311479</v>
       </c>
       <c r="AL47">
-        <v>9.130000000000001</v>
+        <v>3.12</v>
       </c>
       <c r="AM47">
-        <v>9.130000000000001</v>
+        <v>3.12</v>
       </c>
       <c r="AN47">
-        <v>-1.079927338782925</v>
+        <v>-2.113264283327764</v>
       </c>
       <c r="AO47">
-        <v>-12.37677984665936</v>
+        <v>-4.134615384615385</v>
       </c>
       <c r="AP47">
-        <v>-0.3423456575618691</v>
+        <v>-1.023997169692667</v>
       </c>
       <c r="AQ47">
-        <v>-12.37677984665936</v>
+        <v>-4.134615384615385</v>
       </c>
     </row>
     <row r="48">
@@ -6644,7 +6671,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Heritage Insurance Holdings, Inc. (NYSE:HRTG)</t>
+          <t>Hallmark Financial Services, Inc. (NasdaqGM:HALL)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6653,118 +6680,115 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.103</v>
+        <v>-0.158</v>
       </c>
       <c r="G48">
-        <v>0.001351970669110907</v>
+        <v>-0.7179023508137432</v>
       </c>
       <c r="H48">
-        <v>0.001351970669110907</v>
+        <v>-0.7179023508137432</v>
       </c>
       <c r="I48">
-        <v>-0.09767579923723847</v>
+        <v>-0.5745332803290847</v>
       </c>
       <c r="J48">
-        <v>-0.09767579923723847</v>
+        <v>-0.5745332803290847</v>
       </c>
       <c r="K48">
-        <v>-216.1</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="L48">
-        <v>-0.3301252673388329</v>
+        <v>-0.4816154309825196</v>
       </c>
       <c r="M48">
-        <v>20.45</v>
+        <v>-0</v>
       </c>
       <c r="N48">
-        <v>0.4504405286343612</v>
+        <v>-0</v>
       </c>
       <c r="O48">
-        <v>-0.0946321147616844</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>6.45</v>
+        <v>-0</v>
       </c>
       <c r="Q48">
-        <v>0.1420704845814978</v>
+        <v>-0</v>
       </c>
       <c r="R48">
-        <v>-0.02984729291994447</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>14</v>
-      </c>
-      <c r="T48">
-        <v>0.684596577017115</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>297.5</v>
+        <v>75.7</v>
       </c>
       <c r="V48">
-        <v>6.552863436123348</v>
+        <v>41.36612021857923</v>
       </c>
       <c r="W48">
-        <v>-0.5335802469135802</v>
+        <v>-1.214285714285714</v>
       </c>
       <c r="X48">
-        <v>0.1971632971127908</v>
+        <v>1.621244015742531</v>
       </c>
       <c r="Y48">
-        <v>-0.730743544026371</v>
+        <v>-2.835529730028245</v>
       </c>
       <c r="Z48">
-        <v>18.84126458614309</v>
+        <v>2.729724856074644</v>
       </c>
       <c r="AA48">
-        <v>-1.840335577091803</v>
+        <v>-1.568317775956404</v>
       </c>
       <c r="AB48">
-        <v>0.07359495605362198</v>
+        <v>0.06301487633426857</v>
       </c>
       <c r="AC48">
-        <v>-1.913930533145425</v>
+        <v>-1.631332652290672</v>
       </c>
       <c r="AD48">
-        <v>144.4</v>
+        <v>105.5</v>
       </c>
       <c r="AE48">
-        <v>29.04289090348152</v>
+        <v>19.17535603297576</v>
       </c>
       <c r="AF48">
-        <v>173.4428909034815</v>
+        <v>124.6753560329758</v>
       </c>
       <c r="AG48">
-        <v>-124.0571090965185</v>
+        <v>48.97535603297577</v>
       </c>
       <c r="AH48">
-        <v>0.7925452373044038</v>
+        <v>0.9855342093221493</v>
       </c>
       <c r="AI48">
-        <v>0.5957311558089206</v>
+        <v>1.06646402067163</v>
       </c>
       <c r="AJ48">
-        <v>1.577188769349388</v>
+        <v>0.96398017565683</v>
       </c>
       <c r="AK48">
-        <v>19.51470506687694</v>
+        <v>1.188567719055305</v>
       </c>
       <c r="AL48">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="AM48">
-        <v>7.77</v>
+        <v>7.62</v>
       </c>
       <c r="AN48">
-        <v>-2.903679871305048</v>
+        <v>-1.177718240678723</v>
       </c>
       <c r="AO48">
-        <v>-8.069498069498071</v>
+        <v>-12.29658792650919</v>
       </c>
       <c r="AP48">
-        <v>2.494613092630575</v>
+        <v>-0.5467219918840787</v>
       </c>
       <c r="AQ48">
-        <v>-8.069498069498071</v>
+        <v>-12.29658792650919</v>
       </c>
     </row>
     <row r="49">
@@ -6775,7 +6799,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Atlas Financial Holdings, Inc. (OTCPK:AFHI.F)</t>
+          <t>Root, Inc. (NasdaqGS:ROOT)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6783,35 +6807,32 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D49">
-        <v>-0.491</v>
-      </c>
       <c r="G49">
-        <v>-0.9845938375350141</v>
+        <v>-0.7167420814479638</v>
       </c>
       <c r="H49">
-        <v>-0.9845938375350141</v>
+        <v>-0.7167420814479638</v>
       </c>
       <c r="I49">
-        <v>-1.744946096816675</v>
+        <v>-0.3562186371767791</v>
       </c>
       <c r="J49">
-        <v>-1.744946096816675</v>
+        <v>-0.3562186371767791</v>
       </c>
       <c r="K49">
-        <v>-12.6</v>
+        <v>-181.7</v>
       </c>
       <c r="L49">
-        <v>-1.764705882352941</v>
+        <v>-0.5481146304675716</v>
       </c>
       <c r="M49">
-        <v>-0</v>
+        <v>0.9</v>
       </c>
       <c r="N49">
-        <v>-0</v>
+        <v>0.005921052631578948</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>-0.004953219592735278</v>
       </c>
       <c r="P49">
         <v>-0</v>
@@ -6823,76 +6844,70 @@
         <v>0</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
       </c>
       <c r="U49">
-        <v>0.082</v>
+        <v>635.3</v>
       </c>
       <c r="V49">
-        <v>0.354978354978355</v>
+        <v>4.179605263157894</v>
       </c>
       <c r="W49">
-        <v>0.4864864864864865</v>
+        <v>-0.5491084919915382</v>
       </c>
       <c r="X49">
-        <v>4.907118653796467</v>
+        <v>0.1155973369244474</v>
       </c>
       <c r="Y49">
-        <v>-4.42063216730998</v>
-      </c>
-      <c r="Z49">
-        <v>1.157291910772673</v>
-      </c>
-      <c r="AA49">
-        <v>-2.019412002580287</v>
+        <v>-0.6647058289159856</v>
       </c>
       <c r="AB49">
-        <v>0.07485957289384888</v>
-      </c>
-      <c r="AC49">
-        <v>-2.094271575474136</v>
+        <v>0.06868251935894222</v>
       </c>
       <c r="AD49">
-        <v>36.1</v>
+        <v>298.3</v>
       </c>
       <c r="AE49">
-        <v>0.1895756563553068</v>
+        <v>11.43239112051144</v>
       </c>
       <c r="AF49">
-        <v>36.28957565635531</v>
+        <v>309.7323911205115</v>
       </c>
       <c r="AG49">
-        <v>36.20757565635531</v>
+        <v>-325.5676088794885</v>
       </c>
       <c r="AH49">
-        <v>0.9936747984978763</v>
+        <v>0.6708049880773294</v>
       </c>
       <c r="AI49">
-        <v>9.096099129877823</v>
+        <v>0.5172271836213677</v>
       </c>
       <c r="AJ49">
-        <v>0.9936605645023419</v>
+        <v>1.8757394365301</v>
       </c>
       <c r="AK49">
-        <v>9.265994785658728</v>
+        <v>8.9275831041011</v>
       </c>
       <c r="AL49">
-        <v>2.77</v>
+        <v>45</v>
       </c>
       <c r="AM49">
-        <v>2.77</v>
+        <v>45</v>
       </c>
       <c r="AN49">
-        <v>-2.978302120287105</v>
+        <v>-2.785247432306256</v>
       </c>
       <c r="AO49">
-        <v>-4.548736462093863</v>
+        <v>-2.644444444444444</v>
       </c>
       <c r="AP49">
-        <v>-2.98717726725149</v>
+        <v>3.039846954990556</v>
       </c>
       <c r="AQ49">
-        <v>-4.548736462093863</v>
+        <v>-2.644444444444444</v>
       </c>
     </row>
     <row r="50">
@@ -6903,7 +6918,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Root, Inc. (NasdaqGS:ROOT)</t>
+          <t>American Coastal Insurance Corporation (NasdaqCM:ACIC)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6911,32 +6926,35 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D50">
+        <v>-0.076</v>
+      </c>
       <c r="G50">
-        <v>-1.419597234746018</v>
+        <v>-0.8641293226928587</v>
       </c>
       <c r="H50">
-        <v>-1.419597234746018</v>
+        <v>-0.8641293226928587</v>
       </c>
       <c r="I50">
-        <v>-0.8671306664394877</v>
+        <v>-0.7184183278132029</v>
       </c>
       <c r="J50">
-        <v>-0.8671306664394877</v>
+        <v>-0.7184183278132029</v>
       </c>
       <c r="K50">
-        <v>-340.2</v>
+        <v>-1.14</v>
       </c>
       <c r="L50">
-        <v>-1.022542831379621</v>
+        <v>-0.002332719459791283</v>
       </c>
       <c r="M50">
-        <v>-0</v>
+        <v>0.025</v>
       </c>
       <c r="N50">
-        <v>-0</v>
+        <v>6.019744762822057e-05</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>-0.02192982456140351</v>
       </c>
       <c r="P50">
         <v>-0</v>
@@ -6948,320 +6966,70 @@
         <v>0</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>0.025</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
       </c>
       <c r="U50">
-        <v>819.7</v>
+        <v>111.1</v>
       </c>
       <c r="V50">
-        <v>12.94944707740916</v>
+        <v>0.2675174572598122</v>
       </c>
       <c r="W50">
-        <v>-0.5349056603773584</v>
+        <v>-0.01417910447761194</v>
       </c>
       <c r="X50">
-        <v>0.2297096255795503</v>
+        <v>0.0774140157625689</v>
       </c>
       <c r="Y50">
-        <v>-0.7646152859569088</v>
-      </c>
-      <c r="Z50">
-        <v>17.91419573016451</v>
-      </c>
-      <c r="AA50">
-        <v>-15.53394848222498</v>
+        <v>-0.09159312024018083</v>
       </c>
       <c r="AB50">
-        <v>0.07566898854427065</v>
-      </c>
-      <c r="AC50">
-        <v>-15.60961747076925</v>
+        <v>0.06898017509129253</v>
       </c>
       <c r="AD50">
-        <v>293.9</v>
+        <v>148.6</v>
       </c>
       <c r="AE50">
-        <v>14.97186362208761</v>
+        <v>1.590184011561589</v>
       </c>
       <c r="AF50">
-        <v>308.8718636220876</v>
+        <v>150.1901840115616</v>
       </c>
       <c r="AG50">
-        <v>-510.8281363779125</v>
+        <v>39.09018401156158</v>
       </c>
       <c r="AH50">
-        <v>0.8299172877177078</v>
+        <v>0.2655929108196348</v>
       </c>
       <c r="AI50">
-        <v>0.4108585045121563</v>
+        <v>0.5546367367775381</v>
       </c>
       <c r="AJ50">
-        <v>1.141443620757169</v>
+        <v>0.08602779150389164</v>
       </c>
       <c r="AK50">
-        <v>7.520125880326864</v>
+        <v>0.2447876446102125</v>
       </c>
       <c r="AL50">
-        <v>26.1</v>
+        <v>10.7</v>
       </c>
       <c r="AM50">
-        <v>26.1</v>
+        <v>10.7</v>
       </c>
       <c r="AN50">
-        <v>-1.066787658802178</v>
+        <v>-0.4344101989926127</v>
       </c>
       <c r="AO50">
-        <v>-11.10344827586207</v>
+        <v>-32.86915887850468</v>
       </c>
       <c r="AP50">
-        <v>1.854185612986978</v>
+        <v>-0.1142743917572026</v>
       </c>
       <c r="AQ50">
-        <v>-11.10344827586207</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>HCI Group, Inc. (NYSE:HCI)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D51">
-        <v>0.14</v>
-      </c>
-      <c r="F51">
-        <v>0.25</v>
-      </c>
-      <c r="G51">
-        <v>0.04879040455377109</v>
-      </c>
-      <c r="H51">
-        <v>0.04879040455377109</v>
-      </c>
-      <c r="I51">
-        <v>-0.1252220374048718</v>
-      </c>
-      <c r="J51">
-        <v>-0.1252220374048718</v>
-      </c>
-      <c r="K51">
-        <v>-60</v>
-      </c>
-      <c r="L51">
-        <v>-0.1219760113844277</v>
-      </c>
-      <c r="M51">
-        <v>92.10000000000001</v>
-      </c>
-      <c r="N51">
-        <v>0.2656475338909721</v>
-      </c>
-      <c r="O51">
-        <v>-1.535</v>
-      </c>
-      <c r="P51">
-        <v>15.9</v>
-      </c>
-      <c r="Q51">
-        <v>0.04586097490625902</v>
-      </c>
-      <c r="R51">
-        <v>-0.265</v>
-      </c>
-      <c r="S51">
-        <v>76.2</v>
-      </c>
-      <c r="T51">
-        <v>0.8273615635179152</v>
-      </c>
-      <c r="U51">
-        <v>355.7</v>
-      </c>
-      <c r="V51">
-        <v>1.025959042399769</v>
-      </c>
-      <c r="W51">
-        <v>-0.2058319039451115</v>
-      </c>
-      <c r="X51">
-        <v>0.09871889657678715</v>
-      </c>
-      <c r="Y51">
-        <v>-0.3045508005218986</v>
-      </c>
-      <c r="AB51">
-        <v>0.07679870545314799</v>
-      </c>
-      <c r="AD51">
-        <v>211.7</v>
-      </c>
-      <c r="AE51">
-        <v>2.083600997282181</v>
-      </c>
-      <c r="AF51">
-        <v>213.7836009972822</v>
-      </c>
-      <c r="AG51">
-        <v>-141.9163990027178</v>
-      </c>
-      <c r="AH51">
-        <v>0.3814270401790379</v>
-      </c>
-      <c r="AI51">
-        <v>0.4470743048306612</v>
-      </c>
-      <c r="AJ51">
-        <v>-0.6930066583046427</v>
-      </c>
-      <c r="AK51">
-        <v>-1.158656324987268</v>
-      </c>
-      <c r="AL51">
-        <v>5.59</v>
-      </c>
-      <c r="AM51">
-        <v>5.59</v>
-      </c>
-      <c r="AN51">
-        <v>-3.843500363108206</v>
-      </c>
-      <c r="AO51">
-        <v>-11.19856887298748</v>
-      </c>
-      <c r="AP51">
-        <v>2.576550453934601</v>
-      </c>
-      <c r="AQ51">
-        <v>-11.19856887298748</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Hallmark Financial Services, Inc. (NasdaqGM:HALL)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>-0.0186</v>
-      </c>
-      <c r="G52">
-        <v>0.0567113137646053</v>
-      </c>
-      <c r="H52">
-        <v>0.0567113137646053</v>
-      </c>
-      <c r="I52">
-        <v>-0.2326234236343938</v>
-      </c>
-      <c r="J52">
-        <v>-0.2326234236343938</v>
-      </c>
-      <c r="K52">
-        <v>-103.4</v>
-      </c>
-      <c r="L52">
-        <v>-0.2946708463949844</v>
-      </c>
-      <c r="M52">
-        <v>-0</v>
-      </c>
-      <c r="N52">
-        <v>-0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>-0</v>
-      </c>
-      <c r="Q52">
-        <v>-0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>129.5</v>
-      </c>
-      <c r="V52">
-        <v>12.21698113207547</v>
-      </c>
-      <c r="W52">
-        <v>-0.5815523059617548</v>
-      </c>
-      <c r="X52">
-        <v>0.4429675047269</v>
-      </c>
-      <c r="Y52">
-        <v>-1.024519810688655</v>
-      </c>
-      <c r="AB52">
-        <v>0.07258618802739705</v>
-      </c>
-      <c r="AD52">
-        <v>105.3</v>
-      </c>
-      <c r="AE52">
-        <v>19.98779676654398</v>
-      </c>
-      <c r="AF52">
-        <v>125.287796766544</v>
-      </c>
-      <c r="AG52">
-        <v>-4.212203233456023</v>
-      </c>
-      <c r="AH52">
-        <v>0.921994467110164</v>
-      </c>
-      <c r="AI52">
-        <v>0.6556556665918899</v>
-      </c>
-      <c r="AJ52">
-        <v>-0.6594140965031005</v>
-      </c>
-      <c r="AK52">
-        <v>-0.06839347167139119</v>
-      </c>
-      <c r="AL52">
-        <v>5.41</v>
-      </c>
-      <c r="AM52">
-        <v>5.41</v>
-      </c>
-      <c r="AN52">
-        <v>-1.416655455401588</v>
-      </c>
-      <c r="AO52">
-        <v>-14.75046210720887</v>
-      </c>
-      <c r="AP52">
-        <v>0.05666895242104161</v>
-      </c>
-      <c r="AQ52">
-        <v>-14.75046210720887</v>
+        <v>-32.86915887850468</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05719999999999999</v>
+        <v>0.0755</v>
       </c>
       <c r="E2">
-        <v>0.194</v>
+        <v>0.118</v>
       </c>
       <c r="F2">
-        <v>0.179</v>
+        <v>0.157</v>
       </c>
       <c r="G2">
-        <v>0.1162169937983505</v>
+        <v>0.09484963737817985</v>
       </c>
       <c r="H2">
-        <v>0.1162169937983505</v>
+        <v>0.09484963737817985</v>
       </c>
       <c r="I2">
-        <v>0.1386099265400012</v>
+        <v>0.1373118071733863</v>
       </c>
       <c r="J2">
-        <v>0.1098931331467856</v>
+        <v>0.1129775513079826</v>
       </c>
       <c r="K2">
-        <v>6216</v>
+        <v>37117.57</v>
       </c>
       <c r="L2">
-        <v>0.09935426123649382</v>
+        <v>0.09916481833643333</v>
       </c>
       <c r="M2">
-        <v>2325</v>
+        <v>11706.007</v>
       </c>
       <c r="N2">
-        <v>0.0317926544610222</v>
+        <v>0.02281324755801637</v>
       </c>
       <c r="O2">
-        <v>0.374034749034749</v>
+        <v>0.3153764376277865</v>
       </c>
       <c r="P2">
-        <v>999</v>
+        <v>6261.217</v>
       </c>
       <c r="Q2">
-        <v>0.01366058572325212</v>
+        <v>0.01220217051258047</v>
       </c>
       <c r="R2">
-        <v>0.1607142857142857</v>
+        <v>0.1686860696969117</v>
       </c>
       <c r="S2">
-        <v>1326</v>
+        <v>5444.79</v>
       </c>
       <c r="T2">
-        <v>0.5703225806451613</v>
+        <v>0.4651278612766933</v>
       </c>
       <c r="U2">
-        <v>1320</v>
+        <v>26762.808</v>
       </c>
       <c r="V2">
-        <v>0.01805002317787067</v>
+        <v>0.05215668880529978</v>
       </c>
       <c r="W2">
-        <v>0.1715973568987902</v>
+        <v>0.1690218882649561</v>
       </c>
       <c r="X2">
-        <v>0.08181218707589334</v>
+        <v>0.07772388427249186</v>
       </c>
       <c r="Y2">
-        <v>0.08978516982289687</v>
+        <v>0.09129800399246427</v>
       </c>
       <c r="Z2">
-        <v>1.342084273676151</v>
+        <v>1.906019677529167</v>
       </c>
       <c r="AA2">
-        <v>0.1478221028481652</v>
+        <v>0.1940798113815241</v>
       </c>
       <c r="AB2">
-        <v>0.07146778284040908</v>
+        <v>0.07275602231344144</v>
       </c>
       <c r="AC2">
-        <v>0.07635432000775609</v>
+        <v>0.1223796281579822</v>
       </c>
       <c r="AD2">
-        <v>17567</v>
+        <v>75367.492</v>
       </c>
       <c r="AE2">
-        <v>630.0427797568332</v>
+        <v>3853.547068743034</v>
       </c>
       <c r="AF2">
-        <v>18197.04277975683</v>
+        <v>79221.03906874303</v>
       </c>
       <c r="AG2">
-        <v>16877.04277975683</v>
+        <v>52458.23106874303</v>
       </c>
       <c r="AH2">
-        <v>0.1992511998720966</v>
+        <v>0.1337415499911722</v>
       </c>
       <c r="AI2">
-        <v>0.2837035693704046</v>
+        <v>0.2646075754971278</v>
       </c>
       <c r="AJ2">
-        <v>0.1875078161413717</v>
+        <v>0.0927509753990659</v>
       </c>
       <c r="AK2">
-        <v>0.2686527003209061</v>
+        <v>0.1924169850546408</v>
       </c>
       <c r="AL2">
-        <v>819</v>
+        <v>3492.646</v>
       </c>
       <c r="AM2">
-        <v>819</v>
+        <v>3429.246</v>
       </c>
       <c r="AN2">
-        <v>1.740858190466753</v>
+        <v>1.373843268231983</v>
       </c>
       <c r="AO2">
-        <v>10.57387057387057</v>
+        <v>14.64017824881193</v>
       </c>
       <c r="AP2">
-        <v>1.67248466750142</v>
+        <v>0.9562396957185526</v>
       </c>
       <c r="AQ2">
-        <v>10.57387057387057</v>
+        <v>14.91084629099225</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
+          <t>Bowhead Specialty Holdings Inc. (NYSE:BOW)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,107 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.139</v>
-      </c>
-      <c r="F3">
-        <v>0.179</v>
-      </c>
       <c r="G3">
-        <v>0.09856203961007455</v>
+        <v>0.08455409920328963</v>
       </c>
       <c r="H3">
-        <v>0.09856203961007455</v>
+        <v>0.08455409920328963</v>
       </c>
       <c r="I3">
-        <v>0.1330495401382684</v>
+        <v>0.1172996066395147</v>
       </c>
       <c r="J3">
-        <v>0.1078401535857544</v>
+        <v>0.09057623168857017</v>
       </c>
       <c r="K3">
-        <v>4543</v>
+        <v>29.4</v>
       </c>
       <c r="L3">
-        <v>0.1001940805434255</v>
+        <v>0.07555898226676946</v>
       </c>
       <c r="M3">
-        <v>1867</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03413999041812803</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.4109619194364957</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>943</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01724371235366616</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.2075720889280211</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>924</v>
-      </c>
-      <c r="T3">
-        <v>0.4949116229244778</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>772</v>
+        <v>132.9</v>
       </c>
       <c r="V3">
-        <v>0.01411680375082744</v>
-      </c>
-      <c r="W3">
-        <v>0.2274001401541696</v>
+        <v>0.1145689655172414</v>
       </c>
       <c r="X3">
-        <v>0.07765159069914243</v>
-      </c>
-      <c r="Y3">
-        <v>0.1497485494550272</v>
+        <v>0.07440371830529449</v>
       </c>
       <c r="Z3">
-        <v>1.914187172670229</v>
+        <v>634.1106730738984</v>
       </c>
       <c r="AA3">
-        <v>0.2064262386926384</v>
+        <v>5</v>
       </c>
       <c r="AB3">
-        <v>0.07280633415532219</v>
+        <v>0.07438730023481029</v>
       </c>
       <c r="AC3">
-        <v>0.1336199045373163</v>
+        <v>4.92561269976519</v>
       </c>
       <c r="AD3">
-        <v>8033</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>226.3387552531685</v>
+        <v>0.6136152828240676</v>
       </c>
       <c r="AF3">
-        <v>8259.338755253168</v>
+        <v>0.6136152828240676</v>
       </c>
       <c r="AG3">
-        <v>7487.338755253168</v>
+        <v>-132.2863847171759</v>
       </c>
       <c r="AH3">
-        <v>0.1312132111869391</v>
+        <v>0.0005286990215727729</v>
       </c>
       <c r="AI3">
-        <v>0.2297110538013345</v>
+        <v>0.001679234864713893</v>
       </c>
       <c r="AJ3">
-        <v>0.1204256784297834</v>
+        <v>-0.1287191127469602</v>
       </c>
       <c r="AK3">
-        <v>0.2128092165254</v>
+        <v>-0.5689403803569348</v>
       </c>
       <c r="AL3">
-        <v>392</v>
+        <v>0.477</v>
       </c>
       <c r="AM3">
-        <v>392</v>
+        <v>0.477</v>
       </c>
       <c r="AN3">
-        <v>1.181323529411765</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>15.2984693877551</v>
+        <v>94.75890985324949</v>
       </c>
       <c r="AP3">
-        <v>1.101079228713701</v>
+        <v>-2.798882547333614</v>
       </c>
       <c r="AQ3">
-        <v>15.2984693877551</v>
+        <v>94.75890985324949</v>
       </c>
     </row>
     <row r="4">
@@ -853,130 +835,6243 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>HCI Group, Inc. (NYSE:HCI)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.265</v>
+      </c>
+      <c r="E4">
+        <v>0.6559999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.25</v>
+      </c>
+      <c r="G4">
+        <v>0.1807405434203516</v>
+      </c>
+      <c r="H4">
+        <v>0.1807405434203516</v>
+      </c>
+      <c r="I4">
+        <v>0.3123476443505241</v>
+      </c>
+      <c r="J4">
+        <v>0.2316190921570869</v>
+      </c>
+      <c r="K4">
+        <v>145.5</v>
+      </c>
+      <c r="L4">
+        <v>0.1937932871603623</v>
+      </c>
+      <c r="M4">
+        <v>16.84</v>
+      </c>
+      <c r="N4">
+        <v>0.01371447186252952</v>
+      </c>
+      <c r="O4">
+        <v>0.1157388316151203</v>
+      </c>
+      <c r="P4">
+        <v>15.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.01286749735320466</v>
+      </c>
+      <c r="R4">
+        <v>0.1085910652920962</v>
+      </c>
+      <c r="S4">
+        <v>1.039999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0.06175771971496432</v>
+      </c>
+      <c r="U4">
+        <v>518.8</v>
+      </c>
+      <c r="V4">
+        <v>0.4225099763824415</v>
+      </c>
+      <c r="W4">
+        <v>0.727863931965983</v>
+      </c>
+      <c r="X4">
+        <v>0.07845230932911759</v>
+      </c>
+      <c r="Y4">
+        <v>0.6494116226368654</v>
+      </c>
+      <c r="Z4">
+        <v>8.773903837280594</v>
+      </c>
+      <c r="AA4">
+        <v>2.032203641464512</v>
+      </c>
+      <c r="AB4">
+        <v>0.07256600961539189</v>
+      </c>
+      <c r="AC4">
+        <v>1.95963763184912</v>
+      </c>
+      <c r="AD4">
+        <v>231.1</v>
+      </c>
+      <c r="AE4">
+        <v>1.371943108132393</v>
+      </c>
+      <c r="AF4">
+        <v>232.4719431081324</v>
+      </c>
+      <c r="AG4">
+        <v>-286.3280568918676</v>
+      </c>
+      <c r="AH4">
+        <v>0.1591868045707306</v>
+      </c>
+      <c r="AI4">
+        <v>0.3317842899159097</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.3040957825768444</v>
+      </c>
+      <c r="AK4">
+        <v>-1.574338801239015</v>
+      </c>
+      <c r="AL4">
+        <v>12.8</v>
+      </c>
+      <c r="AM4">
+        <v>12.8</v>
+      </c>
+      <c r="AN4">
+        <v>0.9722952647411489</v>
+      </c>
+      <c r="AO4">
+        <v>18.3203125</v>
+      </c>
+      <c r="AP4">
+        <v>-1.204653456852</v>
+      </c>
+      <c r="AQ4">
+        <v>18.3203125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tiptree Inc. (NasdaqCM:TIPT)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.229</v>
+      </c>
+      <c r="E5">
+        <v>0.231</v>
+      </c>
+      <c r="G5">
+        <v>0.06899677679290894</v>
+      </c>
+      <c r="H5">
+        <v>0.06899677679290894</v>
+      </c>
+      <c r="I5">
+        <v>0.08688638249423418</v>
+      </c>
+      <c r="J5">
+        <v>0.04717955900743764</v>
+      </c>
+      <c r="K5">
+        <v>40.7</v>
+      </c>
+      <c r="L5">
+        <v>0.02049758259468171</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>0.01940491591203105</v>
+      </c>
+      <c r="O5">
+        <v>0.3685503685503685</v>
+      </c>
+      <c r="P5">
+        <v>15</v>
+      </c>
+      <c r="Q5">
+        <v>0.01940491591203105</v>
+      </c>
+      <c r="R5">
+        <v>0.3685503685503685</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>396.2</v>
+      </c>
+      <c r="V5">
+        <v>0.51254851228978</v>
+      </c>
+      <c r="W5">
+        <v>0.1027518303458722</v>
+      </c>
+      <c r="X5">
+        <v>0.08772894193832803</v>
+      </c>
+      <c r="Y5">
+        <v>0.01502288840754422</v>
+      </c>
+      <c r="Z5">
+        <v>24.23177529128396</v>
+      </c>
+      <c r="AA5">
+        <v>1.143244472210101</v>
+      </c>
+      <c r="AB5">
+        <v>0.06999306613514084</v>
+      </c>
+      <c r="AC5">
+        <v>1.07325140607496</v>
+      </c>
+      <c r="AD5">
+        <v>432.8</v>
+      </c>
+      <c r="AE5">
+        <v>47.94199459724313</v>
+      </c>
+      <c r="AF5">
+        <v>480.7419945972431</v>
+      </c>
+      <c r="AG5">
+        <v>84.54199459724316</v>
+      </c>
+      <c r="AH5">
+        <v>0.383445714244962</v>
+      </c>
+      <c r="AI5">
+        <v>0.4228377497548096</v>
+      </c>
+      <c r="AJ5">
+        <v>0.09858641924230138</v>
+      </c>
+      <c r="AK5">
+        <v>0.1141314995151725</v>
+      </c>
+      <c r="AL5">
+        <v>31.4</v>
+      </c>
+      <c r="AM5">
+        <v>31.4</v>
+      </c>
+      <c r="AN5">
+        <v>2.118349566834712</v>
+      </c>
+      <c r="AO5">
+        <v>5.490445859872612</v>
+      </c>
+      <c r="AP5">
+        <v>0.4137927394510458</v>
+      </c>
+      <c r="AQ5">
+        <v>5.490445859872612</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Heritage Insurance Holdings, Inc. (NYSE:HRTG)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0978</v>
+      </c>
+      <c r="E6">
+        <v>0.296</v>
+      </c>
+      <c r="G6">
+        <v>0.09159632102809626</v>
+      </c>
+      <c r="H6">
+        <v>0.09159632102809626</v>
+      </c>
+      <c r="I6">
+        <v>0.1241798732999281</v>
+      </c>
+      <c r="J6">
+        <v>0.1031736116485018</v>
+      </c>
+      <c r="K6">
+        <v>72.2</v>
+      </c>
+      <c r="L6">
+        <v>0.09096636008567469</v>
+      </c>
+      <c r="M6">
+        <v>0.432</v>
+      </c>
+      <c r="N6">
+        <v>0.001225531914893617</v>
+      </c>
+      <c r="O6">
+        <v>0.005983379501385042</v>
+      </c>
+      <c r="P6">
+        <v>0.011</v>
+      </c>
+      <c r="Q6">
+        <v>3.120567375886524E-05</v>
+      </c>
+      <c r="R6">
+        <v>0.0001523545706371191</v>
+      </c>
+      <c r="S6">
+        <v>0.421</v>
+      </c>
+      <c r="T6">
+        <v>0.974537037037037</v>
+      </c>
+      <c r="U6">
+        <v>509.9</v>
+      </c>
+      <c r="V6">
+        <v>1.446524822695035</v>
+      </c>
+      <c r="W6">
+        <v>0.476882430647292</v>
+      </c>
+      <c r="X6">
+        <v>0.0831825329324534</v>
+      </c>
+      <c r="Y6">
+        <v>0.3936998977148386</v>
+      </c>
+      <c r="Z6">
+        <v>10.88868625273633</v>
+      </c>
+      <c r="AA6">
+        <v>1.1234250868022</v>
+      </c>
+      <c r="AB6">
+        <v>0.07552678882390104</v>
+      </c>
+      <c r="AC6">
+        <v>1.047898297978298</v>
+      </c>
+      <c r="AD6">
+        <v>137.2</v>
+      </c>
+      <c r="AE6">
+        <v>7.292172809235188</v>
+      </c>
+      <c r="AF6">
+        <v>144.4921728092352</v>
+      </c>
+      <c r="AG6">
+        <v>-365.4078271907648</v>
+      </c>
+      <c r="AH6">
+        <v>0.2907332966483093</v>
+      </c>
+      <c r="AI6">
+        <v>0.3409505462345491</v>
+      </c>
+      <c r="AJ6">
+        <v>28.30901140760577</v>
+      </c>
+      <c r="AK6">
+        <v>4.243607568696791</v>
+      </c>
+      <c r="AL6">
+        <v>11.4</v>
+      </c>
+      <c r="AM6">
+        <v>11.4</v>
+      </c>
+      <c r="AN6">
+        <v>1.259640102827763</v>
+      </c>
+      <c r="AO6">
+        <v>8.62280701754386</v>
+      </c>
+      <c r="AP6">
+        <v>-3.354827645893911</v>
+      </c>
+      <c r="AQ6">
+        <v>8.62280701754386</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Universal Insurance Holdings, Inc. (NYSE:UVE)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.105</v>
+      </c>
+      <c r="E7">
+        <v>-0.0436</v>
+      </c>
+      <c r="G7">
+        <v>0.06762837480148226</v>
+      </c>
+      <c r="H7">
+        <v>0.06762837480148226</v>
+      </c>
+      <c r="I7">
+        <v>0.07259131815775542</v>
+      </c>
+      <c r="J7">
+        <v>0.05127816951260048</v>
+      </c>
+      <c r="K7">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="L7">
+        <v>0.04823980942297512</v>
+      </c>
+      <c r="M7">
+        <v>40.3</v>
+      </c>
+      <c r="N7">
+        <v>0.06765150243411112</v>
+      </c>
+      <c r="O7">
+        <v>0.5528120713305897</v>
+      </c>
+      <c r="P7">
+        <v>22.4</v>
+      </c>
+      <c r="Q7">
+        <v>0.03760282021151586</v>
+      </c>
+      <c r="R7">
+        <v>0.3072702331961591</v>
+      </c>
+      <c r="S7">
+        <v>17.9</v>
+      </c>
+      <c r="T7">
+        <v>0.4441687344913151</v>
+      </c>
+      <c r="U7">
+        <v>333.7</v>
+      </c>
+      <c r="V7">
+        <v>0.560181299311734</v>
+      </c>
+      <c r="W7">
+        <v>0.2417910447761194</v>
+      </c>
+      <c r="X7">
+        <v>0.07804261831450282</v>
+      </c>
+      <c r="Y7">
+        <v>0.1637484264616166</v>
+      </c>
+      <c r="Z7">
+        <v>20.87292817679559</v>
+      </c>
+      <c r="AA7">
+        <v>1.070325549274059</v>
+      </c>
+      <c r="AB7">
+        <v>0.0727235012623</v>
+      </c>
+      <c r="AC7">
+        <v>0.9976020480117591</v>
+      </c>
+      <c r="AD7">
+        <v>101.4</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>101.4</v>
+      </c>
+      <c r="AG7">
+        <v>-232.3</v>
+      </c>
+      <c r="AH7">
+        <v>0.1454597618706068</v>
+      </c>
+      <c r="AI7">
+        <v>0.2021531100478469</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.6392405063291137</v>
+      </c>
+      <c r="AK7">
+        <v>-1.383561643835616</v>
+      </c>
+      <c r="AL7">
+        <v>6.5</v>
+      </c>
+      <c r="AM7">
+        <v>6.5</v>
+      </c>
+      <c r="AN7">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AO7">
+        <v>16.87692307692308</v>
+      </c>
+      <c r="AP7">
+        <v>-1.985470085470085</v>
+      </c>
+      <c r="AQ7">
+        <v>16.87692307692308</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>American Coastal Insurance Corporation (NasdaqCM:ACIC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.182</v>
+      </c>
+      <c r="G8">
+        <v>0.3696698762035763</v>
+      </c>
+      <c r="H8">
+        <v>0.3696698762035763</v>
+      </c>
+      <c r="I8">
+        <v>0.4059325686999869</v>
+      </c>
+      <c r="J8">
+        <v>0.3164708455705132</v>
+      </c>
+      <c r="K8">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="L8">
+        <v>0.2926409903713892</v>
+      </c>
+      <c r="M8">
+        <v>0.024</v>
+      </c>
+      <c r="N8">
+        <v>3.699136868064118E-05</v>
+      </c>
+      <c r="O8">
+        <v>0.000282021151586369</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>0.024</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>183.1</v>
+      </c>
+      <c r="V8">
+        <v>0.2822133168927251</v>
+      </c>
+      <c r="W8">
+        <v>0.7056384742951907</v>
+      </c>
+      <c r="X8">
+        <v>0.07933893858695136</v>
+      </c>
+      <c r="Y8">
+        <v>0.6262995357082393</v>
+      </c>
+      <c r="Z8">
+        <v>2.926759206244541</v>
+      </c>
+      <c r="AA8">
+        <v>0.9262339607814939</v>
+      </c>
+      <c r="AB8">
+        <v>0.0751237279320318</v>
+      </c>
+      <c r="AC8">
+        <v>0.8511102328494621</v>
+      </c>
+      <c r="AD8">
+        <v>148.9</v>
+      </c>
+      <c r="AE8">
+        <v>0.7590451102189796</v>
+      </c>
+      <c r="AF8">
+        <v>149.659045110219</v>
+      </c>
+      <c r="AG8">
+        <v>-33.44095488978101</v>
+      </c>
+      <c r="AH8">
+        <v>0.1874348421834962</v>
+      </c>
+      <c r="AI8">
+        <v>0.3656829260057374</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.05434380977335158</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1478647686785355</v>
+      </c>
+      <c r="AL8">
+        <v>11.9</v>
+      </c>
+      <c r="AM8">
+        <v>11.9</v>
+      </c>
+      <c r="AN8">
+        <v>1.16878733408165</v>
+      </c>
+      <c r="AO8">
+        <v>9.882352941176469</v>
+      </c>
+      <c r="AP8">
+        <v>-0.2624940531549488</v>
+      </c>
+      <c r="AQ8">
+        <v>9.882352941176469</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kingstone Companies, Inc. (NasdaqCM:KINS)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.017</v>
+      </c>
+      <c r="G9">
+        <v>-0.002606951871657754</v>
+      </c>
+      <c r="H9">
+        <v>-0.002606951871657754</v>
+      </c>
+      <c r="I9">
+        <v>0.1633682520059689</v>
+      </c>
+      <c r="J9">
+        <v>0.1263912427714472</v>
+      </c>
+      <c r="K9">
+        <v>15.9</v>
+      </c>
+      <c r="L9">
+        <v>0.1062834224598931</v>
+      </c>
+      <c r="M9">
+        <v>0.973</v>
+      </c>
+      <c r="N9">
+        <v>0.005186567164179105</v>
+      </c>
+      <c r="O9">
+        <v>0.06119496855345911</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>0.973</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>33.8</v>
+      </c>
+      <c r="V9">
+        <v>0.1801705756929637</v>
+      </c>
+      <c r="W9">
+        <v>0.6</v>
+      </c>
+      <c r="X9">
+        <v>0.076375118850562</v>
+      </c>
+      <c r="Y9">
+        <v>0.5236248811494379</v>
+      </c>
+      <c r="Z9">
+        <v>4.08235134164382</v>
+      </c>
+      <c r="AA9">
+        <v>0.5159734595000472</v>
+      </c>
+      <c r="AB9">
+        <v>0.07472261221849057</v>
+      </c>
+      <c r="AC9">
+        <v>0.4412508472815567</v>
+      </c>
+      <c r="AD9">
+        <v>17.3</v>
+      </c>
+      <c r="AE9">
+        <v>0.04554749953522959</v>
+      </c>
+      <c r="AF9">
+        <v>17.34554749953523</v>
+      </c>
+      <c r="AG9">
+        <v>-16.45445250046477</v>
+      </c>
+      <c r="AH9">
+        <v>0.08463490771652195</v>
+      </c>
+      <c r="AI9">
+        <v>0.2251336782263746</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.09614303580120571</v>
+      </c>
+      <c r="AK9">
+        <v>-0.3804889393674946</v>
+      </c>
+      <c r="AL9">
+        <v>3.88</v>
+      </c>
+      <c r="AM9">
+        <v>3.88</v>
+      </c>
+      <c r="AN9">
+        <v>0.6419533192326247</v>
+      </c>
+      <c r="AO9">
+        <v>6.288659793814433</v>
+      </c>
+      <c r="AP9">
+        <v>-0.6105774797010936</v>
+      </c>
+      <c r="AQ9">
+        <v>6.288659793814433</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kinsale Capital Group, Inc. (NYSE:KNSL)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.404</v>
+      </c>
+      <c r="E10">
+        <v>0.523</v>
+      </c>
+      <c r="F10">
+        <v>0.15</v>
+      </c>
+      <c r="G10">
+        <v>0.2604480545001965</v>
+      </c>
+      <c r="H10">
+        <v>0.2604480545001965</v>
+      </c>
+      <c r="I10">
+        <v>0.3380715315079261</v>
+      </c>
+      <c r="J10">
+        <v>0.2732761579527614</v>
+      </c>
+      <c r="K10">
+        <v>409.1</v>
+      </c>
+      <c r="L10">
+        <v>0.2679811345473602</v>
+      </c>
+      <c r="M10">
+        <v>20.71</v>
+      </c>
+      <c r="N10">
+        <v>0.001911945272759165</v>
+      </c>
+      <c r="O10">
+        <v>0.0506233194817893</v>
+      </c>
+      <c r="P10">
+        <v>13.7</v>
+      </c>
+      <c r="Q10">
+        <v>0.001264782725099013</v>
+      </c>
+      <c r="R10">
+        <v>0.03348814470789538</v>
+      </c>
+      <c r="S10">
+        <v>7.010000000000002</v>
+      </c>
+      <c r="T10">
+        <v>0.3384838242394979</v>
+      </c>
+      <c r="U10">
+        <v>111.7</v>
+      </c>
+      <c r="V10">
+        <v>0.01031213360536933</v>
+      </c>
+      <c r="W10">
+        <v>0.4428447715955835</v>
+      </c>
+      <c r="X10">
+        <v>0.07475684377270443</v>
+      </c>
+      <c r="Y10">
+        <v>0.3680879278228791</v>
+      </c>
+      <c r="Z10">
+        <v>1.615962739494019</v>
+      </c>
+      <c r="AA10">
+        <v>0.4416040888437447</v>
+      </c>
+      <c r="AB10">
+        <v>0.07420063576266858</v>
+      </c>
+      <c r="AC10">
+        <v>0.3674034530810761</v>
+      </c>
+      <c r="AD10">
+        <v>184.1</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>184.1</v>
+      </c>
+      <c r="AG10">
+        <v>72.39999999999999</v>
+      </c>
+      <c r="AH10">
+        <v>0.01671205519244735</v>
+      </c>
+      <c r="AI10">
+        <v>0.1137121680049413</v>
+      </c>
+      <c r="AJ10">
+        <v>0.006639582550003209</v>
+      </c>
+      <c r="AK10">
+        <v>0.04803290652159489</v>
+      </c>
+      <c r="AL10">
+        <v>10</v>
+      </c>
+      <c r="AM10">
+        <v>10</v>
+      </c>
+      <c r="AN10">
+        <v>0.3541746825702193</v>
+      </c>
+      <c r="AO10">
+        <v>51.61</v>
+      </c>
+      <c r="AP10">
+        <v>0.1392843401308195</v>
+      </c>
+      <c r="AQ10">
+        <v>51.61</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fidelity National Financial, Inc. (NYSE:FNF)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.116</v>
+      </c>
+      <c r="E11">
+        <v>-0.00395</v>
+      </c>
+      <c r="G11">
+        <v>0.114929785661493</v>
+      </c>
+      <c r="H11">
+        <v>0.114929785661493</v>
+      </c>
+      <c r="I11">
+        <v>0.1029096375588648</v>
+      </c>
+      <c r="J11">
+        <v>0.08427849976865497</v>
+      </c>
+      <c r="K11">
+        <v>751</v>
+      </c>
+      <c r="L11">
+        <v>0.05550628233555063</v>
+      </c>
+      <c r="M11">
+        <v>542</v>
+      </c>
+      <c r="N11">
+        <v>0.03528163467234297</v>
+      </c>
+      <c r="O11">
+        <v>0.7217043941411452</v>
+      </c>
+      <c r="P11">
+        <v>525</v>
+      </c>
+      <c r="Q11">
+        <v>0.03417501513464956</v>
+      </c>
+      <c r="R11">
+        <v>0.6990679094540613</v>
+      </c>
+      <c r="S11">
+        <v>17</v>
+      </c>
+      <c r="T11">
+        <v>0.03136531365313653</v>
+      </c>
+      <c r="U11">
+        <v>4681</v>
+      </c>
+      <c r="V11">
+        <v>0.3047109444672278</v>
+      </c>
+      <c r="W11">
+        <v>0.121955180253329</v>
+      </c>
+      <c r="X11">
+        <v>0.08076358665225908</v>
+      </c>
+      <c r="Y11">
+        <v>0.04119159360106993</v>
+      </c>
+      <c r="Z11">
+        <v>5.195527277110944</v>
+      </c>
+      <c r="AA11">
+        <v>0.4378712444220352</v>
+      </c>
+      <c r="AB11">
+        <v>0.07116316925266443</v>
+      </c>
+      <c r="AC11">
+        <v>0.3667080751693708</v>
+      </c>
+      <c r="AD11">
+        <v>4186</v>
+      </c>
+      <c r="AE11">
+        <v>378.1630191427985</v>
+      </c>
+      <c r="AF11">
+        <v>4564.163019142798</v>
+      </c>
+      <c r="AG11">
+        <v>-116.8369808572015</v>
+      </c>
+      <c r="AH11">
+        <v>0.2290526334395009</v>
+      </c>
+      <c r="AI11">
+        <v>0.3389356725189366</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.007663821917043643</v>
+      </c>
+      <c r="AK11">
+        <v>-0.01329935262471678</v>
+      </c>
+      <c r="AL11">
+        <v>197</v>
+      </c>
+      <c r="AM11">
+        <v>197</v>
+      </c>
+      <c r="AN11">
+        <v>2.008637236084453</v>
+      </c>
+      <c r="AO11">
+        <v>6.730964467005077</v>
+      </c>
+      <c r="AP11">
+        <v>-0.05606381039213125</v>
+      </c>
+      <c r="AQ11">
+        <v>6.730964467005077</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mercury General Corporation (NYSE:MCY)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0755</v>
+      </c>
+      <c r="E12">
+        <v>0.22</v>
+      </c>
+      <c r="G12">
+        <v>0.03579328373215363</v>
+      </c>
+      <c r="H12">
+        <v>0.03579328373215363</v>
+      </c>
+      <c r="I12">
+        <v>0.1299962337386428</v>
+      </c>
+      <c r="J12">
+        <v>0.1052907258034009</v>
+      </c>
+      <c r="K12">
+        <v>558.3</v>
+      </c>
+      <c r="L12">
+        <v>0.1020602160759008</v>
+      </c>
+      <c r="M12">
+        <v>70.3</v>
+      </c>
+      <c r="N12">
+        <v>0.01909755236206569</v>
+      </c>
+      <c r="O12">
+        <v>0.1259179652516568</v>
+      </c>
+      <c r="P12">
+        <v>70.3</v>
+      </c>
+      <c r="Q12">
+        <v>0.01909755236206569</v>
+      </c>
+      <c r="R12">
+        <v>0.1259179652516568</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>616.3</v>
+      </c>
+      <c r="V12">
+        <v>0.1674227812338703</v>
+      </c>
+      <c r="W12">
+        <v>0.4062431783453394</v>
+      </c>
+      <c r="X12">
+        <v>0.07781665558671899</v>
+      </c>
+      <c r="Y12">
+        <v>0.3284265227586204</v>
+      </c>
+      <c r="Z12">
+        <v>3.733972750893541</v>
+      </c>
+      <c r="AA12">
+        <v>0.3931527010717026</v>
+      </c>
+      <c r="AB12">
+        <v>0.0728125851566945</v>
+      </c>
+      <c r="AC12">
+        <v>0.3203401159150081</v>
+      </c>
+      <c r="AD12">
+        <v>574</v>
+      </c>
+      <c r="AE12">
+        <v>13.80801289751119</v>
+      </c>
+      <c r="AF12">
+        <v>587.8080128975112</v>
+      </c>
+      <c r="AG12">
+        <v>-28.49198710248879</v>
+      </c>
+      <c r="AH12">
+        <v>0.1376951696128345</v>
+      </c>
+      <c r="AI12">
+        <v>0.2399110609831304</v>
+      </c>
+      <c r="AJ12">
+        <v>-0.007800450254142355</v>
+      </c>
+      <c r="AK12">
+        <v>-0.01553706107842226</v>
+      </c>
+      <c r="AL12">
+        <v>31.1</v>
+      </c>
+      <c r="AM12">
+        <v>31.1</v>
+      </c>
+      <c r="AN12">
+        <v>0.7304843594899336</v>
+      </c>
+      <c r="AO12">
+        <v>22.72025723472669</v>
+      </c>
+      <c r="AP12">
+        <v>-0.03625949642710274</v>
+      </c>
+      <c r="AQ12">
+        <v>22.72025723472669</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Erie Indemnity Company (NasdaqGS:ERIE)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.08470000000000001</v>
+      </c>
+      <c r="E13">
+        <v>0.118</v>
+      </c>
+      <c r="G13">
+        <v>0.1627131509745981</v>
+      </c>
+      <c r="H13">
+        <v>0.1627131509745981</v>
+      </c>
+      <c r="I13">
+        <v>0.1796296798330035</v>
+      </c>
+      <c r="J13">
+        <v>0.142399938988681</v>
+      </c>
+      <c r="K13">
+        <v>559.2</v>
+      </c>
+      <c r="L13">
+        <v>0.1515981240003253</v>
+      </c>
+      <c r="M13">
+        <v>233.6</v>
+      </c>
+      <c r="N13">
+        <v>0.01083714133283849</v>
+      </c>
+      <c r="O13">
+        <v>0.4177396280400572</v>
+      </c>
+      <c r="P13">
+        <v>233.6</v>
+      </c>
+      <c r="Q13">
+        <v>0.01083714133283849</v>
+      </c>
+      <c r="R13">
+        <v>0.4177396280400572</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>197.7</v>
+      </c>
+      <c r="V13">
+        <v>0.009171673122868873</v>
+      </c>
+      <c r="W13">
+        <v>0.3469197841057138</v>
+      </c>
+      <c r="X13">
+        <v>0.07440024392467787</v>
+      </c>
+      <c r="Y13">
+        <v>0.2725195401810359</v>
+      </c>
+      <c r="Z13">
+        <v>2.444466534128562</v>
+      </c>
+      <c r="AA13">
+        <v>0.3480918853197797</v>
+      </c>
+      <c r="AB13">
+        <v>0.07438816611882786</v>
+      </c>
+      <c r="AC13">
+        <v>0.2737037192009518</v>
+      </c>
+      <c r="AD13">
+        <v>7.91</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>7.91</v>
+      </c>
+      <c r="AG13">
+        <v>-189.79</v>
+      </c>
+      <c r="AH13">
+        <v>0.0003668250986277217</v>
+      </c>
+      <c r="AI13">
+        <v>0.004044153360839711</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.008882925023320077</v>
+      </c>
+      <c r="AK13">
+        <v>-0.1079450122567839</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-63.4</v>
+      </c>
+      <c r="AN13">
+        <v>0.0111267407511605</v>
+      </c>
+      <c r="AP13">
+        <v>-0.2669714446476298</v>
+      </c>
+      <c r="AQ13">
+        <v>-10.45110410094637</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>The Progressive Corporation (NYSE:PGR)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.147</v>
+      </c>
+      <c r="E14">
+        <v>0.207</v>
+      </c>
+      <c r="F14">
+        <v>0.487</v>
+      </c>
+      <c r="G14">
+        <v>0.07604010038994212</v>
+      </c>
+      <c r="H14">
+        <v>0.07604010038994212</v>
+      </c>
+      <c r="I14">
+        <v>0.1468428546262494</v>
+      </c>
+      <c r="J14">
+        <v>0.1162205636658923</v>
+      </c>
+      <c r="K14">
+        <v>8111.3</v>
+      </c>
+      <c r="L14">
+        <v>0.1127205062854888</v>
+      </c>
+      <c r="M14">
+        <v>868.3</v>
+      </c>
+      <c r="N14">
+        <v>0.006185957740568783</v>
+      </c>
+      <c r="O14">
+        <v>0.1070481920284048</v>
+      </c>
+      <c r="P14">
+        <v>673.6</v>
+      </c>
+      <c r="Q14">
+        <v>0.004798872663880149</v>
+      </c>
+      <c r="R14">
+        <v>0.08304464142615857</v>
+      </c>
+      <c r="S14">
+        <v>194.6999999999999</v>
+      </c>
+      <c r="T14">
+        <v>0.2242312564781757</v>
+      </c>
+      <c r="U14">
+        <v>136.1</v>
+      </c>
+      <c r="V14">
+        <v>0.0009696059524259028</v>
+      </c>
+      <c r="W14">
+        <v>0.4799188232927449</v>
+      </c>
+      <c r="X14">
+        <v>0.07547167236256844</v>
+      </c>
+      <c r="Y14">
+        <v>0.4044471509301765</v>
+      </c>
+      <c r="Z14">
+        <v>2.985324481232343</v>
+      </c>
+      <c r="AA14">
+        <v>0.3469560939344103</v>
+      </c>
+      <c r="AB14">
+        <v>0.07371681428384731</v>
+      </c>
+      <c r="AC14">
+        <v>0.273239279650563</v>
+      </c>
+      <c r="AD14">
+        <v>6891.8</v>
+      </c>
+      <c r="AE14">
+        <v>172.8814340393328</v>
+      </c>
+      <c r="AF14">
+        <v>7064.681434039333</v>
+      </c>
+      <c r="AG14">
+        <v>6928.581434039333</v>
+      </c>
+      <c r="AH14">
+        <v>0.04791856749051131</v>
+      </c>
+      <c r="AI14">
+        <v>0.2064248850664922</v>
+      </c>
+      <c r="AJ14">
+        <v>0.04703884728772498</v>
+      </c>
+      <c r="AK14">
+        <v>0.2032564401940397</v>
+      </c>
+      <c r="AL14">
+        <v>278.8</v>
+      </c>
+      <c r="AM14">
+        <v>278.8</v>
+      </c>
+      <c r="AN14">
+        <v>0.6324376904158866</v>
+      </c>
+      <c r="AO14">
+        <v>37.75932568149211</v>
+      </c>
+      <c r="AP14">
+        <v>0.635813000957983</v>
+      </c>
+      <c r="AQ14">
+        <v>37.75932568149211</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Assurant, Inc. (NYSE:AIZ)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0399</v>
+      </c>
+      <c r="E15">
+        <v>0.215</v>
+      </c>
+      <c r="G15">
+        <v>0.09743275659674375</v>
+      </c>
+      <c r="H15">
+        <v>0.09743275659674375</v>
+      </c>
+      <c r="I15">
+        <v>0.08813624199998817</v>
+      </c>
+      <c r="J15">
+        <v>0.07229141477905877</v>
+      </c>
+      <c r="K15">
+        <v>741.4</v>
+      </c>
+      <c r="L15">
+        <v>0.06306674152333316</v>
+      </c>
+      <c r="M15">
+        <v>479.8</v>
+      </c>
+      <c r="N15">
+        <v>0.04387545151113346</v>
+      </c>
+      <c r="O15">
+        <v>0.6471540329107095</v>
+      </c>
+      <c r="P15">
+        <v>153.3</v>
+      </c>
+      <c r="Q15">
+        <v>0.01401856339444927</v>
+      </c>
+      <c r="R15">
+        <v>0.2067709738332884</v>
+      </c>
+      <c r="S15">
+        <v>326.5</v>
+      </c>
+      <c r="T15">
+        <v>0.6804918716131722</v>
+      </c>
+      <c r="U15">
+        <v>1813.4</v>
+      </c>
+      <c r="V15">
+        <v>0.1658268940606282</v>
+      </c>
+      <c r="W15">
+        <v>0.1651004320135394</v>
+      </c>
+      <c r="X15">
+        <v>0.07854266787260786</v>
+      </c>
+      <c r="Y15">
+        <v>0.08655776414093153</v>
+      </c>
+      <c r="Z15">
+        <v>4.567062193916571</v>
+      </c>
+      <c r="AA15">
+        <v>0.3301593873821809</v>
+      </c>
+      <c r="AB15">
+        <v>0.07210629562541389</v>
+      </c>
+      <c r="AC15">
+        <v>0.2580530917567671</v>
+      </c>
+      <c r="AD15">
+        <v>2082.5</v>
+      </c>
+      <c r="AE15">
+        <v>33.93983148269538</v>
+      </c>
+      <c r="AF15">
+        <v>2116.439831482695</v>
+      </c>
+      <c r="AG15">
+        <v>303.0398314826953</v>
+      </c>
+      <c r="AH15">
+        <v>0.1621551936960062</v>
+      </c>
+      <c r="AI15">
+        <v>0.2871018076959196</v>
+      </c>
+      <c r="AJ15">
+        <v>0.02696434198985397</v>
+      </c>
+      <c r="AK15">
+        <v>0.0545198459738398</v>
+      </c>
+      <c r="AL15">
+        <v>107</v>
+      </c>
+      <c r="AM15">
+        <v>107</v>
+      </c>
+      <c r="AN15">
+        <v>1.655800270334738</v>
+      </c>
+      <c r="AO15">
+        <v>9.599065420560747</v>
+      </c>
+      <c r="AP15">
+        <v>0.2409476277989149</v>
+      </c>
+      <c r="AQ15">
+        <v>9.599065420560747</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RLI Corp. (NYSE:RLI)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.141</v>
+      </c>
+      <c r="E16">
+        <v>0.29</v>
+      </c>
+      <c r="G16">
+        <v>0.2173050770625567</v>
+      </c>
+      <c r="H16">
+        <v>0.2173050770625567</v>
+      </c>
+      <c r="I16">
+        <v>0.295201446239552</v>
+      </c>
+      <c r="J16">
+        <v>0.2365558867191825</v>
+      </c>
+      <c r="K16">
+        <v>419.5</v>
+      </c>
+      <c r="L16">
+        <v>0.2377039891205802</v>
+      </c>
+      <c r="M16">
+        <v>51.2</v>
+      </c>
+      <c r="N16">
+        <v>0.006778942908590192</v>
+      </c>
+      <c r="O16">
+        <v>0.1220500595947557</v>
+      </c>
+      <c r="P16">
+        <v>51.2</v>
+      </c>
+      <c r="Q16">
+        <v>0.006778942908590192</v>
+      </c>
+      <c r="R16">
+        <v>0.1220500595947557</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>60.6</v>
+      </c>
+      <c r="V16">
+        <v>0.008023514458214172</v>
+      </c>
+      <c r="W16">
+        <v>0.3229158648294974</v>
+      </c>
+      <c r="X16">
+        <v>0.07471631159735165</v>
+      </c>
+      <c r="Y16">
+        <v>0.2481995532321457</v>
+      </c>
+      <c r="Z16">
+        <v>1.308526651277842</v>
+      </c>
+      <c r="AA16">
+        <v>0.3095396822887126</v>
+      </c>
+      <c r="AB16">
+        <v>0.07418257840899602</v>
+      </c>
+      <c r="AC16">
+        <v>0.2353571038797166</v>
+      </c>
+      <c r="AD16">
+        <v>100</v>
+      </c>
+      <c r="AE16">
+        <v>14.09243838219379</v>
+      </c>
+      <c r="AF16">
+        <v>114.0924383821938</v>
+      </c>
+      <c r="AG16">
+        <v>53.49243838219379</v>
+      </c>
+      <c r="AH16">
+        <v>0.0148811841693541</v>
+      </c>
+      <c r="AI16">
+        <v>0.06125793374028259</v>
+      </c>
+      <c r="AJ16">
+        <v>0.007032656029929249</v>
+      </c>
+      <c r="AK16">
+        <v>0.02968680995754735</v>
+      </c>
+      <c r="AL16">
+        <v>6.21</v>
+      </c>
+      <c r="AM16">
+        <v>6.21</v>
+      </c>
+      <c r="AN16">
+        <v>0.1877264450243105</v>
+      </c>
+      <c r="AO16">
+        <v>83.6876006441224</v>
+      </c>
+      <c r="AP16">
+        <v>0.1004194529317122</v>
+      </c>
+      <c r="AQ16">
+        <v>83.6876006441224</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cincinnati Financial Corporation (NasdaqGS:CINF)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.134</v>
+      </c>
+      <c r="E17">
+        <v>0.273</v>
+      </c>
+      <c r="F17">
+        <v>0.083</v>
+      </c>
+      <c r="G17">
+        <v>0.2009049773755656</v>
+      </c>
+      <c r="H17">
+        <v>0.2009049773755656</v>
+      </c>
+      <c r="I17">
+        <v>0.3228210072928541</v>
+      </c>
+      <c r="J17">
+        <v>0.256154172238062</v>
+      </c>
+      <c r="K17">
+        <v>3070</v>
+      </c>
+      <c r="L17">
+        <v>0.2525709584533114</v>
+      </c>
+      <c r="M17">
+        <v>602</v>
+      </c>
+      <c r="N17">
+        <v>0.02680022259321091</v>
+      </c>
+      <c r="O17">
+        <v>0.1960912052117264</v>
+      </c>
+      <c r="P17">
+        <v>481</v>
+      </c>
+      <c r="Q17">
+        <v>0.02141346688925988</v>
+      </c>
+      <c r="R17">
+        <v>0.1566775244299674</v>
+      </c>
+      <c r="S17">
+        <v>121</v>
+      </c>
+      <c r="T17">
+        <v>0.2009966777408638</v>
+      </c>
+      <c r="U17">
+        <v>1752</v>
+      </c>
+      <c r="V17">
+        <v>0.0779966611018364</v>
+      </c>
+      <c r="W17">
+        <v>0.2889683734939759</v>
+      </c>
+      <c r="X17">
+        <v>0.07518050591612703</v>
+      </c>
+      <c r="Y17">
+        <v>0.2137878675778489</v>
+      </c>
+      <c r="Z17">
+        <v>1.152072282407639</v>
+      </c>
+      <c r="AA17">
+        <v>0.2951081218585436</v>
+      </c>
+      <c r="AB17">
+        <v>0.07389260228482009</v>
+      </c>
+      <c r="AC17">
+        <v>0.2212155195737235</v>
+      </c>
+      <c r="AD17">
+        <v>815</v>
+      </c>
+      <c r="AE17">
+        <v>10.55328177679404</v>
+      </c>
+      <c r="AF17">
+        <v>825.5532817767941</v>
+      </c>
+      <c r="AG17">
+        <v>-926.4467182232059</v>
+      </c>
+      <c r="AH17">
+        <v>0.03544964758487565</v>
+      </c>
+      <c r="AI17">
+        <v>0.05643051881872149</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.04301840760243379</v>
+      </c>
+      <c r="AK17">
+        <v>-0.07194275946302887</v>
+      </c>
+      <c r="AL17">
+        <v>54</v>
+      </c>
+      <c r="AM17">
+        <v>54</v>
+      </c>
+      <c r="AN17">
+        <v>0.2004920049200492</v>
+      </c>
+      <c r="AO17">
+        <v>72.64814814814815</v>
+      </c>
+      <c r="AP17">
+        <v>-0.2279081717646263</v>
+      </c>
+      <c r="AQ17">
+        <v>72.64814814814815</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Markel Group Inc. (NYSE:MKL)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.169</v>
+      </c>
+      <c r="E18">
+        <v>0.412</v>
+      </c>
+      <c r="G18">
+        <v>0.1830297951475982</v>
+      </c>
+      <c r="H18">
+        <v>0.1830297951475982</v>
+      </c>
+      <c r="I18">
+        <v>0.2437324664446062</v>
+      </c>
+      <c r="J18">
+        <v>0.1914614562346421</v>
+      </c>
+      <c r="K18">
+        <v>2967.2</v>
+      </c>
+      <c r="L18">
+        <v>0.1703104641752237</v>
+      </c>
+      <c r="M18">
+        <v>565</v>
+      </c>
+      <c r="N18">
+        <v>0.02544666783766377</v>
+      </c>
+      <c r="O18">
+        <v>0.1904152062550553</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>-0</v>
+      </c>
+      <c r="S18">
+        <v>565</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>3873</v>
+      </c>
+      <c r="V18">
+        <v>0.1744335301509235</v>
+      </c>
+      <c r="W18">
+        <v>0.2213122701811699</v>
+      </c>
+      <c r="X18">
+        <v>0.07922067655498174</v>
+      </c>
+      <c r="Y18">
+        <v>0.1420915936261882</v>
+      </c>
+      <c r="Z18">
+        <v>1.523847525512421</v>
+      </c>
+      <c r="AA18">
+        <v>0.291758066314164</v>
+      </c>
+      <c r="AB18">
+        <v>0.07180146650085617</v>
+      </c>
+      <c r="AC18">
+        <v>0.2199565998133078</v>
+      </c>
+      <c r="AD18">
+        <v>4356.1</v>
+      </c>
+      <c r="AE18">
+        <v>643.0992493106831</v>
+      </c>
+      <c r="AF18">
+        <v>4999.199249310684</v>
+      </c>
+      <c r="AG18">
+        <v>1126.199249310684</v>
+      </c>
+      <c r="AH18">
+        <v>0.1837772038331134</v>
+      </c>
+      <c r="AI18">
+        <v>0.2205983326675269</v>
+      </c>
+      <c r="AJ18">
+        <v>0.04827361433160463</v>
+      </c>
+      <c r="AK18">
+        <v>0.0599392886426349</v>
+      </c>
+      <c r="AL18">
+        <v>195.4</v>
+      </c>
+      <c r="AM18">
+        <v>195.4</v>
+      </c>
+      <c r="AN18">
+        <v>0.9384708188810136</v>
+      </c>
+      <c r="AO18">
+        <v>21.74616171954964</v>
+      </c>
+      <c r="AP18">
+        <v>0.2426264621390188</v>
+      </c>
+      <c r="AQ18">
+        <v>21.74616171954964</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc. (NasdaqGS:PLMR)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.398</v>
+      </c>
+      <c r="E19">
+        <v>0.948</v>
+      </c>
+      <c r="F19">
+        <v>0.199</v>
+      </c>
+      <c r="G19">
+        <v>0.2166832174776564</v>
+      </c>
+      <c r="H19">
+        <v>0.2166832174776564</v>
+      </c>
+      <c r="I19">
+        <v>0.2821020388347661</v>
+      </c>
+      <c r="J19">
+        <v>0.2190985770477604</v>
+      </c>
+      <c r="K19">
+        <v>108.5</v>
+      </c>
+      <c r="L19">
+        <v>0.2154915590863952</v>
+      </c>
+      <c r="M19">
+        <v>0.132</v>
+      </c>
+      <c r="N19">
+        <v>4.723564143853999E-05</v>
+      </c>
+      <c r="O19">
+        <v>0.001216589861751152</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>0.132</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>86.5</v>
+      </c>
+      <c r="V19">
+        <v>0.03095365897298264</v>
+      </c>
+      <c r="W19">
+        <v>0.2575361974839782</v>
+      </c>
+      <c r="X19">
+        <v>0.07440022587854321</v>
+      </c>
+      <c r="Y19">
+        <v>0.1831359716054349</v>
+      </c>
+      <c r="Z19">
+        <v>1.193345373681865</v>
+      </c>
+      <c r="AA19">
+        <v>0.2614602733002244</v>
+      </c>
+      <c r="AB19">
+        <v>0.0743881757667753</v>
+      </c>
+      <c r="AC19">
+        <v>0.1870720975334491</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>1.02311723347628</v>
+      </c>
+      <c r="AF19">
+        <v>1.02311723347628</v>
+      </c>
+      <c r="AG19">
+        <v>-85.47688276652372</v>
+      </c>
+      <c r="AH19">
+        <v>0.0003659841791931894</v>
+      </c>
+      <c r="AI19">
+        <v>0.001452624808759652</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.03155265904626717</v>
+      </c>
+      <c r="AK19">
+        <v>-0.1383517067947813</v>
+      </c>
+      <c r="AL19">
+        <v>1.88</v>
+      </c>
+      <c r="AM19">
+        <v>1.88</v>
+      </c>
+      <c r="AN19">
+        <v>0</v>
+      </c>
+      <c r="AO19">
+        <v>75.31914893617021</v>
+      </c>
+      <c r="AP19">
+        <v>-0.5938245191952628</v>
+      </c>
+      <c r="AQ19">
+        <v>75.31914893617021</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Allstate Corporation (NYSE:ALL)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.079</v>
+      </c>
+      <c r="E20">
+        <v>0.108</v>
+      </c>
+      <c r="F20">
+        <v>1.75</v>
+      </c>
+      <c r="G20">
+        <v>0.01447975397232189</v>
+      </c>
+      <c r="H20">
+        <v>0.01447975397232189</v>
+      </c>
+      <c r="I20">
+        <v>0.09075309775064502</v>
+      </c>
+      <c r="J20">
+        <v>0.07410001910132448</v>
+      </c>
+      <c r="K20">
+        <v>4228</v>
+      </c>
+      <c r="L20">
+        <v>0.06772168118913378</v>
+      </c>
+      <c r="M20">
+        <v>952</v>
+      </c>
+      <c r="N20">
+        <v>0.01864783600873628</v>
+      </c>
+      <c r="O20">
+        <v>0.2251655629139073</v>
+      </c>
+      <c r="P20">
+        <v>952</v>
+      </c>
+      <c r="Q20">
+        <v>0.01864783600873628</v>
+      </c>
+      <c r="R20">
+        <v>0.2251655629139073</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>816</v>
+      </c>
+      <c r="V20">
+        <v>0.01598385943605966</v>
+      </c>
+      <c r="W20">
+        <v>0.3357687420584498</v>
+      </c>
+      <c r="X20">
+        <v>0.07789666341846516</v>
+      </c>
+      <c r="Y20">
+        <v>0.2578720786399846</v>
+      </c>
+      <c r="Z20">
+        <v>3.387609861374899</v>
+      </c>
+      <c r="AA20">
+        <v>0.2510219554357152</v>
+      </c>
+      <c r="AB20">
+        <v>0.07241214939207889</v>
+      </c>
+      <c r="AC20">
+        <v>0.1786098060436363</v>
+      </c>
+      <c r="AD20">
+        <v>8092</v>
+      </c>
+      <c r="AE20">
+        <v>250.5130061586506</v>
+      </c>
+      <c r="AF20">
+        <v>8342.513006158651</v>
+      </c>
+      <c r="AG20">
+        <v>7526.513006158651</v>
+      </c>
+      <c r="AH20">
+        <v>0.1404605040796554</v>
+      </c>
+      <c r="AI20">
+        <v>0.2858932947614024</v>
+      </c>
+      <c r="AJ20">
+        <v>0.1284869974228615</v>
+      </c>
+      <c r="AK20">
+        <v>0.2653496291131265</v>
+      </c>
+      <c r="AL20">
+        <v>406</v>
+      </c>
+      <c r="AM20">
+        <v>406</v>
+      </c>
+      <c r="AN20">
+        <v>1.287509944311854</v>
+      </c>
+      <c r="AO20">
+        <v>13.85221674876847</v>
+      </c>
+      <c r="AP20">
+        <v>1.197535880057065</v>
+      </c>
+      <c r="AQ20">
+        <v>13.85221674876847</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>American Financial Group, Inc. (NYSE:AFG)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.00893</v>
+      </c>
+      <c r="E21">
+        <v>0.0638</v>
+      </c>
+      <c r="G21">
+        <v>0.1615715007579586</v>
+      </c>
+      <c r="H21">
+        <v>0.1615715007579586</v>
+      </c>
+      <c r="I21">
+        <v>0.1587293471431663</v>
+      </c>
+      <c r="J21">
+        <v>0.1247258697920402</v>
+      </c>
+      <c r="K21">
+        <v>895</v>
+      </c>
+      <c r="L21">
+        <v>0.1130621526023244</v>
+      </c>
+      <c r="M21">
+        <v>297</v>
+      </c>
+      <c r="N21">
+        <v>0.02584249132057741</v>
+      </c>
+      <c r="O21">
+        <v>0.3318435754189944</v>
+      </c>
+      <c r="P21">
+        <v>237</v>
+      </c>
+      <c r="Q21">
+        <v>0.02062178600328904</v>
+      </c>
+      <c r="R21">
+        <v>0.264804469273743</v>
+      </c>
+      <c r="S21">
+        <v>60</v>
+      </c>
+      <c r="T21">
+        <v>0.202020202020202</v>
+      </c>
+      <c r="U21">
+        <v>1322</v>
+      </c>
+      <c r="V21">
+        <v>0.1150295404909203</v>
+      </c>
+      <c r="W21">
+        <v>0.2248178849535293</v>
+      </c>
+      <c r="X21">
+        <v>0.07757839262552134</v>
+      </c>
+      <c r="Y21">
+        <v>0.1472394923280079</v>
+      </c>
+      <c r="Z21">
+        <v>1.887236683125677</v>
+      </c>
+      <c r="AA21">
+        <v>0.2353872368062951</v>
+      </c>
+      <c r="AB21">
+        <v>0.07256873553722612</v>
+      </c>
+      <c r="AC21">
+        <v>0.1628185012690689</v>
+      </c>
+      <c r="AD21">
+        <v>1485</v>
+      </c>
+      <c r="AE21">
+        <v>222.492440073479</v>
+      </c>
+      <c r="AF21">
+        <v>1707.492440073479</v>
+      </c>
+      <c r="AG21">
+        <v>385.492440073479</v>
+      </c>
+      <c r="AH21">
+        <v>0.1293536020649086</v>
+      </c>
+      <c r="AI21">
+        <v>0.2661514226730072</v>
+      </c>
+      <c r="AJ21">
+        <v>0.03245379648615074</v>
+      </c>
+      <c r="AK21">
+        <v>0.07568332428268369</v>
+      </c>
+      <c r="AL21">
+        <v>103</v>
+      </c>
+      <c r="AM21">
+        <v>103</v>
+      </c>
+      <c r="AN21">
+        <v>1.076867295141407</v>
+      </c>
+      <c r="AO21">
+        <v>12.27184466019417</v>
+      </c>
+      <c r="AP21">
+        <v>0.2795449166595206</v>
+      </c>
+      <c r="AQ21">
+        <v>12.27184466019417</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Skyward Specialty Insurance Group, Inc. (NasdaqGS:SKWD)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="F22">
+        <v>0.18</v>
+      </c>
+      <c r="G22">
+        <v>0.1135427158685102</v>
+      </c>
+      <c r="H22">
+        <v>0.1135427158685102</v>
+      </c>
+      <c r="I22">
+        <v>0.167178285083289</v>
+      </c>
+      <c r="J22">
+        <v>0.1301032404868204</v>
+      </c>
+      <c r="K22">
+        <v>133.7</v>
+      </c>
+      <c r="L22">
+        <v>0.1224246863840308</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>-0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>-0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>105.6</v>
+      </c>
+      <c r="V22">
+        <v>0.05210440617752997</v>
+      </c>
+      <c r="W22">
+        <v>0.249719835636907</v>
+      </c>
+      <c r="X22">
+        <v>0.07570411860884027</v>
+      </c>
+      <c r="Y22">
+        <v>0.1740157170280667</v>
+      </c>
+      <c r="Z22">
+        <v>1.774696071496307</v>
+      </c>
+      <c r="AA22">
+        <v>0.2308937097808993</v>
+      </c>
+      <c r="AB22">
+        <v>0.07373102195844242</v>
+      </c>
+      <c r="AC22">
+        <v>0.1571626878224569</v>
+      </c>
+      <c r="AD22">
+        <v>119</v>
+      </c>
+      <c r="AE22">
+        <v>4.972974302700479</v>
+      </c>
+      <c r="AF22">
+        <v>123.9729743027005</v>
+      </c>
+      <c r="AG22">
+        <v>18.37297430270048</v>
+      </c>
+      <c r="AH22">
+        <v>0.05764380535022787</v>
+      </c>
+      <c r="AI22">
+        <v>0.1345378299309469</v>
+      </c>
+      <c r="AJ22">
+        <v>0.008984018924295373</v>
+      </c>
+      <c r="AK22">
+        <v>0.02251940544838276</v>
+      </c>
+      <c r="AL22">
+        <v>10.2</v>
+      </c>
+      <c r="AM22">
+        <v>10.2</v>
+      </c>
+      <c r="AN22">
+        <v>0.6354461472739895</v>
+      </c>
+      <c r="AO22">
+        <v>17.83333333333334</v>
+      </c>
+      <c r="AP22">
+        <v>0.09810954398836165</v>
+      </c>
+      <c r="AQ22">
+        <v>17.83333333333334</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>AMERISAFE, Inc. (NasdaqGS:AMSF)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.0332</v>
+      </c>
+      <c r="E23">
+        <v>-0.0454</v>
+      </c>
+      <c r="F23">
+        <v>0.1</v>
+      </c>
+      <c r="G23">
+        <v>0.25</v>
+      </c>
+      <c r="H23">
+        <v>0.25</v>
+      </c>
+      <c r="I23">
+        <v>0.2418252057681795</v>
+      </c>
+      <c r="J23">
+        <v>0.1948565306321026</v>
+      </c>
+      <c r="K23">
+        <v>61.4</v>
+      </c>
+      <c r="L23">
+        <v>0.1947969543147208</v>
+      </c>
+      <c r="M23">
+        <v>35.53</v>
+      </c>
+      <c r="N23">
+        <v>0.03620707225109549</v>
+      </c>
+      <c r="O23">
+        <v>0.5786644951140065</v>
+      </c>
+      <c r="P23">
+        <v>27.7</v>
+      </c>
+      <c r="Q23">
+        <v>0.02822786100071334</v>
+      </c>
+      <c r="R23">
+        <v>0.4511400651465798</v>
+      </c>
+      <c r="S23">
+        <v>7.830000000000002</v>
+      </c>
+      <c r="T23">
+        <v>0.2203771460737405</v>
+      </c>
+      <c r="U23">
+        <v>63.7</v>
+      </c>
+      <c r="V23">
+        <v>0.06491388973810253</v>
+      </c>
+      <c r="W23">
+        <v>0.1827924977671926</v>
+      </c>
+      <c r="X23">
+        <v>0.07439299701525778</v>
+      </c>
+      <c r="Y23">
+        <v>0.1083995007519348</v>
+      </c>
+      <c r="Z23">
+        <v>1.13902264373782</v>
+      </c>
+      <c r="AA23">
+        <v>0.2219460006701571</v>
+      </c>
+      <c r="AB23">
+        <v>0.07439196564596864</v>
+      </c>
+      <c r="AC23">
+        <v>0.1475540350241885</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0.02847570934908135</v>
+      </c>
+      <c r="AF23">
+        <v>0.02847570934908135</v>
+      </c>
+      <c r="AG23">
+        <v>-63.67152429065092</v>
+      </c>
+      <c r="AH23">
+        <v>2.901751050125984E-05</v>
+      </c>
+      <c r="AI23">
+        <v>9.056339215091854E-05</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.06938704059007246</v>
+      </c>
+      <c r="AK23">
+        <v>-0.2539461228347298</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>-0.8223214078788428</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>W. R. Berkley Corporation (NYSE:WRB)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.109</v>
+      </c>
+      <c r="E24">
+        <v>0.178</v>
+      </c>
+      <c r="F24">
+        <v>0.13</v>
+      </c>
+      <c r="G24">
+        <v>0.1453921137607447</v>
+      </c>
+      <c r="H24">
+        <v>0.1453921137607447</v>
+      </c>
+      <c r="I24">
+        <v>0.1673262503216092</v>
+      </c>
+      <c r="J24">
+        <v>0.1296133740343396</v>
+      </c>
+      <c r="K24">
+        <v>1577.4</v>
+      </c>
+      <c r="L24">
+        <v>0.1195670300016676</v>
+      </c>
+      <c r="M24">
+        <v>464.2</v>
+      </c>
+      <c r="N24">
+        <v>0.02081595680756226</v>
+      </c>
+      <c r="O24">
+        <v>0.2942817294281729</v>
+      </c>
+      <c r="P24">
+        <v>121.3</v>
+      </c>
+      <c r="Q24">
+        <v>0.005439413099434086</v>
+      </c>
+      <c r="R24">
+        <v>0.07689869405350576</v>
+      </c>
+      <c r="S24">
+        <v>342.9</v>
+      </c>
+      <c r="T24">
+        <v>0.7386902197328737</v>
+      </c>
+      <c r="U24">
+        <v>1573.2</v>
+      </c>
+      <c r="V24">
+        <v>0.07054645249818388</v>
+      </c>
+      <c r="W24">
+        <v>0.2280930071143502</v>
+      </c>
+      <c r="X24">
+        <v>0.07732296289698079</v>
+      </c>
+      <c r="Y24">
+        <v>0.1507700442173694</v>
+      </c>
+      <c r="Z24">
+        <v>1.620302767282626</v>
+      </c>
+      <c r="AA24">
+        <v>0.2100129086246786</v>
+      </c>
+      <c r="AB24">
+        <v>0.07269736230233828</v>
+      </c>
+      <c r="AC24">
+        <v>0.1373155463223403</v>
+      </c>
+      <c r="AD24">
+        <v>2837.4</v>
+      </c>
+      <c r="AE24">
+        <v>210.1585500356936</v>
+      </c>
+      <c r="AF24">
+        <v>3047.558550035694</v>
+      </c>
+      <c r="AG24">
+        <v>1474.358550035694</v>
+      </c>
+      <c r="AH24">
+        <v>0.1202299029328336</v>
+      </c>
+      <c r="AI24">
+        <v>0.2653059586452695</v>
+      </c>
+      <c r="AJ24">
+        <v>0.06201412938678856</v>
+      </c>
+      <c r="AK24">
+        <v>0.1487184242580112</v>
+      </c>
+      <c r="AL24">
+        <v>127</v>
+      </c>
+      <c r="AM24">
+        <v>127</v>
+      </c>
+      <c r="AN24">
+        <v>56.52191235059761</v>
+      </c>
+      <c r="AO24">
+        <v>17.31732283464567</v>
+      </c>
+      <c r="AP24">
+        <v>29.36969223178673</v>
+      </c>
+      <c r="AQ24">
+        <v>17.31732283464567</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Travelers Companies, Inc. (NYSE:TRV)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="E25">
+        <v>0.139</v>
+      </c>
+      <c r="F25">
+        <v>0.179</v>
+      </c>
+      <c r="G25">
+        <v>0.09856203961007455</v>
+      </c>
+      <c r="H25">
+        <v>0.09856203961007455</v>
+      </c>
+      <c r="I25">
+        <v>0.1330495401382684</v>
+      </c>
+      <c r="J25">
+        <v>0.1078401535857544</v>
+      </c>
+      <c r="K25">
+        <v>4543</v>
+      </c>
+      <c r="L25">
+        <v>0.1001940805434255</v>
+      </c>
+      <c r="M25">
+        <v>1867</v>
+      </c>
+      <c r="N25">
+        <v>0.03413999041812803</v>
+      </c>
+      <c r="O25">
+        <v>0.4109619194364957</v>
+      </c>
+      <c r="P25">
+        <v>943</v>
+      </c>
+      <c r="Q25">
+        <v>0.01724371235366616</v>
+      </c>
+      <c r="R25">
+        <v>0.2075720889280211</v>
+      </c>
+      <c r="S25">
+        <v>924</v>
+      </c>
+      <c r="T25">
+        <v>0.4949116229244778</v>
+      </c>
+      <c r="U25">
+        <v>772</v>
+      </c>
+      <c r="V25">
+        <v>0.01411680375082744</v>
+      </c>
+      <c r="W25">
+        <v>0.2274001401541696</v>
+      </c>
+      <c r="X25">
+        <v>0.07763111295826472</v>
+      </c>
+      <c r="Y25">
+        <v>0.1497690271959049</v>
+      </c>
+      <c r="Z25">
+        <v>1.914187172670229</v>
+      </c>
+      <c r="AA25">
+        <v>0.2064262386926384</v>
+      </c>
+      <c r="AB25">
+        <v>0.0727885433645829</v>
+      </c>
+      <c r="AC25">
+        <v>0.1336376953280555</v>
+      </c>
+      <c r="AD25">
+        <v>8033</v>
+      </c>
+      <c r="AE25">
+        <v>226.3387552531685</v>
+      </c>
+      <c r="AF25">
+        <v>8259.338755253168</v>
+      </c>
+      <c r="AG25">
+        <v>7487.338755253168</v>
+      </c>
+      <c r="AH25">
+        <v>0.1312132111869391</v>
+      </c>
+      <c r="AI25">
+        <v>0.2297110538013345</v>
+      </c>
+      <c r="AJ25">
+        <v>0.1204256784297834</v>
+      </c>
+      <c r="AK25">
+        <v>0.2128092165254</v>
+      </c>
+      <c r="AL25">
+        <v>392</v>
+      </c>
+      <c r="AM25">
+        <v>392</v>
+      </c>
+      <c r="AN25">
+        <v>1.181323529411765</v>
+      </c>
+      <c r="AO25">
+        <v>15.2984693877551</v>
+      </c>
+      <c r="AP25">
+        <v>1.101079228713701</v>
+      </c>
+      <c r="AQ25">
+        <v>15.2984693877551</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>The Hartford Financial Services Group, Inc. (NYSE:HIG)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>0.0545</v>
+      </c>
+      <c r="E26">
+        <v>0.118</v>
+      </c>
+      <c r="F26">
+        <v>0.121</v>
+      </c>
+      <c r="G26">
+        <v>0.1430762153044012</v>
+      </c>
+      <c r="H26">
+        <v>0.1430762153044012</v>
+      </c>
+      <c r="I26">
+        <v>0.1513870148899211</v>
+      </c>
+      <c r="J26">
+        <v>0.1231010115708915</v>
+      </c>
+      <c r="K26">
+        <v>3029</v>
+      </c>
+      <c r="L26">
+        <v>0.1161248274804478</v>
+      </c>
+      <c r="M26">
+        <v>1973</v>
+      </c>
+      <c r="N26">
+        <v>0.06221207601666136</v>
+      </c>
+      <c r="O26">
+        <v>0.6513700891383295</v>
+      </c>
+      <c r="P26">
+        <v>548</v>
+      </c>
+      <c r="Q26">
+        <v>0.01727938046484056</v>
+      </c>
+      <c r="R26">
+        <v>0.1809177946517002</v>
+      </c>
+      <c r="S26">
+        <v>1425</v>
+      </c>
+      <c r="T26">
+        <v>0.722250380131779</v>
+      </c>
+      <c r="U26">
+        <v>223</v>
+      </c>
+      <c r="V26">
+        <v>0.007031572707407747</v>
+      </c>
+      <c r="W26">
+        <v>0.2269763956538029</v>
+      </c>
+      <c r="X26">
+        <v>0.07743185263832068</v>
+      </c>
+      <c r="Y26">
+        <v>0.1495445430154823</v>
+      </c>
+      <c r="Z26">
+        <v>1.61469788412885</v>
+      </c>
+      <c r="AA26">
+        <v>0.1987709429176397</v>
+      </c>
+      <c r="AB26">
+        <v>0.07264220049848366</v>
+      </c>
+      <c r="AC26">
+        <v>0.126128742419156</v>
+      </c>
+      <c r="AD26">
+        <v>4359</v>
+      </c>
+      <c r="AE26">
+        <v>136.105518056491</v>
+      </c>
+      <c r="AF26">
+        <v>4495.105518056491</v>
+      </c>
+      <c r="AG26">
+        <v>4272.105518056491</v>
+      </c>
+      <c r="AH26">
+        <v>0.1241426166010439</v>
+      </c>
+      <c r="AI26">
+        <v>0.2090444803092224</v>
+      </c>
+      <c r="AJ26">
+        <v>0.1187150869772283</v>
+      </c>
+      <c r="AK26">
+        <v>0.2007558427955888</v>
+      </c>
+      <c r="AL26">
+        <v>228</v>
+      </c>
+      <c r="AM26">
+        <v>228</v>
+      </c>
+      <c r="AN26">
+        <v>1.016794961511547</v>
+      </c>
+      <c r="AO26">
+        <v>17.29385964912281</v>
+      </c>
+      <c r="AP26">
+        <v>0.9965256631808936</v>
+      </c>
+      <c r="AQ26">
+        <v>17.29385964912281</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kemper Corporation (NYSE:KMPR)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>-0.00755</v>
+      </c>
+      <c r="E27">
+        <v>-0.08019999999999999</v>
+      </c>
+      <c r="F27">
+        <v>0.1</v>
+      </c>
+      <c r="G27">
+        <v>0.02836634837152156</v>
+      </c>
+      <c r="H27">
+        <v>0.02836634837152156</v>
+      </c>
+      <c r="I27">
+        <v>0.1239813784854935</v>
+      </c>
+      <c r="J27">
+        <v>0.09990804800709589</v>
+      </c>
+      <c r="K27">
+        <v>271.8</v>
+      </c>
+      <c r="L27">
+        <v>0.05858642467613649</v>
+      </c>
+      <c r="M27">
+        <v>105.4</v>
+      </c>
+      <c r="N27">
+        <v>0.02476969355141944</v>
+      </c>
+      <c r="O27">
+        <v>0.387785136129507</v>
+      </c>
+      <c r="P27">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="Q27">
+        <v>0.01889452904681331</v>
+      </c>
+      <c r="R27">
+        <v>0.2958057395143488</v>
+      </c>
+      <c r="S27">
+        <v>25</v>
+      </c>
+      <c r="T27">
+        <v>0.2371916508538899</v>
+      </c>
+      <c r="U27">
+        <v>56.9</v>
+      </c>
+      <c r="V27">
+        <v>0.01337187441248355</v>
+      </c>
+      <c r="W27">
+        <v>0.1151060856307966</v>
+      </c>
+      <c r="X27">
+        <v>0.08433422178794864</v>
+      </c>
+      <c r="Y27">
+        <v>0.03077186384284795</v>
+      </c>
+      <c r="Z27">
+        <v>1.895629867895701</v>
+      </c>
+      <c r="AA27">
+        <v>0.1893886798454085</v>
+      </c>
+      <c r="AB27">
+        <v>0.07075816594860013</v>
+      </c>
+      <c r="AC27">
+        <v>0.1186305138968084</v>
+      </c>
+      <c r="AD27">
+        <v>1912.2</v>
+      </c>
+      <c r="AE27">
+        <v>60.56595396124995</v>
+      </c>
+      <c r="AF27">
+        <v>1972.76595396125</v>
+      </c>
+      <c r="AG27">
+        <v>1915.86595396125</v>
+      </c>
+      <c r="AH27">
+        <v>0.3167592707706579</v>
+      </c>
+      <c r="AI27">
+        <v>0.4159175481333721</v>
+      </c>
+      <c r="AJ27">
+        <v>0.3104594843507453</v>
+      </c>
+      <c r="AK27">
+        <v>0.4088256989217159</v>
+      </c>
+      <c r="AL27">
+        <v>56.2</v>
+      </c>
+      <c r="AM27">
+        <v>56.2</v>
+      </c>
+      <c r="AN27">
+        <v>3.014186633039092</v>
+      </c>
+      <c r="AO27">
+        <v>10.08718861209964</v>
+      </c>
+      <c r="AP27">
+        <v>3.019965248993143</v>
+      </c>
+      <c r="AQ27">
+        <v>10.08718861209964</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Employers Holdings, Inc. (NYSE:EIG)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.0203</v>
+      </c>
+      <c r="E28">
+        <v>-0.0209</v>
+      </c>
+      <c r="G28">
+        <v>0.1910541694762868</v>
+      </c>
+      <c r="H28">
+        <v>0.1910541694762868</v>
+      </c>
+      <c r="I28">
+        <v>0.1945842435103822</v>
+      </c>
+      <c r="J28">
+        <v>0.1553701450826142</v>
+      </c>
+      <c r="K28">
+        <v>135.9</v>
+      </c>
+      <c r="L28">
+        <v>0.1527309507754552</v>
+      </c>
+      <c r="M28">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="N28">
+        <v>0.06049597220028431</v>
+      </c>
+      <c r="O28">
+        <v>0.5636497424576894</v>
+      </c>
+      <c r="P28">
+        <v>30</v>
+      </c>
+      <c r="Q28">
+        <v>0.0236929395040278</v>
+      </c>
+      <c r="R28">
+        <v>0.2207505518763797</v>
+      </c>
+      <c r="S28">
+        <v>46.59999999999999</v>
+      </c>
+      <c r="T28">
+        <v>0.6083550913838119</v>
+      </c>
+      <c r="U28">
+        <v>143.3</v>
+      </c>
+      <c r="V28">
+        <v>0.1131732743642395</v>
+      </c>
+      <c r="W28">
+        <v>0.1478781284004353</v>
+      </c>
+      <c r="X28">
+        <v>0.07448373903729942</v>
+      </c>
+      <c r="Y28">
+        <v>0.07339438936313585</v>
+      </c>
+      <c r="Z28">
+        <v>1.085261313830461</v>
+      </c>
+      <c r="AA28">
+        <v>0.1686172077823871</v>
+      </c>
+      <c r="AB28">
+        <v>0.07433256401740851</v>
+      </c>
+      <c r="AC28">
+        <v>0.09428464376497864</v>
+      </c>
+      <c r="AD28">
+        <v>0.1</v>
+      </c>
+      <c r="AE28">
+        <v>5.294700622309723</v>
+      </c>
+      <c r="AF28">
+        <v>5.394700622309722</v>
+      </c>
+      <c r="AG28">
+        <v>-137.9052993776903</v>
+      </c>
+      <c r="AH28">
+        <v>0.004242468625946296</v>
+      </c>
+      <c r="AI28">
+        <v>0.004909652930847224</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.1222245387677783</v>
+      </c>
+      <c r="AK28">
+        <v>-0.1443286909784776</v>
+      </c>
+      <c r="AL28">
+        <v>0.7</v>
+      </c>
+      <c r="AM28">
+        <v>0.7</v>
+      </c>
+      <c r="AN28">
+        <v>0.0005617977528089888</v>
+      </c>
+      <c r="AO28">
+        <v>246.4285714285714</v>
+      </c>
+      <c r="AP28">
+        <v>-0.7747488729083724</v>
+      </c>
+      <c r="AQ28">
+        <v>246.4285714285714</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>The Hanover Insurance Group, Inc. (NYSE:THG)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>0.0548</v>
+      </c>
+      <c r="E29">
+        <v>-0.0357</v>
+      </c>
+      <c r="G29">
+        <v>0.01318364903993918</v>
+      </c>
+      <c r="H29">
+        <v>0.01318364903993918</v>
+      </c>
+      <c r="I29">
+        <v>0.08259596564163123</v>
+      </c>
+      <c r="J29">
+        <v>0.06332068467762411</v>
+      </c>
+      <c r="K29">
+        <v>366</v>
+      </c>
+      <c r="L29">
+        <v>0.05920509875604588</v>
+      </c>
+      <c r="M29">
+        <v>122</v>
+      </c>
+      <c r="N29">
+        <v>0.0218916542554146</v>
+      </c>
+      <c r="O29">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P29">
+        <v>122</v>
+      </c>
+      <c r="Q29">
+        <v>0.0218916542554146</v>
+      </c>
+      <c r="R29">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>427.1</v>
+      </c>
+      <c r="V29">
+        <v>0.07663873387284897</v>
+      </c>
+      <c r="W29">
+        <v>0.1729433445163729</v>
+      </c>
+      <c r="X29">
+        <v>0.07740878843913718</v>
+      </c>
+      <c r="Y29">
+        <v>0.09553455607723571</v>
+      </c>
+      <c r="Z29">
+        <v>2.548186314921681</v>
+      </c>
+      <c r="AA29">
+        <v>0.1613529021469927</v>
+      </c>
+      <c r="AB29">
+        <v>0.07265384345778814</v>
+      </c>
+      <c r="AC29">
+        <v>0.08869905868920461</v>
+      </c>
+      <c r="AD29">
+        <v>783.9</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>783.9</v>
+      </c>
+      <c r="AG29">
+        <v>356.8</v>
+      </c>
+      <c r="AH29">
+        <v>0.1233167631512711</v>
+      </c>
+      <c r="AI29">
+        <v>0.2140867380380162</v>
+      </c>
+      <c r="AJ29">
+        <v>0.06017167816247027</v>
+      </c>
+      <c r="AK29">
+        <v>0.1103107126294636</v>
+      </c>
+      <c r="AL29">
+        <v>34.1</v>
+      </c>
+      <c r="AM29">
+        <v>34.1</v>
+      </c>
+      <c r="AN29">
+        <v>1.526582278481013</v>
+      </c>
+      <c r="AO29">
+        <v>14.97360703812317</v>
+      </c>
+      <c r="AP29">
+        <v>0.6948393378773124</v>
+      </c>
+      <c r="AQ29">
+        <v>14.97360703812317</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Stewart Information Services Corporation (NYSE:STC)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>0.0486</v>
+      </c>
+      <c r="E30">
+        <v>-0.07980000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.06031548360315484</v>
+      </c>
+      <c r="H30">
+        <v>0.06031548360315484</v>
+      </c>
+      <c r="I30">
+        <v>0.05784830165543114</v>
+      </c>
+      <c r="J30">
+        <v>0.04381549971854559</v>
+      </c>
+      <c r="K30">
+        <v>59.4</v>
+      </c>
+      <c r="L30">
+        <v>0.02465753424657534</v>
+      </c>
+      <c r="M30">
+        <v>56.83</v>
+      </c>
+      <c r="N30">
+        <v>0.03037575498423219</v>
+      </c>
+      <c r="O30">
+        <v>0.9567340067340068</v>
+      </c>
+      <c r="P30">
+        <v>53</v>
+      </c>
+      <c r="Q30">
+        <v>0.02832861189801699</v>
+      </c>
+      <c r="R30">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="S30">
+        <v>3.829999999999998</v>
+      </c>
+      <c r="T30">
+        <v>0.06739398205173321</v>
+      </c>
+      <c r="U30">
+        <v>174.1</v>
+      </c>
+      <c r="V30">
+        <v>0.09305681757442941</v>
+      </c>
+      <c r="W30">
+        <v>0.04393816110659072</v>
+      </c>
+      <c r="X30">
+        <v>0.0809992765395485</v>
+      </c>
+      <c r="Y30">
+        <v>-0.03706111543295778</v>
+      </c>
+      <c r="Z30">
+        <v>3.629011083461655</v>
+      </c>
+      <c r="AA30">
+        <v>0.159006934106013</v>
+      </c>
+      <c r="AB30">
+        <v>0.07169011424004215</v>
+      </c>
+      <c r="AC30">
+        <v>0.08731681986597081</v>
+      </c>
+      <c r="AD30">
+        <v>445.7</v>
+      </c>
+      <c r="AE30">
+        <v>130.717206560332</v>
+      </c>
+      <c r="AF30">
+        <v>576.417206560332</v>
+      </c>
+      <c r="AG30">
+        <v>402.317206560332</v>
+      </c>
+      <c r="AH30">
+        <v>0.2355302389960629</v>
+      </c>
+      <c r="AI30">
+        <v>0.289552531449857</v>
+      </c>
+      <c r="AJ30">
+        <v>0.1769814188451834</v>
+      </c>
+      <c r="AK30">
+        <v>0.2214650423366287</v>
+      </c>
+      <c r="AL30">
+        <v>19.7</v>
+      </c>
+      <c r="AM30">
+        <v>19.7</v>
+      </c>
+      <c r="AN30">
+        <v>1.961707746478873</v>
+      </c>
+      <c r="AO30">
+        <v>6.076142131979696</v>
+      </c>
+      <c r="AP30">
+        <v>1.770762352818363</v>
+      </c>
+      <c r="AQ30">
+        <v>6.076142131979696</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Old Republic International Corporation (NYSE:ORI)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>0.0447</v>
+      </c>
+      <c r="E31">
+        <v>0.0684</v>
+      </c>
+      <c r="F31">
+        <v>0.1</v>
+      </c>
+      <c r="G31">
+        <v>0.1054808939805635</v>
+      </c>
+      <c r="H31">
+        <v>0.1054808939805635</v>
+      </c>
+      <c r="I31">
+        <v>0.1561141093668395</v>
+      </c>
+      <c r="J31">
+        <v>0.1245037890241149</v>
+      </c>
+      <c r="K31">
+        <v>938.2</v>
+      </c>
+      <c r="L31">
+        <v>0.1148319502582556</v>
+      </c>
+      <c r="M31">
+        <v>1097.5</v>
+      </c>
+      <c r="N31">
+        <v>0.120457463972517</v>
+      </c>
+      <c r="O31">
+        <v>1.169793221061607</v>
+      </c>
+      <c r="P31">
+        <v>273.9</v>
+      </c>
+      <c r="Q31">
+        <v>0.03006223178320949</v>
+      </c>
+      <c r="R31">
+        <v>0.2919420166275847</v>
+      </c>
+      <c r="S31">
+        <v>823.6</v>
+      </c>
+      <c r="T31">
+        <v>0.7504328018223235</v>
+      </c>
+      <c r="U31">
+        <v>525.2</v>
+      </c>
+      <c r="V31">
+        <v>0.05764397273655212</v>
+      </c>
+      <c r="W31">
+        <v>0.1585976063290283</v>
+      </c>
+      <c r="X31">
+        <v>0.07961624528161693</v>
+      </c>
+      <c r="Y31">
+        <v>0.07898136104741141</v>
+      </c>
+      <c r="Z31">
+        <v>1.077083755758131</v>
+      </c>
+      <c r="AA31">
+        <v>0.1341010086882117</v>
+      </c>
+      <c r="AB31">
+        <v>0.0716307804044425</v>
+      </c>
+      <c r="AC31">
+        <v>0.06247022828376918</v>
+      </c>
+      <c r="AD31">
+        <v>1988.4</v>
+      </c>
+      <c r="AE31">
+        <v>231.0825182552398</v>
+      </c>
+      <c r="AF31">
+        <v>2219.48251825524</v>
+      </c>
+      <c r="AG31">
+        <v>1694.28251825524</v>
+      </c>
+      <c r="AH31">
+        <v>0.1958842376090837</v>
+      </c>
+      <c r="AI31">
+        <v>0.2561498241391706</v>
+      </c>
+      <c r="AJ31">
+        <v>0.1567998648259625</v>
+      </c>
+      <c r="AK31">
+        <v>0.2081534912208763</v>
+      </c>
+      <c r="AL31">
+        <v>73.2</v>
+      </c>
+      <c r="AM31">
+        <v>73.2</v>
+      </c>
+      <c r="AN31">
+        <v>1.463996465910764</v>
+      </c>
+      <c r="AO31">
+        <v>17.26229508196721</v>
+      </c>
+      <c r="AP31">
+        <v>1.247447002102224</v>
+      </c>
+      <c r="AQ31">
+        <v>17.26229508196721</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Investors Title Company (NasdaqGS:ITIC)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0815</v>
+      </c>
+      <c r="E32">
+        <v>0.07150000000000001</v>
+      </c>
+      <c r="G32">
+        <v>0.124896265560166</v>
+      </c>
+      <c r="H32">
+        <v>0.124896265560166</v>
+      </c>
+      <c r="I32">
+        <v>0.1483524779201255</v>
+      </c>
+      <c r="J32">
+        <v>0.1214875019758506</v>
+      </c>
+      <c r="K32">
+        <v>28.5</v>
+      </c>
+      <c r="L32">
+        <v>0.1182572614107884</v>
+      </c>
+      <c r="M32">
+        <v>4.57</v>
+      </c>
+      <c r="N32">
+        <v>0.01024433983411791</v>
+      </c>
+      <c r="O32">
+        <v>0.1603508771929825</v>
+      </c>
+      <c r="P32">
+        <v>3.47</v>
+      </c>
+      <c r="Q32">
+        <v>0.007778524994395876</v>
+      </c>
+      <c r="R32">
+        <v>0.1217543859649123</v>
+      </c>
+      <c r="S32">
+        <v>1.1</v>
+      </c>
+      <c r="T32">
+        <v>0.2407002188183807</v>
+      </c>
+      <c r="U32">
+        <v>25.5</v>
+      </c>
+      <c r="V32">
+        <v>0.05716207128446536</v>
+      </c>
+      <c r="W32">
+        <v>0.1127819548872181</v>
+      </c>
+      <c r="X32">
+        <v>0.07469701063219829</v>
+      </c>
+      <c r="Y32">
+        <v>0.03808494425501976</v>
+      </c>
+      <c r="Z32">
+        <v>1.101124012236965</v>
+      </c>
+      <c r="AA32">
+        <v>0.1337728056122948</v>
+      </c>
+      <c r="AB32">
+        <v>0.07423167173945094</v>
+      </c>
+      <c r="AC32">
+        <v>0.05954113387284385</v>
+      </c>
+      <c r="AD32">
+        <v>0.652</v>
+      </c>
+      <c r="AE32">
+        <v>5.685264106248789</v>
+      </c>
+      <c r="AF32">
+        <v>6.33726410624879</v>
+      </c>
+      <c r="AG32">
+        <v>-19.16273589375121</v>
+      </c>
+      <c r="AH32">
+        <v>0.01400694551269448</v>
+      </c>
+      <c r="AI32">
+        <v>0.02282569714353469</v>
+      </c>
+      <c r="AJ32">
+        <v>-0.04488419612156956</v>
+      </c>
+      <c r="AK32">
+        <v>-0.07600120498521858</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+      <c r="AN32">
+        <v>0.01571463003133285</v>
+      </c>
+      <c r="AP32">
+        <v>-0.4618639646601883</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CNA Financial Corporation (NYSE:CNA)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.06269999999999999</v>
+      </c>
+      <c r="E33">
+        <v>0.152</v>
+      </c>
+      <c r="F33">
+        <v>0.0167</v>
+      </c>
+      <c r="G33">
+        <v>0.1219477569562748</v>
+      </c>
+      <c r="H33">
+        <v>0.1219477569562748</v>
+      </c>
+      <c r="I33">
+        <v>0.1263946794367721</v>
+      </c>
+      <c r="J33">
+        <v>0.09996670100908341</v>
+      </c>
+      <c r="K33">
+        <v>1305</v>
+      </c>
+      <c r="L33">
+        <v>0.09263202725724021</v>
+      </c>
+      <c r="M33">
+        <v>166.3</v>
+      </c>
+      <c r="N33">
+        <v>0.01269407508053066</v>
+      </c>
+      <c r="O33">
+        <v>0.1274329501915709</v>
+      </c>
+      <c r="P33">
+        <v>146.3</v>
+      </c>
+      <c r="Q33">
+        <v>0.01116742744607117</v>
+      </c>
+      <c r="R33">
+        <v>0.1121072796934866</v>
+      </c>
+      <c r="S33">
+        <v>20</v>
+      </c>
+      <c r="T33">
+        <v>0.1202645820805773</v>
+      </c>
+      <c r="U33">
+        <v>456</v>
+      </c>
+      <c r="V33">
+        <v>0.03480756606567638</v>
+      </c>
+      <c r="W33">
+        <v>0.1523998598621978</v>
+      </c>
+      <c r="X33">
+        <v>0.07958747841855886</v>
+      </c>
+      <c r="Y33">
+        <v>0.07281238144363898</v>
+      </c>
+      <c r="Z33">
+        <v>1.234948973861009</v>
+      </c>
+      <c r="AA33">
+        <v>0.1234537748314379</v>
+      </c>
+      <c r="AB33">
+        <v>0.07164302226091365</v>
+      </c>
+      <c r="AC33">
+        <v>0.05181075257052421</v>
+      </c>
+      <c r="AD33">
+        <v>2972</v>
+      </c>
+      <c r="AE33">
+        <v>201.7587804737703</v>
+      </c>
+      <c r="AF33">
+        <v>3173.75878047377</v>
+      </c>
+      <c r="AG33">
+        <v>2717.75878047377</v>
+      </c>
+      <c r="AH33">
+        <v>0.1950159034395687</v>
+      </c>
+      <c r="AI33">
+        <v>0.2278074743098475</v>
+      </c>
+      <c r="AJ33">
+        <v>0.1718104146068921</v>
+      </c>
+      <c r="AK33">
+        <v>0.2016776067861777</v>
+      </c>
+      <c r="AL33">
+        <v>135</v>
+      </c>
+      <c r="AM33">
+        <v>135</v>
+      </c>
+      <c r="AN33">
+        <v>1.563387690689111</v>
+      </c>
+      <c r="AO33">
+        <v>13.22222222222222</v>
+      </c>
+      <c r="AP33">
+        <v>1.429646912400721</v>
+      </c>
+      <c r="AQ33">
+        <v>13.22222222222222</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Safety Insurance Group, Inc. (NasdaqGS:SAFT)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>0.04969999999999999</v>
+      </c>
+      <c r="E34">
+        <v>-0.0358</v>
+      </c>
+      <c r="G34">
+        <v>0.02949528258679125</v>
+      </c>
+      <c r="H34">
+        <v>0.02949528258679125</v>
+      </c>
+      <c r="I34">
+        <v>0.08887409844458559</v>
+      </c>
+      <c r="J34">
+        <v>0.06961028862465971</v>
+      </c>
+      <c r="K34">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="L34">
+        <v>0.0686085921040579</v>
+      </c>
+      <c r="M34">
+        <v>53.3</v>
+      </c>
+      <c r="N34">
+        <v>0.04359205038030588</v>
+      </c>
+      <c r="O34">
+        <v>0.7116154873164218</v>
+      </c>
+      <c r="P34">
+        <v>53.3</v>
+      </c>
+      <c r="Q34">
+        <v>0.04359205038030588</v>
+      </c>
+      <c r="R34">
+        <v>0.7116154873164218</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>62.6</v>
+      </c>
+      <c r="V34">
+        <v>0.05119816798887707</v>
+      </c>
+      <c r="W34">
+        <v>0.09731064050928934</v>
+      </c>
+      <c r="X34">
+        <v>0.07523212930466616</v>
+      </c>
+      <c r="Y34">
+        <v>0.02207851120462317</v>
+      </c>
+      <c r="Z34">
+        <v>1.418564618732201</v>
+      </c>
+      <c r="AA34">
+        <v>0.0987466925426789</v>
+      </c>
+      <c r="AB34">
+        <v>0.0738611002969224</v>
+      </c>
+      <c r="AC34">
+        <v>0.0248855922457565</v>
+      </c>
+      <c r="AD34">
+        <v>30</v>
+      </c>
+      <c r="AE34">
+        <v>17.88073364022947</v>
+      </c>
+      <c r="AF34">
+        <v>47.88073364022947</v>
+      </c>
+      <c r="AG34">
+        <v>-14.71926635977054</v>
+      </c>
+      <c r="AH34">
+        <v>0.03768413322548231</v>
+      </c>
+      <c r="AI34">
+        <v>0.05324336644732885</v>
+      </c>
+      <c r="AJ34">
+        <v>-0.01218501748402417</v>
+      </c>
+      <c r="AK34">
+        <v>-0.0175924528532287</v>
+      </c>
+      <c r="AL34">
+        <v>0.506</v>
+      </c>
+      <c r="AM34">
+        <v>0.506</v>
+      </c>
+      <c r="AN34">
+        <v>0.273972602739726</v>
+      </c>
+      <c r="AO34">
+        <v>189.7233201581028</v>
+      </c>
+      <c r="AP34">
+        <v>-0.1344225238335209</v>
+      </c>
+      <c r="AQ34">
+        <v>189.7233201581028</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Loews Corporation (NYSE:L)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D35">
         <v>0.03759999999999999</v>
       </c>
-      <c r="E4">
+      <c r="E35">
         <v>0.249</v>
       </c>
-      <c r="G4">
+      <c r="G35">
         <v>0.162698873533852</v>
       </c>
-      <c r="H4">
+      <c r="H35">
         <v>0.162698873533852</v>
       </c>
-      <c r="I4">
+      <c r="I35">
         <v>0.1532492855126737</v>
       </c>
-      <c r="J4">
+      <c r="J35">
         <v>0.1187865275265701</v>
       </c>
-      <c r="K4">
+      <c r="K35">
         <v>1673</v>
       </c>
-      <c r="L4">
+      <c r="L35">
         <v>0.09714318894437347</v>
       </c>
-      <c r="M4">
+      <c r="M35">
         <v>458</v>
       </c>
-      <c r="N4">
+      <c r="N35">
         <v>0.0248325968498387</v>
       </c>
-      <c r="O4">
+      <c r="O35">
         <v>0.273759713090257</v>
       </c>
-      <c r="P4">
+      <c r="P35">
         <v>56</v>
       </c>
-      <c r="Q4">
+      <c r="Q35">
         <v>0.003036300051508662</v>
       </c>
-      <c r="R4">
+      <c r="R35">
         <v>0.03347280334728033</v>
       </c>
-      <c r="S4">
+      <c r="S35">
         <v>402</v>
       </c>
-      <c r="T4">
+      <c r="T35">
         <v>0.8777292576419214</v>
       </c>
-      <c r="U4">
+      <c r="U35">
         <v>548</v>
       </c>
-      <c r="V4">
+      <c r="V35">
         <v>0.02971236478976333</v>
       </c>
-      <c r="W4">
+      <c r="W35">
         <v>0.1157945736434109</v>
       </c>
-      <c r="X4">
-        <v>0.08597278345264425</v>
-      </c>
-      <c r="Y4">
-        <v>0.0298217901907666</v>
-      </c>
-      <c r="Z4">
+      <c r="X35">
+        <v>0.08594695592466771</v>
+      </c>
+      <c r="Y35">
+        <v>0.02984761771874314</v>
+      </c>
+      <c r="Z35">
         <v>0.751078164009262</v>
       </c>
-      <c r="AA4">
+      <c r="AA35">
         <v>0.08921796700369192</v>
       </c>
-      <c r="AB4">
-        <v>0.07012923152549599</v>
-      </c>
-      <c r="AC4">
-        <v>0.01908873547819592</v>
-      </c>
-      <c r="AD4">
+      <c r="AB35">
+        <v>0.07011244752958715</v>
+      </c>
+      <c r="AC35">
+        <v>0.01910551947410477</v>
+      </c>
+      <c r="AD35">
         <v>9534</v>
       </c>
-      <c r="AE4">
+      <c r="AE35">
         <v>403.7040245036647</v>
       </c>
-      <c r="AF4">
+      <c r="AF35">
         <v>9937.704024503664</v>
       </c>
-      <c r="AG4">
+      <c r="AG35">
         <v>9389.704024503664</v>
       </c>
-      <c r="AH4">
+      <c r="AH35">
         <v>0.3501508962031239</v>
       </c>
-      <c r="AI4">
+      <c r="AI35">
         <v>0.3525795919755694</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ35">
         <v>0.3373562029092016</v>
       </c>
-      <c r="AK4">
+      <c r="AK35">
         <v>0.3397425493875587</v>
       </c>
-      <c r="AL4">
+      <c r="AL35">
         <v>427</v>
       </c>
-      <c r="AM4">
+      <c r="AM35">
         <v>427</v>
       </c>
-      <c r="AN4">
+      <c r="AN35">
         <v>2.896991795806746</v>
       </c>
-      <c r="AO4">
+      <c r="AO35">
         <v>6.236533957845433</v>
       </c>
-      <c r="AP4">
+      <c r="AP35">
         <v>2.85314616362919</v>
       </c>
-      <c r="AQ4">
+      <c r="AQ35">
         <v>6.236533957845433</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ICC Holdings, Inc. (NasdaqCM:ICCH)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>0.102</v>
+      </c>
+      <c r="E36">
+        <v>0.366</v>
+      </c>
+      <c r="G36">
+        <v>0.06994594594594594</v>
+      </c>
+      <c r="H36">
+        <v>0.06994594594594594</v>
+      </c>
+      <c r="I36">
+        <v>0.09178378378378378</v>
+      </c>
+      <c r="J36">
+        <v>0.07090877158747194</v>
+      </c>
+      <c r="K36">
+        <v>6.42</v>
+      </c>
+      <c r="L36">
+        <v>0.06940540540540541</v>
+      </c>
+      <c r="M36">
+        <v>0.201</v>
+      </c>
+      <c r="N36">
+        <v>0.00291304347826087</v>
+      </c>
+      <c r="O36">
+        <v>0.03130841121495327</v>
+      </c>
+      <c r="P36">
+        <v>-0</v>
+      </c>
+      <c r="Q36">
+        <v>-0</v>
+      </c>
+      <c r="R36">
+        <v>-0</v>
+      </c>
+      <c r="S36">
+        <v>0.201</v>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+      <c r="U36">
+        <v>11</v>
+      </c>
+      <c r="V36">
+        <v>0.1594202898550725</v>
+      </c>
+      <c r="W36">
+        <v>0.1077181208053691</v>
+      </c>
+      <c r="X36">
+        <v>0.07905417496649858</v>
+      </c>
+      <c r="Y36">
+        <v>0.02866394583887054</v>
+      </c>
+      <c r="Z36">
+        <v>1.28597247323787</v>
+      </c>
+      <c r="AA36">
+        <v>0.09118672837260053</v>
+      </c>
+      <c r="AB36">
+        <v>0.07234360800819527</v>
+      </c>
+      <c r="AC36">
+        <v>0.01884312036440526</v>
+      </c>
+      <c r="AD36">
+        <v>15</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>15</v>
+      </c>
+      <c r="AG36">
+        <v>4</v>
+      </c>
+      <c r="AH36">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="AI36">
+        <v>0.170261066969353</v>
+      </c>
+      <c r="AJ36">
+        <v>0.0547945205479452</v>
+      </c>
+      <c r="AK36">
+        <v>0.05188067444876784</v>
+      </c>
+      <c r="AL36">
+        <v>0.185</v>
+      </c>
+      <c r="AM36">
+        <v>0.185</v>
+      </c>
+      <c r="AN36">
+        <v>1.607717041800643</v>
+      </c>
+      <c r="AO36">
+        <v>45.89189189189189</v>
+      </c>
+      <c r="AP36">
+        <v>0.4287245444801715</v>
+      </c>
+      <c r="AQ36">
+        <v>45.89189189189189</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>United Fire Group, Inc. (NasdaqGS:UFCS)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>0.00808</v>
+      </c>
+      <c r="E37">
+        <v>0.421</v>
+      </c>
+      <c r="G37">
+        <v>-0.02153209109730849</v>
+      </c>
+      <c r="H37">
+        <v>-0.02153209109730849</v>
+      </c>
+      <c r="I37">
+        <v>0.05879393459715322</v>
+      </c>
+      <c r="J37">
+        <v>0.04781779420969767</v>
+      </c>
+      <c r="K37">
+        <v>50.1</v>
+      </c>
+      <c r="L37">
+        <v>0.04149068322981367</v>
+      </c>
+      <c r="M37">
+        <v>16.2</v>
+      </c>
+      <c r="N37">
+        <v>0.02246879334257975</v>
+      </c>
+      <c r="O37">
+        <v>0.3233532934131736</v>
+      </c>
+      <c r="P37">
+        <v>16.2</v>
+      </c>
+      <c r="Q37">
+        <v>0.02246879334257975</v>
+      </c>
+      <c r="R37">
+        <v>0.3233532934131736</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>197.4</v>
+      </c>
+      <c r="V37">
+        <v>0.2737864077669903</v>
+      </c>
+      <c r="W37">
+        <v>0.07768646301752211</v>
+      </c>
+      <c r="X37">
+        <v>0.07871488805571519</v>
+      </c>
+      <c r="Y37">
+        <v>-0.001028425038193087</v>
+      </c>
+      <c r="Z37">
+        <v>1.84624101238498</v>
+      </c>
+      <c r="AA37">
+        <v>0.08828317279172887</v>
+      </c>
+      <c r="AB37">
+        <v>0.0724677038011257</v>
+      </c>
+      <c r="AC37">
+        <v>0.01581546899060317</v>
+      </c>
+      <c r="AD37">
+        <v>117</v>
+      </c>
+      <c r="AE37">
+        <v>28.33161986968738</v>
+      </c>
+      <c r="AF37">
+        <v>145.3316198696874</v>
+      </c>
+      <c r="AG37">
+        <v>-52.06838013031262</v>
+      </c>
+      <c r="AH37">
+        <v>0.1677551835076134</v>
+      </c>
+      <c r="AI37">
+        <v>0.1560806407691607</v>
+      </c>
+      <c r="AJ37">
+        <v>-0.07783812064446274</v>
+      </c>
+      <c r="AK37">
+        <v>-0.07096379482672438</v>
+      </c>
+      <c r="AL37">
+        <v>5.67</v>
+      </c>
+      <c r="AM37">
+        <v>5.67</v>
+      </c>
+      <c r="AN37">
+        <v>1.3347022587269</v>
+      </c>
+      <c r="AO37">
+        <v>11.8694885361552</v>
+      </c>
+      <c r="AP37">
+        <v>-0.5939810646852911</v>
+      </c>
+      <c r="AQ37">
+        <v>11.8694885361552</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Selective Insurance Group, Inc. (NasdaqGS:SIGI)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>0.113</v>
+      </c>
+      <c r="E38">
+        <v>0.00068</v>
+      </c>
+      <c r="F38">
+        <v>0.164</v>
+      </c>
+      <c r="G38">
+        <v>0.1098176420695505</v>
+      </c>
+      <c r="H38">
+        <v>0.1098176420695505</v>
+      </c>
+      <c r="I38">
+        <v>0.0687270663993341</v>
+      </c>
+      <c r="J38">
+        <v>0.05488410202826173</v>
+      </c>
+      <c r="K38">
+        <v>236.3</v>
+      </c>
+      <c r="L38">
+        <v>0.05010602205258694</v>
+      </c>
+      <c r="M38">
+        <v>98.8</v>
+      </c>
+      <c r="N38">
+        <v>0.01737753935449829</v>
+      </c>
+      <c r="O38">
+        <v>0.4181125687685145</v>
+      </c>
+      <c r="P38">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="Q38">
+        <v>0.01461612874857092</v>
+      </c>
+      <c r="R38">
+        <v>0.3516716038933559</v>
+      </c>
+      <c r="S38">
+        <v>15.7</v>
+      </c>
+      <c r="T38">
+        <v>0.1589068825910931</v>
+      </c>
+      <c r="U38">
+        <v>0.098</v>
+      </c>
+      <c r="V38">
+        <v>1.723683053381409E-05</v>
+      </c>
+      <c r="W38">
+        <v>0.09666993945344461</v>
+      </c>
+      <c r="X38">
+        <v>0.07647708011204407</v>
+      </c>
+      <c r="Y38">
+        <v>0.02019285934140054</v>
+      </c>
+      <c r="Z38">
+        <v>1.480431941455767</v>
+      </c>
+      <c r="AA38">
+        <v>0.08125217772075592</v>
+      </c>
+      <c r="AB38">
+        <v>0.07314326136140344</v>
+      </c>
+      <c r="AC38">
+        <v>0.008108916359352486</v>
+      </c>
+      <c r="AD38">
+        <v>508.2</v>
+      </c>
+      <c r="AE38">
+        <v>44.51577430370173</v>
+      </c>
+      <c r="AF38">
+        <v>552.7157743037017</v>
+      </c>
+      <c r="AG38">
+        <v>552.6177743037017</v>
+      </c>
+      <c r="AH38">
+        <v>0.08860158005121181</v>
+      </c>
+      <c r="AI38">
+        <v>0.1485589116759337</v>
+      </c>
+      <c r="AJ38">
+        <v>0.08858726210333291</v>
+      </c>
+      <c r="AK38">
+        <v>0.1485364837574263</v>
+      </c>
+      <c r="AL38">
+        <v>28.8</v>
+      </c>
+      <c r="AM38">
+        <v>28.8</v>
+      </c>
+      <c r="AN38">
+        <v>1.385420642276866</v>
+      </c>
+      <c r="AO38">
+        <v>11.29861111111111</v>
+      </c>
+      <c r="AP38">
+        <v>1.506509389628978</v>
+      </c>
+      <c r="AQ38">
+        <v>11.29861111111111</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>First American Financial Corporation (NYSE:FAF)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.00062</v>
+      </c>
+      <c r="E39">
+        <v>-0.306</v>
+      </c>
+      <c r="G39">
+        <v>0.1013912776935783</v>
+      </c>
+      <c r="H39">
+        <v>0.1013912776935783</v>
+      </c>
+      <c r="I39">
+        <v>0.0476529623342444</v>
+      </c>
+      <c r="J39">
+        <v>0.04311240095687174</v>
+      </c>
+      <c r="K39">
+        <v>92.8</v>
+      </c>
+      <c r="L39">
+        <v>0.01580300733954328</v>
+      </c>
+      <c r="M39">
+        <v>297.7</v>
+      </c>
+      <c r="N39">
+        <v>0.04628708253000808</v>
+      </c>
+      <c r="O39">
+        <v>3.207974137931034</v>
+      </c>
+      <c r="P39">
+        <v>219.7</v>
+      </c>
+      <c r="Q39">
+        <v>0.03415946265315007</v>
+      </c>
+      <c r="R39">
+        <v>2.367456896551724</v>
+      </c>
+      <c r="S39">
+        <v>78</v>
+      </c>
+      <c r="T39">
+        <v>0.2620087336244541</v>
+      </c>
+      <c r="U39">
+        <v>2953.4</v>
+      </c>
+      <c r="V39">
+        <v>0.4592014428758007</v>
+      </c>
+      <c r="W39">
+        <v>0.02049832125817282</v>
+      </c>
+      <c r="X39">
+        <v>0.08426741863816603</v>
+      </c>
+      <c r="Y39">
+        <v>-0.0637690973799932</v>
+      </c>
+      <c r="Z39">
+        <v>1.776020238565425</v>
+      </c>
+      <c r="AA39">
+        <v>0.07656849663255161</v>
+      </c>
+      <c r="AB39">
+        <v>0.0699472184561238</v>
+      </c>
+      <c r="AC39">
+        <v>0.006621278176427811</v>
+      </c>
+      <c r="AD39">
+        <v>2725.9</v>
+      </c>
+      <c r="AE39">
+        <v>235.8375464230829</v>
+      </c>
+      <c r="AF39">
+        <v>2961.737546423083</v>
+      </c>
+      <c r="AG39">
+        <v>8.33754642308304</v>
+      </c>
+      <c r="AH39">
+        <v>0.3153019394635607</v>
+      </c>
+      <c r="AI39">
+        <v>0.3668996160517907</v>
+      </c>
+      <c r="AJ39">
+        <v>0.00129466262102401</v>
+      </c>
+      <c r="AK39">
+        <v>0.001628765021544167</v>
+      </c>
+      <c r="AL39">
+        <v>139.2</v>
+      </c>
+      <c r="AM39">
+        <v>139.2</v>
+      </c>
+      <c r="AN39">
+        <v>5.123872180451128</v>
+      </c>
+      <c r="AO39">
+        <v>1.746408045977011</v>
+      </c>
+      <c r="AP39">
+        <v>0.01567207974263729</v>
+      </c>
+      <c r="AQ39">
+        <v>1.746408045977011</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Global Indemnity Group, LLC (NYSE:GBLI)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>-0.0397</v>
+      </c>
+      <c r="G40">
+        <v>0.0831638418079096</v>
+      </c>
+      <c r="H40">
+        <v>0.0831638418079096</v>
+      </c>
+      <c r="I40">
+        <v>0.1235171983214107</v>
+      </c>
+      <c r="J40">
+        <v>0.09622851497133156</v>
+      </c>
+      <c r="K40">
+        <v>40.1</v>
+      </c>
+      <c r="L40">
+        <v>0.09062146892655368</v>
+      </c>
+      <c r="M40">
+        <v>17.129</v>
+      </c>
+      <c r="N40">
+        <v>0.03475852272727273</v>
+      </c>
+      <c r="O40">
+        <v>0.4271571072319202</v>
+      </c>
+      <c r="P40">
+        <v>16.6</v>
+      </c>
+      <c r="Q40">
+        <v>0.03368506493506494</v>
+      </c>
+      <c r="R40">
+        <v>0.4139650872817955</v>
+      </c>
+      <c r="S40">
+        <v>0.5289999999999999</v>
+      </c>
+      <c r="T40">
+        <v>0.03088329733201003</v>
+      </c>
+      <c r="U40">
+        <v>31</v>
+      </c>
+      <c r="V40">
+        <v>0.06290584415584416</v>
+      </c>
+      <c r="W40">
+        <v>0.0639859581937131</v>
+      </c>
+      <c r="X40">
+        <v>0.07486530636856081</v>
+      </c>
+      <c r="Y40">
+        <v>-0.01087934817484772</v>
+      </c>
+      <c r="Z40">
+        <v>0.7496846258306001</v>
+      </c>
+      <c r="AA40">
+        <v>0.07214103824051701</v>
+      </c>
+      <c r="AB40">
+        <v>0.07418526618929815</v>
+      </c>
+      <c r="AC40">
+        <v>-0.002044227948781133</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>10.86819871387891</v>
+      </c>
+      <c r="AF40">
+        <v>10.86819871387891</v>
+      </c>
+      <c r="AG40">
+        <v>-20.1318012861211</v>
+      </c>
+      <c r="AH40">
+        <v>0.02157809196933804</v>
+      </c>
+      <c r="AI40">
+        <v>0.01558012354048942</v>
+      </c>
+      <c r="AJ40">
+        <v>-0.04259182517651778</v>
+      </c>
+      <c r="AK40">
+        <v>-0.03020216284689959</v>
+      </c>
+      <c r="AL40">
+        <v>0.005</v>
+      </c>
+      <c r="AM40">
+        <v>0.005</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>10820</v>
+      </c>
+      <c r="AP40">
+        <v>-0.351156485018683</v>
+      </c>
+      <c r="AQ40">
+        <v>10820</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Donegal Group Inc. (NasdaqGS:DGIC.A)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>0.0417</v>
+      </c>
+      <c r="E41">
+        <v>0.067</v>
+      </c>
+      <c r="G41">
+        <v>0.01021346134204882</v>
+      </c>
+      <c r="H41">
+        <v>0.01021346134204882</v>
+      </c>
+      <c r="I41">
+        <v>0.03166173016035134</v>
+      </c>
+      <c r="J41">
+        <v>0.02610520135737578</v>
+      </c>
+      <c r="K41">
+        <v>24.9</v>
+      </c>
+      <c r="L41">
+        <v>0.02543151874170156</v>
+      </c>
+      <c r="M41">
+        <v>22.5</v>
+      </c>
+      <c r="N41">
+        <v>0.04353715170278638</v>
+      </c>
+      <c r="O41">
+        <v>0.9036144578313253</v>
+      </c>
+      <c r="P41">
+        <v>22.5</v>
+      </c>
+      <c r="Q41">
+        <v>0.04353715170278638</v>
+      </c>
+      <c r="R41">
+        <v>0.9036144578313253</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>28.7</v>
+      </c>
+      <c r="V41">
+        <v>0.05553405572755418</v>
+      </c>
+      <c r="W41">
+        <v>0.05260933868582294</v>
+      </c>
+      <c r="X41">
+        <v>0.0758446770534571</v>
+      </c>
+      <c r="Y41">
+        <v>-0.02323533836763416</v>
+      </c>
+      <c r="Z41">
+        <v>2.044178132242103</v>
+      </c>
+      <c r="AA41">
+        <v>0.05336368175252441</v>
+      </c>
+      <c r="AB41">
+        <v>0.0734981498753654</v>
+      </c>
+      <c r="AC41">
+        <v>-0.02013446812284099</v>
+      </c>
+      <c r="AD41">
+        <v>35</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>35</v>
+      </c>
+      <c r="AG41">
+        <v>6.300000000000001</v>
+      </c>
+      <c r="AH41">
+        <v>0.06342877854295036</v>
+      </c>
+      <c r="AI41">
+        <v>0.0638220277169949</v>
+      </c>
+      <c r="AJ41">
+        <v>0.01204358631236858</v>
+      </c>
+      <c r="AK41">
+        <v>0.01212237829517029</v>
+      </c>
+      <c r="AL41">
+        <v>0.833</v>
+      </c>
+      <c r="AM41">
+        <v>0.833</v>
+      </c>
+      <c r="AN41">
+        <v>1</v>
+      </c>
+      <c r="AO41">
+        <v>37.21488595438176</v>
+      </c>
+      <c r="AP41">
+        <v>0.18</v>
+      </c>
+      <c r="AQ41">
+        <v>37.21488595438176</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ProAssurance Corporation (NYSE:PRA)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>0.04559999999999999</v>
+      </c>
+      <c r="E42">
+        <v>0.0364</v>
+      </c>
+      <c r="F42">
+        <v>0.273</v>
+      </c>
+      <c r="G42">
+        <v>0.05050765789020822</v>
+      </c>
+      <c r="H42">
+        <v>0.05050765789020822</v>
+      </c>
+      <c r="I42">
+        <v>0.07682357464791016</v>
+      </c>
+      <c r="J42">
+        <v>0.05962840631516492</v>
+      </c>
+      <c r="K42">
+        <v>43</v>
+      </c>
+      <c r="L42">
+        <v>0.03699879538805713</v>
+      </c>
+      <c r="M42">
+        <v>-0</v>
+      </c>
+      <c r="N42">
+        <v>-0</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-0</v>
+      </c>
+      <c r="Q42">
+        <v>-0</v>
+      </c>
+      <c r="R42">
+        <v>-0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>45.3</v>
+      </c>
+      <c r="V42">
+        <v>0.05565794323626981</v>
+      </c>
+      <c r="W42">
+        <v>0.0424985174935758</v>
+      </c>
+      <c r="X42">
+        <v>0.08602293199416999</v>
+      </c>
+      <c r="Y42">
+        <v>-0.04352441450059419</v>
+      </c>
+      <c r="Z42">
+        <v>0.8383296203072707</v>
+      </c>
+      <c r="AA42">
+        <v>0.04998825922571986</v>
+      </c>
+      <c r="AB42">
+        <v>0.07035793406222372</v>
+      </c>
+      <c r="AC42">
+        <v>-0.02036967483650386</v>
+      </c>
+      <c r="AD42">
+        <v>425.9</v>
+      </c>
+      <c r="AE42">
+        <v>15.52820772099402</v>
+      </c>
+      <c r="AF42">
+        <v>441.428207720994</v>
+      </c>
+      <c r="AG42">
+        <v>396.128207720994</v>
+      </c>
+      <c r="AH42">
+        <v>0.3516436617977318</v>
+      </c>
+      <c r="AI42">
+        <v>0.2639129279796454</v>
+      </c>
+      <c r="AJ42">
+        <v>0.3273710523385852</v>
+      </c>
+      <c r="AK42">
+        <v>0.2434224428984459</v>
+      </c>
+      <c r="AL42">
+        <v>23.7</v>
+      </c>
+      <c r="AM42">
+        <v>23.7</v>
+      </c>
+      <c r="AN42">
+        <v>3.803018126618448</v>
+      </c>
+      <c r="AO42">
+        <v>3.759493670886076</v>
+      </c>
+      <c r="AP42">
+        <v>3.537174816688936</v>
+      </c>
+      <c r="AQ42">
+        <v>3.759493670886076</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ambac Financial Group, Inc. (NYSE:AMBC)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>0.0339</v>
+      </c>
+      <c r="G43">
+        <v>0.2688442211055276</v>
+      </c>
+      <c r="H43">
+        <v>0.2688442211055276</v>
+      </c>
+      <c r="I43">
+        <v>0.1388313906421798</v>
+      </c>
+      <c r="J43">
+        <v>0.1388313906421798</v>
+      </c>
+      <c r="K43">
+        <v>-23</v>
+      </c>
+      <c r="L43">
+        <v>-0.05778894472361809</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>0.001666111296234588</v>
+      </c>
+      <c r="O43">
+        <v>-0.04347826086956522</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="U43">
+        <v>70</v>
+      </c>
+      <c r="V43">
+        <v>0.1166277907364212</v>
+      </c>
+      <c r="W43">
+        <v>-0.01819620253164557</v>
+      </c>
+      <c r="X43">
+        <v>0.2510245636266599</v>
+      </c>
+      <c r="Y43">
+        <v>-0.2692207661583054</v>
+      </c>
+      <c r="Z43">
+        <v>0.07304460421379906</v>
+      </c>
+      <c r="AA43">
+        <v>0.01014088398190935</v>
+      </c>
+      <c r="AB43">
+        <v>0.06416138843517007</v>
+      </c>
+      <c r="AC43">
+        <v>-0.05402050445326072</v>
+      </c>
+      <c r="AD43">
+        <v>4920</v>
+      </c>
+      <c r="AE43">
+        <v>23.72553262206228</v>
+      </c>
+      <c r="AF43">
+        <v>4943.725532622062</v>
+      </c>
+      <c r="AG43">
+        <v>4873.725532622062</v>
+      </c>
+      <c r="AH43">
+        <v>0.8917373625478464</v>
+      </c>
+      <c r="AI43">
+        <v>0.7251282717332757</v>
+      </c>
+      <c r="AJ43">
+        <v>0.8903529110100081</v>
+      </c>
+      <c r="AK43">
+        <v>0.7222767892766094</v>
+      </c>
+      <c r="AL43">
+        <v>68</v>
+      </c>
+      <c r="AM43">
+        <v>68</v>
+      </c>
+      <c r="AN43">
+        <v>47.30769230769231</v>
+      </c>
+      <c r="AO43">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="AP43">
+        <v>46.86274550598137</v>
+      </c>
+      <c r="AQ43">
+        <v>0.8235294117647058</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NI Holdings, Inc. (NasdaqCM:NODK)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>0.0883</v>
+      </c>
+      <c r="G44">
+        <v>0.009624712790400817</v>
+      </c>
+      <c r="H44">
+        <v>0.009624712790400817</v>
+      </c>
+      <c r="I44">
+        <v>-0.003059250888143661</v>
+      </c>
+      <c r="J44">
+        <v>-0.003059250888143661</v>
+      </c>
+      <c r="K44">
+        <v>-9.279999999999999</v>
+      </c>
+      <c r="L44">
+        <v>-0.02369160071483278</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>39.1</v>
+      </c>
+      <c r="V44">
+        <v>0.1206045650832819</v>
+      </c>
+      <c r="W44">
+        <v>-0.04064826982041173</v>
+      </c>
+      <c r="X44">
+        <v>0.07451649908237785</v>
+      </c>
+      <c r="Y44">
+        <v>-0.1151647689027896</v>
+      </c>
+      <c r="Z44">
+        <v>2.105160841760778</v>
+      </c>
+      <c r="AA44">
+        <v>-0.006440215174841916</v>
+      </c>
+      <c r="AB44">
+        <v>0.07431124140341613</v>
+      </c>
+      <c r="AC44">
+        <v>-0.08075145657825805</v>
+      </c>
+      <c r="AD44">
+        <v>0.23</v>
+      </c>
+      <c r="AE44">
+        <v>1.64654286442936</v>
+      </c>
+      <c r="AF44">
+        <v>1.87654286442936</v>
+      </c>
+      <c r="AG44">
+        <v>-37.22345713557064</v>
+      </c>
+      <c r="AH44">
+        <v>0.005754915235376367</v>
+      </c>
+      <c r="AI44">
+        <v>0.007713620237834028</v>
+      </c>
+      <c r="AJ44">
+        <v>-0.1297090583224267</v>
+      </c>
+      <c r="AK44">
+        <v>-0.182310154797197</v>
+      </c>
+      <c r="AL44">
+        <v>0</v>
+      </c>
+      <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="AP44">
+        <v>-85.17953577933785</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Trupanion, Inc. (NasdaqGM:TRUP)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>0.281</v>
+      </c>
+      <c r="G45">
+        <v>-0.01912875743449606</v>
+      </c>
+      <c r="H45">
+        <v>-0.01912875743449606</v>
+      </c>
+      <c r="I45">
+        <v>-0.007386272303488184</v>
+      </c>
+      <c r="J45">
+        <v>-0.007386272303488184</v>
+      </c>
+      <c r="K45">
+        <v>-13.5</v>
+      </c>
+      <c r="L45">
+        <v>-0.01085034560360071</v>
+      </c>
+      <c r="M45">
+        <v>1.63</v>
+      </c>
+      <c r="N45">
+        <v>0.0007986281234688878</v>
+      </c>
+      <c r="O45">
+        <v>-0.1207407407407407</v>
+      </c>
+      <c r="P45">
+        <v>-0</v>
+      </c>
+      <c r="Q45">
+        <v>-0</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>1.63</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="U45">
+        <v>137.5</v>
+      </c>
+      <c r="V45">
+        <v>0.06736893679568839</v>
+      </c>
+      <c r="W45">
+        <v>-0.04663212435233161</v>
+      </c>
+      <c r="X45">
+        <v>0.07574669508431778</v>
+      </c>
+      <c r="Y45">
+        <v>-0.1223788194366494</v>
+      </c>
+      <c r="Z45">
+        <v>5.502874834144185</v>
+      </c>
+      <c r="AA45">
+        <v>-0.04064573197700133</v>
+      </c>
+      <c r="AB45">
+        <v>0.07410289514129342</v>
+      </c>
+      <c r="AC45">
+        <v>-0.1147486271182948</v>
+      </c>
+      <c r="AD45">
+        <v>128.9</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>128.9</v>
+      </c>
+      <c r="AG45">
+        <v>-8.599999999999994</v>
+      </c>
+      <c r="AH45">
+        <v>0.05940365915479976</v>
+      </c>
+      <c r="AI45">
+        <v>0.2870184814072589</v>
+      </c>
+      <c r="AJ45">
+        <v>-0.004231450501869708</v>
+      </c>
+      <c r="AK45">
+        <v>-0.02759948652118098</v>
+      </c>
+      <c r="AL45">
+        <v>14.8</v>
+      </c>
+      <c r="AM45">
+        <v>14.8</v>
+      </c>
+      <c r="AN45">
+        <v>20.2037617554859</v>
+      </c>
+      <c r="AO45">
+        <v>-0.6209459459459459</v>
+      </c>
+      <c r="AP45">
+        <v>-1.34796238244514</v>
+      </c>
+      <c r="AQ45">
+        <v>-0.6209459459459459</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kingsway Financial Services Inc. (NYSE:KFS)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>0.138</v>
+      </c>
+      <c r="G46">
+        <v>0.07679558011049724</v>
+      </c>
+      <c r="H46">
+        <v>0.07679558011049724</v>
+      </c>
+      <c r="I46">
+        <v>-0.00757778678188458</v>
+      </c>
+      <c r="J46">
+        <v>-0.00757778678188458</v>
+      </c>
+      <c r="K46">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="L46">
+        <v>-0.08720073664825047</v>
+      </c>
+      <c r="M46">
+        <v>7.17</v>
+      </c>
+      <c r="N46">
+        <v>0.03106585788561525</v>
+      </c>
+      <c r="O46">
+        <v>-0.7571277719112988</v>
+      </c>
+      <c r="P46">
+        <v>-0</v>
+      </c>
+      <c r="Q46">
+        <v>-0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>7.17</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46">
+        <v>6.51</v>
+      </c>
+      <c r="V46">
+        <v>0.02820623916811092</v>
+      </c>
+      <c r="W46">
+        <v>-0.2996835443037975</v>
+      </c>
+      <c r="X46">
+        <v>0.07993785264495523</v>
+      </c>
+      <c r="Y46">
+        <v>-0.3796213969487527</v>
+      </c>
+      <c r="Z46">
+        <v>15.32872444801602</v>
+      </c>
+      <c r="AA46">
+        <v>-0.1161578055053268</v>
+      </c>
+      <c r="AB46">
+        <v>0.07203504403113986</v>
+      </c>
+      <c r="AC46">
+        <v>-0.1881928495364666</v>
+      </c>
+      <c r="AD46">
+        <v>58.5</v>
+      </c>
+      <c r="AE46">
+        <v>1.184738222563326</v>
+      </c>
+      <c r="AF46">
+        <v>59.68473822256333</v>
+      </c>
+      <c r="AG46">
+        <v>53.17473822256333</v>
+      </c>
+      <c r="AH46">
+        <v>0.2054660034388248</v>
+      </c>
+      <c r="AI46">
+        <v>0.751841469266183</v>
+      </c>
+      <c r="AJ46">
+        <v>0.1872516497607895</v>
+      </c>
+      <c r="AK46">
+        <v>0.7296731284325833</v>
+      </c>
+      <c r="AL46">
+        <v>4.61</v>
+      </c>
+      <c r="AM46">
+        <v>4.61</v>
+      </c>
+      <c r="AN46">
+        <v>9.74350433044637</v>
+      </c>
+      <c r="AO46">
+        <v>-0.2364425162689805</v>
+      </c>
+      <c r="AP46">
+        <v>8.856552002425605</v>
+      </c>
+      <c r="AQ46">
+        <v>-0.2364425162689805</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MBIA Inc. (NYSE:MBI)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="K47">
+        <v>-534</v>
+      </c>
+      <c r="M47">
+        <v>7</v>
+      </c>
+      <c r="N47">
+        <v>0.02123142250530786</v>
+      </c>
+      <c r="O47">
+        <v>-0.01310861423220974</v>
+      </c>
+      <c r="P47">
+        <v>-0</v>
+      </c>
+      <c r="Q47">
+        <v>-0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>7</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="U47">
+        <v>74</v>
+      </c>
+      <c r="V47">
+        <v>0.2244464664846831</v>
+      </c>
+      <c r="W47">
+        <v>0.4309927360774818</v>
+      </c>
+      <c r="X47">
+        <v>0.2953794672912011</v>
+      </c>
+      <c r="Y47">
+        <v>0.1356132687862807</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>-0.1461736042440931</v>
+      </c>
+      <c r="AB47">
+        <v>0.07794913770628373</v>
+      </c>
+      <c r="AC47">
+        <v>-0.2241227419503769</v>
+      </c>
+      <c r="AD47">
+        <v>3385</v>
+      </c>
+      <c r="AE47">
+        <v>12.61655959985168</v>
+      </c>
+      <c r="AF47">
+        <v>3397.616559599852</v>
+      </c>
+      <c r="AG47">
+        <v>3323.616559599852</v>
+      </c>
+      <c r="AH47">
+        <v>0.9115449426610025</v>
+      </c>
+      <c r="AI47">
+        <v>2.410312603424817</v>
+      </c>
+      <c r="AJ47">
+        <v>0.9097532352805168</v>
+      </c>
+      <c r="AK47">
+        <v>2.488451146933669</v>
+      </c>
+      <c r="AL47">
+        <v>222</v>
+      </c>
+      <c r="AM47">
+        <v>222</v>
+      </c>
+      <c r="AN47">
+        <v>1128.333333333333</v>
+      </c>
+      <c r="AO47">
+        <v>-1.364864864864865</v>
+      </c>
+      <c r="AP47">
+        <v>1107.872186533284</v>
+      </c>
+      <c r="AQ47">
+        <v>-1.364864864864865</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lemonade, Inc. (NYSE:LMND)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>0.57</v>
+      </c>
+      <c r="G48">
+        <v>-0.4123857868020304</v>
+      </c>
+      <c r="H48">
+        <v>-0.4123857868020304</v>
+      </c>
+      <c r="I48">
+        <v>-0.4087551004356634</v>
+      </c>
+      <c r="J48">
+        <v>-0.4087551004356634</v>
+      </c>
+      <c r="K48">
+        <v>-214.6</v>
+      </c>
+      <c r="L48">
+        <v>-0.4357360406091371</v>
+      </c>
+      <c r="M48">
+        <v>-0</v>
+      </c>
+      <c r="N48">
+        <v>-0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>329.8</v>
+      </c>
+      <c r="V48">
+        <v>0.1259211179412776</v>
+      </c>
+      <c r="W48">
+        <v>-0.2952263034805338</v>
+      </c>
+      <c r="X48">
+        <v>0.07516168195298178</v>
+      </c>
+      <c r="Y48">
+        <v>-0.3703879854335156</v>
+      </c>
+      <c r="Z48">
+        <v>0.9648171165078867</v>
+      </c>
+      <c r="AA48">
+        <v>-0.3943739173602284</v>
+      </c>
+      <c r="AB48">
+        <v>0.0745275066507847</v>
+      </c>
+      <c r="AC48">
+        <v>-0.4689014240110131</v>
+      </c>
+      <c r="AD48">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="AE48">
+        <v>26.55943482282127</v>
+      </c>
+      <c r="AF48">
+        <v>93.95943482282127</v>
+      </c>
+      <c r="AG48">
+        <v>-235.8405651771787</v>
+      </c>
+      <c r="AH48">
+        <v>0.03463228030201903</v>
+      </c>
+      <c r="AI48">
+        <v>0.1367758124568957</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.09895715159298712</v>
+      </c>
+      <c r="AK48">
+        <v>-0.6603229319538316</v>
+      </c>
+      <c r="AL48">
+        <v>0</v>
+      </c>
+      <c r="AM48">
+        <v>0</v>
+      </c>
+      <c r="AN48">
+        <v>-0.3831722569641842</v>
+      </c>
+      <c r="AP48">
+        <v>1.340765009534842</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Hallmark Financial Services, Inc. (OTCPK:HALL)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>-0.158</v>
+      </c>
+      <c r="G49">
+        <v>-0.7179023508137432</v>
+      </c>
+      <c r="H49">
+        <v>-0.7179023508137432</v>
+      </c>
+      <c r="I49">
+        <v>-0.5740453752807924</v>
+      </c>
+      <c r="J49">
+        <v>-0.5740453752807924</v>
+      </c>
+      <c r="K49">
+        <v>-79.90000000000001</v>
+      </c>
+      <c r="L49">
+        <v>-0.4816154309825196</v>
+      </c>
+      <c r="M49">
+        <v>-0</v>
+      </c>
+      <c r="N49">
+        <v>-0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>-0</v>
+      </c>
+      <c r="Q49">
+        <v>-0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="U49">
+        <v>75.7</v>
+      </c>
+      <c r="V49">
+        <v>4205.555555555556</v>
+      </c>
+      <c r="W49">
+        <v>-1.214285714285714</v>
+      </c>
+      <c r="X49">
+        <v>148.1240870961255</v>
+      </c>
+      <c r="Y49">
+        <v>-149.3383728104112</v>
+      </c>
+      <c r="Z49">
+        <v>2.748024591261964</v>
+      </c>
+      <c r="AA49">
+        <v>-1</v>
+      </c>
+      <c r="AB49">
+        <v>0.06479567108919734</v>
+      </c>
+      <c r="AC49">
+        <v>-1.064795671089197</v>
+      </c>
+      <c r="AD49">
+        <v>105.5</v>
+      </c>
+      <c r="AE49">
+        <v>18.7706387954172</v>
+      </c>
+      <c r="AF49">
+        <v>124.2706387954172</v>
+      </c>
+      <c r="AG49">
+        <v>48.5706387954172</v>
+      </c>
+      <c r="AH49">
+        <v>0.9998551758215839</v>
+      </c>
+      <c r="AI49">
+        <v>1.06669491326691</v>
+      </c>
+      <c r="AJ49">
+        <v>0.9996295430280361</v>
+      </c>
+      <c r="AK49">
+        <v>1.190438194827301</v>
+      </c>
+      <c r="AL49">
+        <v>7.62</v>
+      </c>
+      <c r="AM49">
+        <v>7.62</v>
+      </c>
+      <c r="AN49">
+        <v>-1.177718240678723</v>
+      </c>
+      <c r="AO49">
+        <v>-12.29658792650919</v>
+      </c>
+      <c r="AP49">
+        <v>-0.5422040499600044</v>
+      </c>
+      <c r="AQ49">
+        <v>-12.29658792650919</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Conifer Holdings, Inc. (NasdaqCM:CNFR)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>-0.0467</v>
+      </c>
+      <c r="G50">
+        <v>-0.3235294117647059</v>
+      </c>
+      <c r="H50">
+        <v>-0.3235294117647059</v>
+      </c>
+      <c r="I50">
+        <v>-0.3428039315489111</v>
+      </c>
+      <c r="J50">
+        <v>-0.3428039315489111</v>
+      </c>
+      <c r="K50">
+        <v>30.3</v>
+      </c>
+      <c r="L50">
+        <v>0.4050802139037433</v>
+      </c>
+      <c r="M50">
+        <v>0.836</v>
+      </c>
+      <c r="N50">
+        <v>0.05846153846153845</v>
+      </c>
+      <c r="O50">
+        <v>0.02759075907590759</v>
+      </c>
+      <c r="P50">
+        <v>0.836</v>
+      </c>
+      <c r="Q50">
+        <v>0.05846153846153845</v>
+      </c>
+      <c r="R50">
+        <v>0.02759075907590759</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>32.4</v>
+      </c>
+      <c r="V50">
+        <v>2.265734265734265</v>
+      </c>
+      <c r="W50">
+        <v>2.567796610169491</v>
+      </c>
+      <c r="X50">
+        <v>0.1007533501629589</v>
+      </c>
+      <c r="Y50">
+        <v>2.467043260006533</v>
+      </c>
+      <c r="Z50">
+        <v>3.145676303340526</v>
+      </c>
+      <c r="AA50">
+        <v>-1</v>
+      </c>
+      <c r="AB50">
+        <v>0.06909975358283837</v>
+      </c>
+      <c r="AC50">
+        <v>-1.069099753582838</v>
+      </c>
+      <c r="AD50">
+        <v>16.5</v>
+      </c>
+      <c r="AE50">
+        <v>1.078670399292742</v>
+      </c>
+      <c r="AF50">
+        <v>17.57867039929274</v>
+      </c>
+      <c r="AG50">
+        <v>-14.82132960070726</v>
+      </c>
+      <c r="AH50">
+        <v>0.5514242024247894</v>
+      </c>
+      <c r="AI50">
+        <v>0.2636325873630377</v>
+      </c>
+      <c r="AJ50">
+        <v>28.42986391066249</v>
+      </c>
+      <c r="AK50">
+        <v>-0.43237761056838</v>
+      </c>
+      <c r="AL50">
+        <v>4.87</v>
+      </c>
+      <c r="AM50">
+        <v>4.87</v>
+      </c>
+      <c r="AN50">
+        <v>-0.6867560143178224</v>
+      </c>
+      <c r="AO50">
+        <v>-5.277207392197125</v>
+      </c>
+      <c r="AP50">
+        <v>0.6168871056649986</v>
+      </c>
+      <c r="AQ50">
+        <v>-5.277207392197125</v>
       </c>
     </row>
   </sheetData>
